--- a/SubRes_Tmpl/SubRES_H2-Production.xlsx
+++ b/SubRes_Tmpl/SubRES_H2-Production.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\KiNESYS_BattCircularity-main\SubRes_Tmpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAED1AB2-A62B-458E-8164-D340B4772D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="7510" activeTab="4"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SectFuel" sheetId="2" r:id="rId1"/>
@@ -12,13 +18,15 @@
     <sheet name="HPL" sheetId="6" r:id="rId3"/>
     <sheet name="H2 transport" sheetId="7" r:id="rId4"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId5"/>
+    <sheet name="ELC_Storage_for_NoCir" sheetId="8" r:id="rId6"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId6"/>
     <externalReference r:id="rId7"/>
     <externalReference r:id="rId8"/>
     <externalReference r:id="rId9"/>
     <externalReference r:id="rId10"/>
+    <externalReference r:id="rId11"/>
+    <externalReference r:id="rId12"/>
   </externalReferences>
   <definedNames>
     <definedName name="Cars_12" localSheetId="2">'[1]TechRep-Doc'!#REF!</definedName>
@@ -81,12 +89,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Rocco De Miglio</author>
   </authors>
   <commentList>
-    <comment ref="O39" authorId="0">
+    <comment ref="O39" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -113,8 +121,239 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>xli9</author>
+    <author>Amit Kanudia</author>
+  </authors>
+  <commentList>
+    <comment ref="AY16" authorId="0" shapeId="0" xr:uid="{EA01F337-7F4E-4132-974F-6C5A8A25B61E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="134"/>
+          </rPr>
+          <t>xli9:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+25 is too </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Y17" authorId="0" shapeId="0" xr:uid="{04F754FD-C078-4E73-8BC3-C49CA8833423}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="134"/>
+          </rPr>
+          <t>xli9:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+new grid storage generally not goes to repurpose within SOH&lt;60%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P19" authorId="1" shapeId="0" xr:uid="{17337A87-D2C8-4371-88C6-081E963DD595}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Amit Kanudia:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+01-01-2020
+This will take care of regions that don't appear in the Restart file for nuclear
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AY19" authorId="0" shapeId="0" xr:uid="{B0C10560-606B-4310-8DBD-85670C1DEEB4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="134"/>
+          </rPr>
+          <t>xli9:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+25 is too </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L22" authorId="0" shapeId="0" xr:uid="{E954BFD3-CC45-4C0A-8224-AFC7688E7351}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="134"/>
+          </rPr>
+          <t>xli9:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+25 is too </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AY22" authorId="0" shapeId="0" xr:uid="{C2921F16-DF04-40BD-BCE6-289DAE2D9B66}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="134"/>
+          </rPr>
+          <t>xli9:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+25 is too </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AY25" authorId="0" shapeId="0" xr:uid="{250861E9-3059-4630-8059-DF3D14976839}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="134"/>
+          </rPr>
+          <t>xli9:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+25 is too </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AY28" authorId="0" shapeId="0" xr:uid="{756D646C-BB86-4492-B127-C09AAA0568EA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="134"/>
+          </rPr>
+          <t>xli9:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+25 is too </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AY31" authorId="0" shapeId="0" xr:uid="{478598BE-F4B2-4A49-A622-C71AEE8EEC47}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="134"/>
+          </rPr>
+          <t>xli9:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+25 is too </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C33" authorId="0" shapeId="0" xr:uid="{2FE0E485-8383-44B0-86DB-EA78EE6C8A8D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+          </rPr>
+          <t>xli9:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+          </rPr>
+          <t xml:space="preserve">
+LFP stationary storage, we assume consumes same energy with EV battery for manufacturing (virgin)</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="237">
   <si>
     <t>~FI_T</t>
   </si>
@@ -650,23 +889,203 @@
   </si>
   <si>
     <t>BIOBSL</t>
+  </si>
+  <si>
+    <t>limtype</t>
+  </si>
+  <si>
+    <t>m_lithium</t>
+  </si>
+  <si>
+    <t>m_nickel</t>
+  </si>
+  <si>
+    <t>m_cobalt</t>
+  </si>
+  <si>
+    <t>m_manganese</t>
+  </si>
+  <si>
+    <t>m_aluminum</t>
+  </si>
+  <si>
+    <t>m_copper</t>
+  </si>
+  <si>
+    <t>m_graphite</t>
+  </si>
+  <si>
+    <t>STGTSS</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt</t>
+  </si>
+  <si>
+    <t>4h battery storage -  50MW/200MWh--LFP by default</t>
+  </si>
+  <si>
+    <t>GWh</t>
+  </si>
+  <si>
+    <t>FX</t>
+  </si>
+  <si>
+    <t>ELE</t>
+  </si>
+  <si>
+    <t>E_Nuc_Accounting</t>
+  </si>
+  <si>
+    <t>Dummy tech to control exog and endog nuclear</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt_LMO</t>
+  </si>
+  <si>
+    <t>4h battery storage -  50MW/200MWh</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt_NCA</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt_NMC111</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt_NMC532</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt_NMC622</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt_NMC811</t>
+  </si>
+  <si>
+    <t>~FI_T: USD15</t>
+  </si>
+  <si>
+    <t>Comm-OUT-A</t>
+  </si>
+  <si>
+    <t>S_EFF</t>
+  </si>
+  <si>
+    <t>NCAP_AFC~DAYNITE</t>
+  </si>
+  <si>
+    <t>FLO_FUNC~ELC</t>
+  </si>
+  <si>
+    <t>CAP_BND~UP</t>
+  </si>
+  <si>
+    <t>FLO_FUNC~AuxStoIN</t>
+  </si>
+  <si>
+    <t>CAP_BND~UP~0</t>
+  </si>
+  <si>
+    <t>STG_MAXCYC</t>
+  </si>
+  <si>
+    <t>PKNO</t>
+  </si>
+  <si>
+    <t>AuxStoOUT</t>
+  </si>
+  <si>
+    <t>MultiR-LFP</t>
+  </si>
+  <si>
+    <t>AuxStoIN</t>
+  </si>
+  <si>
+    <t>DumGrid</t>
+  </si>
+  <si>
+    <t>Csets</t>
+  </si>
+  <si>
+    <t>ENV</t>
+  </si>
+  <si>
+    <t>Aux commodity for storage charging</t>
+  </si>
+  <si>
+    <t>Aux commodity for storage discharging</t>
+  </si>
+  <si>
+    <t>INDELC</t>
+  </si>
+  <si>
+    <t>INDCOA</t>
+  </si>
+  <si>
+    <t>INDNGA</t>
+  </si>
+  <si>
+    <t>INDOIL</t>
+  </si>
+  <si>
+    <t>~FI_T: NCAP_ICOM</t>
+  </si>
+  <si>
+    <t>Tra_EV_Batt-LFP_virgin_package</t>
+  </si>
+  <si>
+    <t>Tra_EV_Batt-LMO_virgin_package</t>
+  </si>
+  <si>
+    <t>Tra_EV_Batt-NCA_virgin_package</t>
+  </si>
+  <si>
+    <t>Tra_EV_Batt-NMC111_virgin_package</t>
+  </si>
+  <si>
+    <t>Tra_EV_Batt-NMC532_virgin_package</t>
+  </si>
+  <si>
+    <t>Tra_EV_Batt-NMC622_virgin_package</t>
+  </si>
+  <si>
+    <t>Tra_EV_Batt-NMC811_virgin_package</t>
+  </si>
+  <si>
+    <t>~FI_T: NCAP_OCOM</t>
+  </si>
+  <si>
+    <t>recy-LFP</t>
+  </si>
+  <si>
+    <t>recy-LMO</t>
+  </si>
+  <si>
+    <t>recy-NCA</t>
+  </si>
+  <si>
+    <t>recy-NMC111</t>
+  </si>
+  <si>
+    <t>recy-NMC532</t>
+  </si>
+  <si>
+    <t>recy-NMC622</t>
+  </si>
+  <si>
+    <t>recy-NMC811</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="8">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* \-??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="#,##0.0_ "/>
-    <numFmt numFmtId="179" formatCode="0.0"/>
-    <numFmt numFmtId="180" formatCode="\Te\x\t"/>
-    <numFmt numFmtId="181" formatCode="0.000"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="5">
+    <numFmt numFmtId="168" formatCode="#,##0.0_ "/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="\Te\x\t"/>
+    <numFmt numFmtId="171" formatCode="0.000"/>
+    <numFmt numFmtId="172" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -784,127 +1203,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
@@ -915,8 +1213,54 @@
       <name val="Tahoma"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.199999999999999"/>
+      <color rgb="FF212529"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+    </font>
   </fonts>
-  <fills count="47">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -931,7 +1275,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.39994506668294322"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -943,7 +1287,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.0499893185216834"/>
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -967,7 +1311,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -985,7 +1329,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -997,7 +1341,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1015,186 +1359,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -1336,7 +1524,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.399975585192419"/>
+        <color theme="4" tint="0.39994506668294322"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1413,7 +1601,7 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </left>
       <right/>
       <top/>
@@ -1423,7 +1611,7 @@
     <border>
       <left/>
       <right style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </right>
       <top/>
       <bottom/>
@@ -1440,7 +1628,7 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </left>
       <right/>
       <top style="thin">
@@ -1452,7 +1640,7 @@
     <border>
       <left/>
       <right style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </right>
       <top style="thin">
         <color auto="1"/>
@@ -1462,7 +1650,7 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </left>
       <right/>
       <top/>
@@ -1474,7 +1662,7 @@
     <border>
       <left/>
       <right style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </right>
       <top/>
       <bottom style="thin">
@@ -1482,235 +1670,18 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="27" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="158">
+  <cellXfs count="187">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1734,7 +1705,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1746,7 +1717,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1755,39 +1726,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="180" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="49"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="13"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="14"/>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="49" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="15"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="49" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="24" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="2"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="6" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="6" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="6" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="5" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1802,25 +1764,25 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="10" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="10" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="10" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="10" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="10" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1832,49 +1794,49 @@
     <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="11" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="11" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="11" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="11" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="10" fillId="10" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="10" fillId="10" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="10" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="10" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="10" fillId="12" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="12" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="10" fillId="12" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="12" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1883,68 +1845,65 @@
     <xf numFmtId="0" fontId="10" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="10" fillId="14" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="14" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="10" fillId="14" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="14" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="10" fillId="12" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="12" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="12" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="10" fillId="12" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="12" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="12" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="10" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="10" fillId="15" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="15" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="10" fillId="15" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="15" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="10" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="10" fillId="16" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="16" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="10" fillId="16" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="16" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="15" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="10" fillId="15" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="15" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="15" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="10" fillId="15" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="15" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="15" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1954,9 +1913,6 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="10" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1987,16 +1943,16 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="11" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="11" fillId="9" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="11" fillId="9" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="11" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="9" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="9" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2005,16 +1961,16 @@
     <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="10" fillId="10" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="10" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="10" fillId="10" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="10" fillId="10" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="10" fillId="10" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="10" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="10" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2023,16 +1979,16 @@
     <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="10" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="10" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="10" fillId="11" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="10" fillId="11" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="10" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="11" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="11" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2041,16 +1997,16 @@
     <xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="12" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="11" fillId="12" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="11" fillId="12" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="11" fillId="12" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="11" fillId="12" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="12" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="12" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="12" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2059,16 +2015,16 @@
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="14" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="11" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="11" fillId="14" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="11" fillId="14" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="11" fillId="14" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="14" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="14" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2077,31 +2033,31 @@
     <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="12" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="11" fillId="12" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="11" fillId="12" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="11" fillId="12" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="11" fillId="12" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="12" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="12" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="12" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="10" fillId="15" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="10" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="10" fillId="15" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="10" fillId="15" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="10" fillId="15" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="15" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="15" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="15" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2110,16 +2066,16 @@
     <xf numFmtId="0" fontId="10" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="10" fillId="16" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="10" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="10" fillId="16" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="10" fillId="16" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="10" fillId="16" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="16" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="16" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="16" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2128,16 +2084,16 @@
     <xf numFmtId="0" fontId="10" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="10" fillId="15" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="10" fillId="15" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="10" fillId="15" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="10" fillId="15" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="10" fillId="15" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="15" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="15" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="15" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2146,72 +2102,99 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="7" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="170" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="7"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="7" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="18" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="0" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="7" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" xfId="7" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="8">
+    <cellStyle name="Heading 2" xfId="2" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="3" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="4" builtinId="19"/>
+    <cellStyle name="Neutral" xfId="5" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
-    <cellStyle name="Normal 2" xfId="49"/>
+    <cellStyle name="Normal 10" xfId="7" xr:uid="{D443C77F-8BEB-4EA0-8CEE-750345F457C3}"/>
+    <cellStyle name="Normal 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="New Microsoft Excel Worksheet"/>
       <sheetName val="AGR_Fuels"/>
@@ -2227,8 +2210,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="IEA Data"/>
       <sheetName val="E&amp;D Drivers"/>
@@ -2340,8 +2326,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="IEA Data"/>
       <sheetName val="E&amp;D Drivers"/>
@@ -2453,8 +2442,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Cover"/>
       <sheetName val="H2 transport"/>
@@ -2490,8 +2482,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Cover"/>
       <sheetName val="ELC_Lists"/>
@@ -2519,6 +2514,88 @@
       <sheetData sheetId="9" refreshError="1"/>
       <sheetData sheetId="10" refreshError="1"/>
       <sheetData sheetId="11" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Discuss_log"/>
+      <sheetName val="Cover"/>
+      <sheetName val="Small_cars"/>
+      <sheetName val="Large_cars"/>
+      <sheetName val="Medium_cars"/>
+      <sheetName val="LCVs"/>
+      <sheetName val="Hdt"/>
+      <sheetName val="2-3wheelers"/>
+      <sheetName val="Bus_coach"/>
+      <sheetName val="Critical_materials"/>
+      <sheetName val="Repurposed_Bat_AuxStout"/>
+      <sheetName val="R_strategies_n_GridBattery"/>
+      <sheetName val="R_strategies_RecycledEV_batt"/>
+      <sheetName val="EnergyUseFromEverBatt_Min_"/>
+      <sheetName val="Recyc_energy_use_Anna__SAME"/>
+      <sheetName val="Recyc_energy_use_Anna_15per_mor"/>
+      <sheetName val="Recyc_energy_use_Anna_15less"/>
+      <sheetName val="LIB mass distribution"/>
+      <sheetName val="HGVs&lt;16t"/>
+      <sheetName val="HGVs&gt;16t"/>
+      <sheetName val="Aviation"/>
+      <sheetName val="Rail"/>
+      <sheetName val="Inland_navigation"/>
+      <sheetName val="Maritime"/>
+      <sheetName val="Infrastructure"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13">
+        <row r="6">
+          <cell r="AW6">
+            <v>4.7300000000000002E-2</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="AW7">
+            <v>0.17116666666666699</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="AW8">
+            <v>0.46636666666666698</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="AW9">
+            <v>9.5666666666666705E-2</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2776,45 +2853,45 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B3:P7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="11.8545454545455" customWidth="1"/>
-    <col min="3" max="3" width="9.42727272727273" customWidth="1"/>
-    <col min="4" max="4" width="15.2818181818182" customWidth="1"/>
+    <col min="2" max="2" width="11.86328125" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" customWidth="1"/>
+    <col min="4" max="4" width="15.265625" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="6.42727272727273" customWidth="1"/>
-    <col min="7" max="7" width="8.28181818181818" customWidth="1"/>
-    <col min="9" max="9" width="11.2818181818182" customWidth="1"/>
-    <col min="10" max="10" width="11.8545454545455" customWidth="1"/>
-    <col min="11" max="11" width="20.5727272727273" customWidth="1"/>
-    <col min="12" max="12" width="8.57272727272727" customWidth="1"/>
-    <col min="13" max="13" width="4.57272727272727" customWidth="1"/>
-    <col min="14" max="14" width="5.28181818181818" customWidth="1"/>
-    <col min="15" max="15" width="10.2818181818182" customWidth="1"/>
-    <col min="16" max="16" width="7.85454545454545" customWidth="1"/>
+    <col min="6" max="6" width="6.3984375" customWidth="1"/>
+    <col min="7" max="7" width="8.265625" customWidth="1"/>
+    <col min="9" max="9" width="11.265625" customWidth="1"/>
+    <col min="10" max="10" width="11.86328125" customWidth="1"/>
+    <col min="11" max="11" width="20.59765625" customWidth="1"/>
+    <col min="12" max="12" width="8.59765625" customWidth="1"/>
+    <col min="13" max="13" width="4.59765625" customWidth="1"/>
+    <col min="14" max="14" width="5.265625" customWidth="1"/>
+    <col min="15" max="15" width="10.265625" customWidth="1"/>
+    <col min="16" max="16" width="7.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="4:16">
+    <row r="3" spans="2:16">
       <c r="D3" t="s">
         <v>0</v>
       </c>
-      <c r="I3" s="157" t="s">
+      <c r="I3" s="152" t="s">
         <v>1</v>
       </c>
-      <c r="J3" s="157"/>
-      <c r="K3" s="157"/>
-      <c r="L3" s="157"/>
-      <c r="M3" s="157"/>
-      <c r="N3" s="157"/>
-      <c r="O3" s="157"/>
-      <c r="P3" s="157"/>
+      <c r="J3" s="152"/>
+      <c r="K3" s="152"/>
+      <c r="L3" s="152"/>
+      <c r="M3" s="152"/>
+      <c r="N3" s="152"/>
+      <c r="O3" s="152"/>
+      <c r="P3" s="152"/>
     </row>
     <row r="4" spans="2:16">
       <c r="B4" t="s">
@@ -2835,32 +2912,32 @@
       <c r="G4" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="157" t="s">
+      <c r="I4" s="152" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="157" t="s">
+      <c r="J4" s="152" t="s">
         <v>2</v>
       </c>
-      <c r="K4" s="157" t="s">
+      <c r="K4" s="152" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="157" t="s">
+      <c r="L4" s="152" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="157" t="s">
+      <c r="M4" s="152" t="s">
         <v>11</v>
       </c>
-      <c r="N4" s="157" t="s">
+      <c r="N4" s="152" t="s">
         <v>12</v>
       </c>
-      <c r="O4" s="157" t="s">
+      <c r="O4" s="152" t="s">
         <v>13</v>
       </c>
-      <c r="P4" s="157" t="s">
+      <c r="P4" s="152" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="2:14">
+    <row r="5" spans="2:16">
       <c r="B5" t="s">
         <v>15</v>
       </c>
@@ -2877,24 +2954,24 @@
       <c r="I5" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="157" t="str">
+      <c r="J5" s="152" t="str">
         <f t="shared" ref="J5" si="0">B5</f>
         <v>H2_STG</v>
       </c>
-      <c r="K5" s="157" t="s">
+      <c r="K5" s="152" t="s">
         <v>18</v>
       </c>
-      <c r="L5" s="157" t="s">
+      <c r="L5" s="152" t="s">
         <v>19</v>
       </c>
-      <c r="M5" s="157" t="s">
+      <c r="M5" s="152" t="s">
         <v>20</v>
       </c>
-      <c r="N5" s="157" t="s">
+      <c r="N5" s="152" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="2:14">
+    <row r="6" spans="2:16">
       <c r="B6" t="s">
         <v>22</v>
       </c>
@@ -2911,24 +2988,24 @@
       <c r="I6" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="157" t="str">
+      <c r="J6" s="152" t="str">
         <f t="shared" ref="J6:J7" si="1">B6</f>
         <v>NGA_STG</v>
       </c>
-      <c r="K6" s="157" t="s">
+      <c r="K6" s="152" t="s">
         <v>24</v>
       </c>
-      <c r="L6" s="157" t="s">
+      <c r="L6" s="152" t="s">
         <v>25</v>
       </c>
-      <c r="M6" s="157" t="s">
+      <c r="M6" s="152" t="s">
         <v>20</v>
       </c>
-      <c r="N6" s="157" t="s">
+      <c r="N6" s="152" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="2:14">
+    <row r="7" spans="2:16">
       <c r="B7" t="s">
         <v>26</v>
       </c>
@@ -2945,82 +3022,80 @@
       <c r="I7" t="s">
         <v>17</v>
       </c>
-      <c r="J7" s="157" t="str">
+      <c r="J7" s="152" t="str">
         <f t="shared" si="1"/>
         <v>LNG_STG</v>
       </c>
-      <c r="K7" s="157" t="s">
+      <c r="K7" s="152" t="s">
         <v>28</v>
       </c>
-      <c r="L7" s="157" t="s">
+      <c r="L7" s="152" t="s">
         <v>25</v>
       </c>
-      <c r="M7" s="157" t="s">
+      <c r="M7" s="152" t="s">
         <v>20</v>
       </c>
-      <c r="N7" s="157" t="s">
+      <c r="N7" s="152" t="s">
         <v>21</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Y39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="2" width="11.1363636363636" customWidth="1"/>
+    <col min="1" max="2" width="11.1328125" customWidth="1"/>
     <col min="3" max="5" width="14" customWidth="1"/>
-    <col min="6" max="8" width="11.8545454545455" customWidth="1"/>
-    <col min="9" max="9" width="20.2818181818182" customWidth="1"/>
-    <col min="10" max="10" width="15.5727272727273" customWidth="1"/>
-    <col min="11" max="11" width="20.2818181818182" customWidth="1"/>
-    <col min="12" max="12" width="15.5727272727273" customWidth="1"/>
-    <col min="13" max="13" width="20.2818181818182" customWidth="1"/>
-    <col min="14" max="14" width="15.5727272727273" customWidth="1"/>
-    <col min="15" max="15" width="18.8545454545455" customWidth="1"/>
-    <col min="16" max="16" width="4.42727272727273" customWidth="1"/>
-    <col min="17" max="17" width="8.13636363636364" customWidth="1"/>
-    <col min="20" max="20" width="18.1363636363636" customWidth="1"/>
+    <col min="6" max="8" width="11.86328125" customWidth="1"/>
+    <col min="9" max="9" width="20.265625" customWidth="1"/>
+    <col min="10" max="10" width="15.59765625" customWidth="1"/>
+    <col min="11" max="11" width="20.265625" customWidth="1"/>
+    <col min="12" max="12" width="15.59765625" customWidth="1"/>
+    <col min="13" max="13" width="20.265625" customWidth="1"/>
+    <col min="14" max="14" width="15.59765625" customWidth="1"/>
+    <col min="15" max="15" width="18.86328125" customWidth="1"/>
+    <col min="16" max="16" width="4.3984375" customWidth="1"/>
+    <col min="17" max="17" width="8.1328125" customWidth="1"/>
+    <col min="20" max="20" width="18.1328125" customWidth="1"/>
     <col min="21" max="21" width="24" customWidth="1"/>
-    <col min="22" max="22" width="4.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="4.13636363636364" customWidth="1"/>
-    <col min="24" max="24" width="7.70909090909091" customWidth="1"/>
-    <col min="25" max="25" width="7.13636363636364" customWidth="1"/>
+    <col min="22" max="22" width="4.59765625" customWidth="1"/>
+    <col min="23" max="23" width="4.1328125" customWidth="1"/>
+    <col min="24" max="24" width="7.73046875" customWidth="1"/>
+    <col min="25" max="25" width="7.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33.75" customHeight="1" spans="1:20">
+    <row r="1" spans="1:20" ht="33.75" customHeight="1">
       <c r="A1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="153" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="32" t="s">
+      <c r="D1" s="153"/>
+      <c r="E1" s="153"/>
+      <c r="F1" s="154" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="31"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="31" t="s">
+      <c r="G1" s="153"/>
+      <c r="H1" s="155"/>
+      <c r="I1" s="153" t="s">
         <v>32</v>
       </c>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="87" t="s">
+      <c r="J1" s="153"/>
+      <c r="K1" s="153"/>
+      <c r="L1" s="153"/>
+      <c r="M1" s="153"/>
+      <c r="N1" s="153"/>
+      <c r="O1" s="156" t="s">
         <v>33</v>
       </c>
-      <c r="P1" s="88"/>
-      <c r="Q1" s="88"/>
+      <c r="P1" s="84"/>
+      <c r="Q1" s="84"/>
       <c r="S1" t="s">
         <v>34</v>
       </c>
@@ -3028,954 +3103,954 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="3:17">
-      <c r="C2" s="34" t="s">
+    <row r="2" spans="1:20">
+      <c r="C2" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="34" t="s">
+      <c r="D2" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="34" t="s">
+      <c r="E2" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="34" t="s">
+      <c r="G2" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="H2" s="34" t="s">
+      <c r="H2" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="I2" s="34" t="s">
+      <c r="I2" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="J2" s="34" t="s">
+      <c r="J2" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="K2" s="34" t="str">
+      <c r="K2" s="31" t="str">
         <f>I2</f>
         <v>input~GASNGA</v>
       </c>
-      <c r="L2" s="34" t="str">
+      <c r="L2" s="31" t="str">
         <f>J2</f>
         <v>input~ELC_gc</v>
       </c>
-      <c r="M2" s="34" t="str">
+      <c r="M2" s="31" t="str">
         <f>K2</f>
         <v>input~GASNGA</v>
       </c>
-      <c r="N2" s="34" t="str">
+      <c r="N2" s="31" t="str">
         <f>L2</f>
         <v>input~ELC_gc</v>
       </c>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
-    </row>
-    <row r="3" spans="3:17">
-      <c r="C3" s="34">
+      <c r="O2" s="157"/>
+      <c r="P2" s="84"/>
+      <c r="Q2" s="84"/>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="C3" s="31">
         <v>2020</v>
       </c>
-      <c r="D3" s="34">
+      <c r="D3" s="31">
         <v>2030</v>
       </c>
-      <c r="E3" s="34">
+      <c r="E3" s="31">
         <v>2050</v>
       </c>
-      <c r="F3" s="34">
+      <c r="F3" s="31">
         <f>C3</f>
         <v>2020</v>
       </c>
-      <c r="G3" s="34">
+      <c r="G3" s="31">
         <f t="shared" ref="G3:H3" si="0">D3</f>
         <v>2030</v>
       </c>
-      <c r="H3" s="34">
+      <c r="H3" s="31">
         <f t="shared" si="0"/>
         <v>2050</v>
       </c>
-      <c r="I3" s="34">
+      <c r="I3" s="31">
         <v>2015</v>
       </c>
-      <c r="J3" s="34">
+      <c r="J3" s="31">
         <v>2015</v>
       </c>
-      <c r="K3" s="34">
+      <c r="K3" s="31">
         <v>2030</v>
       </c>
-      <c r="L3" s="34">
+      <c r="L3" s="31">
         <v>2030</v>
       </c>
-      <c r="M3" s="34">
+      <c r="M3" s="31">
         <v>2050</v>
       </c>
-      <c r="N3" s="34">
+      <c r="N3" s="31">
         <v>2050</v>
       </c>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-    </row>
-    <row r="4" ht="26" spans="3:17">
-      <c r="C4" s="35">
+      <c r="O3" s="157"/>
+      <c r="P3" s="84"/>
+      <c r="Q3" s="84"/>
+    </row>
+    <row r="4" spans="1:20" ht="26.25">
+      <c r="C4" s="32">
         <v>2020</v>
       </c>
-      <c r="D4" s="35">
+      <c r="D4" s="32">
         <v>2030</v>
       </c>
-      <c r="E4" s="35" t="s">
+      <c r="E4" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="36">
+      <c r="F4" s="33">
         <v>2015</v>
       </c>
-      <c r="G4" s="35">
+      <c r="G4" s="32">
         <v>2030</v>
       </c>
-      <c r="H4" s="37" t="s">
+      <c r="H4" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="35" t="s">
+      <c r="I4" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="J4" s="35" t="s">
+      <c r="J4" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="K4" s="89" t="s">
+      <c r="K4" s="85" t="s">
         <v>43</v>
       </c>
-      <c r="L4" s="90" t="s">
+      <c r="L4" s="86" t="s">
         <v>44</v>
       </c>
-      <c r="M4" s="35" t="s">
+      <c r="M4" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="N4" s="35" t="s">
+      <c r="N4" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="O4" s="91"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-    </row>
-    <row r="5" spans="3:17">
-      <c r="C5" s="38">
+      <c r="O4" s="158"/>
+      <c r="P4" s="84"/>
+      <c r="Q4" s="84"/>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="C5" s="35">
         <v>550</v>
       </c>
-      <c r="D5" s="38">
+      <c r="D5" s="35">
         <v>500</v>
       </c>
-      <c r="E5" s="38">
+      <c r="E5" s="35">
         <v>450</v>
       </c>
-      <c r="F5" s="39">
+      <c r="F5" s="36">
         <v>22</v>
       </c>
-      <c r="G5" s="40">
+      <c r="G5" s="37">
         <v>20</v>
       </c>
-      <c r="H5" s="41">
+      <c r="H5" s="38">
         <v>18</v>
       </c>
-      <c r="I5" s="92">
+      <c r="I5" s="87">
         <v>1.33</v>
       </c>
-      <c r="J5" s="92">
-        <v>0.094</v>
-      </c>
-      <c r="K5" s="93">
+      <c r="J5" s="87">
+        <v>9.4E-2</v>
+      </c>
+      <c r="K5" s="88">
         <v>1.3</v>
       </c>
-      <c r="L5" s="94">
-        <v>0.094</v>
-      </c>
-      <c r="M5" s="92">
+      <c r="L5" s="89">
+        <v>9.4E-2</v>
+      </c>
+      <c r="M5" s="87">
         <v>1.28</v>
       </c>
-      <c r="N5" s="92">
-        <v>0.094</v>
-      </c>
-      <c r="O5" s="95" t="s">
+      <c r="N5" s="87">
+        <v>9.4E-2</v>
+      </c>
+      <c r="O5" s="90" t="s">
         <v>47</v>
       </c>
-      <c r="P5" s="96"/>
-      <c r="Q5" s="96"/>
-    </row>
-    <row r="6" spans="3:17">
-      <c r="C6" s="42">
+      <c r="P5" s="91"/>
+      <c r="Q5" s="91"/>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="C6" s="39">
         <v>900</v>
       </c>
-      <c r="D6" s="42">
+      <c r="D6" s="39">
         <v>850</v>
       </c>
-      <c r="E6" s="42">
+      <c r="E6" s="39">
         <v>800</v>
       </c>
-      <c r="F6" s="43">
+      <c r="F6" s="40">
         <v>36</v>
       </c>
-      <c r="G6" s="44">
+      <c r="G6" s="41">
         <v>34</v>
       </c>
-      <c r="H6" s="45">
+      <c r="H6" s="42">
         <v>32</v>
       </c>
-      <c r="I6" s="97">
+      <c r="I6" s="92">
         <v>1.33</v>
       </c>
-      <c r="J6" s="97">
-        <v>1.094</v>
-      </c>
-      <c r="K6" s="98">
+      <c r="J6" s="92">
+        <v>1.0940000000000001</v>
+      </c>
+      <c r="K6" s="93">
         <v>1.3</v>
       </c>
-      <c r="L6" s="99">
-        <v>1.094</v>
-      </c>
-      <c r="M6" s="97">
+      <c r="L6" s="94">
+        <v>1.0940000000000001</v>
+      </c>
+      <c r="M6" s="92">
         <v>1.28</v>
       </c>
-      <c r="N6" s="97">
-        <v>1.094</v>
-      </c>
-      <c r="O6" s="100" t="s">
+      <c r="N6" s="92">
+        <v>1.0940000000000001</v>
+      </c>
+      <c r="O6" s="95" t="s">
         <v>48</v>
       </c>
-      <c r="P6" s="101"/>
-      <c r="Q6" s="101"/>
-    </row>
-    <row r="7" spans="3:17">
-      <c r="C7" s="38">
+      <c r="P6" s="96"/>
+      <c r="Q6" s="96"/>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="C7" s="35">
         <v>1978</v>
       </c>
-      <c r="D7" s="38">
+      <c r="D7" s="35">
         <v>1598</v>
       </c>
-      <c r="E7" s="38">
+      <c r="E7" s="35">
         <v>1450</v>
       </c>
-      <c r="F7" s="39">
+      <c r="F7" s="36">
         <v>57</v>
       </c>
-      <c r="G7" s="40">
+      <c r="G7" s="37">
         <v>31</v>
       </c>
-      <c r="H7" s="41">
+      <c r="H7" s="38">
         <v>28</v>
       </c>
-      <c r="I7" s="92">
+      <c r="I7" s="87">
         <v>1.53</v>
       </c>
-      <c r="J7" s="92">
-        <v>0.094</v>
-      </c>
-      <c r="K7" s="93">
+      <c r="J7" s="87">
+        <v>9.4E-2</v>
+      </c>
+      <c r="K7" s="88">
         <v>1.47</v>
       </c>
-      <c r="L7" s="94">
-        <v>0.094</v>
-      </c>
-      <c r="M7" s="92">
+      <c r="L7" s="89">
+        <v>9.4E-2</v>
+      </c>
+      <c r="M7" s="87">
         <v>1.43</v>
       </c>
-      <c r="N7" s="92">
-        <v>0.094</v>
-      </c>
-      <c r="O7" s="95" t="s">
+      <c r="N7" s="87">
+        <v>9.4E-2</v>
+      </c>
+      <c r="O7" s="90" t="s">
         <v>49</v>
       </c>
-      <c r="P7" s="96"/>
-      <c r="Q7" s="96"/>
-    </row>
-    <row r="8" spans="3:17">
-      <c r="C8" s="46">
+      <c r="P7" s="91"/>
+      <c r="Q7" s="91"/>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="C8" s="43">
         <v>1610</v>
       </c>
-      <c r="D8" s="46">
+      <c r="D8" s="43">
         <v>740</v>
       </c>
-      <c r="E8" s="46">
+      <c r="E8" s="43">
         <v>200</v>
       </c>
-      <c r="F8" s="43">
+      <c r="F8" s="40">
         <v>49</v>
       </c>
-      <c r="G8" s="44">
+      <c r="G8" s="41">
         <v>15</v>
       </c>
-      <c r="H8" s="45">
+      <c r="H8" s="42">
         <v>10</v>
       </c>
-      <c r="I8" s="97">
+      <c r="I8" s="92">
         <v>0</v>
       </c>
-      <c r="J8" s="97">
+      <c r="J8" s="92">
         <v>1.39</v>
       </c>
-      <c r="K8" s="98">
+      <c r="K8" s="93">
         <v>0</v>
       </c>
-      <c r="L8" s="99">
+      <c r="L8" s="94">
         <v>1.19</v>
       </c>
-      <c r="M8" s="97">
+      <c r="M8" s="92">
         <v>0</v>
       </c>
-      <c r="N8" s="97">
+      <c r="N8" s="92">
         <v>1.17</v>
       </c>
-      <c r="O8" s="100" t="s">
+      <c r="O8" s="95" t="s">
         <v>50</v>
       </c>
-      <c r="P8" s="101"/>
-      <c r="Q8" s="101"/>
-    </row>
-    <row r="9" spans="3:17">
-      <c r="C9" s="47">
+      <c r="P8" s="96"/>
+      <c r="Q8" s="96"/>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="C9" s="44">
         <v>2530</v>
       </c>
-      <c r="D9" s="47">
+      <c r="D9" s="44">
         <v>1175</v>
       </c>
-      <c r="E9" s="47">
+      <c r="E9" s="44">
         <v>350</v>
       </c>
-      <c r="F9" s="39">
+      <c r="F9" s="36">
         <v>77</v>
       </c>
-      <c r="G9" s="40">
+      <c r="G9" s="37">
         <v>34</v>
       </c>
-      <c r="H9" s="41">
+      <c r="H9" s="38">
         <v>18</v>
       </c>
-      <c r="I9" s="92">
+      <c r="I9" s="87">
         <v>0</v>
       </c>
-      <c r="J9" s="92">
+      <c r="J9" s="87">
         <v>1.5</v>
       </c>
-      <c r="K9" s="93">
+      <c r="K9" s="88">
         <v>0</v>
       </c>
-      <c r="L9" s="94">
+      <c r="L9" s="89">
         <v>1.25</v>
       </c>
-      <c r="M9" s="92">
+      <c r="M9" s="87">
         <v>0</v>
       </c>
-      <c r="N9" s="92">
+      <c r="N9" s="87">
         <v>1.19</v>
       </c>
-      <c r="O9" s="95" t="s">
+      <c r="O9" s="90" t="s">
         <v>51</v>
       </c>
-      <c r="P9" s="96"/>
-      <c r="Q9" s="96"/>
-    </row>
-    <row r="10" spans="3:17">
-      <c r="C10" s="46">
+      <c r="P9" s="91"/>
+      <c r="Q9" s="91"/>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="C10" s="43">
         <v>1265</v>
       </c>
-      <c r="D10" s="46">
+      <c r="D10" s="43">
         <v>600</v>
       </c>
-      <c r="E10" s="46">
+      <c r="E10" s="43">
         <v>180</v>
       </c>
-      <c r="F10" s="43">
+      <c r="F10" s="40">
         <v>28</v>
       </c>
-      <c r="G10" s="44">
+      <c r="G10" s="41">
         <v>14</v>
       </c>
-      <c r="H10" s="45">
+      <c r="H10" s="42">
         <v>9</v>
       </c>
-      <c r="I10" s="97">
+      <c r="I10" s="92">
         <v>0</v>
       </c>
-      <c r="J10" s="97">
+      <c r="J10" s="92">
         <v>1.3952</v>
       </c>
-      <c r="K10" s="98">
+      <c r="K10" s="93">
         <v>0</v>
       </c>
-      <c r="L10" s="99">
+      <c r="L10" s="94">
         <v>1.268</v>
       </c>
-      <c r="M10" s="97">
+      <c r="M10" s="92">
         <v>0</v>
       </c>
-      <c r="N10" s="97">
+      <c r="N10" s="92">
         <v>1.18</v>
       </c>
-      <c r="O10" s="100" t="s">
+      <c r="O10" s="95" t="s">
         <v>52</v>
       </c>
-      <c r="P10" s="101"/>
-      <c r="Q10" s="101"/>
-    </row>
-    <row r="11" spans="3:17">
-      <c r="C11" s="47">
+      <c r="P10" s="96"/>
+      <c r="Q10" s="96"/>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="C11" s="44">
         <v>1897.5</v>
       </c>
-      <c r="D11" s="47">
+      <c r="D11" s="44">
         <v>715</v>
       </c>
-      <c r="E11" s="47">
+      <c r="E11" s="44">
         <v>300</v>
       </c>
-      <c r="F11" s="39">
+      <c r="F11" s="36">
         <v>41</v>
       </c>
-      <c r="G11" s="40">
+      <c r="G11" s="37">
         <v>17</v>
       </c>
-      <c r="H11" s="41">
+      <c r="H11" s="38">
         <v>15</v>
       </c>
-      <c r="I11" s="92">
+      <c r="I11" s="87">
         <v>0</v>
       </c>
-      <c r="J11" s="92">
+      <c r="J11" s="87">
         <v>1.3952</v>
       </c>
-      <c r="K11" s="93">
+      <c r="K11" s="88">
         <v>0</v>
       </c>
-      <c r="L11" s="94">
+      <c r="L11" s="89">
         <v>1.268</v>
       </c>
-      <c r="M11" s="92">
+      <c r="M11" s="87">
         <v>0</v>
       </c>
-      <c r="N11" s="92">
+      <c r="N11" s="87">
         <v>1.2</v>
       </c>
-      <c r="O11" s="95" t="s">
+      <c r="O11" s="90" t="s">
         <v>53</v>
       </c>
-      <c r="P11" s="96"/>
-      <c r="Q11" s="96"/>
-    </row>
-    <row r="12" spans="3:17">
-      <c r="C12" s="46">
-        <v>3332.08823529412</v>
-      </c>
-      <c r="D12" s="46">
+      <c r="P11" s="91"/>
+      <c r="Q11" s="91"/>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="C12" s="43">
+        <v>3332.0882352941198</v>
+      </c>
+      <c r="D12" s="43">
         <v>1421.39215686275</v>
       </c>
-      <c r="E12" s="46">
+      <c r="E12" s="43">
         <v>600</v>
       </c>
-      <c r="F12" s="43">
-        <v>55.825</v>
-      </c>
-      <c r="G12" s="44">
+      <c r="F12" s="40">
+        <v>55.825000000000003</v>
+      </c>
+      <c r="G12" s="41">
         <v>36.18</v>
       </c>
-      <c r="H12" s="45">
+      <c r="H12" s="42">
         <v>39</v>
       </c>
-      <c r="I12" s="97">
-        <v>1.99666703875969</v>
-      </c>
-      <c r="J12" s="97">
-        <v>0.83712</v>
-      </c>
-      <c r="K12" s="98">
+      <c r="I12" s="92">
+        <v>1.9966670387596901</v>
+      </c>
+      <c r="J12" s="92">
+        <v>0.83711999999999998</v>
+      </c>
+      <c r="K12" s="93">
         <v>1.45562727909392</v>
       </c>
-      <c r="L12" s="99">
-        <v>0.7608</v>
-      </c>
-      <c r="M12" s="97">
-        <v>0.333333333333333</v>
-      </c>
-      <c r="N12" s="97">
-        <v>0.708</v>
-      </c>
-      <c r="O12" s="100" t="s">
+      <c r="L12" s="94">
+        <v>0.76080000000000003</v>
+      </c>
+      <c r="M12" s="92">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="N12" s="92">
+        <v>0.70799999999999996</v>
+      </c>
+      <c r="O12" s="95" t="s">
         <v>54</v>
       </c>
-      <c r="P12" s="101"/>
-      <c r="Q12" s="101"/>
-    </row>
-    <row r="13" spans="3:17">
-      <c r="C13" s="47">
-        <v>5331.34117647059</v>
-      </c>
-      <c r="D13" s="47">
-        <v>2920.89411764706</v>
-      </c>
-      <c r="E13" s="47">
+      <c r="P12" s="96"/>
+      <c r="Q12" s="96"/>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="C13" s="44">
+        <v>5331.3411764705897</v>
+      </c>
+      <c r="D13" s="44">
+        <v>2920.8941176470598</v>
+      </c>
+      <c r="E13" s="44">
         <v>1100</v>
       </c>
-      <c r="F13" s="39">
-        <v>94.9025</v>
-      </c>
-      <c r="G13" s="40">
-        <v>63.315</v>
-      </c>
-      <c r="H13" s="41">
+      <c r="F13" s="36">
+        <v>94.902500000000003</v>
+      </c>
+      <c r="G13" s="37">
+        <v>63.314999999999998</v>
+      </c>
+      <c r="H13" s="38">
         <v>48.75</v>
       </c>
-      <c r="I13" s="92">
-        <v>1.99666703875969</v>
-      </c>
-      <c r="J13" s="92">
-        <v>0.83712</v>
-      </c>
-      <c r="K13" s="93">
+      <c r="I13" s="87">
+        <v>1.9966670387596901</v>
+      </c>
+      <c r="J13" s="87">
+        <v>0.83711999999999998</v>
+      </c>
+      <c r="K13" s="88">
         <v>1.45562727909392</v>
       </c>
-      <c r="L13" s="94">
-        <v>0.7608</v>
-      </c>
-      <c r="M13" s="92">
-        <v>0.333333333333333</v>
-      </c>
-      <c r="N13" s="92">
+      <c r="L13" s="89">
+        <v>0.76080000000000003</v>
+      </c>
+      <c r="M13" s="87">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="N13" s="87">
         <v>0.72</v>
       </c>
-      <c r="O13" s="95" t="s">
+      <c r="O13" s="90" t="s">
         <v>55</v>
       </c>
-      <c r="P13" s="96"/>
-      <c r="Q13" s="96"/>
-    </row>
-    <row r="14" spans="3:17">
-      <c r="C14" s="48">
+      <c r="P13" s="91"/>
+      <c r="Q13" s="91"/>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="C14" s="45">
         <v>1200</v>
       </c>
-      <c r="D14" s="48">
+      <c r="D14" s="45">
         <v>733</v>
       </c>
-      <c r="E14" s="48">
+      <c r="E14" s="45">
         <v>263</v>
       </c>
-      <c r="F14" s="49">
+      <c r="F14" s="46">
         <v>42</v>
       </c>
-      <c r="G14" s="50">
+      <c r="G14" s="47">
         <v>22</v>
       </c>
-      <c r="H14" s="51">
+      <c r="H14" s="48">
         <v>9</v>
       </c>
-      <c r="I14" s="102">
+      <c r="I14" s="97">
         <v>0</v>
       </c>
-      <c r="J14" s="103">
+      <c r="J14" s="98">
         <v>0.01</v>
       </c>
-      <c r="K14" s="104">
+      <c r="K14" s="99">
         <v>0</v>
       </c>
-      <c r="L14" s="105">
+      <c r="L14" s="100">
         <v>0.01</v>
       </c>
-      <c r="M14" s="103">
+      <c r="M14" s="98">
         <v>0</v>
       </c>
-      <c r="N14" s="103">
+      <c r="N14" s="98">
         <v>0.01</v>
       </c>
-      <c r="O14" s="106" t="s">
+      <c r="O14" s="101" t="s">
         <v>56</v>
       </c>
-      <c r="P14" s="107"/>
-      <c r="Q14" s="107"/>
-    </row>
-    <row r="15" spans="3:17">
-      <c r="C15" s="52">
+      <c r="P14" s="102"/>
+      <c r="Q14" s="102"/>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="C15" s="49">
         <v>450</v>
       </c>
-      <c r="D15" s="52">
+      <c r="D15" s="49">
         <v>450</v>
       </c>
-      <c r="E15" s="52">
+      <c r="E15" s="49">
         <v>450</v>
       </c>
-      <c r="F15" s="53">
+      <c r="F15" s="50">
         <v>18</v>
       </c>
-      <c r="G15" s="54">
+      <c r="G15" s="51">
         <v>18</v>
       </c>
-      <c r="H15" s="55">
+      <c r="H15" s="52">
         <v>18</v>
       </c>
-      <c r="I15" s="108">
+      <c r="I15" s="103">
         <v>0.265822784810126</v>
       </c>
-      <c r="J15" s="109">
+      <c r="J15" s="104">
         <v>0.06</v>
       </c>
-      <c r="K15" s="110">
+      <c r="K15" s="105">
         <v>0.265822784810126</v>
       </c>
-      <c r="L15" s="111">
+      <c r="L15" s="106">
         <v>0.06</v>
       </c>
-      <c r="M15" s="109">
+      <c r="M15" s="104">
         <v>0.265822784810126</v>
       </c>
-      <c r="N15" s="109">
+      <c r="N15" s="104">
         <v>0.06</v>
       </c>
-      <c r="O15" s="112" t="s">
+      <c r="O15" s="107" t="s">
         <v>57</v>
       </c>
-      <c r="P15" s="113"/>
-      <c r="Q15" s="113"/>
-    </row>
-    <row r="16" spans="3:17">
-      <c r="C16" s="56">
+      <c r="P15" s="108"/>
+      <c r="Q15" s="108"/>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="C16" s="53">
         <v>200</v>
       </c>
-      <c r="D16" s="56">
+      <c r="D16" s="53">
         <v>200</v>
       </c>
-      <c r="E16" s="56">
+      <c r="E16" s="53">
         <v>200</v>
       </c>
-      <c r="F16" s="57">
+      <c r="F16" s="54">
         <v>20</v>
       </c>
-      <c r="G16" s="58">
+      <c r="G16" s="55">
         <v>20</v>
       </c>
-      <c r="H16" s="59">
+      <c r="H16" s="56">
         <v>20</v>
       </c>
-      <c r="I16" s="114">
-        <v>0.013</v>
-      </c>
-      <c r="J16" s="115">
-        <v>0.036</v>
-      </c>
-      <c r="K16" s="116">
-        <v>0.013</v>
-      </c>
-      <c r="L16" s="117">
-        <v>0.036</v>
-      </c>
-      <c r="M16" s="115">
-        <v>0.013</v>
-      </c>
-      <c r="N16" s="115">
-        <v>0.036</v>
-      </c>
-      <c r="O16" s="118" t="s">
+      <c r="I16" s="109">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="J16" s="110">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="K16" s="111">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="L16" s="112">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="M16" s="110">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="N16" s="110">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="O16" s="113" t="s">
         <v>58</v>
       </c>
-      <c r="P16" s="119"/>
-      <c r="Q16" s="119"/>
-    </row>
-    <row r="17" spans="3:17">
-      <c r="C17" s="52">
+      <c r="P16" s="114"/>
+      <c r="Q16" s="114"/>
+    </row>
+    <row r="17" spans="1:25">
+      <c r="C17" s="49">
         <v>175</v>
       </c>
-      <c r="D17" s="52">
+      <c r="D17" s="49">
         <v>175</v>
       </c>
-      <c r="E17" s="52">
+      <c r="E17" s="49">
         <v>175</v>
       </c>
-      <c r="F17" s="53">
+      <c r="F17" s="50">
         <v>5</v>
       </c>
-      <c r="G17" s="54">
+      <c r="G17" s="51">
         <v>5</v>
       </c>
-      <c r="H17" s="55">
+      <c r="H17" s="52">
         <v>5</v>
       </c>
-      <c r="I17" s="108">
-        <v>0.014</v>
-      </c>
-      <c r="J17" s="109">
+      <c r="I17" s="103">
+        <v>1.4E-2</v>
+      </c>
+      <c r="J17" s="104">
         <v>0</v>
       </c>
-      <c r="K17" s="110">
-        <v>0.014</v>
-      </c>
-      <c r="L17" s="111">
+      <c r="K17" s="105">
+        <v>1.4E-2</v>
+      </c>
+      <c r="L17" s="106">
         <v>0</v>
       </c>
-      <c r="M17" s="109">
-        <v>0.014</v>
-      </c>
-      <c r="N17" s="109">
+      <c r="M17" s="104">
+        <v>1.4E-2</v>
+      </c>
+      <c r="N17" s="104">
         <v>0</v>
       </c>
-      <c r="O17" s="112" t="s">
+      <c r="O17" s="107" t="s">
         <v>59</v>
       </c>
-      <c r="P17" s="113"/>
-      <c r="Q17" s="113"/>
-    </row>
-    <row r="18" spans="3:17">
-      <c r="C18" s="60">
+      <c r="P17" s="108"/>
+      <c r="Q17" s="108"/>
+    </row>
+    <row r="18" spans="1:25">
+      <c r="C18" s="57">
         <v>1000</v>
       </c>
-      <c r="D18" s="60">
+      <c r="D18" s="57">
         <v>720</v>
       </c>
-      <c r="E18" s="60">
+      <c r="E18" s="57">
         <v>364</v>
       </c>
-      <c r="F18" s="61">
+      <c r="F18" s="58">
         <v>50</v>
       </c>
-      <c r="G18" s="62">
+      <c r="G18" s="59">
         <v>31</v>
       </c>
-      <c r="H18" s="63">
+      <c r="H18" s="60">
         <v>18</v>
       </c>
-      <c r="I18" s="120">
+      <c r="I18" s="115">
         <v>0.2389</v>
       </c>
-      <c r="J18" s="121">
-        <v>0.03056</v>
-      </c>
-      <c r="K18" s="122">
+      <c r="J18" s="116">
+        <v>3.056E-2</v>
+      </c>
+      <c r="K18" s="117">
         <v>0.2389</v>
       </c>
-      <c r="L18" s="123">
-        <v>0.03056</v>
-      </c>
-      <c r="M18" s="121">
+      <c r="L18" s="118">
+        <v>3.056E-2</v>
+      </c>
+      <c r="M18" s="116">
         <v>0.2389</v>
       </c>
-      <c r="N18" s="121">
-        <v>0.03056</v>
-      </c>
-      <c r="O18" s="124" t="s">
+      <c r="N18" s="116">
+        <v>3.056E-2</v>
+      </c>
+      <c r="O18" s="119" t="s">
         <v>60</v>
       </c>
-      <c r="P18" s="125"/>
-      <c r="Q18" s="125"/>
-    </row>
-    <row r="19" spans="3:17">
-      <c r="C19" s="64">
+      <c r="P18" s="120"/>
+      <c r="Q18" s="120"/>
+    </row>
+    <row r="19" spans="1:25">
+      <c r="C19" s="61">
         <v>1556</v>
       </c>
-      <c r="D19" s="64">
+      <c r="D19" s="61">
         <v>1143</v>
       </c>
-      <c r="E19" s="65">
+      <c r="E19" s="62">
         <v>673</v>
       </c>
-      <c r="F19" s="66">
+      <c r="F19" s="63">
         <v>54</v>
       </c>
-      <c r="G19" s="67">
+      <c r="G19" s="64">
         <v>40</v>
       </c>
-      <c r="H19" s="68">
+      <c r="H19" s="65">
         <v>24</v>
       </c>
-      <c r="I19" s="126">
-        <v>0.035</v>
-      </c>
-      <c r="J19" s="127">
+      <c r="I19" s="121">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="J19" s="122">
         <v>0.02</v>
       </c>
-      <c r="K19" s="128">
-        <v>0.035</v>
-      </c>
-      <c r="L19" s="129">
+      <c r="K19" s="123">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="L19" s="124">
         <v>0.02</v>
       </c>
-      <c r="M19" s="127">
-        <v>0.035</v>
-      </c>
-      <c r="N19" s="127">
+      <c r="M19" s="122">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="N19" s="122">
         <v>0.02</v>
       </c>
-      <c r="O19" s="130" t="s">
+      <c r="O19" s="125" t="s">
         <v>61</v>
       </c>
-      <c r="P19" s="131"/>
-      <c r="Q19" s="131"/>
-    </row>
-    <row r="20" spans="3:17">
-      <c r="C20" s="69">
+      <c r="P19" s="126"/>
+      <c r="Q19" s="126"/>
+    </row>
+    <row r="20" spans="1:25">
+      <c r="C20" s="66">
         <v>2332</v>
       </c>
-      <c r="D20" s="69">
+      <c r="D20" s="66">
         <v>1511</v>
       </c>
-      <c r="E20" s="69">
+      <c r="E20" s="66">
         <v>965</v>
       </c>
-      <c r="F20" s="70">
+      <c r="F20" s="67">
         <v>163</v>
       </c>
-      <c r="G20" s="71">
+      <c r="G20" s="68">
         <v>106</v>
       </c>
-      <c r="H20" s="72">
+      <c r="H20" s="69">
         <v>68</v>
       </c>
-      <c r="I20" s="132">
-        <v>0.463266666666667</v>
-      </c>
-      <c r="J20" s="133">
+      <c r="I20" s="127">
+        <v>0.46326666666666699</v>
+      </c>
+      <c r="J20" s="128">
         <v>1.91881040892193</v>
       </c>
-      <c r="K20" s="134">
-        <v>0.39244195142278</v>
-      </c>
-      <c r="L20" s="135">
+      <c r="K20" s="129">
+        <v>0.39244195142277999</v>
+      </c>
+      <c r="L20" s="130">
         <v>1.60098120886331</v>
       </c>
-      <c r="M20" s="133">
+      <c r="M20" s="128">
         <v>0.37890902062421</v>
       </c>
-      <c r="N20" s="133">
-        <v>1.56940834539103</v>
-      </c>
-      <c r="O20" s="136" t="s">
+      <c r="N20" s="128">
+        <v>1.5694083453910299</v>
+      </c>
+      <c r="O20" s="131" t="s">
         <v>62</v>
       </c>
-      <c r="P20" s="125"/>
-      <c r="Q20" s="125"/>
-    </row>
-    <row r="21" spans="3:17">
-      <c r="C21" s="73">
-        <v>769.876819708847</v>
-      </c>
-      <c r="D21" s="73">
-        <v>648.044461034383</v>
-      </c>
-      <c r="E21" s="73">
-        <v>518.290592438013</v>
-      </c>
-      <c r="F21" s="74">
+      <c r="P20" s="120"/>
+      <c r="Q20" s="120"/>
+    </row>
+    <row r="21" spans="1:25">
+      <c r="C21" s="70">
+        <v>769.87681970884705</v>
+      </c>
+      <c r="D21" s="70">
+        <v>648.04446103438295</v>
+      </c>
+      <c r="E21" s="70">
+        <v>518.29059243801305</v>
+      </c>
+      <c r="F21" s="71">
         <v>26.9456886898096</v>
       </c>
-      <c r="G21" s="75">
-        <v>22.6815561362034</v>
-      </c>
-      <c r="H21" s="76">
+      <c r="G21" s="72">
+        <v>22.681556136203401</v>
+      </c>
+      <c r="H21" s="73">
         <v>18.1401707353305</v>
       </c>
-      <c r="I21" s="137">
-        <v>2.77777777777778</v>
-      </c>
-      <c r="J21" s="138">
-        <v>2.22222222222222</v>
-      </c>
-      <c r="K21" s="139">
-        <v>1.66666666666667</v>
-      </c>
-      <c r="L21" s="140">
-        <v>1.38888888888889</v>
-      </c>
-      <c r="M21" s="138">
-        <v>1.13888888888889</v>
-      </c>
-      <c r="N21" s="138">
+      <c r="I21" s="132">
+        <v>2.7777777777777799</v>
+      </c>
+      <c r="J21" s="133">
+        <v>2.2222222222222201</v>
+      </c>
+      <c r="K21" s="134">
+        <v>1.6666666666666701</v>
+      </c>
+      <c r="L21" s="135">
+        <v>1.3888888888888899</v>
+      </c>
+      <c r="M21" s="133">
+        <v>1.1388888888888899</v>
+      </c>
+      <c r="N21" s="133">
         <v>0.3</v>
       </c>
-      <c r="O21" s="141" t="s">
+      <c r="O21" s="136" t="s">
         <v>63</v>
       </c>
-      <c r="P21" s="142"/>
-      <c r="Q21" s="142"/>
-    </row>
-    <row r="22" spans="3:17">
-      <c r="C22" s="77">
-        <v>1259.79843225084</v>
-      </c>
-      <c r="D22" s="77">
-        <v>894.301356227448</v>
-      </c>
-      <c r="E22" s="77">
+      <c r="P21" s="137"/>
+      <c r="Q21" s="137"/>
+    </row>
+    <row r="22" spans="1:25">
+      <c r="C22" s="74">
+        <v>1259.7984322508401</v>
+      </c>
+      <c r="D22" s="74">
+        <v>894.30135622744797</v>
+      </c>
+      <c r="E22" s="74">
         <v>495</v>
       </c>
-      <c r="F22" s="78">
-        <v>44.0929451287794</v>
-      </c>
-      <c r="G22" s="79">
-        <v>31.3005474679607</v>
-      </c>
-      <c r="H22" s="80">
-        <v>17.325</v>
-      </c>
-      <c r="I22" s="143">
+      <c r="F22" s="75">
+        <v>44.092945128779398</v>
+      </c>
+      <c r="G22" s="76">
+        <v>31.300547467960701</v>
+      </c>
+      <c r="H22" s="77">
+        <v>17.324999999999999</v>
+      </c>
+      <c r="I22" s="138">
         <v>2</v>
       </c>
-      <c r="J22" s="144">
+      <c r="J22" s="139">
         <v>0.3</v>
       </c>
-      <c r="K22" s="145">
+      <c r="K22" s="140">
         <v>1.80555555555556</v>
       </c>
-      <c r="L22" s="146">
+      <c r="L22" s="141">
         <v>0.3</v>
       </c>
-      <c r="M22" s="144">
+      <c r="M22" s="139">
         <v>1.5</v>
       </c>
-      <c r="N22" s="144">
+      <c r="N22" s="139">
         <v>0.3</v>
       </c>
-      <c r="O22" s="147" t="s">
+      <c r="O22" s="142" t="s">
         <v>64</v>
       </c>
-      <c r="P22" s="148"/>
-      <c r="Q22" s="148"/>
-    </row>
-    <row r="23" spans="3:17">
-      <c r="C23" s="81">
+      <c r="P22" s="143"/>
+      <c r="Q22" s="143"/>
+    </row>
+    <row r="23" spans="1:25">
+      <c r="C23" s="78">
         <v>174</v>
       </c>
-      <c r="D23" s="81">
+      <c r="D23" s="78">
         <v>174</v>
       </c>
-      <c r="E23" s="81">
+      <c r="E23" s="78">
         <v>174</v>
       </c>
-      <c r="F23" s="82">
+      <c r="F23" s="79">
         <v>3</v>
       </c>
-      <c r="G23" s="83">
+      <c r="G23" s="80">
         <v>3</v>
       </c>
-      <c r="H23" s="84">
+      <c r="H23" s="81">
         <v>3</v>
       </c>
-      <c r="I23" s="149">
+      <c r="I23" s="144">
         <v>0</v>
       </c>
-      <c r="J23" s="150">
-        <v>0.205882352941176</v>
-      </c>
-      <c r="K23" s="151">
+      <c r="J23" s="145">
+        <v>0.20588235294117599</v>
+      </c>
+      <c r="K23" s="146">
         <v>0</v>
       </c>
-      <c r="L23" s="152">
-        <v>0.205882352941176</v>
-      </c>
-      <c r="M23" s="150">
+      <c r="L23" s="147">
+        <v>0.20588235294117599</v>
+      </c>
+      <c r="M23" s="145">
         <v>0</v>
       </c>
-      <c r="N23" s="150">
-        <v>0.205882352941176</v>
-      </c>
-      <c r="O23" s="153" t="s">
+      <c r="N23" s="145">
+        <v>0.20588235294117599</v>
+      </c>
+      <c r="O23" s="148" t="s">
         <v>65</v>
       </c>
-      <c r="P23" s="142"/>
-      <c r="Q23" s="142"/>
-    </row>
-    <row r="26" ht="17.75" spans="3:19">
+      <c r="P23" s="137"/>
+      <c r="Q23" s="137"/>
+    </row>
+    <row r="26" spans="1:25" ht="16.899999999999999">
       <c r="C26" s="25" t="s">
         <v>66</v>
       </c>
@@ -3983,7 +4058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" ht="15.25" spans="1:25">
+    <row r="27" spans="1:25">
       <c r="A27" s="29" t="s">
         <v>4</v>
       </c>
@@ -4106,7 +4181,7 @@
       </c>
       <c r="J28" s="1">
         <f t="shared" si="2"/>
-        <v>0.094</v>
+        <v>9.4E-2</v>
       </c>
       <c r="K28" s="1">
         <f t="shared" si="2"/>
@@ -4114,7 +4189,7 @@
       </c>
       <c r="L28" s="1">
         <f t="shared" si="2"/>
-        <v>0.094</v>
+        <v>9.4E-2</v>
       </c>
       <c r="M28" s="1">
         <f t="shared" si="2"/>
@@ -4122,16 +4197,16 @@
       </c>
       <c r="N28" s="1">
         <f t="shared" si="2"/>
-        <v>0.094</v>
-      </c>
-      <c r="O28" s="154" t="s">
+        <v>9.4E-2</v>
+      </c>
+      <c r="O28" s="149" t="s">
         <v>70</v>
       </c>
       <c r="P28">
         <v>25</v>
       </c>
       <c r="Q28">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="S28" t="str">
         <f>IF(O28="","*","PRE")</f>
@@ -4193,25 +4268,25 @@
         <f t="shared" si="4"/>
         <v>1.33</v>
       </c>
-      <c r="J29" s="155">
+      <c r="J29" s="150">
         <f t="shared" si="4"/>
-        <v>1.094</v>
+        <v>1.0940000000000001</v>
       </c>
       <c r="K29" s="1">
         <f t="shared" si="4"/>
         <v>1.3</v>
       </c>
-      <c r="L29" s="155">
+      <c r="L29" s="150">
         <f t="shared" si="4"/>
-        <v>1.094</v>
+        <v>1.0940000000000001</v>
       </c>
       <c r="M29" s="1">
         <f t="shared" si="4"/>
         <v>1.28</v>
       </c>
-      <c r="N29" s="155">
+      <c r="N29" s="150">
         <f t="shared" si="4"/>
-        <v>1.094</v>
+        <v>1.0940000000000001</v>
       </c>
       <c r="O29" t="s">
         <v>73</v>
@@ -4220,7 +4295,7 @@
         <v>25</v>
       </c>
       <c r="Q29">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="S29" t="str">
         <f t="shared" ref="S29:S39" si="5">IF(O29="","*","PRE")</f>
@@ -4284,7 +4359,7 @@
       </c>
       <c r="J30" s="1">
         <f t="shared" si="7"/>
-        <v>0.094</v>
+        <v>9.4E-2</v>
       </c>
       <c r="K30" s="1">
         <f t="shared" si="7"/>
@@ -4292,7 +4367,7 @@
       </c>
       <c r="L30" s="1">
         <f t="shared" si="7"/>
-        <v>0.094</v>
+        <v>9.4E-2</v>
       </c>
       <c r="M30" s="1">
         <f t="shared" si="7"/>
@@ -4300,9 +4375,9 @@
       </c>
       <c r="N30" s="1">
         <f t="shared" si="7"/>
-        <v>0.094</v>
-      </c>
-      <c r="O30" s="154" t="s">
+        <v>9.4E-2</v>
+      </c>
+      <c r="O30" s="149" t="s">
         <v>70</v>
       </c>
       <c r="S30" t="str">
@@ -4383,7 +4458,7 @@
         <v>25</v>
       </c>
       <c r="Q31">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="S31" t="str">
         <f t="shared" si="5"/>
@@ -4456,7 +4531,7 @@
         <f t="shared" si="9"/>
         <v>1.19</v>
       </c>
-      <c r="O32" s="154" t="s">
+      <c r="O32" s="149" t="s">
         <v>70</v>
       </c>
       <c r="S32" t="str">
@@ -4537,7 +4612,7 @@
         <v>25</v>
       </c>
       <c r="Q33">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="S33" t="str">
         <f t="shared" si="5"/>
@@ -4610,7 +4685,7 @@
         <f t="shared" si="11"/>
         <v>1.2</v>
       </c>
-      <c r="O34" s="154" t="s">
+      <c r="O34" s="149" t="s">
         <v>70</v>
       </c>
       <c r="S34" t="str">
@@ -4647,7 +4722,7 @@
       </c>
       <c r="C35" s="22">
         <f t="shared" ref="C35:N35" si="12">C12</f>
-        <v>3332.08823529412</v>
+        <v>3332.0882352941198</v>
       </c>
       <c r="D35" s="22">
         <f t="shared" si="12"/>
@@ -4659,7 +4734,7 @@
       </c>
       <c r="F35" s="22">
         <f t="shared" si="12"/>
-        <v>55.825</v>
+        <v>55.825000000000003</v>
       </c>
       <c r="G35" s="22">
         <f t="shared" si="12"/>
@@ -4671,11 +4746,11 @@
       </c>
       <c r="I35" s="1">
         <f t="shared" si="12"/>
-        <v>1.99666703875969</v>
+        <v>1.9966670387596901</v>
       </c>
       <c r="J35" s="1">
         <f t="shared" si="12"/>
-        <v>0.83712</v>
+        <v>0.83711999999999998</v>
       </c>
       <c r="K35" s="1">
         <f t="shared" si="12"/>
@@ -4683,15 +4758,15 @@
       </c>
       <c r="L35" s="1">
         <f t="shared" si="12"/>
-        <v>0.7608</v>
+        <v>0.76080000000000003</v>
       </c>
       <c r="M35" s="1">
         <f t="shared" si="12"/>
-        <v>0.333333333333333</v>
+        <v>0.33333333333333298</v>
       </c>
       <c r="N35" s="1">
         <f t="shared" si="12"/>
-        <v>0.708</v>
+        <v>0.70799999999999996</v>
       </c>
       <c r="O35" t="s">
         <v>76</v>
@@ -4700,7 +4775,7 @@
         <v>25</v>
       </c>
       <c r="Q35">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="S35" t="str">
         <f t="shared" si="5"/>
@@ -4727,14 +4802,14 @@
         <v>72</v>
       </c>
     </row>
-    <row r="36" spans="3:25">
+    <row r="36" spans="1:25">
       <c r="C36" s="22">
         <f t="shared" ref="C36:N36" si="13">C13</f>
-        <v>5331.34117647059</v>
+        <v>5331.3411764705897</v>
       </c>
       <c r="D36" s="22">
         <f t="shared" si="13"/>
-        <v>2920.89411764706</v>
+        <v>2920.8941176470598</v>
       </c>
       <c r="E36" s="22">
         <f t="shared" si="13"/>
@@ -4742,11 +4817,11 @@
       </c>
       <c r="F36" s="22">
         <f t="shared" si="13"/>
-        <v>94.9025</v>
+        <v>94.902500000000003</v>
       </c>
       <c r="G36" s="22">
         <f t="shared" si="13"/>
-        <v>63.315</v>
+        <v>63.314999999999998</v>
       </c>
       <c r="H36" s="22">
         <f t="shared" si="13"/>
@@ -4754,11 +4829,11 @@
       </c>
       <c r="I36" s="1">
         <f t="shared" si="13"/>
-        <v>1.99666703875969</v>
+        <v>1.9966670387596901</v>
       </c>
       <c r="J36" s="1">
         <f t="shared" si="13"/>
-        <v>0.83712</v>
+        <v>0.83711999999999998</v>
       </c>
       <c r="K36" s="1">
         <f t="shared" si="13"/>
@@ -4766,17 +4841,17 @@
       </c>
       <c r="L36" s="1">
         <f t="shared" si="13"/>
-        <v>0.7608</v>
+        <v>0.76080000000000003</v>
       </c>
       <c r="M36" s="1">
         <f t="shared" si="13"/>
-        <v>0.333333333333333</v>
+        <v>0.33333333333333298</v>
       </c>
       <c r="N36" s="1">
         <f t="shared" si="13"/>
         <v>0.72</v>
       </c>
-      <c r="O36" s="154" t="s">
+      <c r="O36" s="149" t="s">
         <v>70</v>
       </c>
       <c r="S36" t="str">
@@ -4804,18 +4879,18 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="3:25">
+    <row r="37" spans="1:25">
       <c r="C37" s="22">
         <f t="shared" ref="C37:N37" si="14">C21</f>
-        <v>769.876819708847</v>
+        <v>769.87681970884705</v>
       </c>
       <c r="D37" s="22">
         <f t="shared" si="14"/>
-        <v>648.044461034383</v>
+        <v>648.04446103438295</v>
       </c>
       <c r="E37" s="22">
         <f t="shared" si="14"/>
-        <v>518.290592438013</v>
+        <v>518.29059243801305</v>
       </c>
       <c r="F37" s="22">
         <f t="shared" si="14"/>
@@ -4823,7 +4898,7 @@
       </c>
       <c r="G37" s="22">
         <f t="shared" si="14"/>
-        <v>22.6815561362034</v>
+        <v>22.681556136203401</v>
       </c>
       <c r="H37" s="22">
         <f t="shared" si="14"/>
@@ -4831,29 +4906,29 @@
       </c>
       <c r="I37" s="1">
         <f t="shared" si="14"/>
-        <v>2.77777777777778</v>
+        <v>2.7777777777777799</v>
       </c>
       <c r="J37" s="1">
         <f t="shared" si="14"/>
-        <v>2.22222222222222</v>
+        <v>2.2222222222222201</v>
       </c>
       <c r="K37" s="1">
         <f t="shared" si="14"/>
-        <v>1.66666666666667</v>
+        <v>1.6666666666666701</v>
       </c>
       <c r="L37" s="1">
         <f t="shared" si="14"/>
-        <v>1.38888888888889</v>
+        <v>1.3888888888888899</v>
       </c>
       <c r="M37" s="1">
         <f t="shared" si="14"/>
-        <v>1.13888888888889</v>
+        <v>1.1388888888888899</v>
       </c>
       <c r="N37" s="1">
         <f t="shared" si="14"/>
         <v>0.3</v>
       </c>
-      <c r="O37" s="154" t="s">
+      <c r="O37" s="149" t="s">
         <v>70</v>
       </c>
       <c r="S37" t="str">
@@ -4881,14 +4956,14 @@
         <v>72</v>
       </c>
     </row>
-    <row r="38" spans="3:25">
+    <row r="38" spans="1:25">
       <c r="C38" s="22">
         <f t="shared" ref="C38:N38" si="15">C22</f>
-        <v>1259.79843225084</v>
+        <v>1259.7984322508401</v>
       </c>
       <c r="D38" s="22">
         <f t="shared" si="15"/>
-        <v>894.301356227448</v>
+        <v>894.30135622744797</v>
       </c>
       <c r="E38" s="22">
         <f t="shared" si="15"/>
@@ -4896,15 +4971,15 @@
       </c>
       <c r="F38" s="22">
         <f t="shared" si="15"/>
-        <v>44.0929451287794</v>
+        <v>44.092945128779398</v>
       </c>
       <c r="G38" s="22">
         <f t="shared" si="15"/>
-        <v>31.3005474679607</v>
+        <v>31.300547467960701</v>
       </c>
       <c r="H38" s="22">
         <f t="shared" si="15"/>
-        <v>17.325</v>
+        <v>17.324999999999999</v>
       </c>
       <c r="I38" s="1">
         <f t="shared" si="15"/>
@@ -4930,7 +5005,7 @@
         <f t="shared" si="15"/>
         <v>0.3</v>
       </c>
-      <c r="O38" s="154" t="s">
+      <c r="O38" s="149" t="s">
         <v>70</v>
       </c>
       <c r="S38" t="str">
@@ -4959,77 +5034,77 @@
       </c>
     </row>
     <row r="39" spans="1:25">
-      <c r="A39" s="85" t="str">
+      <c r="A39" s="82" t="str">
         <f>A35</f>
         <v>HH2</v>
       </c>
-      <c r="B39" s="85" t="s">
+      <c r="B39" s="82" t="s">
         <v>69</v>
       </c>
-      <c r="C39" s="86">
+      <c r="C39" s="83">
         <f>C29</f>
         <v>900</v>
       </c>
-      <c r="D39" s="86">
+      <c r="D39" s="83">
         <f t="shared" ref="D39:H39" si="16">D29</f>
         <v>850</v>
       </c>
-      <c r="E39" s="86">
+      <c r="E39" s="83">
         <f t="shared" si="16"/>
         <v>800</v>
       </c>
-      <c r="F39" s="86">
+      <c r="F39" s="83">
         <f t="shared" si="16"/>
         <v>36</v>
       </c>
-      <c r="G39" s="86">
+      <c r="G39" s="83">
         <f t="shared" si="16"/>
         <v>34</v>
       </c>
-      <c r="H39" s="86">
+      <c r="H39" s="83">
         <f t="shared" si="16"/>
         <v>32</v>
       </c>
-      <c r="I39" s="156">
+      <c r="I39" s="151">
         <v>1.25</v>
       </c>
-      <c r="J39" s="156">
+      <c r="J39" s="151">
         <v>0.12</v>
       </c>
-      <c r="K39" s="156">
+      <c r="K39" s="151">
         <v>1.25</v>
       </c>
-      <c r="L39" s="156">
+      <c r="L39" s="151">
         <v>0.12</v>
       </c>
-      <c r="M39" s="156">
+      <c r="M39" s="151">
         <v>1.25</v>
       </c>
-      <c r="N39" s="156">
+      <c r="N39" s="151">
         <v>0.12</v>
       </c>
-      <c r="O39" s="85" t="s">
+      <c r="O39" s="82" t="s">
         <v>77</v>
       </c>
-      <c r="P39" s="85">
+      <c r="P39" s="82">
         <v>25</v>
       </c>
-      <c r="Q39" s="85">
-        <v>31.536</v>
-      </c>
-      <c r="R39" s="85"/>
-      <c r="S39" s="85" t="str">
+      <c r="Q39" s="82">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="R39" s="82"/>
+      <c r="S39" s="82" t="str">
         <f t="shared" si="5"/>
         <v>PRE</v>
       </c>
-      <c r="T39" s="85" t="str">
+      <c r="T39" s="82" t="str">
         <f t="shared" si="6"/>
         <v>H2prd_Gas_ATR_CCS</v>
       </c>
-      <c r="U39" s="85" t="s">
+      <c r="U39" s="82" t="s">
         <v>78</v>
       </c>
-      <c r="V39" s="85" t="s">
+      <c r="V39" s="82" t="s">
         <v>71</v>
       </c>
       <c r="W39" t="s">
@@ -5050,39 +5125,37 @@
     <mergeCell ref="O1:O4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B3:Q12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9" style="24"/>
-    <col min="2" max="2" width="12.8545454545455" style="24" customWidth="1"/>
-    <col min="3" max="3" width="8.85454545454546" style="24" customWidth="1"/>
-    <col min="4" max="4" width="14.8545454545455" style="24" customWidth="1"/>
+    <col min="2" max="2" width="12.86328125" style="24" customWidth="1"/>
+    <col min="3" max="3" width="8.86328125" style="24" customWidth="1"/>
+    <col min="4" max="4" width="14.86328125" style="24" customWidth="1"/>
     <col min="5" max="5" width="9" style="24" customWidth="1"/>
-    <col min="6" max="6" width="10.2818181818182" style="24" customWidth="1"/>
-    <col min="7" max="7" width="4.57272727272727" style="24" customWidth="1"/>
-    <col min="8" max="8" width="11.5727272727273" style="24" customWidth="1"/>
-    <col min="9" max="9" width="11.2818181818182" style="24" customWidth="1"/>
-    <col min="10" max="10" width="11.4272727272727" style="24" customWidth="1"/>
-    <col min="11" max="11" width="5.57272727272727" style="24" customWidth="1"/>
+    <col min="6" max="6" width="10.265625" style="24" customWidth="1"/>
+    <col min="7" max="7" width="4.59765625" style="24" customWidth="1"/>
+    <col min="8" max="8" width="11.59765625" style="24" customWidth="1"/>
+    <col min="9" max="9" width="11.265625" style="24" customWidth="1"/>
+    <col min="10" max="10" width="11.3984375" style="24" customWidth="1"/>
+    <col min="11" max="11" width="5.59765625" style="24" customWidth="1"/>
     <col min="12" max="12" width="9" style="24"/>
-    <col min="13" max="13" width="11.2818181818182" style="24" customWidth="1"/>
-    <col min="14" max="14" width="12.8545454545455" style="24" customWidth="1"/>
-    <col min="15" max="15" width="15.2818181818182" style="24" customWidth="1"/>
-    <col min="16" max="16" width="4.57272727272727" style="24" customWidth="1"/>
+    <col min="13" max="13" width="11.265625" style="24" customWidth="1"/>
+    <col min="14" max="14" width="12.86328125" style="24" customWidth="1"/>
+    <col min="15" max="15" width="15.265625" style="24" customWidth="1"/>
+    <col min="16" max="16" width="4.59765625" style="24" customWidth="1"/>
     <col min="17" max="17" width="5" style="24" customWidth="1"/>
     <col min="18" max="16384" width="9" style="24"/>
   </cols>
   <sheetData>
-    <row r="3" ht="17.75" spans="4:17">
+    <row r="3" spans="2:17" ht="16.899999999999999">
       <c r="D3" s="25" t="s">
         <v>79</v>
       </c>
@@ -5094,7 +5167,7 @@
       <c r="P3" s="29"/>
       <c r="Q3" s="29"/>
     </row>
-    <row r="4" ht="16" spans="2:17">
+    <row r="4" spans="2:17" ht="14.25">
       <c r="B4" s="26" t="s">
         <v>80</v>
       </c>
@@ -5152,7 +5225,7 @@
         <v>91</v>
       </c>
       <c r="E5" s="24">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="F5" s="27">
         <v>0.6</v>
@@ -5161,10 +5234,10 @@
         <v>0.6</v>
       </c>
       <c r="H5" s="27">
-        <v>189.216</v>
+        <v>189.21600000000001</v>
       </c>
       <c r="I5" s="27">
-        <v>88.3008</v>
+        <v>88.300799999999995</v>
       </c>
       <c r="J5" s="24">
         <v>60</v>
@@ -5201,7 +5274,7 @@
         <v>91</v>
       </c>
       <c r="E6" s="24">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="F6" s="27">
         <v>0.6</v>
@@ -5210,10 +5283,10 @@
         <v>0.6</v>
       </c>
       <c r="H6" s="27">
-        <v>189.216</v>
+        <v>189.21600000000001</v>
       </c>
       <c r="I6" s="27">
-        <v>88.3008</v>
+        <v>88.300799999999995</v>
       </c>
       <c r="J6" s="24">
         <v>60</v>
@@ -5247,7 +5320,7 @@
         <v>91</v>
       </c>
       <c r="E7" s="24">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="F7" s="27">
         <v>0.1</v>
@@ -5256,16 +5329,16 @@
         <v>0.6</v>
       </c>
       <c r="H7" s="27">
-        <v>141.912</v>
+        <v>141.91200000000001</v>
       </c>
       <c r="I7" s="27">
-        <v>75.6864</v>
+        <v>75.686400000000006</v>
       </c>
       <c r="J7" s="24">
         <v>60</v>
       </c>
       <c r="K7" s="30">
-        <v>0.869565217391304</v>
+        <v>0.86956521739130399</v>
       </c>
       <c r="N7" s="24" t="str">
         <f t="shared" si="0"/>
@@ -5293,7 +5366,7 @@
         <v>91</v>
       </c>
       <c r="E8" s="24">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="F8" s="27">
         <v>0.3</v>
@@ -5328,7 +5401,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="9" ht="13" spans="2:17">
+    <row r="9" spans="2:17" ht="13.15">
       <c r="B9" s="28" t="s">
         <v>99</v>
       </c>
@@ -5340,7 +5413,7 @@
       </c>
       <c r="E9" s="24">
         <f t="shared" ref="E9:K9" si="1">E7</f>
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="F9" s="27">
         <f t="shared" si="1"/>
@@ -5352,11 +5425,11 @@
       </c>
       <c r="H9" s="27">
         <f t="shared" si="1"/>
-        <v>141.912</v>
+        <v>141.91200000000001</v>
       </c>
       <c r="I9" s="27">
         <f t="shared" si="1"/>
-        <v>75.6864</v>
+        <v>75.686400000000006</v>
       </c>
       <c r="J9" s="24">
         <f t="shared" si="1"/>
@@ -5364,7 +5437,7 @@
       </c>
       <c r="K9" s="30">
         <f t="shared" si="1"/>
-        <v>0.869565217391304</v>
+        <v>0.86956521739130399</v>
       </c>
       <c r="N9" s="24" t="str">
         <f t="shared" si="0"/>
@@ -5393,7 +5466,7 @@
       </c>
       <c r="E10" s="24">
         <f>E8</f>
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="F10" s="27"/>
       <c r="G10" s="27"/>
@@ -5424,7 +5497,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="2:14">
+    <row r="11" spans="2:17">
       <c r="B11" s="24" t="s">
         <v>70</v>
       </c>
@@ -5462,38 +5535,37 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:AK40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="8" max="8" width="17.5727272727273" customWidth="1"/>
-    <col min="10" max="10" width="10.8545454545455" customWidth="1"/>
+    <col min="8" max="8" width="17.59765625" customWidth="1"/>
+    <col min="10" max="10" width="10.86328125" customWidth="1"/>
     <col min="11" max="13" width="5" customWidth="1"/>
-    <col min="14" max="14" width="8.42727272727273" customWidth="1"/>
+    <col min="14" max="14" width="8.3984375" customWidth="1"/>
     <col min="15" max="15" width="2" customWidth="1"/>
-    <col min="16" max="16" width="3.57272727272727" customWidth="1"/>
-    <col min="17" max="17" width="17.5727272727273" customWidth="1"/>
+    <col min="16" max="16" width="3.59765625" customWidth="1"/>
+    <col min="17" max="17" width="17.59765625" customWidth="1"/>
     <col min="21" max="21" width="2" customWidth="1"/>
-    <col min="22" max="22" width="17.5727272727273" customWidth="1"/>
+    <col min="22" max="22" width="17.59765625" customWidth="1"/>
     <col min="23" max="25" width="6" customWidth="1"/>
     <col min="26" max="26" width="2" customWidth="1"/>
-    <col min="27" max="27" width="17.5727272727273" customWidth="1"/>
-    <col min="28" max="28" width="11.4272727272727" customWidth="1"/>
+    <col min="27" max="27" width="17.59765625" customWidth="1"/>
+    <col min="28" max="28" width="11.3984375" customWidth="1"/>
     <col min="29" max="31" width="5" customWidth="1"/>
-    <col min="33" max="33" width="19.8545454545455" customWidth="1"/>
-    <col min="34" max="34" width="5.57272727272727" customWidth="1"/>
+    <col min="33" max="33" width="19.86328125" customWidth="1"/>
+    <col min="34" max="34" width="5.59765625" customWidth="1"/>
     <col min="35" max="37" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:37">
       <c r="A1" s="2" t="s">
         <v>109</v>
       </c>
@@ -5525,7 +5597,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="2" spans="1:34">
+    <row r="2" spans="1:37">
       <c r="A2" s="4" t="s">
         <v>119</v>
       </c>
@@ -5615,7 +5687,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:34">
+    <row r="3" spans="1:37">
       <c r="A3" s="7" t="s">
         <v>128</v>
       </c>
@@ -5653,7 +5725,7 @@
         <v>439.05</v>
       </c>
       <c r="N3" s="20">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="O3" s="22"/>
       <c r="P3" s="23">
@@ -5665,15 +5737,15 @@
       </c>
       <c r="R3" s="20">
         <f>$P3*K3</f>
-        <v>29.109</v>
+        <v>29.109000000000002</v>
       </c>
       <c r="S3" s="20">
         <f t="shared" ref="S3:T5" si="2">$P3*L3</f>
-        <v>13.226</v>
+        <v>13.226000000000001</v>
       </c>
       <c r="T3" s="20">
         <f t="shared" si="2"/>
-        <v>8.781</v>
+        <v>8.7810000000000006</v>
       </c>
       <c r="V3" t="str">
         <f t="shared" ref="V3:V5" si="3">$H3</f>
@@ -5714,7 +5786,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:34">
+    <row r="4" spans="1:37">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="10">
@@ -5724,7 +5796,7 @@
         <v>661.3</v>
       </c>
       <c r="E4" s="9">
-        <v>138.45</v>
+        <v>138.44999999999999</v>
       </c>
       <c r="F4" s="9">
         <v>1368.75</v>
@@ -5742,17 +5814,17 @@
         <v>338.75</v>
       </c>
       <c r="L4" s="22">
-        <v>138.45</v>
+        <v>138.44999999999999</v>
       </c>
       <c r="M4" s="22">
         <v>87.3</v>
       </c>
       <c r="N4" s="20">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="O4" s="20"/>
       <c r="P4" s="23">
-        <v>0.035</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="Q4" t="str">
         <f t="shared" si="1"/>
@@ -5760,28 +5832,28 @@
       </c>
       <c r="R4" s="20">
         <f t="shared" ref="R4:R5" si="4">$P4*K4</f>
-        <v>11.85625</v>
+        <v>11.856249999999999</v>
       </c>
       <c r="S4" s="20">
         <f t="shared" si="2"/>
-        <v>4.84575</v>
+        <v>4.8457499999999998</v>
       </c>
       <c r="T4" s="20">
         <f t="shared" si="2"/>
-        <v>3.0555</v>
+        <v>3.0554999999999999</v>
       </c>
       <c r="V4" t="str">
         <f t="shared" si="3"/>
         <v>H2Conv_LOHC</v>
       </c>
       <c r="W4">
-        <v>0.925</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="X4">
         <v>0.95</v>
       </c>
       <c r="Y4">
-        <v>0.975</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="AA4" t="str">
         <f t="shared" ref="AA4:AA5" si="5">H4</f>
@@ -5809,7 +5881,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:34">
+    <row r="5" spans="1:37">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="11">
@@ -5843,7 +5915,7 @@
         <v>799.5</v>
       </c>
       <c r="N5" s="20">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="O5" s="20"/>
       <c r="P5" s="23">
@@ -5889,7 +5961,7 @@
         <v>0.255</v>
       </c>
       <c r="AD5" s="1">
-        <v>0.225</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="AE5" s="1">
         <v>0.1875</v>
@@ -5904,7 +5976,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:37">
       <c r="A6" s="10" t="s">
         <v>134</v>
       </c>
@@ -5916,13 +5988,13 @@
         <v>0.02</v>
       </c>
       <c r="E6" s="13">
-        <v>0.035</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="F6" s="13">
         <v>0.04</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:37">
       <c r="A7" s="7" t="s">
         <v>136</v>
       </c>
@@ -5936,7 +6008,7 @@
         <v>0.875</v>
       </c>
       <c r="E7" s="13">
-        <v>0.925</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="F7" s="13">
         <v>0.95</v>
@@ -5945,7 +6017,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:37">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="10">
@@ -5969,7 +6041,7 @@
         <v>0.255</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:37">
       <c r="A9" s="14"/>
       <c r="B9" s="14"/>
       <c r="C9" s="10">
@@ -5979,7 +6051,7 @@
         <v>0.875</v>
       </c>
       <c r="E9" s="13">
-        <v>0.975</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="F9" s="13">
         <v>1</v>
@@ -5990,10 +6062,10 @@
       </c>
       <c r="I9">
         <f>F11*3.6/120</f>
-        <v>0.225</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+        <v>0.22500000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:37">
       <c r="A10" s="15" t="s">
         <v>139</v>
       </c>
@@ -6021,7 +6093,7 @@
         <v>0.1875</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:37">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="10">
@@ -6037,7 +6109,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="12" spans="1:27">
+    <row r="12" spans="1:37">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="11">
@@ -6065,7 +6137,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="13" spans="1:34">
+    <row r="13" spans="1:37">
       <c r="A13" s="4" t="s">
         <v>141</v>
       </c>
@@ -6147,7 +6219,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="14" spans="1:34">
+    <row r="14" spans="1:37">
       <c r="A14" s="7" t="s">
         <v>128</v>
       </c>
@@ -6164,7 +6236,7 @@
         <v>752.1</v>
       </c>
       <c r="F14" s="17">
-        <v>649.45</v>
+        <v>649.45000000000005</v>
       </c>
       <c r="H14" t="s">
         <v>143</v>
@@ -6185,11 +6257,11 @@
         <v>276.55</v>
       </c>
       <c r="N14" s="20">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="O14" s="22"/>
       <c r="P14" s="23">
-        <v>0.035</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="Q14" t="str">
         <f t="shared" ref="Q14:Q16" si="6">$H14</f>
@@ -6197,15 +6269,15 @@
       </c>
       <c r="R14" s="20">
         <f>$P14*K14</f>
-        <v>40.39175</v>
+        <v>40.391750000000002</v>
       </c>
       <c r="S14" s="20">
         <f t="shared" ref="S14:T16" si="7">$P14*L14</f>
-        <v>16.02475</v>
+        <v>16.024750000000001</v>
       </c>
       <c r="T14" s="20">
         <f t="shared" si="7"/>
-        <v>9.67925</v>
+        <v>9.6792499999999997</v>
       </c>
       <c r="V14" t="str">
         <f t="shared" ref="V14:V16" si="8">$H14</f>
@@ -6225,10 +6297,10 @@
         <v>0.06</v>
       </c>
       <c r="AD14" s="1">
-        <v>0.045</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="AE14" s="1">
-        <v>0.0225</v>
+        <v>2.2499999999999999E-2</v>
       </c>
       <c r="AF14" s="1">
         <v>0.4</v>
@@ -6240,7 +6312,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:34">
+    <row r="15" spans="1:37">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="10">
@@ -6274,11 +6346,11 @@
         <v>169.75</v>
       </c>
       <c r="N15" s="20">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="O15" s="20"/>
       <c r="P15" s="23">
-        <v>0.045</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="Q15" t="str">
         <f t="shared" si="6"/>
@@ -6286,15 +6358,15 @@
       </c>
       <c r="R15" s="20">
         <f t="shared" ref="R15:R16" si="9">$P15*K15</f>
-        <v>33.8445</v>
+        <v>33.844499999999996</v>
       </c>
       <c r="S15" s="20">
         <f t="shared" si="7"/>
-        <v>14.4675</v>
+        <v>14.467499999999999</v>
       </c>
       <c r="T15" s="20">
         <f t="shared" si="7"/>
-        <v>7.63875</v>
+        <v>7.6387499999999999</v>
       </c>
       <c r="V15" t="str">
         <f t="shared" si="8"/>
@@ -6354,7 +6426,7 @@
         <v>16</v>
       </c>
       <c r="K16" s="22">
-        <v>649.45</v>
+        <v>649.45000000000005</v>
       </c>
       <c r="L16" s="22">
         <v>267.3</v>
@@ -6363,11 +6435,11 @@
         <v>125.45</v>
       </c>
       <c r="N16" s="20">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="O16" s="20"/>
       <c r="P16" s="23">
-        <v>0.035</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="Q16" t="str">
         <f t="shared" si="6"/>
@@ -6379,11 +6451,11 @@
       </c>
       <c r="S16" s="20">
         <f t="shared" si="7"/>
-        <v>9.3555</v>
+        <v>9.3554999999999993</v>
       </c>
       <c r="T16" s="20">
         <f t="shared" si="7"/>
-        <v>4.39075</v>
+        <v>4.3907499999999997</v>
       </c>
       <c r="V16" t="str">
         <f t="shared" si="8"/>
@@ -6400,13 +6472,13 @@
         <v>102</v>
       </c>
       <c r="AC16" s="1">
-        <v>0.0225</v>
+        <v>2.2499999999999999E-2</v>
       </c>
       <c r="AD16" s="1">
-        <v>0.01575</v>
+        <v>1.575E-2</v>
       </c>
       <c r="AE16" s="1">
-        <v>0.009</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="AF16" s="1">
         <v>0.4</v>
@@ -6421,7 +6493,7 @@
       <c r="AJ16" s="1"/>
       <c r="AK16" s="1"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:33">
       <c r="A17" s="11" t="s">
         <v>134</v>
       </c>
@@ -6430,16 +6502,16 @@
       </c>
       <c r="C17" s="18"/>
       <c r="D17" s="13">
-        <v>0.035</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="E17" s="13">
-        <v>0.045</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="F17" s="13">
-        <v>0.035</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27">
+        <v>3.5000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33">
       <c r="A18" s="10" t="s">
         <v>136</v>
       </c>
@@ -6492,7 +6564,7 @@
       </c>
       <c r="J19" s="20">
         <f t="shared" si="11"/>
-        <v>0.0225</v>
+        <v>2.2499999999999999E-2</v>
       </c>
       <c r="AA19" t="s">
         <v>120</v>
@@ -6529,11 +6601,11 @@
         <v>2</v>
       </c>
       <c r="F20" s="9">
-        <v>0.525</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="H20" s="20">
         <f t="shared" ref="H20:H24" si="12">D20*3.6/120</f>
-        <v>0.045</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="I20" s="20">
         <f t="shared" si="11"/>
@@ -6541,7 +6613,7 @@
       </c>
       <c r="J20" s="20">
         <f t="shared" si="11"/>
-        <v>0.01575</v>
+        <v>1.575E-2</v>
       </c>
       <c r="AA20" t="str">
         <f>V14</f>
@@ -6554,10 +6626,10 @@
         <v>0.42</v>
       </c>
       <c r="AD20" s="1">
-        <v>0.3315</v>
+        <v>0.33150000000000002</v>
       </c>
       <c r="AE20" s="1">
-        <v>0.243</v>
+        <v>0.24299999999999999</v>
       </c>
       <c r="AF20" t="s">
         <v>149</v>
@@ -6583,7 +6655,7 @@
       </c>
       <c r="H21" s="20">
         <f t="shared" si="12"/>
-        <v>0.0225</v>
+        <v>2.2499999999999999E-2</v>
       </c>
       <c r="I21" s="20">
         <f t="shared" si="11"/>
@@ -6591,7 +6663,7 @@
       </c>
       <c r="J21" s="20">
         <f t="shared" si="11"/>
-        <v>0.009</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="AA21" t="str">
         <f>V15</f>
@@ -6604,10 +6676,10 @@
         <v>0.51</v>
       </c>
       <c r="AD21" s="1">
-        <v>0.4245</v>
+        <v>0.42449999999999999</v>
       </c>
       <c r="AE21" s="1">
-        <v>0.339</v>
+        <v>0.33900000000000002</v>
       </c>
       <c r="AF21" t="s">
         <v>149</v>
@@ -6616,7 +6688,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:33">
       <c r="A22" s="15" t="s">
         <v>150</v>
       </c>
@@ -6648,7 +6720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:33">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="10">
@@ -6665,18 +6737,18 @@
       </c>
       <c r="H23" s="20">
         <f t="shared" si="12"/>
-        <v>0.3315</v>
+        <v>0.33150000000000002</v>
       </c>
       <c r="I23" s="20">
         <f t="shared" si="11"/>
-        <v>0.4245</v>
+        <v>0.42449999999999999</v>
       </c>
       <c r="J23" s="20">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:33">
       <c r="A24" s="14"/>
       <c r="B24" s="14"/>
       <c r="C24" s="10">
@@ -6693,18 +6765,18 @@
       </c>
       <c r="H24" s="20">
         <f t="shared" si="12"/>
-        <v>0.243</v>
+        <v>0.24299999999999999</v>
       </c>
       <c r="I24" s="20">
         <f t="shared" si="11"/>
-        <v>0.339</v>
+        <v>0.33900000000000002</v>
       </c>
       <c r="J24" s="20">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="8:12">
+    <row r="27" spans="1:33">
       <c r="H27" s="21" t="s">
         <v>1</v>
       </c>
@@ -6713,7 +6785,7 @@
       <c r="K27" s="21"/>
       <c r="L27" s="21"/>
     </row>
-    <row r="28" spans="8:12">
+    <row r="28" spans="1:33">
       <c r="H28" s="21" t="s">
         <v>8</v>
       </c>
@@ -6730,7 +6802,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="8:12">
+    <row r="29" spans="1:33">
       <c r="H29" t="s">
         <v>108</v>
       </c>
@@ -6745,7 +6817,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="9:12">
+    <row r="30" spans="1:33">
       <c r="I30" t="str">
         <f t="shared" ref="I30:I31" si="13">H4</f>
         <v>H2Conv_LOHC</v>
@@ -6757,7 +6829,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="9:12">
+    <row r="31" spans="1:33">
       <c r="I31" t="str">
         <f t="shared" si="13"/>
         <v>H2Conv_Liquid</v>
@@ -6769,7 +6841,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="32" spans="9:12">
+    <row r="32" spans="1:33">
       <c r="I32" t="str">
         <f>H14</f>
         <v>H2ReConv_Ammonia</v>
@@ -6781,7 +6853,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="9:12">
+    <row r="33" spans="8:15">
       <c r="I33" t="str">
         <f t="shared" ref="I33:I34" si="14">H15</f>
         <v>H2ReConv_LOHC</v>
@@ -6793,7 +6865,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="34" spans="9:12">
+    <row r="34" spans="8:15">
       <c r="I34" t="str">
         <f t="shared" si="14"/>
         <v>H2ReConv_Liquid</v>
@@ -6805,7 +6877,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="8:8">
+    <row r="37" spans="8:15">
       <c r="H37" t="s">
         <v>151</v>
       </c>
@@ -6836,7 +6908,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="39" spans="8:11">
+    <row r="39" spans="8:15">
       <c r="H39" t="s">
         <v>160</v>
       </c>
@@ -6850,7 +6922,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="9:11">
+    <row r="40" spans="8:15">
       <c r="I40" t="s">
         <v>113</v>
       </c>
@@ -6863,42 +6935,40 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B3:Y5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="11.2818181818182" customWidth="1"/>
-    <col min="3" max="3" width="14.5727272727273" customWidth="1"/>
-    <col min="4" max="4" width="26.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="20.2818181818182" customWidth="1"/>
+    <col min="2" max="2" width="11.265625" customWidth="1"/>
+    <col min="3" max="3" width="14.59765625" customWidth="1"/>
+    <col min="4" max="4" width="26.3984375" customWidth="1"/>
+    <col min="5" max="5" width="20.265625" customWidth="1"/>
     <col min="6" max="6" width="5" customWidth="1"/>
-    <col min="7" max="7" width="4.57272727272727" customWidth="1"/>
+    <col min="7" max="7" width="4.59765625" customWidth="1"/>
     <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="9" max="9" width="10.2818181818182" customWidth="1"/>
-    <col min="10" max="10" width="7.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="17.8545454545455" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
+    <col min="9" max="9" width="10.265625" customWidth="1"/>
+    <col min="10" max="10" width="7.86328125" customWidth="1"/>
+    <col min="12" max="12" width="17.86328125" customWidth="1"/>
+    <col min="13" max="13" width="9.3984375" customWidth="1"/>
     <col min="14" max="14" width="12" customWidth="1"/>
-    <col min="15" max="15" width="8.85454545454546" customWidth="1"/>
+    <col min="15" max="15" width="8.86328125" customWidth="1"/>
     <col min="16" max="16" width="14" customWidth="1"/>
-    <col min="17" max="17" width="6.85454545454545" customWidth="1"/>
-    <col min="18" max="18" width="11.8545454545455" customWidth="1"/>
-    <col min="19" max="19" width="7.85454545454545" customWidth="1"/>
-    <col min="20" max="20" width="12.8545454545455" customWidth="1"/>
-    <col min="21" max="21" width="4.57272727272727" customWidth="1"/>
+    <col min="17" max="17" width="6.86328125" customWidth="1"/>
+    <col min="18" max="18" width="11.86328125" customWidth="1"/>
+    <col min="19" max="19" width="7.86328125" customWidth="1"/>
+    <col min="20" max="20" width="12.86328125" customWidth="1"/>
+    <col min="21" max="21" width="4.59765625" customWidth="1"/>
     <col min="22" max="22" width="9" customWidth="1"/>
-    <col min="23" max="23" width="4.42727272727273" customWidth="1"/>
+    <col min="23" max="23" width="4.3984375" customWidth="1"/>
     <col min="24" max="24" width="5" customWidth="1"/>
     <col min="25" max="25" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:14">
+    <row r="3" spans="2:25">
       <c r="B3" t="s">
         <v>162</v>
       </c>
@@ -7019,16 +7089,16 @@
         <v>71</v>
       </c>
       <c r="S5" s="1">
-        <v>2.13470319634703</v>
+        <v>2.1347031963470302</v>
       </c>
       <c r="T5" s="1">
         <v>1.72231735159817</v>
       </c>
       <c r="U5" s="1">
-        <v>0.5525</v>
+        <v>0.55249999999999999</v>
       </c>
       <c r="V5" s="1">
-        <v>0.5525</v>
+        <v>0.55249999999999999</v>
       </c>
       <c r="W5">
         <v>20</v>
@@ -7037,11 +7107,1635 @@
         <v>0.85</v>
       </c>
       <c r="Y5">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AB78640-24CE-4D20-B6B4-CE7AB4FCE28A}">
+  <sheetPr>
+    <tabColor theme="4"/>
+  </sheetPr>
+  <dimension ref="B1:BO66"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="2" max="2" width="32.53125" customWidth="1"/>
+    <col min="3" max="3" width="30.73046875" customWidth="1"/>
+    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="5" max="5" width="29.9296875" customWidth="1"/>
+    <col min="6" max="9" width="33.73046875" customWidth="1"/>
+    <col min="10" max="10" width="19.265625" customWidth="1"/>
+    <col min="11" max="11" width="14.59765625" customWidth="1"/>
+    <col min="12" max="12" width="14.265625" customWidth="1"/>
+    <col min="13" max="13" width="13.06640625" customWidth="1"/>
+    <col min="14" max="14" width="12.796875" customWidth="1"/>
+    <col min="15" max="15" width="6.796875" customWidth="1"/>
+    <col min="16" max="16" width="15.33203125" customWidth="1"/>
+    <col min="17" max="17" width="6.19921875" customWidth="1"/>
+    <col min="18" max="18" width="14.53125" customWidth="1"/>
+    <col min="23" max="23" width="20.19921875" customWidth="1"/>
+    <col min="24" max="24" width="18.53125" customWidth="1"/>
+    <col min="25" max="25" width="19.19921875" customWidth="1"/>
+    <col min="32" max="32" width="118.73046875" customWidth="1"/>
+    <col min="36" max="36" width="13.53125" customWidth="1"/>
+    <col min="48" max="48" width="14.53125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:51">
+      <c r="X1" s="159"/>
+      <c r="Y1" s="160" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z1" s="159"/>
+      <c r="AA1" s="159"/>
+      <c r="AB1" s="159"/>
+      <c r="AC1" s="159"/>
+      <c r="AD1" s="159"/>
+      <c r="AE1" s="159"/>
+      <c r="AF1" s="159"/>
+    </row>
+    <row r="2" spans="2:51">
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W2" s="161"/>
+      <c r="X2" s="160"/>
+      <c r="Y2" s="159"/>
+      <c r="Z2" s="160"/>
+      <c r="AA2" s="160"/>
+      <c r="AB2" s="160"/>
+      <c r="AC2" s="160"/>
+      <c r="AD2" s="160"/>
+      <c r="AE2" s="160"/>
+      <c r="AF2" s="160"/>
+    </row>
+    <row r="3" spans="2:51">
+      <c r="B3" s="152" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="152" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="152" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="152" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="152" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="152" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="152" t="s">
+        <v>13</v>
+      </c>
+      <c r="X3" s="160" t="s">
+        <v>176</v>
+      </c>
+      <c r="Y3" s="160" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z3" s="160" t="s">
+        <v>177</v>
+      </c>
+      <c r="AA3" s="160" t="s">
+        <v>178</v>
+      </c>
+      <c r="AB3" s="160" t="s">
+        <v>179</v>
+      </c>
+      <c r="AC3" s="160" t="s">
+        <v>180</v>
+      </c>
+      <c r="AD3" s="160" t="s">
+        <v>181</v>
+      </c>
+      <c r="AE3" s="160" t="s">
+        <v>182</v>
+      </c>
+      <c r="AF3" s="160" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="4" spans="2:51">
+      <c r="B4" s="152" t="s">
+        <v>184</v>
+      </c>
+      <c r="C4" s="152" t="s">
+        <v>185</v>
+      </c>
+      <c r="D4" s="152" t="s">
+        <v>186</v>
+      </c>
+      <c r="E4" s="152" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="152" t="s">
+        <v>187</v>
+      </c>
+      <c r="G4" s="152" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="152"/>
+      <c r="X4" s="162" t="s">
+        <v>188</v>
+      </c>
+      <c r="Y4" s="160" t="s">
+        <v>185</v>
+      </c>
+      <c r="Z4" s="160">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="AA4" s="160">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="160">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="160">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="160">
+        <v>3.528</v>
+      </c>
+      <c r="AE4" s="160">
+        <v>0.94599999999999995</v>
+      </c>
+      <c r="AF4" s="160">
+        <v>1.085</v>
+      </c>
+    </row>
+    <row r="5" spans="2:51">
+      <c r="B5" s="152" t="s">
+        <v>189</v>
+      </c>
+      <c r="C5" s="152" t="s">
+        <v>190</v>
+      </c>
+      <c r="D5" s="152" t="s">
+        <v>191</v>
+      </c>
+      <c r="E5" s="152" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="152" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" s="152" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="152"/>
+      <c r="W5" s="161"/>
+      <c r="X5" s="163"/>
+      <c r="Y5" s="161"/>
+      <c r="Z5" s="161"/>
+      <c r="AA5" s="161"/>
+      <c r="AB5" s="161"/>
+      <c r="AC5" s="161"/>
+      <c r="AD5" s="161"/>
+      <c r="AE5" s="161"/>
+      <c r="AF5" s="161"/>
+    </row>
+    <row r="6" spans="2:51">
+      <c r="B6" s="152" t="s">
+        <v>184</v>
+      </c>
+      <c r="C6" s="152" t="s">
+        <v>192</v>
+      </c>
+      <c r="D6" s="152" t="s">
+        <v>193</v>
+      </c>
+      <c r="E6" s="152" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="152" t="s">
+        <v>187</v>
+      </c>
+      <c r="G6" s="152" t="s">
+        <v>19</v>
+      </c>
+      <c r="W6" s="161"/>
+      <c r="X6" s="163"/>
+      <c r="Y6" s="161"/>
+      <c r="Z6" s="161"/>
+      <c r="AA6" s="161"/>
+      <c r="AB6" s="161"/>
+      <c r="AC6" s="161"/>
+      <c r="AD6" s="161"/>
+      <c r="AE6" s="161"/>
+      <c r="AF6" s="161"/>
+    </row>
+    <row r="7" spans="2:51">
+      <c r="B7" s="152"/>
+      <c r="C7" s="152" t="s">
+        <v>194</v>
+      </c>
+      <c r="E7" s="152" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="152" t="s">
+        <v>187</v>
+      </c>
+      <c r="G7" s="152" t="s">
+        <v>19</v>
+      </c>
+      <c r="W7" s="161"/>
+      <c r="X7" s="163"/>
+      <c r="Y7" s="161"/>
+      <c r="Z7" s="161"/>
+      <c r="AA7" s="161"/>
+      <c r="AB7" s="161"/>
+      <c r="AC7" s="161"/>
+      <c r="AD7" s="161"/>
+      <c r="AE7" s="161"/>
+      <c r="AF7" s="161"/>
+    </row>
+    <row r="8" spans="2:51">
+      <c r="B8" s="152"/>
+      <c r="C8" s="152" t="s">
+        <v>195</v>
+      </c>
+      <c r="E8" s="152" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="152" t="s">
+        <v>187</v>
+      </c>
+      <c r="G8" s="152" t="s">
+        <v>19</v>
+      </c>
+      <c r="W8" s="161"/>
+      <c r="X8" s="163"/>
+      <c r="Y8" s="161"/>
+      <c r="Z8" s="161"/>
+      <c r="AA8" s="161"/>
+      <c r="AB8" s="161"/>
+      <c r="AC8" s="161"/>
+      <c r="AD8" s="161"/>
+      <c r="AE8" s="161"/>
+      <c r="AF8" s="161"/>
+    </row>
+    <row r="9" spans="2:51">
+      <c r="B9" s="152"/>
+      <c r="C9" s="152" t="s">
+        <v>196</v>
+      </c>
+      <c r="E9" s="152" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="152" t="s">
+        <v>187</v>
+      </c>
+      <c r="G9" s="152" t="s">
+        <v>19</v>
+      </c>
+      <c r="W9" s="161"/>
+      <c r="X9" s="163"/>
+      <c r="Y9" s="161"/>
+      <c r="Z9" s="161"/>
+      <c r="AA9" s="161"/>
+      <c r="AB9" s="161"/>
+      <c r="AC9" s="161"/>
+      <c r="AD9" s="161"/>
+      <c r="AE9" s="161"/>
+      <c r="AF9" s="161"/>
+    </row>
+    <row r="10" spans="2:51">
+      <c r="B10" s="152"/>
+      <c r="C10" s="152" t="s">
+        <v>197</v>
+      </c>
+      <c r="E10" s="152" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="152" t="s">
+        <v>187</v>
+      </c>
+      <c r="G10" s="152" t="s">
+        <v>19</v>
+      </c>
+      <c r="W10" s="161"/>
+      <c r="X10" s="163"/>
+      <c r="Y10" s="161"/>
+      <c r="Z10" s="161"/>
+      <c r="AA10" s="161"/>
+      <c r="AB10" s="161"/>
+      <c r="AC10" s="161"/>
+      <c r="AD10" s="161"/>
+      <c r="AE10" s="161"/>
+      <c r="AF10" s="161"/>
+    </row>
+    <row r="11" spans="2:51">
+      <c r="B11" s="152"/>
+      <c r="C11" s="152" t="s">
+        <v>198</v>
+      </c>
+      <c r="E11" s="152" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="152" t="s">
+        <v>187</v>
+      </c>
+      <c r="G11" s="152" t="s">
+        <v>19</v>
+      </c>
+      <c r="W11" s="161"/>
+      <c r="X11" s="163"/>
+      <c r="Y11" s="161"/>
+      <c r="Z11" s="161"/>
+      <c r="AA11" s="161"/>
+      <c r="AB11" s="161"/>
+      <c r="AC11" s="161"/>
+      <c r="AD11" s="161"/>
+      <c r="AE11" s="161"/>
+      <c r="AF11" s="161"/>
+    </row>
+    <row r="12" spans="2:51">
+      <c r="B12" s="152"/>
+      <c r="E12" s="152"/>
+      <c r="F12" s="152"/>
+      <c r="G12" s="152"/>
+      <c r="W12" s="161"/>
+      <c r="X12" s="163"/>
+      <c r="Y12" s="161"/>
+      <c r="Z12" s="161"/>
+      <c r="AA12" s="161"/>
+      <c r="AB12" s="161"/>
+      <c r="AC12" s="161"/>
+      <c r="AD12" s="161"/>
+      <c r="AE12" s="161"/>
+      <c r="AF12" s="161"/>
+    </row>
+    <row r="13" spans="2:51">
+      <c r="W13" s="161"/>
+      <c r="X13" s="163"/>
+      <c r="Y13" s="161"/>
+      <c r="Z13" s="161"/>
+      <c r="AA13" s="161"/>
+      <c r="AB13" s="161"/>
+      <c r="AC13" s="161"/>
+      <c r="AD13" s="161"/>
+      <c r="AE13" s="161"/>
+      <c r="AF13" s="161"/>
+    </row>
+    <row r="14" spans="2:51">
+      <c r="G14" t="s">
+        <v>199</v>
+      </c>
+      <c r="W14" s="161"/>
+      <c r="X14" s="163"/>
+      <c r="Y14" s="161"/>
+      <c r="Z14" s="161"/>
+      <c r="AA14" s="161"/>
+      <c r="AB14" s="161"/>
+      <c r="AC14" s="161"/>
+      <c r="AD14" s="161"/>
+      <c r="AE14" s="161"/>
+      <c r="AK14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="15" spans="2:51">
+      <c r="B15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" t="s">
+        <v>125</v>
+      </c>
+      <c r="E15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" t="s">
+        <v>200</v>
+      </c>
+      <c r="G15" t="s">
+        <v>147</v>
+      </c>
+      <c r="H15" t="s">
+        <v>201</v>
+      </c>
+      <c r="I15" t="s">
+        <v>68</v>
+      </c>
+      <c r="J15" t="s">
+        <v>202</v>
+      </c>
+      <c r="K15" t="s">
+        <v>203</v>
+      </c>
+      <c r="L15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M15" t="s">
+        <v>204</v>
+      </c>
+      <c r="N15" t="s">
+        <v>167</v>
+      </c>
+      <c r="O15" t="s">
+        <v>205</v>
+      </c>
+      <c r="P15" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>6</v>
+      </c>
+      <c r="R15" s="164" t="s">
+        <v>207</v>
+      </c>
+      <c r="V15" s="165" t="s">
+        <v>208</v>
+      </c>
+      <c r="W15" s="161"/>
+      <c r="X15" s="161"/>
+      <c r="Y15" s="161"/>
+      <c r="Z15" s="161"/>
+      <c r="AA15" s="161"/>
+      <c r="AB15" s="161"/>
+      <c r="AC15" s="161"/>
+      <c r="AD15" s="161"/>
+      <c r="AE15" s="161"/>
+      <c r="AF15" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>200</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>147</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>201</v>
+      </c>
+      <c r="AM15" t="s">
+        <v>68</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>202</v>
+      </c>
+      <c r="AO15" t="s">
+        <v>203</v>
+      </c>
+      <c r="AP15" t="s">
+        <v>67</v>
+      </c>
+      <c r="AQ15" t="s">
+        <v>204</v>
+      </c>
+      <c r="AR15" t="s">
+        <v>167</v>
+      </c>
+      <c r="AS15" t="s">
+        <v>205</v>
+      </c>
+      <c r="AT15" t="s">
+        <v>206</v>
+      </c>
+      <c r="AU15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AV15" s="164" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="16" spans="2:51">
+      <c r="B16" t="s">
+        <v>185</v>
+      </c>
+      <c r="C16" t="s">
+        <v>102</v>
+      </c>
+      <c r="E16" t="s">
+        <v>102</v>
+      </c>
+      <c r="G16" t="s">
+        <v>160</v>
+      </c>
+      <c r="H16">
+        <v>0.92</v>
+      </c>
+      <c r="I16" s="1">
+        <v>1.3140000000000001</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="L16" s="166">
+        <v>100</v>
+      </c>
+      <c r="Q16">
+        <v>2020</v>
+      </c>
+      <c r="R16">
+        <v>7000</v>
+      </c>
+      <c r="V16" s="165">
+        <v>1</v>
+      </c>
+      <c r="W16" s="161"/>
+      <c r="X16" s="161"/>
+      <c r="Y16" s="161"/>
+      <c r="Z16" s="161"/>
+      <c r="AA16" s="161"/>
+      <c r="AB16" s="161"/>
+      <c r="AC16" s="161"/>
+      <c r="AD16" s="161"/>
+      <c r="AE16" s="161"/>
+      <c r="AF16" t="s">
+        <v>192</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>102</v>
+      </c>
+      <c r="AI16" t="s">
+        <v>102</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>160</v>
+      </c>
+      <c r="AL16" s="166">
+        <v>0.9</v>
+      </c>
+      <c r="AM16" s="1">
+        <v>1.3140000000000001</v>
+      </c>
+      <c r="AN16">
+        <v>1</v>
+      </c>
+      <c r="AP16">
+        <v>100</v>
+      </c>
+      <c r="AU16">
+        <v>2020</v>
+      </c>
+      <c r="AV16" s="166">
+        <v>3000</v>
+      </c>
+      <c r="AY16" s="166">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="2:67" s="165" customFormat="1" ht="15.4">
+      <c r="D17" s="167"/>
+      <c r="F17" s="165" t="s">
+        <v>209</v>
+      </c>
+      <c r="G17" s="165" t="str">
+        <f>F17</f>
+        <v>AuxStoOUT</v>
+      </c>
+      <c r="I17" s="168"/>
+      <c r="K17" s="168">
+        <f>1/H16</f>
+        <v>1.0869565217391304</v>
+      </c>
+      <c r="W17"/>
+      <c r="Y17" s="169" t="s">
+        <v>210</v>
+      </c>
+      <c r="Z17" s="170"/>
+      <c r="AA17"/>
+      <c r="AB17"/>
+      <c r="AC17"/>
+      <c r="AD17"/>
+      <c r="AE17"/>
+      <c r="AF17"/>
+      <c r="AG17"/>
+      <c r="AH17" s="152"/>
+      <c r="AI17"/>
+      <c r="AJ17" t="s">
+        <v>209</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>209</v>
+      </c>
+      <c r="AL17"/>
+      <c r="AM17" s="1"/>
+      <c r="AN17"/>
+      <c r="AO17" s="1">
+        <v>1.0869565217391299</v>
+      </c>
+      <c r="AQ17"/>
+      <c r="AR17"/>
+      <c r="AS17"/>
+      <c r="AT17"/>
+      <c r="AU17"/>
+      <c r="AV17"/>
+      <c r="AW17"/>
+      <c r="AX17"/>
+      <c r="AY17"/>
+      <c r="AZ17"/>
+      <c r="BA17"/>
+      <c r="BB17"/>
+      <c r="BC17"/>
+      <c r="BD17"/>
+      <c r="BE17"/>
+      <c r="BF17"/>
+      <c r="BG17"/>
+      <c r="BH17"/>
+      <c r="BI17"/>
+      <c r="BJ17"/>
+      <c r="BK17"/>
+      <c r="BL17"/>
+      <c r="BM17"/>
+      <c r="BN17"/>
+      <c r="BO17"/>
+    </row>
+    <row r="18" spans="2:67">
+      <c r="D18" s="152"/>
+      <c r="F18" s="152" t="str">
+        <f>C25</f>
+        <v>AuxStoIN</v>
+      </c>
+      <c r="G18" t="s">
+        <v>102</v>
+      </c>
+      <c r="I18" s="1"/>
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="V18" s="165"/>
+      <c r="AH18" s="152"/>
+      <c r="AJ18" s="152" t="s">
+        <v>211</v>
+      </c>
+      <c r="AK18" t="s">
+        <v>102</v>
+      </c>
+      <c r="AM18" s="1"/>
+      <c r="AS18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:67">
+      <c r="B19" t="s">
+        <v>190</v>
+      </c>
+      <c r="E19" t="s">
+        <v>212</v>
+      </c>
+      <c r="I19" s="1">
+        <v>29.891943130000001</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>3</v>
+      </c>
+      <c r="V19" s="165"/>
+      <c r="AF19" t="s">
+        <v>194</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>102</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>102</v>
+      </c>
+      <c r="AK19" t="s">
+        <v>160</v>
+      </c>
+      <c r="AL19" s="166">
+        <v>0.94</v>
+      </c>
+      <c r="AM19" s="1">
+        <f>AM16</f>
+        <v>1.3140000000000001</v>
+      </c>
+      <c r="AN19">
+        <v>1</v>
+      </c>
+      <c r="AP19">
+        <v>100</v>
+      </c>
+      <c r="AU19">
+        <v>2020</v>
+      </c>
+      <c r="AV19" s="166">
+        <v>3500</v>
+      </c>
+      <c r="AY19" s="166">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="2:67">
+      <c r="AH20" s="152"/>
+      <c r="AJ20" t="s">
+        <v>209</v>
+      </c>
+      <c r="AK20" t="s">
+        <v>209</v>
+      </c>
+      <c r="AM20" s="1"/>
+      <c r="AO20" s="1">
+        <v>1.0869565217391299</v>
+      </c>
+    </row>
+    <row r="21" spans="2:67">
+      <c r="AH21" s="152"/>
+      <c r="AJ21" s="152" t="s">
+        <v>211</v>
+      </c>
+      <c r="AK21" t="s">
+        <v>102</v>
+      </c>
+      <c r="AM21" s="1"/>
+      <c r="AS21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:67">
+      <c r="L22" s="166">
+        <v>20</v>
+      </c>
+      <c r="X22" s="161"/>
+      <c r="Y22" s="161"/>
+      <c r="Z22" s="161"/>
+      <c r="AF22" t="s">
+        <v>195</v>
+      </c>
+      <c r="AG22" t="s">
+        <v>102</v>
+      </c>
+      <c r="AI22" t="s">
+        <v>102</v>
+      </c>
+      <c r="AK22" t="s">
+        <v>160</v>
+      </c>
+      <c r="AL22" s="166">
+        <v>0.94</v>
+      </c>
+      <c r="AM22" s="1">
+        <f>AM19</f>
+        <v>1.3140000000000001</v>
+      </c>
+      <c r="AN22">
+        <v>1</v>
+      </c>
+      <c r="AP22">
+        <v>100</v>
+      </c>
+      <c r="AU22">
+        <v>2020</v>
+      </c>
+      <c r="AV22" s="166">
+        <v>4000</v>
+      </c>
+      <c r="AY22" s="166">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="2:67">
+      <c r="B23" s="152" t="s">
+        <v>151</v>
+      </c>
+      <c r="C23" s="152"/>
+      <c r="D23" s="152"/>
+      <c r="E23" s="152"/>
+      <c r="F23" s="152"/>
+      <c r="G23" s="152"/>
+      <c r="H23" s="152"/>
+      <c r="I23" s="152"/>
+      <c r="X23" s="171"/>
+      <c r="Y23" s="171"/>
+      <c r="Z23" s="161"/>
+      <c r="AH23" s="152"/>
+      <c r="AJ23" t="s">
+        <v>209</v>
+      </c>
+      <c r="AK23" t="s">
+        <v>209</v>
+      </c>
+      <c r="AL23" s="166"/>
+      <c r="AM23" s="1"/>
+      <c r="AO23" s="1">
+        <v>1.0869565217391299</v>
+      </c>
+    </row>
+    <row r="24" spans="2:67">
+      <c r="B24" s="152" t="s">
+        <v>213</v>
+      </c>
+      <c r="C24" s="152" t="s">
+        <v>153</v>
+      </c>
+      <c r="D24" s="152" t="s">
+        <v>154</v>
+      </c>
+      <c r="E24" s="152" t="s">
+        <v>155</v>
+      </c>
+      <c r="F24" s="152" t="s">
+        <v>156</v>
+      </c>
+      <c r="G24" s="152" t="s">
+        <v>157</v>
+      </c>
+      <c r="H24" s="152" t="s">
+        <v>158</v>
+      </c>
+      <c r="I24" s="152" t="s">
+        <v>159</v>
+      </c>
+      <c r="X24" s="171"/>
+      <c r="Y24" s="172"/>
+      <c r="Z24" s="170"/>
+      <c r="AH24" s="152"/>
+      <c r="AJ24" s="152" t="s">
+        <v>211</v>
+      </c>
+      <c r="AK24" t="s">
+        <v>102</v>
+      </c>
+      <c r="AL24" s="166"/>
+      <c r="AM24" s="1"/>
+      <c r="AS24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:67">
+      <c r="B25" s="152" t="s">
+        <v>214</v>
+      </c>
+      <c r="C25" s="152" t="s">
+        <v>211</v>
+      </c>
+      <c r="D25" s="152" t="s">
+        <v>215</v>
+      </c>
+      <c r="E25" s="152" t="s">
+        <v>20</v>
+      </c>
+      <c r="F25" s="152"/>
+      <c r="G25" s="152" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" s="152"/>
+      <c r="I25" s="152"/>
+      <c r="X25" s="170"/>
+      <c r="Y25" s="171"/>
+      <c r="AF25" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG25" t="s">
+        <v>102</v>
+      </c>
+      <c r="AI25" t="s">
+        <v>102</v>
+      </c>
+      <c r="AK25" t="s">
+        <v>160</v>
+      </c>
+      <c r="AL25" s="166">
+        <v>0.94</v>
+      </c>
+      <c r="AM25" s="1">
+        <f>AM22</f>
+        <v>1.3140000000000001</v>
+      </c>
+      <c r="AN25">
+        <v>1</v>
+      </c>
+      <c r="AP25">
+        <v>100</v>
+      </c>
+      <c r="AU25">
+        <v>2020</v>
+      </c>
+      <c r="AV25" s="166">
+        <v>4000</v>
+      </c>
+      <c r="AY25" s="166">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="2:67">
+      <c r="C26" s="152" t="s">
+        <v>209</v>
+      </c>
+      <c r="D26" s="152" t="s">
+        <v>216</v>
+      </c>
+      <c r="E26" s="152" t="s">
+        <v>20</v>
+      </c>
+      <c r="F26" s="152"/>
+      <c r="G26" s="152" t="s">
+        <v>19</v>
+      </c>
+      <c r="W26" s="161"/>
+      <c r="X26" s="171"/>
+      <c r="Y26" s="171"/>
+      <c r="AH26" s="152"/>
+      <c r="AJ26" t="s">
+        <v>209</v>
+      </c>
+      <c r="AK26" t="s">
+        <v>209</v>
+      </c>
+      <c r="AL26" s="166"/>
+      <c r="AM26" s="1"/>
+      <c r="AO26" s="1">
+        <v>1.0869565217391299</v>
+      </c>
+    </row>
+    <row r="27" spans="2:67">
+      <c r="W27" s="161"/>
+      <c r="X27" s="161"/>
+      <c r="Y27" s="161"/>
+      <c r="AH27" s="152"/>
+      <c r="AJ27" s="152" t="s">
+        <v>211</v>
+      </c>
+      <c r="AK27" t="s">
+        <v>102</v>
+      </c>
+      <c r="AL27" s="166"/>
+      <c r="AM27" s="1"/>
+      <c r="AS27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:67">
+      <c r="W28" s="161"/>
+      <c r="X28" s="161"/>
+      <c r="Y28" s="161"/>
+      <c r="AF28" t="s">
+        <v>197</v>
+      </c>
+      <c r="AG28" t="s">
+        <v>102</v>
+      </c>
+      <c r="AI28" t="s">
+        <v>102</v>
+      </c>
+      <c r="AK28" t="s">
+        <v>160</v>
+      </c>
+      <c r="AL28" s="166">
+        <v>0.94</v>
+      </c>
+      <c r="AM28" s="1">
+        <f>AM25</f>
+        <v>1.3140000000000001</v>
+      </c>
+      <c r="AN28">
+        <v>1</v>
+      </c>
+      <c r="AP28">
+        <v>100</v>
+      </c>
+      <c r="AU28">
+        <v>2020</v>
+      </c>
+      <c r="AV28" s="166">
+        <v>4000</v>
+      </c>
+      <c r="AY28" s="166">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="2:67">
+      <c r="B29" s="159"/>
+      <c r="C29" s="159"/>
+      <c r="D29" s="159"/>
+      <c r="E29" s="159"/>
+      <c r="W29" s="161"/>
+      <c r="X29" s="161"/>
+      <c r="Y29" s="161"/>
+      <c r="AH29" s="152"/>
+      <c r="AJ29" t="s">
+        <v>209</v>
+      </c>
+      <c r="AK29" t="s">
+        <v>209</v>
+      </c>
+      <c r="AL29" s="166"/>
+      <c r="AM29" s="1"/>
+      <c r="AO29" s="1">
+        <v>1.0869565217391299</v>
+      </c>
+    </row>
+    <row r="30" spans="2:67">
+      <c r="B30" s="159"/>
+      <c r="C30" s="159"/>
+      <c r="D30" s="173" t="s">
+        <v>118</v>
+      </c>
+      <c r="E30" s="159"/>
+      <c r="W30" s="161"/>
+      <c r="X30" s="161"/>
+      <c r="Y30" s="161"/>
+      <c r="AH30" s="152"/>
+      <c r="AJ30" s="152" t="s">
+        <v>211</v>
+      </c>
+      <c r="AK30" t="s">
+        <v>102</v>
+      </c>
+      <c r="AL30" s="166"/>
+      <c r="AM30" s="1"/>
+      <c r="AS30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:67">
+      <c r="B31" s="173"/>
+      <c r="C31" s="173"/>
+      <c r="D31" s="159"/>
+      <c r="E31" s="173"/>
+      <c r="W31" s="161"/>
+      <c r="X31" s="161"/>
+      <c r="Y31" s="161"/>
+      <c r="AF31" t="s">
+        <v>198</v>
+      </c>
+      <c r="AG31" t="s">
+        <v>102</v>
+      </c>
+      <c r="AI31" t="s">
+        <v>102</v>
+      </c>
+      <c r="AK31" t="s">
+        <v>160</v>
+      </c>
+      <c r="AL31" s="166">
+        <v>0.94</v>
+      </c>
+      <c r="AM31" s="1">
+        <f>AM28</f>
+        <v>1.3140000000000001</v>
+      </c>
+      <c r="AN31">
+        <v>1</v>
+      </c>
+      <c r="AP31">
+        <v>100</v>
+      </c>
+      <c r="AU31">
+        <v>2020</v>
+      </c>
+      <c r="AV31" s="166">
+        <v>4000</v>
+      </c>
+      <c r="AY31" s="166">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="2:67">
+      <c r="B32" s="160" t="s">
+        <v>176</v>
+      </c>
+      <c r="C32" s="173" t="s">
+        <v>2</v>
+      </c>
+      <c r="D32" s="173" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="173">
+        <v>2019</v>
+      </c>
+      <c r="AH32" s="152"/>
+      <c r="AJ32" t="s">
+        <v>209</v>
+      </c>
+      <c r="AK32" t="s">
+        <v>209</v>
+      </c>
+      <c r="AM32" s="1"/>
+      <c r="AO32" s="1">
+        <v>1.0869565217391299</v>
+      </c>
+    </row>
+    <row r="33" spans="2:45">
+      <c r="B33" s="162" t="s">
+        <v>188</v>
+      </c>
+      <c r="C33" s="174" t="s">
+        <v>185</v>
+      </c>
+      <c r="D33" s="175" t="s">
+        <v>217</v>
+      </c>
+      <c r="E33" s="176">
+        <f>[6]EnergyUseFromEverBatt_Min_!$AW$6</f>
+        <v>4.7300000000000002E-2</v>
+      </c>
+      <c r="AH33" s="152"/>
+      <c r="AJ33" s="152" t="s">
+        <v>211</v>
+      </c>
+      <c r="AK33" t="s">
+        <v>102</v>
+      </c>
+      <c r="AM33" s="1"/>
+      <c r="AS33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:45" ht="15.4">
+      <c r="B34" s="162" t="s">
+        <v>188</v>
+      </c>
+      <c r="C34" s="177" t="str">
+        <f t="shared" ref="C34:C36" si="0">C33</f>
+        <v>EN_STG_4hBatt</v>
+      </c>
+      <c r="D34" s="175" t="s">
+        <v>218</v>
+      </c>
+      <c r="E34" s="176">
+        <f>[6]EnergyUseFromEverBatt_Min_!$AW$7</f>
+        <v>0.17116666666666699</v>
+      </c>
+    </row>
+    <row r="35" spans="2:45" ht="15.4">
+      <c r="B35" s="162" t="s">
+        <v>188</v>
+      </c>
+      <c r="C35" s="177" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG_4hBatt</v>
+      </c>
+      <c r="D35" s="175" t="s">
+        <v>219</v>
+      </c>
+      <c r="E35" s="176">
+        <f>[6]EnergyUseFromEverBatt_Min_!$AW$8</f>
+        <v>0.46636666666666698</v>
+      </c>
+    </row>
+    <row r="36" spans="2:45" ht="15.4">
+      <c r="B36" s="162" t="s">
+        <v>188</v>
+      </c>
+      <c r="C36" s="177" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG_4hBatt</v>
+      </c>
+      <c r="D36" s="175" t="s">
+        <v>220</v>
+      </c>
+      <c r="E36" s="176">
+        <f>[6]EnergyUseFromEverBatt_Min_!$AW$9</f>
+        <v>9.5666666666666705E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="2:45">
+      <c r="B43" s="178" t="s">
+        <v>221</v>
+      </c>
+      <c r="C43" s="178"/>
+      <c r="D43" s="179"/>
+      <c r="E43" s="179"/>
+      <c r="F43" s="179"/>
+      <c r="G43" s="179"/>
+      <c r="H43" s="179"/>
+      <c r="I43" s="179"/>
+      <c r="J43" s="164"/>
+      <c r="K43" s="164"/>
+      <c r="L43" s="164"/>
+      <c r="M43" s="164"/>
+      <c r="N43" s="164"/>
+      <c r="O43" s="164"/>
+      <c r="P43" s="164"/>
+      <c r="Q43" s="164"/>
+      <c r="R43" s="164"/>
+      <c r="S43" s="171"/>
+    </row>
+    <row r="44" spans="2:45" ht="15.4">
+      <c r="B44" s="178" t="s">
+        <v>80</v>
+      </c>
+      <c r="C44" s="180" t="s">
+        <v>222</v>
+      </c>
+      <c r="D44" s="181" t="s">
+        <v>223</v>
+      </c>
+      <c r="E44" s="181" t="s">
+        <v>224</v>
+      </c>
+      <c r="F44" s="181" t="s">
+        <v>225</v>
+      </c>
+      <c r="G44" s="181" t="s">
+        <v>226</v>
+      </c>
+      <c r="H44" s="181" t="s">
+        <v>227</v>
+      </c>
+      <c r="I44" s="181" t="s">
+        <v>228</v>
+      </c>
+      <c r="J44" s="164"/>
+      <c r="K44" s="164"/>
+      <c r="L44" s="182"/>
+      <c r="M44" s="182"/>
+      <c r="N44" s="164"/>
+      <c r="O44" s="164"/>
+      <c r="P44" s="182"/>
+      <c r="Q44" s="182"/>
+      <c r="R44" s="164"/>
+      <c r="S44" s="164"/>
+    </row>
+    <row r="45" spans="2:45" ht="15.4">
+      <c r="B45" s="183" t="s">
+        <v>185</v>
+      </c>
+      <c r="C45" s="178">
+        <v>1</v>
+      </c>
+      <c r="D45" s="179"/>
+      <c r="E45" s="179"/>
+      <c r="F45" s="179"/>
+      <c r="G45" s="179"/>
+      <c r="H45" s="179"/>
+      <c r="I45" s="179"/>
+      <c r="J45" s="171"/>
+      <c r="K45" s="164"/>
+      <c r="L45" s="164"/>
+      <c r="M45" s="164"/>
+      <c r="N45" s="164"/>
+      <c r="O45" s="164"/>
+      <c r="P45" s="164"/>
+      <c r="Q45" s="164"/>
+      <c r="R45" s="164"/>
+      <c r="S45" s="164"/>
+    </row>
+    <row r="46" spans="2:45">
+      <c r="B46" s="179" t="str">
+        <f t="shared" ref="B46:B51" si="1">C6</f>
+        <v>EN_STG_4hBatt_LMO</v>
+      </c>
+      <c r="C46" s="179"/>
+      <c r="D46" s="179">
+        <v>1</v>
+      </c>
+      <c r="E46" s="179"/>
+      <c r="F46" s="179"/>
+      <c r="G46" s="179"/>
+      <c r="H46" s="179"/>
+      <c r="I46" s="179"/>
+      <c r="J46" s="171"/>
+      <c r="K46" s="164"/>
+      <c r="L46" s="164"/>
+      <c r="M46" s="164"/>
+      <c r="N46" s="164"/>
+      <c r="O46" s="164"/>
+      <c r="P46" s="164"/>
+      <c r="Q46" s="164"/>
+      <c r="R46" s="164"/>
+      <c r="S46" s="164"/>
+    </row>
+    <row r="47" spans="2:45">
+      <c r="B47" s="179" t="str">
+        <f t="shared" si="1"/>
+        <v>EN_STG_4hBatt_NCA</v>
+      </c>
+      <c r="C47" s="179"/>
+      <c r="D47" s="179"/>
+      <c r="E47" s="179">
+        <v>1</v>
+      </c>
+      <c r="F47" s="179"/>
+      <c r="G47" s="179"/>
+      <c r="H47" s="179"/>
+      <c r="I47" s="179"/>
+      <c r="J47" s="171"/>
+      <c r="K47" s="164"/>
+      <c r="L47" s="164"/>
+      <c r="M47" s="164"/>
+      <c r="N47" s="164"/>
+      <c r="O47" s="164"/>
+      <c r="P47" s="164"/>
+      <c r="Q47" s="164"/>
+      <c r="R47" s="164"/>
+      <c r="S47" s="164"/>
+    </row>
+    <row r="48" spans="2:45">
+      <c r="B48" s="179" t="str">
+        <f t="shared" si="1"/>
+        <v>EN_STG_4hBatt_NMC111</v>
+      </c>
+      <c r="C48" s="179"/>
+      <c r="D48" s="179"/>
+      <c r="E48" s="179"/>
+      <c r="F48" s="179">
+        <v>1</v>
+      </c>
+      <c r="G48" s="179"/>
+      <c r="H48" s="179"/>
+      <c r="I48" s="179"/>
+      <c r="J48" s="171"/>
+      <c r="K48" s="164"/>
+      <c r="L48" s="164"/>
+      <c r="M48" s="164"/>
+      <c r="N48" s="164"/>
+      <c r="O48" s="164"/>
+      <c r="P48" s="164"/>
+      <c r="Q48" s="164"/>
+      <c r="R48" s="164"/>
+      <c r="S48" s="164"/>
+    </row>
+    <row r="49" spans="2:19">
+      <c r="B49" s="179" t="str">
+        <f t="shared" si="1"/>
+        <v>EN_STG_4hBatt_NMC532</v>
+      </c>
+      <c r="C49" s="179"/>
+      <c r="D49" s="179"/>
+      <c r="E49" s="179"/>
+      <c r="F49" s="179"/>
+      <c r="G49" s="179">
+        <v>1</v>
+      </c>
+      <c r="H49" s="179"/>
+      <c r="I49" s="179"/>
+      <c r="J49" s="171"/>
+      <c r="K49" s="164"/>
+      <c r="L49" s="164"/>
+      <c r="M49" s="164"/>
+      <c r="N49" s="164"/>
+      <c r="O49" s="164"/>
+      <c r="P49" s="164"/>
+      <c r="Q49" s="164"/>
+      <c r="R49" s="164"/>
+      <c r="S49" s="164"/>
+    </row>
+    <row r="50" spans="2:19">
+      <c r="B50" s="179" t="str">
+        <f t="shared" si="1"/>
+        <v>EN_STG_4hBatt_NMC622</v>
+      </c>
+      <c r="C50" s="179"/>
+      <c r="D50" s="179"/>
+      <c r="E50" s="179"/>
+      <c r="F50" s="179"/>
+      <c r="G50" s="179"/>
+      <c r="H50" s="179">
+        <v>1</v>
+      </c>
+      <c r="I50" s="179"/>
+      <c r="J50" s="171"/>
+      <c r="K50" s="164"/>
+      <c r="L50" s="164"/>
+      <c r="M50" s="164"/>
+      <c r="N50" s="164"/>
+      <c r="O50" s="164"/>
+      <c r="P50" s="164"/>
+      <c r="Q50" s="164"/>
+      <c r="R50" s="164"/>
+      <c r="S50" s="164"/>
+    </row>
+    <row r="51" spans="2:19">
+      <c r="B51" s="179" t="str">
+        <f t="shared" si="1"/>
+        <v>EN_STG_4hBatt_NMC811</v>
+      </c>
+      <c r="C51" s="179"/>
+      <c r="D51" s="179"/>
+      <c r="E51" s="179"/>
+      <c r="F51" s="179"/>
+      <c r="G51" s="179"/>
+      <c r="H51" s="179"/>
+      <c r="I51" s="179">
+        <v>1</v>
+      </c>
+      <c r="J51" s="171"/>
+      <c r="K51" s="164"/>
+      <c r="L51" s="164"/>
+      <c r="M51" s="164"/>
+      <c r="N51" s="164"/>
+      <c r="O51" s="164"/>
+      <c r="P51" s="164"/>
+      <c r="Q51" s="164"/>
+      <c r="R51" s="164"/>
+      <c r="S51" s="164"/>
+    </row>
+    <row r="52" spans="2:19">
+      <c r="B52" s="164"/>
+      <c r="C52" s="164"/>
+      <c r="D52" s="164"/>
+      <c r="E52" s="164"/>
+      <c r="F52" s="164"/>
+      <c r="G52" s="164"/>
+      <c r="H52" s="164"/>
+      <c r="I52" s="164"/>
+      <c r="J52" s="184"/>
+      <c r="K52" s="164"/>
+      <c r="L52" s="164"/>
+      <c r="M52" s="164"/>
+      <c r="N52" s="164"/>
+      <c r="O52" s="164"/>
+      <c r="P52" s="164"/>
+      <c r="Q52" s="164"/>
+      <c r="R52" s="164"/>
+      <c r="S52" s="164"/>
+    </row>
+    <row r="53" spans="2:19">
+      <c r="B53" s="171"/>
+      <c r="C53" s="171"/>
+      <c r="D53" s="171"/>
+      <c r="E53" s="171"/>
+      <c r="F53" s="171"/>
+      <c r="G53" s="171"/>
+      <c r="H53" s="171"/>
+      <c r="I53" s="171"/>
+      <c r="J53" s="171"/>
+      <c r="K53" s="171"/>
+      <c r="L53" s="171"/>
+      <c r="M53" s="171"/>
+      <c r="N53" s="171"/>
+      <c r="O53" s="171"/>
+      <c r="P53" s="171"/>
+      <c r="Q53" s="171"/>
+      <c r="R53" s="171"/>
+      <c r="S53" s="171"/>
+    </row>
+    <row r="54" spans="2:19">
+      <c r="B54" s="171"/>
+      <c r="C54" s="171"/>
+      <c r="D54" s="171"/>
+      <c r="E54" s="171"/>
+      <c r="F54" s="171"/>
+      <c r="G54" s="171"/>
+      <c r="H54" s="171"/>
+      <c r="I54" s="171"/>
+      <c r="J54" s="171"/>
+      <c r="K54" s="171"/>
+      <c r="L54" s="171"/>
+      <c r="M54" s="171"/>
+      <c r="N54" s="171"/>
+      <c r="O54" s="171"/>
+      <c r="P54" s="171"/>
+      <c r="Q54" s="171"/>
+      <c r="R54" s="171"/>
+      <c r="S54" s="171"/>
+    </row>
+    <row r="58" spans="2:19">
+      <c r="B58" s="185" t="s">
+        <v>229</v>
+      </c>
+      <c r="C58" s="185"/>
+      <c r="D58" s="185"/>
+      <c r="E58" s="185"/>
+      <c r="F58" s="185"/>
+      <c r="G58" s="185"/>
+      <c r="H58" s="185"/>
+      <c r="I58" s="185"/>
+    </row>
+    <row r="59" spans="2:19">
+      <c r="B59" s="185" t="s">
+        <v>80</v>
+      </c>
+      <c r="C59" s="186" t="s">
+        <v>230</v>
+      </c>
+      <c r="D59" s="185" t="s">
+        <v>231</v>
+      </c>
+      <c r="E59" s="185" t="s">
+        <v>232</v>
+      </c>
+      <c r="F59" s="185" t="s">
+        <v>233</v>
+      </c>
+      <c r="G59" s="185" t="s">
+        <v>234</v>
+      </c>
+      <c r="H59" s="185" t="s">
+        <v>235</v>
+      </c>
+      <c r="I59" s="185" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="60" spans="2:19">
+      <c r="B60" s="185" t="s">
+        <v>185</v>
+      </c>
+      <c r="C60" s="185">
+        <v>1</v>
+      </c>
+      <c r="D60" s="185"/>
+      <c r="E60" s="185"/>
+      <c r="F60" s="185"/>
+      <c r="G60" s="185"/>
+      <c r="H60" s="185"/>
+      <c r="I60" s="185"/>
+    </row>
+    <row r="61" spans="2:19">
+      <c r="B61" s="185" t="s">
+        <v>192</v>
+      </c>
+      <c r="C61" s="185"/>
+      <c r="D61" s="185">
+        <v>1</v>
+      </c>
+      <c r="E61" s="185"/>
+      <c r="F61" s="185"/>
+      <c r="G61" s="185"/>
+      <c r="H61" s="185"/>
+      <c r="I61" s="185"/>
+    </row>
+    <row r="62" spans="2:19">
+      <c r="B62" s="185" t="s">
+        <v>194</v>
+      </c>
+      <c r="C62" s="185"/>
+      <c r="D62" s="185"/>
+      <c r="E62" s="185">
+        <v>1</v>
+      </c>
+      <c r="F62" s="185"/>
+      <c r="G62" s="185"/>
+      <c r="H62" s="185"/>
+      <c r="I62" s="185"/>
+    </row>
+    <row r="63" spans="2:19">
+      <c r="B63" s="185" t="s">
+        <v>195</v>
+      </c>
+      <c r="C63" s="185"/>
+      <c r="D63" s="185"/>
+      <c r="E63" s="185"/>
+      <c r="F63" s="185">
+        <v>1</v>
+      </c>
+      <c r="G63" s="185"/>
+      <c r="H63" s="185"/>
+      <c r="I63" s="185"/>
+    </row>
+    <row r="64" spans="2:19">
+      <c r="B64" s="185" t="s">
+        <v>196</v>
+      </c>
+      <c r="C64" s="185"/>
+      <c r="D64" s="185"/>
+      <c r="E64" s="185"/>
+      <c r="F64" s="185"/>
+      <c r="G64" s="185">
+        <v>1</v>
+      </c>
+      <c r="H64" s="185"/>
+      <c r="I64" s="185"/>
+    </row>
+    <row r="65" spans="2:9">
+      <c r="B65" s="185" t="s">
+        <v>197</v>
+      </c>
+      <c r="C65" s="185"/>
+      <c r="D65" s="185"/>
+      <c r="E65" s="185"/>
+      <c r="F65" s="185"/>
+      <c r="G65" s="185"/>
+      <c r="H65" s="185">
+        <v>1</v>
+      </c>
+      <c r="I65" s="185"/>
+    </row>
+    <row r="66" spans="2:9">
+      <c r="B66" s="185" t="s">
+        <v>198</v>
+      </c>
+      <c r="C66" s="185"/>
+      <c r="D66" s="185"/>
+      <c r="E66" s="185"/>
+      <c r="F66" s="185"/>
+      <c r="G66" s="185"/>
+      <c r="H66" s="185"/>
+      <c r="I66" s="185">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/SubRes_Tmpl/SubRES_H2-Production.xlsx
+++ b/SubRes_Tmpl/SubRES_H2-Production.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\KiNESYS_BattCircularity-main\SubRes_Tmpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6FFC487-9218-4913-9A98-D81F23139964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="8260" activeTab="5"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SectFuel" sheetId="2" r:id="rId1"/>
@@ -83,12 +89,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Rocco De Miglio</author>
   </authors>
   <commentList>
-    <comment ref="O39" authorId="0">
+    <comment ref="O39" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -116,13 +122,13 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>xli9</author>
     <author>Amit Kanudia</author>
   </authors>
   <commentList>
-    <comment ref="L16" authorId="0">
+    <comment ref="L16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000001000000}">
       <text>
         <r>
           <rPr>
@@ -144,7 +150,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AY16" authorId="0">
+    <comment ref="AZ16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000002000000}">
       <text>
         <r>
           <rPr>
@@ -166,7 +172,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y17" authorId="0">
+    <comment ref="Y17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000003000000}">
       <text>
         <r>
           <rPr>
@@ -188,7 +194,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P19" authorId="1">
+    <comment ref="P19" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0500-000004000000}">
       <text>
         <r>
           <rPr>
@@ -212,7 +218,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AY19" authorId="0">
+    <comment ref="AZ19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000005000000}">
       <text>
         <r>
           <rPr>
@@ -234,7 +240,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AY22" authorId="0">
+    <comment ref="AZ22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000006000000}">
       <text>
         <r>
           <rPr>
@@ -256,7 +262,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AY25" authorId="0">
+    <comment ref="AZ25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000007000000}">
       <text>
         <r>
           <rPr>
@@ -278,7 +284,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AY28" authorId="0">
+    <comment ref="AZ28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000008000000}">
       <text>
         <r>
           <rPr>
@@ -300,7 +306,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AY31" authorId="0">
+    <comment ref="AZ31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000009000000}">
       <text>
         <r>
           <rPr>
@@ -322,7 +328,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C33" authorId="0">
+    <comment ref="C33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -349,7 +355,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="238">
   <si>
     <t>~FI_T</t>
   </si>
@@ -1068,24 +1074,23 @@
   </si>
   <si>
     <t>recy-NMC811</t>
+  </si>
+  <si>
+    <t>PKCNT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="9">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* \-??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="\Te\x\t"/>
-    <numFmt numFmtId="179" formatCode="#,##0.000"/>
-    <numFmt numFmtId="180" formatCode="#,##0.0_ "/>
-    <numFmt numFmtId="181" formatCode="0.0"/>
-    <numFmt numFmtId="182" formatCode="0.000"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="5">
+    <numFmt numFmtId="168" formatCode="\Te\x\t"/>
+    <numFmt numFmtId="169" formatCode="#,##0.000"/>
+    <numFmt numFmtId="170" formatCode="#,##0.0_ "/>
+    <numFmt numFmtId="171" formatCode="0.0"/>
+    <numFmt numFmtId="172" formatCode="0.000"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1113,7 +1118,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.2"/>
+      <sz val="10.199999999999999"/>
       <color rgb="FF212529"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
@@ -1215,127 +1220,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
@@ -1357,8 +1241,15 @@
       <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="48">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1373,7 +1264,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.349986266670736"/>
+        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1385,7 +1276,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1397,7 +1288,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399945066682943"/>
+        <fgColor theme="9" tint="0.39991454817346722"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1409,7 +1300,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.0499893185216834"/>
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1433,7 +1324,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799951170384838"/>
+        <fgColor theme="5" tint="0.79992065187536243"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1451,7 +1342,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799951170384838"/>
+        <fgColor theme="9" tint="0.79992065187536243"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1463,7 +1354,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1479,170 +1370,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="34">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -1784,7 +1513,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.399945066682943"/>
+        <color theme="4" tint="0.39991454817346722"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1830,7 +1559,7 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </left>
       <right/>
       <top/>
@@ -1840,7 +1569,7 @@
     <border>
       <left/>
       <right style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </right>
       <top/>
       <bottom/>
@@ -1857,7 +1586,7 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </left>
       <right/>
       <top style="thin">
@@ -1869,7 +1598,7 @@
     <border>
       <left/>
       <right style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </right>
       <top style="thin">
         <color auto="1"/>
@@ -1910,7 +1639,7 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </left>
       <right/>
       <top/>
@@ -1922,7 +1651,7 @@
     <border>
       <left/>
       <right style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </right>
       <top/>
       <bottom style="thin">
@@ -1930,283 +1659,65 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="51">
+  <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="27" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="9" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="185">
+  <cellXfs count="186">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="178" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="178" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="49" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="6" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -2225,12 +1736,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
@@ -2240,7 +1751,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2249,42 +1760,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="13"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="15"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="14"/>
-    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" xfId="50" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="50" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="50" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="168" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="7"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="2"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="3"/>
+    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" xfId="7" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="7" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="7" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="24" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="5" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2302,19 +1801,16 @@
     <xf numFmtId="0" fontId="11" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="13" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="13" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="13" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2335,13 +1831,13 @@
     <xf numFmtId="0" fontId="13" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="13" fillId="12" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="13" fillId="12" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="13" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2368,25 +1864,25 @@
     <xf numFmtId="0" fontId="14" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="14" fillId="13" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="14" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="14" fillId="13" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="14" fillId="13" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="14" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="14" fillId="13" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="14" fillId="13" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="14" fillId="13" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="14" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="14" fillId="13" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="13" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="13" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="13" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2398,25 +1894,25 @@
     <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="13" fillId="14" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="14" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="14" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="14" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="14" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="13" fillId="14" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="14" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="14" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="14" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="14" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2428,25 +1924,25 @@
     <xf numFmtId="0" fontId="13" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="13" fillId="15" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="15" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="15" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="15" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="15" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="13" fillId="15" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="15" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="15" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="15" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="15" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2458,25 +1954,25 @@
     <xf numFmtId="0" fontId="13" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="13" fillId="16" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="16" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="16" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="14" fillId="16" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="14" fillId="16" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="14" fillId="16" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="14" fillId="16" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="13" fillId="16" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="16" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="16" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="16" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="16" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="16" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="16" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2491,25 +1987,25 @@
     <xf numFmtId="0" fontId="13" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="13" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="18" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="14" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="14" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="14" fillId="18" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="14" fillId="18" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="13" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="18" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="18" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="18" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="17" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2521,25 +2017,25 @@
     <xf numFmtId="0" fontId="13" fillId="16" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="13" fillId="16" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="16" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="16" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="14" fillId="16" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="14" fillId="16" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="14" fillId="16" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="14" fillId="16" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="13" fillId="16" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="16" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="16" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="16" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="16" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="16" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="16" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2548,25 +2044,25 @@
     <xf numFmtId="1" fontId="13" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="13" fillId="19" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="19" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="19" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="19" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="19" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="13" fillId="19" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="19" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="19" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="19" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="19" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="19" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2578,25 +2074,25 @@
     <xf numFmtId="1" fontId="13" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="13" fillId="20" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="20" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="20" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="20" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="20" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="13" fillId="20" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="20" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="20" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="20" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="20" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="20" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2608,25 +2104,25 @@
     <xf numFmtId="0" fontId="13" fillId="19" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="13" fillId="19" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="19" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="19" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="19" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="19" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="19" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="19" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="13" fillId="19" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="19" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="19" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="19" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="19" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="19" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="19" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2637,72 +2133,54 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="51">
+  <cellStyles count="8">
+    <cellStyle name="Heading 2" xfId="2" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="3" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="4" builtinId="19"/>
+    <cellStyle name="Neutral" xfId="5" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
-    <cellStyle name="Normal 10" xfId="49"/>
-    <cellStyle name="Normal 2" xfId="50"/>
+    <cellStyle name="Normal 10" xfId="6" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="Normal 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="New Microsoft Excel Worksheet"/>
       <sheetName val="AGR_Fuels"/>
@@ -2718,8 +2196,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="IEA Data"/>
       <sheetName val="E&amp;D Drivers"/>
@@ -2831,8 +2312,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="IEA Data"/>
       <sheetName val="E&amp;D Drivers"/>
@@ -2944,8 +2428,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Cover"/>
       <sheetName val="H2 transport"/>
@@ -2981,8 +2468,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Cover"/>
       <sheetName val="ELC_Lists"/>
@@ -3016,8 +2506,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Discuss_log"/>
       <sheetName val="Cover"/>
@@ -3062,22 +2555,22 @@
       <sheetData sheetId="13">
         <row r="6">
           <cell r="AW6">
-            <v>0.0473</v>
+            <v>4.7300000000000002E-2</v>
           </cell>
         </row>
         <row r="7">
           <cell r="AW7">
-            <v>0.171166666666667</v>
+            <v>0.17116666666666699</v>
           </cell>
         </row>
         <row r="8">
           <cell r="AW8">
-            <v>0.466366666666667</v>
+            <v>0.46636666666666698</v>
           </cell>
         </row>
         <row r="9">
           <cell r="AW9">
-            <v>0.0956666666666667</v>
+            <v>9.5666666666666705E-2</v>
           </cell>
         </row>
       </sheetData>
@@ -3349,29 +2842,29 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B3:P7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="11.8636363636364" customWidth="1"/>
-    <col min="3" max="3" width="9.4" customWidth="1"/>
-    <col min="4" max="4" width="15.2636363636364" customWidth="1"/>
+    <col min="2" max="2" width="11.86328125" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" customWidth="1"/>
+    <col min="4" max="4" width="15.265625" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="6.4" customWidth="1"/>
-    <col min="7" max="7" width="8.26363636363636" customWidth="1"/>
-    <col min="9" max="9" width="11.2636363636364" customWidth="1"/>
-    <col min="10" max="10" width="11.8636363636364" customWidth="1"/>
-    <col min="11" max="11" width="20.6" customWidth="1"/>
-    <col min="12" max="12" width="8.6" customWidth="1"/>
-    <col min="13" max="13" width="4.6" customWidth="1"/>
-    <col min="14" max="14" width="5.26363636363636" customWidth="1"/>
-    <col min="15" max="15" width="10.2636363636364" customWidth="1"/>
-    <col min="16" max="16" width="7.86363636363636" customWidth="1"/>
+    <col min="6" max="6" width="6.3984375" customWidth="1"/>
+    <col min="7" max="7" width="8.265625" customWidth="1"/>
+    <col min="9" max="9" width="11.265625" customWidth="1"/>
+    <col min="10" max="10" width="11.86328125" customWidth="1"/>
+    <col min="11" max="11" width="20.59765625" customWidth="1"/>
+    <col min="12" max="12" width="8.59765625" customWidth="1"/>
+    <col min="13" max="13" width="4.59765625" customWidth="1"/>
+    <col min="14" max="14" width="5.265625" customWidth="1"/>
+    <col min="15" max="15" width="10.265625" customWidth="1"/>
+    <col min="16" max="16" width="7.86328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:16">
@@ -3537,63 +3030,61 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Y39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="2" width="11.1363636363636" customWidth="1"/>
+    <col min="1" max="2" width="11.1328125" customWidth="1"/>
     <col min="3" max="5" width="14" customWidth="1"/>
-    <col min="6" max="8" width="11.8636363636364" customWidth="1"/>
-    <col min="9" max="9" width="20.2636363636364" customWidth="1"/>
-    <col min="10" max="10" width="15.6" customWidth="1"/>
-    <col min="11" max="11" width="20.2636363636364" customWidth="1"/>
-    <col min="12" max="12" width="15.6" customWidth="1"/>
-    <col min="13" max="13" width="20.2636363636364" customWidth="1"/>
-    <col min="14" max="14" width="15.6" customWidth="1"/>
-    <col min="15" max="15" width="18.8636363636364" customWidth="1"/>
-    <col min="16" max="16" width="4.4" customWidth="1"/>
-    <col min="17" max="17" width="8.13636363636364" customWidth="1"/>
-    <col min="20" max="20" width="18.1363636363636" customWidth="1"/>
+    <col min="6" max="8" width="11.86328125" customWidth="1"/>
+    <col min="9" max="9" width="20.265625" customWidth="1"/>
+    <col min="10" max="10" width="15.59765625" customWidth="1"/>
+    <col min="11" max="11" width="20.265625" customWidth="1"/>
+    <col min="12" max="12" width="15.59765625" customWidth="1"/>
+    <col min="13" max="13" width="20.265625" customWidth="1"/>
+    <col min="14" max="14" width="15.59765625" customWidth="1"/>
+    <col min="15" max="15" width="18.86328125" customWidth="1"/>
+    <col min="16" max="16" width="4.3984375" customWidth="1"/>
+    <col min="17" max="17" width="8.1328125" customWidth="1"/>
+    <col min="20" max="20" width="18.1328125" customWidth="1"/>
     <col min="21" max="21" width="24" customWidth="1"/>
-    <col min="22" max="22" width="4.6" customWidth="1"/>
-    <col min="23" max="23" width="4.13636363636364" customWidth="1"/>
-    <col min="24" max="24" width="7.72727272727273" customWidth="1"/>
-    <col min="25" max="25" width="7.13636363636364" customWidth="1"/>
+    <col min="22" max="22" width="4.59765625" customWidth="1"/>
+    <col min="23" max="23" width="4.1328125" customWidth="1"/>
+    <col min="24" max="24" width="7.73046875" customWidth="1"/>
+    <col min="25" max="25" width="7.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33.75" customHeight="1" spans="1:20">
+    <row r="1" spans="1:20" ht="33.75" customHeight="1">
       <c r="A1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="59" t="s">
+      <c r="C1" s="180" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="60" t="s">
+      <c r="D1" s="180"/>
+      <c r="E1" s="180"/>
+      <c r="F1" s="181" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="59"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="59" t="s">
+      <c r="G1" s="180"/>
+      <c r="H1" s="182"/>
+      <c r="I1" s="180" t="s">
         <v>32</v>
       </c>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="59"/>
-      <c r="O1" s="62" t="s">
+      <c r="J1" s="180"/>
+      <c r="K1" s="180"/>
+      <c r="L1" s="180"/>
+      <c r="M1" s="180"/>
+      <c r="N1" s="180"/>
+      <c r="O1" s="183" t="s">
         <v>33</v>
       </c>
-      <c r="P1" s="63"/>
-      <c r="Q1" s="63"/>
+      <c r="P1" s="59"/>
+      <c r="Q1" s="59"/>
       <c r="S1" t="s">
         <v>34</v>
       </c>
@@ -3602,953 +3093,953 @@
       </c>
     </row>
     <row r="2" spans="1:20">
-      <c r="C2" s="64" t="s">
+      <c r="C2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="64" t="s">
+      <c r="D2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="64" t="s">
+      <c r="E2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="64" t="s">
+      <c r="F2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="64" t="s">
+      <c r="G2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="H2" s="64" t="s">
+      <c r="H2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="I2" s="64" t="s">
+      <c r="I2" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="J2" s="64" t="s">
+      <c r="J2" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="K2" s="64" t="str">
+      <c r="K2" s="60" t="str">
         <f>I2</f>
         <v>input~GASNGA</v>
       </c>
-      <c r="L2" s="64" t="str">
+      <c r="L2" s="60" t="str">
         <f>J2</f>
         <v>input~ELC_gc</v>
       </c>
-      <c r="M2" s="64" t="str">
+      <c r="M2" s="60" t="str">
         <f>K2</f>
         <v>input~GASNGA</v>
       </c>
-      <c r="N2" s="64" t="str">
+      <c r="N2" s="60" t="str">
         <f>L2</f>
         <v>input~ELC_gc</v>
       </c>
-      <c r="O2" s="63"/>
-      <c r="P2" s="63"/>
-      <c r="Q2" s="63"/>
+      <c r="O2" s="184"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
     </row>
     <row r="3" spans="1:20">
-      <c r="C3" s="64">
+      <c r="C3" s="60">
         <v>2020</v>
       </c>
-      <c r="D3" s="64">
+      <c r="D3" s="60">
         <v>2030</v>
       </c>
-      <c r="E3" s="64">
+      <c r="E3" s="60">
         <v>2050</v>
       </c>
-      <c r="F3" s="64">
+      <c r="F3" s="60">
         <f>C3</f>
         <v>2020</v>
       </c>
-      <c r="G3" s="64">
+      <c r="G3" s="60">
         <f t="shared" ref="G3:H3" si="0">D3</f>
         <v>2030</v>
       </c>
-      <c r="H3" s="64">
+      <c r="H3" s="60">
         <f t="shared" si="0"/>
         <v>2050</v>
       </c>
-      <c r="I3" s="64">
+      <c r="I3" s="60">
         <v>2015</v>
       </c>
-      <c r="J3" s="64">
+      <c r="J3" s="60">
         <v>2015</v>
       </c>
-      <c r="K3" s="64">
+      <c r="K3" s="60">
         <v>2030</v>
       </c>
-      <c r="L3" s="64">
+      <c r="L3" s="60">
         <v>2030</v>
       </c>
-      <c r="M3" s="64">
+      <c r="M3" s="60">
         <v>2050</v>
       </c>
-      <c r="N3" s="64">
+      <c r="N3" s="60">
         <v>2050</v>
       </c>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-    </row>
-    <row r="4" ht="26" spans="1:20">
-      <c r="C4" s="65">
+      <c r="O3" s="184"/>
+      <c r="P3" s="59"/>
+      <c r="Q3" s="59"/>
+    </row>
+    <row r="4" spans="1:20" ht="26.25">
+      <c r="C4" s="61">
         <v>2020</v>
       </c>
-      <c r="D4" s="65">
+      <c r="D4" s="61">
         <v>2030</v>
       </c>
-      <c r="E4" s="65" t="s">
+      <c r="E4" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="66">
+      <c r="F4" s="62">
         <v>2015</v>
       </c>
-      <c r="G4" s="65">
+      <c r="G4" s="61">
         <v>2030</v>
       </c>
-      <c r="H4" s="67" t="s">
+      <c r="H4" s="63" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="65" t="s">
+      <c r="I4" s="61" t="s">
         <v>41</v>
       </c>
-      <c r="J4" s="65" t="s">
+      <c r="J4" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="K4" s="68" t="s">
+      <c r="K4" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="L4" s="69" t="s">
+      <c r="L4" s="65" t="s">
         <v>44</v>
       </c>
-      <c r="M4" s="65" t="s">
+      <c r="M4" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="N4" s="65" t="s">
+      <c r="N4" s="61" t="s">
         <v>46</v>
       </c>
-      <c r="O4" s="70"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
+      <c r="O4" s="185"/>
+      <c r="P4" s="59"/>
+      <c r="Q4" s="59"/>
     </row>
     <row r="5" spans="1:20">
-      <c r="C5" s="71">
+      <c r="C5" s="66">
         <v>550</v>
       </c>
-      <c r="D5" s="71">
+      <c r="D5" s="66">
         <v>500</v>
       </c>
-      <c r="E5" s="71">
+      <c r="E5" s="66">
         <v>450</v>
       </c>
-      <c r="F5" s="72">
+      <c r="F5" s="67">
         <v>22</v>
       </c>
-      <c r="G5" s="73">
+      <c r="G5" s="68">
         <v>20</v>
       </c>
-      <c r="H5" s="74">
+      <c r="H5" s="69">
         <v>18</v>
       </c>
-      <c r="I5" s="75">
+      <c r="I5" s="70">
         <v>1.33</v>
       </c>
-      <c r="J5" s="75">
-        <v>0.094</v>
-      </c>
-      <c r="K5" s="76">
+      <c r="J5" s="70">
+        <v>9.4E-2</v>
+      </c>
+      <c r="K5" s="71">
         <v>1.3</v>
       </c>
-      <c r="L5" s="77">
-        <v>0.094</v>
-      </c>
-      <c r="M5" s="75">
+      <c r="L5" s="72">
+        <v>9.4E-2</v>
+      </c>
+      <c r="M5" s="70">
         <v>1.28</v>
       </c>
-      <c r="N5" s="75">
-        <v>0.094</v>
-      </c>
-      <c r="O5" s="78" t="s">
+      <c r="N5" s="70">
+        <v>9.4E-2</v>
+      </c>
+      <c r="O5" s="73" t="s">
         <v>47</v>
       </c>
-      <c r="P5" s="79"/>
-      <c r="Q5" s="79"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
     </row>
     <row r="6" spans="1:20">
-      <c r="C6" s="80">
+      <c r="C6" s="75">
         <v>900</v>
       </c>
-      <c r="D6" s="80">
+      <c r="D6" s="75">
         <v>850</v>
       </c>
-      <c r="E6" s="80">
+      <c r="E6" s="75">
         <v>800</v>
       </c>
-      <c r="F6" s="81">
+      <c r="F6" s="76">
         <v>36</v>
       </c>
-      <c r="G6" s="82">
+      <c r="G6" s="77">
         <v>34</v>
       </c>
-      <c r="H6" s="83">
+      <c r="H6" s="78">
         <v>32</v>
       </c>
-      <c r="I6" s="84">
+      <c r="I6" s="79">
         <v>1.33</v>
       </c>
-      <c r="J6" s="84">
-        <v>1.094</v>
-      </c>
-      <c r="K6" s="85">
+      <c r="J6" s="79">
+        <v>1.0940000000000001</v>
+      </c>
+      <c r="K6" s="80">
         <v>1.3</v>
       </c>
-      <c r="L6" s="86">
-        <v>1.094</v>
-      </c>
-      <c r="M6" s="84">
+      <c r="L6" s="81">
+        <v>1.0940000000000001</v>
+      </c>
+      <c r="M6" s="79">
         <v>1.28</v>
       </c>
-      <c r="N6" s="84">
-        <v>1.094</v>
-      </c>
-      <c r="O6" s="87" t="s">
+      <c r="N6" s="79">
+        <v>1.0940000000000001</v>
+      </c>
+      <c r="O6" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="P6" s="88"/>
-      <c r="Q6" s="88"/>
+      <c r="P6" s="83"/>
+      <c r="Q6" s="83"/>
     </row>
     <row r="7" spans="1:20">
-      <c r="C7" s="71">
+      <c r="C7" s="66">
         <v>1978</v>
       </c>
-      <c r="D7" s="71">
+      <c r="D7" s="66">
         <v>1598</v>
       </c>
-      <c r="E7" s="71">
+      <c r="E7" s="66">
         <v>1450</v>
       </c>
-      <c r="F7" s="72">
+      <c r="F7" s="67">
         <v>57</v>
       </c>
-      <c r="G7" s="73">
+      <c r="G7" s="68">
         <v>31</v>
       </c>
-      <c r="H7" s="74">
+      <c r="H7" s="69">
         <v>28</v>
       </c>
-      <c r="I7" s="75">
+      <c r="I7" s="70">
         <v>1.53</v>
       </c>
-      <c r="J7" s="75">
-        <v>0.094</v>
-      </c>
-      <c r="K7" s="76">
+      <c r="J7" s="70">
+        <v>9.4E-2</v>
+      </c>
+      <c r="K7" s="71">
         <v>1.47</v>
       </c>
-      <c r="L7" s="77">
-        <v>0.094</v>
-      </c>
-      <c r="M7" s="75">
+      <c r="L7" s="72">
+        <v>9.4E-2</v>
+      </c>
+      <c r="M7" s="70">
         <v>1.43</v>
       </c>
-      <c r="N7" s="75">
-        <v>0.094</v>
-      </c>
-      <c r="O7" s="78" t="s">
+      <c r="N7" s="70">
+        <v>9.4E-2</v>
+      </c>
+      <c r="O7" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="P7" s="79"/>
-      <c r="Q7" s="79"/>
+      <c r="P7" s="74"/>
+      <c r="Q7" s="74"/>
     </row>
     <row r="8" spans="1:20">
-      <c r="C8" s="89">
+      <c r="C8" s="84">
         <v>1610</v>
       </c>
-      <c r="D8" s="89">
+      <c r="D8" s="84">
         <v>740</v>
       </c>
-      <c r="E8" s="89">
+      <c r="E8" s="84">
         <v>200</v>
       </c>
-      <c r="F8" s="81">
+      <c r="F8" s="76">
         <v>49</v>
       </c>
-      <c r="G8" s="82">
+      <c r="G8" s="77">
         <v>15</v>
       </c>
-      <c r="H8" s="83">
+      <c r="H8" s="78">
         <v>10</v>
       </c>
-      <c r="I8" s="84">
+      <c r="I8" s="79">
         <v>0</v>
       </c>
-      <c r="J8" s="84">
+      <c r="J8" s="79">
         <v>1.39</v>
       </c>
-      <c r="K8" s="85">
+      <c r="K8" s="80">
         <v>0</v>
       </c>
-      <c r="L8" s="86">
+      <c r="L8" s="81">
         <v>1.19</v>
       </c>
-      <c r="M8" s="84">
+      <c r="M8" s="79">
         <v>0</v>
       </c>
-      <c r="N8" s="84">
+      <c r="N8" s="79">
         <v>1.17</v>
       </c>
-      <c r="O8" s="87" t="s">
+      <c r="O8" s="82" t="s">
         <v>50</v>
       </c>
-      <c r="P8" s="88"/>
-      <c r="Q8" s="88"/>
+      <c r="P8" s="83"/>
+      <c r="Q8" s="83"/>
     </row>
     <row r="9" spans="1:20">
-      <c r="C9" s="90">
+      <c r="C9" s="85">
         <v>2530</v>
       </c>
-      <c r="D9" s="90">
+      <c r="D9" s="85">
         <v>1175</v>
       </c>
-      <c r="E9" s="90">
+      <c r="E9" s="85">
         <v>350</v>
       </c>
-      <c r="F9" s="72">
+      <c r="F9" s="67">
         <v>77</v>
       </c>
-      <c r="G9" s="73">
+      <c r="G9" s="68">
         <v>34</v>
       </c>
-      <c r="H9" s="74">
+      <c r="H9" s="69">
         <v>18</v>
       </c>
-      <c r="I9" s="75">
+      <c r="I9" s="70">
         <v>0</v>
       </c>
-      <c r="J9" s="75">
+      <c r="J9" s="70">
         <v>1.5</v>
       </c>
-      <c r="K9" s="76">
+      <c r="K9" s="71">
         <v>0</v>
       </c>
-      <c r="L9" s="77">
+      <c r="L9" s="72">
         <v>1.25</v>
       </c>
-      <c r="M9" s="75">
+      <c r="M9" s="70">
         <v>0</v>
       </c>
-      <c r="N9" s="75">
+      <c r="N9" s="70">
         <v>1.19</v>
       </c>
-      <c r="O9" s="78" t="s">
+      <c r="O9" s="73" t="s">
         <v>51</v>
       </c>
-      <c r="P9" s="79"/>
-      <c r="Q9" s="79"/>
+      <c r="P9" s="74"/>
+      <c r="Q9" s="74"/>
     </row>
     <row r="10" spans="1:20">
-      <c r="C10" s="89">
+      <c r="C10" s="84">
         <v>1265</v>
       </c>
-      <c r="D10" s="89">
+      <c r="D10" s="84">
         <v>600</v>
       </c>
-      <c r="E10" s="89">
+      <c r="E10" s="84">
         <v>180</v>
       </c>
-      <c r="F10" s="81">
+      <c r="F10" s="76">
         <v>28</v>
       </c>
-      <c r="G10" s="82">
+      <c r="G10" s="77">
         <v>14</v>
       </c>
-      <c r="H10" s="83">
+      <c r="H10" s="78">
         <v>9</v>
       </c>
-      <c r="I10" s="84">
+      <c r="I10" s="79">
         <v>0</v>
       </c>
-      <c r="J10" s="84">
+      <c r="J10" s="79">
         <v>1.3952</v>
       </c>
-      <c r="K10" s="85">
+      <c r="K10" s="80">
         <v>0</v>
       </c>
-      <c r="L10" s="86">
+      <c r="L10" s="81">
         <v>1.268</v>
       </c>
-      <c r="M10" s="84">
+      <c r="M10" s="79">
         <v>0</v>
       </c>
-      <c r="N10" s="84">
+      <c r="N10" s="79">
         <v>1.18</v>
       </c>
-      <c r="O10" s="87" t="s">
+      <c r="O10" s="82" t="s">
         <v>52</v>
       </c>
-      <c r="P10" s="88"/>
-      <c r="Q10" s="88"/>
+      <c r="P10" s="83"/>
+      <c r="Q10" s="83"/>
     </row>
     <row r="11" spans="1:20">
-      <c r="C11" s="90">
+      <c r="C11" s="85">
         <v>1897.5</v>
       </c>
-      <c r="D11" s="90">
+      <c r="D11" s="85">
         <v>715</v>
       </c>
-      <c r="E11" s="90">
+      <c r="E11" s="85">
         <v>300</v>
       </c>
-      <c r="F11" s="72">
+      <c r="F11" s="67">
         <v>41</v>
       </c>
-      <c r="G11" s="73">
+      <c r="G11" s="68">
         <v>17</v>
       </c>
-      <c r="H11" s="74">
+      <c r="H11" s="69">
         <v>15</v>
       </c>
-      <c r="I11" s="75">
+      <c r="I11" s="70">
         <v>0</v>
       </c>
-      <c r="J11" s="75">
+      <c r="J11" s="70">
         <v>1.3952</v>
       </c>
-      <c r="K11" s="76">
+      <c r="K11" s="71">
         <v>0</v>
       </c>
-      <c r="L11" s="77">
+      <c r="L11" s="72">
         <v>1.268</v>
       </c>
-      <c r="M11" s="75">
+      <c r="M11" s="70">
         <v>0</v>
       </c>
-      <c r="N11" s="75">
+      <c r="N11" s="70">
         <v>1.2</v>
       </c>
-      <c r="O11" s="78" t="s">
+      <c r="O11" s="73" t="s">
         <v>53</v>
       </c>
-      <c r="P11" s="79"/>
-      <c r="Q11" s="79"/>
+      <c r="P11" s="74"/>
+      <c r="Q11" s="74"/>
     </row>
     <row r="12" spans="1:20">
-      <c r="C12" s="89">
-        <v>3332.08823529412</v>
-      </c>
-      <c r="D12" s="89">
+      <c r="C12" s="84">
+        <v>3332.0882352941198</v>
+      </c>
+      <c r="D12" s="84">
         <v>1421.39215686275</v>
       </c>
-      <c r="E12" s="89">
+      <c r="E12" s="84">
         <v>600</v>
       </c>
-      <c r="F12" s="81">
-        <v>55.825</v>
-      </c>
-      <c r="G12" s="82">
+      <c r="F12" s="76">
+        <v>55.825000000000003</v>
+      </c>
+      <c r="G12" s="77">
         <v>36.18</v>
       </c>
-      <c r="H12" s="83">
+      <c r="H12" s="78">
         <v>39</v>
       </c>
-      <c r="I12" s="84">
-        <v>1.99666703875969</v>
-      </c>
-      <c r="J12" s="84">
-        <v>0.83712</v>
-      </c>
-      <c r="K12" s="85">
+      <c r="I12" s="79">
+        <v>1.9966670387596901</v>
+      </c>
+      <c r="J12" s="79">
+        <v>0.83711999999999998</v>
+      </c>
+      <c r="K12" s="80">
         <v>1.45562727909392</v>
       </c>
-      <c r="L12" s="86">
-        <v>0.7608</v>
-      </c>
-      <c r="M12" s="84">
-        <v>0.333333333333333</v>
-      </c>
-      <c r="N12" s="84">
-        <v>0.708</v>
-      </c>
-      <c r="O12" s="87" t="s">
+      <c r="L12" s="81">
+        <v>0.76080000000000003</v>
+      </c>
+      <c r="M12" s="79">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="N12" s="79">
+        <v>0.70799999999999996</v>
+      </c>
+      <c r="O12" s="82" t="s">
         <v>54</v>
       </c>
-      <c r="P12" s="88"/>
-      <c r="Q12" s="88"/>
+      <c r="P12" s="83"/>
+      <c r="Q12" s="83"/>
     </row>
     <row r="13" spans="1:20">
-      <c r="C13" s="90">
-        <v>5331.34117647059</v>
-      </c>
-      <c r="D13" s="90">
-        <v>2920.89411764706</v>
-      </c>
-      <c r="E13" s="90">
+      <c r="C13" s="85">
+        <v>5331.3411764705897</v>
+      </c>
+      <c r="D13" s="85">
+        <v>2920.8941176470598</v>
+      </c>
+      <c r="E13" s="85">
         <v>1100</v>
       </c>
-      <c r="F13" s="72">
-        <v>94.9025</v>
-      </c>
-      <c r="G13" s="73">
-        <v>63.315</v>
-      </c>
-      <c r="H13" s="74">
+      <c r="F13" s="67">
+        <v>94.902500000000003</v>
+      </c>
+      <c r="G13" s="68">
+        <v>63.314999999999998</v>
+      </c>
+      <c r="H13" s="69">
         <v>48.75</v>
       </c>
-      <c r="I13" s="75">
-        <v>1.99666703875969</v>
-      </c>
-      <c r="J13" s="75">
-        <v>0.83712</v>
-      </c>
-      <c r="K13" s="76">
+      <c r="I13" s="70">
+        <v>1.9966670387596901</v>
+      </c>
+      <c r="J13" s="70">
+        <v>0.83711999999999998</v>
+      </c>
+      <c r="K13" s="71">
         <v>1.45562727909392</v>
       </c>
-      <c r="L13" s="77">
-        <v>0.7608</v>
-      </c>
-      <c r="M13" s="75">
-        <v>0.333333333333333</v>
-      </c>
-      <c r="N13" s="75">
+      <c r="L13" s="72">
+        <v>0.76080000000000003</v>
+      </c>
+      <c r="M13" s="70">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="N13" s="70">
         <v>0.72</v>
       </c>
-      <c r="O13" s="78" t="s">
+      <c r="O13" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="P13" s="79"/>
-      <c r="Q13" s="79"/>
+      <c r="P13" s="74"/>
+      <c r="Q13" s="74"/>
     </row>
     <row r="14" spans="1:20">
-      <c r="C14" s="91">
+      <c r="C14" s="86">
         <v>1200</v>
       </c>
-      <c r="D14" s="91">
+      <c r="D14" s="86">
         <v>733</v>
       </c>
-      <c r="E14" s="91">
+      <c r="E14" s="86">
         <v>263</v>
       </c>
-      <c r="F14" s="92">
+      <c r="F14" s="87">
         <v>42</v>
       </c>
-      <c r="G14" s="93">
+      <c r="G14" s="88">
         <v>22</v>
       </c>
-      <c r="H14" s="94">
+      <c r="H14" s="89">
         <v>9</v>
       </c>
-      <c r="I14" s="95">
+      <c r="I14" s="90">
         <v>0</v>
       </c>
-      <c r="J14" s="96">
+      <c r="J14" s="91">
         <v>0.01</v>
       </c>
-      <c r="K14" s="97">
+      <c r="K14" s="92">
         <v>0</v>
       </c>
-      <c r="L14" s="98">
+      <c r="L14" s="93">
         <v>0.01</v>
       </c>
-      <c r="M14" s="96">
+      <c r="M14" s="91">
         <v>0</v>
       </c>
-      <c r="N14" s="96">
+      <c r="N14" s="91">
         <v>0.01</v>
       </c>
-      <c r="O14" s="99" t="s">
+      <c r="O14" s="94" t="s">
         <v>56</v>
       </c>
-      <c r="P14" s="100"/>
-      <c r="Q14" s="100"/>
+      <c r="P14" s="95"/>
+      <c r="Q14" s="95"/>
     </row>
     <row r="15" spans="1:20">
-      <c r="C15" s="101">
+      <c r="C15" s="96">
         <v>450</v>
       </c>
-      <c r="D15" s="101">
+      <c r="D15" s="96">
         <v>450</v>
       </c>
-      <c r="E15" s="101">
+      <c r="E15" s="96">
         <v>450</v>
       </c>
-      <c r="F15" s="102">
+      <c r="F15" s="97">
         <v>18</v>
       </c>
-      <c r="G15" s="103">
+      <c r="G15" s="98">
         <v>18</v>
       </c>
-      <c r="H15" s="104">
+      <c r="H15" s="99">
         <v>18</v>
       </c>
-      <c r="I15" s="105">
+      <c r="I15" s="100">
         <v>0.265822784810126</v>
       </c>
-      <c r="J15" s="106">
+      <c r="J15" s="101">
         <v>0.06</v>
       </c>
-      <c r="K15" s="107">
+      <c r="K15" s="102">
         <v>0.265822784810126</v>
       </c>
-      <c r="L15" s="108">
+      <c r="L15" s="103">
         <v>0.06</v>
       </c>
-      <c r="M15" s="106">
+      <c r="M15" s="101">
         <v>0.265822784810126</v>
       </c>
-      <c r="N15" s="106">
+      <c r="N15" s="101">
         <v>0.06</v>
       </c>
-      <c r="O15" s="109" t="s">
+      <c r="O15" s="104" t="s">
         <v>57</v>
       </c>
-      <c r="P15" s="110"/>
-      <c r="Q15" s="110"/>
+      <c r="P15" s="105"/>
+      <c r="Q15" s="105"/>
     </row>
     <row r="16" spans="1:20">
-      <c r="C16" s="111">
+      <c r="C16" s="106">
         <v>200</v>
       </c>
-      <c r="D16" s="111">
+      <c r="D16" s="106">
         <v>200</v>
       </c>
-      <c r="E16" s="111">
+      <c r="E16" s="106">
         <v>200</v>
       </c>
-      <c r="F16" s="112">
+      <c r="F16" s="107">
         <v>20</v>
       </c>
-      <c r="G16" s="113">
+      <c r="G16" s="108">
         <v>20</v>
       </c>
-      <c r="H16" s="114">
+      <c r="H16" s="109">
         <v>20</v>
       </c>
-      <c r="I16" s="115">
-        <v>0.013</v>
-      </c>
-      <c r="J16" s="116">
-        <v>0.036</v>
-      </c>
-      <c r="K16" s="117">
-        <v>0.013</v>
-      </c>
-      <c r="L16" s="118">
-        <v>0.036</v>
-      </c>
-      <c r="M16" s="116">
-        <v>0.013</v>
-      </c>
-      <c r="N16" s="116">
-        <v>0.036</v>
-      </c>
-      <c r="O16" s="119" t="s">
+      <c r="I16" s="110">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="J16" s="111">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="K16" s="112">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="L16" s="113">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="M16" s="111">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="N16" s="111">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="O16" s="114" t="s">
         <v>58</v>
       </c>
-      <c r="P16" s="120"/>
-      <c r="Q16" s="120"/>
+      <c r="P16" s="115"/>
+      <c r="Q16" s="115"/>
     </row>
     <row r="17" spans="1:25">
-      <c r="C17" s="101">
+      <c r="C17" s="96">
         <v>175</v>
       </c>
-      <c r="D17" s="101">
+      <c r="D17" s="96">
         <v>175</v>
       </c>
-      <c r="E17" s="101">
+      <c r="E17" s="96">
         <v>175</v>
       </c>
-      <c r="F17" s="102">
+      <c r="F17" s="97">
         <v>5</v>
       </c>
-      <c r="G17" s="103">
+      <c r="G17" s="98">
         <v>5</v>
       </c>
-      <c r="H17" s="104">
+      <c r="H17" s="99">
         <v>5</v>
       </c>
-      <c r="I17" s="105">
-        <v>0.014</v>
-      </c>
-      <c r="J17" s="106">
+      <c r="I17" s="100">
+        <v>1.4E-2</v>
+      </c>
+      <c r="J17" s="101">
         <v>0</v>
       </c>
-      <c r="K17" s="107">
-        <v>0.014</v>
-      </c>
-      <c r="L17" s="108">
+      <c r="K17" s="102">
+        <v>1.4E-2</v>
+      </c>
+      <c r="L17" s="103">
         <v>0</v>
       </c>
-      <c r="M17" s="106">
-        <v>0.014</v>
-      </c>
-      <c r="N17" s="106">
+      <c r="M17" s="101">
+        <v>1.4E-2</v>
+      </c>
+      <c r="N17" s="101">
         <v>0</v>
       </c>
-      <c r="O17" s="109" t="s">
+      <c r="O17" s="104" t="s">
         <v>59</v>
       </c>
-      <c r="P17" s="110"/>
-      <c r="Q17" s="110"/>
+      <c r="P17" s="105"/>
+      <c r="Q17" s="105"/>
     </row>
     <row r="18" spans="1:25">
-      <c r="C18" s="121">
+      <c r="C18" s="116">
         <v>1000</v>
       </c>
-      <c r="D18" s="121">
+      <c r="D18" s="116">
         <v>720</v>
       </c>
-      <c r="E18" s="121">
+      <c r="E18" s="116">
         <v>364</v>
       </c>
-      <c r="F18" s="122">
+      <c r="F18" s="117">
         <v>50</v>
       </c>
-      <c r="G18" s="123">
+      <c r="G18" s="118">
         <v>31</v>
       </c>
-      <c r="H18" s="124">
+      <c r="H18" s="119">
         <v>18</v>
       </c>
-      <c r="I18" s="125">
+      <c r="I18" s="120">
         <v>0.2389</v>
       </c>
-      <c r="J18" s="126">
-        <v>0.03056</v>
-      </c>
-      <c r="K18" s="127">
+      <c r="J18" s="121">
+        <v>3.056E-2</v>
+      </c>
+      <c r="K18" s="122">
         <v>0.2389</v>
       </c>
-      <c r="L18" s="128">
-        <v>0.03056</v>
-      </c>
-      <c r="M18" s="126">
+      <c r="L18" s="123">
+        <v>3.056E-2</v>
+      </c>
+      <c r="M18" s="121">
         <v>0.2389</v>
       </c>
-      <c r="N18" s="126">
-        <v>0.03056</v>
-      </c>
-      <c r="O18" s="129" t="s">
+      <c r="N18" s="121">
+        <v>3.056E-2</v>
+      </c>
+      <c r="O18" s="124" t="s">
         <v>60</v>
       </c>
-      <c r="P18" s="130"/>
-      <c r="Q18" s="130"/>
+      <c r="P18" s="125"/>
+      <c r="Q18" s="125"/>
     </row>
     <row r="19" spans="1:25">
-      <c r="C19" s="131">
+      <c r="C19" s="126">
         <v>1556</v>
       </c>
-      <c r="D19" s="131">
+      <c r="D19" s="126">
         <v>1143</v>
       </c>
-      <c r="E19" s="132">
+      <c r="E19" s="127">
         <v>673</v>
       </c>
-      <c r="F19" s="133">
+      <c r="F19" s="128">
         <v>54</v>
       </c>
-      <c r="G19" s="134">
+      <c r="G19" s="129">
         <v>40</v>
       </c>
-      <c r="H19" s="135">
+      <c r="H19" s="130">
         <v>24</v>
       </c>
-      <c r="I19" s="136">
-        <v>0.035</v>
-      </c>
-      <c r="J19" s="137">
+      <c r="I19" s="131">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="J19" s="132">
         <v>0.02</v>
       </c>
-      <c r="K19" s="138">
-        <v>0.035</v>
-      </c>
-      <c r="L19" s="139">
+      <c r="K19" s="133">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="L19" s="134">
         <v>0.02</v>
       </c>
-      <c r="M19" s="137">
-        <v>0.035</v>
-      </c>
-      <c r="N19" s="137">
+      <c r="M19" s="132">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="N19" s="132">
         <v>0.02</v>
       </c>
-      <c r="O19" s="140" t="s">
+      <c r="O19" s="135" t="s">
         <v>61</v>
       </c>
-      <c r="P19" s="141"/>
-      <c r="Q19" s="141"/>
+      <c r="P19" s="136"/>
+      <c r="Q19" s="136"/>
     </row>
     <row r="20" spans="1:25">
-      <c r="C20" s="142">
+      <c r="C20" s="137">
         <v>2332</v>
       </c>
-      <c r="D20" s="142">
+      <c r="D20" s="137">
         <v>1511</v>
       </c>
-      <c r="E20" s="142">
+      <c r="E20" s="137">
         <v>965</v>
       </c>
-      <c r="F20" s="143">
+      <c r="F20" s="138">
         <v>163</v>
       </c>
-      <c r="G20" s="144">
+      <c r="G20" s="139">
         <v>106</v>
       </c>
-      <c r="H20" s="145">
+      <c r="H20" s="140">
         <v>68</v>
       </c>
-      <c r="I20" s="146">
-        <v>0.463266666666667</v>
-      </c>
-      <c r="J20" s="147">
+      <c r="I20" s="141">
+        <v>0.46326666666666699</v>
+      </c>
+      <c r="J20" s="142">
         <v>1.91881040892193</v>
       </c>
-      <c r="K20" s="148">
-        <v>0.39244195142278</v>
-      </c>
-      <c r="L20" s="149">
+      <c r="K20" s="143">
+        <v>0.39244195142277999</v>
+      </c>
+      <c r="L20" s="144">
         <v>1.60098120886331</v>
       </c>
-      <c r="M20" s="147">
+      <c r="M20" s="142">
         <v>0.37890902062421</v>
       </c>
-      <c r="N20" s="147">
-        <v>1.56940834539103</v>
-      </c>
-      <c r="O20" s="150" t="s">
+      <c r="N20" s="142">
+        <v>1.5694083453910299</v>
+      </c>
+      <c r="O20" s="145" t="s">
         <v>62</v>
       </c>
-      <c r="P20" s="130"/>
-      <c r="Q20" s="130"/>
+      <c r="P20" s="125"/>
+      <c r="Q20" s="125"/>
     </row>
     <row r="21" spans="1:25">
-      <c r="C21" s="151">
-        <v>769.876819708847</v>
-      </c>
-      <c r="D21" s="151">
-        <v>648.044461034383</v>
-      </c>
-      <c r="E21" s="151">
-        <v>518.290592438013</v>
-      </c>
-      <c r="F21" s="152">
+      <c r="C21" s="146">
+        <v>769.87681970884705</v>
+      </c>
+      <c r="D21" s="146">
+        <v>648.04446103438295</v>
+      </c>
+      <c r="E21" s="146">
+        <v>518.29059243801305</v>
+      </c>
+      <c r="F21" s="147">
         <v>26.9456886898096</v>
       </c>
-      <c r="G21" s="153">
-        <v>22.6815561362034</v>
-      </c>
-      <c r="H21" s="154">
+      <c r="G21" s="148">
+        <v>22.681556136203401</v>
+      </c>
+      <c r="H21" s="149">
         <v>18.1401707353305</v>
       </c>
-      <c r="I21" s="155">
-        <v>2.77777777777778</v>
-      </c>
-      <c r="J21" s="156">
-        <v>2.22222222222222</v>
-      </c>
-      <c r="K21" s="157">
-        <v>1.66666666666667</v>
-      </c>
-      <c r="L21" s="158">
-        <v>1.38888888888889</v>
-      </c>
-      <c r="M21" s="156">
-        <v>1.13888888888889</v>
-      </c>
-      <c r="N21" s="156">
+      <c r="I21" s="150">
+        <v>2.7777777777777799</v>
+      </c>
+      <c r="J21" s="151">
+        <v>2.2222222222222201</v>
+      </c>
+      <c r="K21" s="152">
+        <v>1.6666666666666701</v>
+      </c>
+      <c r="L21" s="153">
+        <v>1.3888888888888899</v>
+      </c>
+      <c r="M21" s="151">
+        <v>1.1388888888888899</v>
+      </c>
+      <c r="N21" s="151">
         <v>0.3</v>
       </c>
-      <c r="O21" s="159" t="s">
+      <c r="O21" s="154" t="s">
         <v>63</v>
       </c>
-      <c r="P21" s="160"/>
-      <c r="Q21" s="160"/>
+      <c r="P21" s="155"/>
+      <c r="Q21" s="155"/>
     </row>
     <row r="22" spans="1:25">
-      <c r="C22" s="161">
-        <v>1259.79843225084</v>
-      </c>
-      <c r="D22" s="161">
-        <v>894.301356227448</v>
-      </c>
-      <c r="E22" s="161">
+      <c r="C22" s="156">
+        <v>1259.7984322508401</v>
+      </c>
+      <c r="D22" s="156">
+        <v>894.30135622744797</v>
+      </c>
+      <c r="E22" s="156">
         <v>495</v>
       </c>
-      <c r="F22" s="162">
-        <v>44.0929451287794</v>
-      </c>
-      <c r="G22" s="163">
-        <v>31.3005474679607</v>
-      </c>
-      <c r="H22" s="164">
-        <v>17.325</v>
-      </c>
-      <c r="I22" s="165">
+      <c r="F22" s="157">
+        <v>44.092945128779398</v>
+      </c>
+      <c r="G22" s="158">
+        <v>31.300547467960701</v>
+      </c>
+      <c r="H22" s="159">
+        <v>17.324999999999999</v>
+      </c>
+      <c r="I22" s="160">
         <v>2</v>
       </c>
-      <c r="J22" s="166">
+      <c r="J22" s="161">
         <v>0.3</v>
       </c>
-      <c r="K22" s="167">
+      <c r="K22" s="162">
         <v>1.80555555555556</v>
       </c>
-      <c r="L22" s="168">
+      <c r="L22" s="163">
         <v>0.3</v>
       </c>
-      <c r="M22" s="166">
+      <c r="M22" s="161">
         <v>1.5</v>
       </c>
-      <c r="N22" s="166">
+      <c r="N22" s="161">
         <v>0.3</v>
       </c>
-      <c r="O22" s="169" t="s">
+      <c r="O22" s="164" t="s">
         <v>64</v>
       </c>
-      <c r="P22" s="170"/>
-      <c r="Q22" s="170"/>
+      <c r="P22" s="165"/>
+      <c r="Q22" s="165"/>
     </row>
     <row r="23" spans="1:25">
-      <c r="C23" s="171">
+      <c r="C23" s="166">
         <v>174</v>
       </c>
-      <c r="D23" s="171">
+      <c r="D23" s="166">
         <v>174</v>
       </c>
-      <c r="E23" s="171">
+      <c r="E23" s="166">
         <v>174</v>
       </c>
-      <c r="F23" s="172">
+      <c r="F23" s="167">
         <v>3</v>
       </c>
-      <c r="G23" s="173">
+      <c r="G23" s="168">
         <v>3</v>
       </c>
-      <c r="H23" s="174">
+      <c r="H23" s="169">
         <v>3</v>
       </c>
-      <c r="I23" s="175">
+      <c r="I23" s="170">
         <v>0</v>
       </c>
-      <c r="J23" s="176">
-        <v>0.205882352941176</v>
-      </c>
-      <c r="K23" s="177">
+      <c r="J23" s="171">
+        <v>0.20588235294117599</v>
+      </c>
+      <c r="K23" s="172">
         <v>0</v>
       </c>
-      <c r="L23" s="178">
-        <v>0.205882352941176</v>
-      </c>
-      <c r="M23" s="176">
+      <c r="L23" s="173">
+        <v>0.20588235294117599</v>
+      </c>
+      <c r="M23" s="171">
         <v>0</v>
       </c>
-      <c r="N23" s="176">
-        <v>0.205882352941176</v>
-      </c>
-      <c r="O23" s="179" t="s">
+      <c r="N23" s="171">
+        <v>0.20588235294117599</v>
+      </c>
+      <c r="O23" s="174" t="s">
         <v>65</v>
       </c>
-      <c r="P23" s="160"/>
-      <c r="Q23" s="160"/>
-    </row>
-    <row r="26" ht="17.75" spans="1:25">
+      <c r="P23" s="155"/>
+      <c r="Q23" s="155"/>
+    </row>
+    <row r="26" spans="1:25" ht="16.899999999999999">
       <c r="C26" s="53" t="s">
         <v>66</v>
       </c>
@@ -4556,7 +4047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" ht="15.25" spans="1:25">
+    <row r="27" spans="1:25">
       <c r="A27" s="54" t="s">
         <v>4</v>
       </c>
@@ -4679,7 +4170,7 @@
       </c>
       <c r="J28" s="9">
         <f t="shared" si="2"/>
-        <v>0.094</v>
+        <v>9.4E-2</v>
       </c>
       <c r="K28" s="9">
         <f t="shared" si="2"/>
@@ -4687,7 +4178,7 @@
       </c>
       <c r="L28" s="9">
         <f t="shared" si="2"/>
-        <v>0.094</v>
+        <v>9.4E-2</v>
       </c>
       <c r="M28" s="9">
         <f t="shared" si="2"/>
@@ -4695,16 +4186,16 @@
       </c>
       <c r="N28" s="9">
         <f t="shared" si="2"/>
-        <v>0.094</v>
-      </c>
-      <c r="O28" s="180" t="s">
+        <v>9.4E-2</v>
+      </c>
+      <c r="O28" s="175" t="s">
         <v>70</v>
       </c>
       <c r="P28">
         <v>25</v>
       </c>
       <c r="Q28">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="S28" t="str">
         <f>IF(O28="","*","PRE")</f>
@@ -4766,25 +4257,25 @@
         <f t="shared" si="4"/>
         <v>1.33</v>
       </c>
-      <c r="J29" s="181">
+      <c r="J29" s="176">
         <f t="shared" si="4"/>
-        <v>1.094</v>
+        <v>1.0940000000000001</v>
       </c>
       <c r="K29" s="9">
         <f t="shared" si="4"/>
         <v>1.3</v>
       </c>
-      <c r="L29" s="181">
+      <c r="L29" s="176">
         <f t="shared" si="4"/>
-        <v>1.094</v>
+        <v>1.0940000000000001</v>
       </c>
       <c r="M29" s="9">
         <f t="shared" si="4"/>
         <v>1.28</v>
       </c>
-      <c r="N29" s="181">
+      <c r="N29" s="176">
         <f t="shared" si="4"/>
-        <v>1.094</v>
+        <v>1.0940000000000001</v>
       </c>
       <c r="O29" t="s">
         <v>73</v>
@@ -4793,7 +4284,7 @@
         <v>25</v>
       </c>
       <c r="Q29">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="S29" t="str">
         <f t="shared" ref="S29:S39" si="5">IF(O29="","*","PRE")</f>
@@ -4857,7 +4348,7 @@
       </c>
       <c r="J30" s="9">
         <f t="shared" si="7"/>
-        <v>0.094</v>
+        <v>9.4E-2</v>
       </c>
       <c r="K30" s="9">
         <f t="shared" si="7"/>
@@ -4865,7 +4356,7 @@
       </c>
       <c r="L30" s="9">
         <f t="shared" si="7"/>
-        <v>0.094</v>
+        <v>9.4E-2</v>
       </c>
       <c r="M30" s="9">
         <f t="shared" si="7"/>
@@ -4873,9 +4364,9 @@
       </c>
       <c r="N30" s="9">
         <f t="shared" si="7"/>
-        <v>0.094</v>
-      </c>
-      <c r="O30" s="180" t="s">
+        <v>9.4E-2</v>
+      </c>
+      <c r="O30" s="175" t="s">
         <v>70</v>
       </c>
       <c r="S30" t="str">
@@ -4956,7 +4447,7 @@
         <v>25</v>
       </c>
       <c r="Q31">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="S31" t="str">
         <f t="shared" si="5"/>
@@ -5029,7 +4520,7 @@
         <f t="shared" si="9"/>
         <v>1.19</v>
       </c>
-      <c r="O32" s="180" t="s">
+      <c r="O32" s="175" t="s">
         <v>70</v>
       </c>
       <c r="S32" t="str">
@@ -5110,7 +4601,7 @@
         <v>25</v>
       </c>
       <c r="Q33">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="S33" t="str">
         <f t="shared" si="5"/>
@@ -5183,7 +4674,7 @@
         <f t="shared" si="11"/>
         <v>1.2</v>
       </c>
-      <c r="O34" s="180" t="s">
+      <c r="O34" s="175" t="s">
         <v>70</v>
       </c>
       <c r="S34" t="str">
@@ -5220,7 +4711,7 @@
       </c>
       <c r="C35" s="38">
         <f t="shared" ref="C35:N35" si="12">C12</f>
-        <v>3332.08823529412</v>
+        <v>3332.0882352941198</v>
       </c>
       <c r="D35" s="38">
         <f t="shared" si="12"/>
@@ -5232,7 +4723,7 @@
       </c>
       <c r="F35" s="38">
         <f t="shared" si="12"/>
-        <v>55.825</v>
+        <v>55.825000000000003</v>
       </c>
       <c r="G35" s="38">
         <f t="shared" si="12"/>
@@ -5244,11 +4735,11 @@
       </c>
       <c r="I35" s="9">
         <f t="shared" si="12"/>
-        <v>1.99666703875969</v>
+        <v>1.9966670387596901</v>
       </c>
       <c r="J35" s="9">
         <f t="shared" si="12"/>
-        <v>0.83712</v>
+        <v>0.83711999999999998</v>
       </c>
       <c r="K35" s="9">
         <f t="shared" si="12"/>
@@ -5256,15 +4747,15 @@
       </c>
       <c r="L35" s="9">
         <f t="shared" si="12"/>
-        <v>0.7608</v>
+        <v>0.76080000000000003</v>
       </c>
       <c r="M35" s="9">
         <f t="shared" si="12"/>
-        <v>0.333333333333333</v>
+        <v>0.33333333333333298</v>
       </c>
       <c r="N35" s="9">
         <f t="shared" si="12"/>
-        <v>0.708</v>
+        <v>0.70799999999999996</v>
       </c>
       <c r="O35" t="s">
         <v>76</v>
@@ -5273,7 +4764,7 @@
         <v>25</v>
       </c>
       <c r="Q35">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="S35" t="str">
         <f t="shared" si="5"/>
@@ -5303,11 +4794,11 @@
     <row r="36" spans="1:25">
       <c r="C36" s="38">
         <f t="shared" ref="C36:N36" si="13">C13</f>
-        <v>5331.34117647059</v>
+        <v>5331.3411764705897</v>
       </c>
       <c r="D36" s="38">
         <f t="shared" si="13"/>
-        <v>2920.89411764706</v>
+        <v>2920.8941176470598</v>
       </c>
       <c r="E36" s="38">
         <f t="shared" si="13"/>
@@ -5315,11 +4806,11 @@
       </c>
       <c r="F36" s="38">
         <f t="shared" si="13"/>
-        <v>94.9025</v>
+        <v>94.902500000000003</v>
       </c>
       <c r="G36" s="38">
         <f t="shared" si="13"/>
-        <v>63.315</v>
+        <v>63.314999999999998</v>
       </c>
       <c r="H36" s="38">
         <f t="shared" si="13"/>
@@ -5327,11 +4818,11 @@
       </c>
       <c r="I36" s="9">
         <f t="shared" si="13"/>
-        <v>1.99666703875969</v>
+        <v>1.9966670387596901</v>
       </c>
       <c r="J36" s="9">
         <f t="shared" si="13"/>
-        <v>0.83712</v>
+        <v>0.83711999999999998</v>
       </c>
       <c r="K36" s="9">
         <f t="shared" si="13"/>
@@ -5339,17 +4830,17 @@
       </c>
       <c r="L36" s="9">
         <f t="shared" si="13"/>
-        <v>0.7608</v>
+        <v>0.76080000000000003</v>
       </c>
       <c r="M36" s="9">
         <f t="shared" si="13"/>
-        <v>0.333333333333333</v>
+        <v>0.33333333333333298</v>
       </c>
       <c r="N36" s="9">
         <f t="shared" si="13"/>
         <v>0.72</v>
       </c>
-      <c r="O36" s="180" t="s">
+      <c r="O36" s="175" t="s">
         <v>70</v>
       </c>
       <c r="S36" t="str">
@@ -5380,15 +4871,15 @@
     <row r="37" spans="1:25">
       <c r="C37" s="38">
         <f t="shared" ref="C37:N37" si="14">C21</f>
-        <v>769.876819708847</v>
+        <v>769.87681970884705</v>
       </c>
       <c r="D37" s="38">
         <f t="shared" si="14"/>
-        <v>648.044461034383</v>
+        <v>648.04446103438295</v>
       </c>
       <c r="E37" s="38">
         <f t="shared" si="14"/>
-        <v>518.290592438013</v>
+        <v>518.29059243801305</v>
       </c>
       <c r="F37" s="38">
         <f t="shared" si="14"/>
@@ -5396,7 +4887,7 @@
       </c>
       <c r="G37" s="38">
         <f t="shared" si="14"/>
-        <v>22.6815561362034</v>
+        <v>22.681556136203401</v>
       </c>
       <c r="H37" s="38">
         <f t="shared" si="14"/>
@@ -5404,29 +4895,29 @@
       </c>
       <c r="I37" s="9">
         <f t="shared" si="14"/>
-        <v>2.77777777777778</v>
+        <v>2.7777777777777799</v>
       </c>
       <c r="J37" s="9">
         <f t="shared" si="14"/>
-        <v>2.22222222222222</v>
+        <v>2.2222222222222201</v>
       </c>
       <c r="K37" s="9">
         <f t="shared" si="14"/>
-        <v>1.66666666666667</v>
+        <v>1.6666666666666701</v>
       </c>
       <c r="L37" s="9">
         <f t="shared" si="14"/>
-        <v>1.38888888888889</v>
+        <v>1.3888888888888899</v>
       </c>
       <c r="M37" s="9">
         <f t="shared" si="14"/>
-        <v>1.13888888888889</v>
+        <v>1.1388888888888899</v>
       </c>
       <c r="N37" s="9">
         <f t="shared" si="14"/>
         <v>0.3</v>
       </c>
-      <c r="O37" s="180" t="s">
+      <c r="O37" s="175" t="s">
         <v>70</v>
       </c>
       <c r="S37" t="str">
@@ -5457,11 +4948,11 @@
     <row r="38" spans="1:25">
       <c r="C38" s="38">
         <f t="shared" ref="C38:N38" si="15">C22</f>
-        <v>1259.79843225084</v>
+        <v>1259.7984322508401</v>
       </c>
       <c r="D38" s="38">
         <f t="shared" si="15"/>
-        <v>894.301356227448</v>
+        <v>894.30135622744797</v>
       </c>
       <c r="E38" s="38">
         <f t="shared" si="15"/>
@@ -5469,15 +4960,15 @@
       </c>
       <c r="F38" s="38">
         <f t="shared" si="15"/>
-        <v>44.0929451287794</v>
+        <v>44.092945128779398</v>
       </c>
       <c r="G38" s="38">
         <f t="shared" si="15"/>
-        <v>31.3005474679607</v>
+        <v>31.300547467960701</v>
       </c>
       <c r="H38" s="38">
         <f t="shared" si="15"/>
-        <v>17.325</v>
+        <v>17.324999999999999</v>
       </c>
       <c r="I38" s="9">
         <f t="shared" si="15"/>
@@ -5503,7 +4994,7 @@
         <f t="shared" si="15"/>
         <v>0.3</v>
       </c>
-      <c r="O38" s="180" t="s">
+      <c r="O38" s="175" t="s">
         <v>70</v>
       </c>
       <c r="S38" t="str">
@@ -5532,77 +5023,77 @@
       </c>
     </row>
     <row r="39" spans="1:25">
-      <c r="A39" s="182" t="str">
+      <c r="A39" s="177" t="str">
         <f>A35</f>
         <v>HH2</v>
       </c>
-      <c r="B39" s="182" t="s">
+      <c r="B39" s="177" t="s">
         <v>69</v>
       </c>
-      <c r="C39" s="183">
+      <c r="C39" s="178">
         <f>C29</f>
         <v>900</v>
       </c>
-      <c r="D39" s="183">
+      <c r="D39" s="178">
         <f t="shared" ref="D39:H39" si="16">D29</f>
         <v>850</v>
       </c>
-      <c r="E39" s="183">
+      <c r="E39" s="178">
         <f t="shared" si="16"/>
         <v>800</v>
       </c>
-      <c r="F39" s="183">
+      <c r="F39" s="178">
         <f t="shared" si="16"/>
         <v>36</v>
       </c>
-      <c r="G39" s="183">
+      <c r="G39" s="178">
         <f t="shared" si="16"/>
         <v>34</v>
       </c>
-      <c r="H39" s="183">
+      <c r="H39" s="178">
         <f t="shared" si="16"/>
         <v>32</v>
       </c>
-      <c r="I39" s="184">
+      <c r="I39" s="179">
         <v>1.25</v>
       </c>
-      <c r="J39" s="184">
+      <c r="J39" s="179">
         <v>0.12</v>
       </c>
-      <c r="K39" s="184">
+      <c r="K39" s="179">
         <v>1.25</v>
       </c>
-      <c r="L39" s="184">
+      <c r="L39" s="179">
         <v>0.12</v>
       </c>
-      <c r="M39" s="184">
+      <c r="M39" s="179">
         <v>1.25</v>
       </c>
-      <c r="N39" s="184">
+      <c r="N39" s="179">
         <v>0.12</v>
       </c>
-      <c r="O39" s="182" t="s">
+      <c r="O39" s="177" t="s">
         <v>77</v>
       </c>
-      <c r="P39" s="182">
+      <c r="P39" s="177">
         <v>25</v>
       </c>
-      <c r="Q39" s="182">
-        <v>31.536</v>
-      </c>
-      <c r="R39" s="182"/>
-      <c r="S39" s="182" t="str">
+      <c r="Q39" s="177">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="R39" s="177"/>
+      <c r="S39" s="177" t="str">
         <f t="shared" si="5"/>
         <v>PRE</v>
       </c>
-      <c r="T39" s="182" t="str">
+      <c r="T39" s="177" t="str">
         <f t="shared" si="6"/>
         <v>H2prd_Gas_ATR_CCS</v>
       </c>
-      <c r="U39" s="182" t="s">
+      <c r="U39" s="177" t="s">
         <v>78</v>
       </c>
-      <c r="V39" s="182" t="s">
+      <c r="V39" s="177" t="s">
         <v>71</v>
       </c>
       <c r="W39" t="s">
@@ -5623,39 +5114,37 @@
     <mergeCell ref="O1:O4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B3:Q12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9" style="52"/>
-    <col min="2" max="2" width="12.8636363636364" style="52" customWidth="1"/>
-    <col min="3" max="3" width="8.86363636363636" style="52" customWidth="1"/>
-    <col min="4" max="4" width="14.8636363636364" style="52" customWidth="1"/>
+    <col min="2" max="2" width="12.86328125" style="52" customWidth="1"/>
+    <col min="3" max="3" width="8.86328125" style="52" customWidth="1"/>
+    <col min="4" max="4" width="14.86328125" style="52" customWidth="1"/>
     <col min="5" max="5" width="9" style="52" customWidth="1"/>
-    <col min="6" max="6" width="10.2636363636364" style="52" customWidth="1"/>
-    <col min="7" max="7" width="4.6" style="52" customWidth="1"/>
-    <col min="8" max="8" width="11.6" style="52" customWidth="1"/>
-    <col min="9" max="9" width="11.2636363636364" style="52" customWidth="1"/>
-    <col min="10" max="10" width="11.4" style="52" customWidth="1"/>
-    <col min="11" max="11" width="5.6" style="52" customWidth="1"/>
+    <col min="6" max="6" width="10.265625" style="52" customWidth="1"/>
+    <col min="7" max="7" width="4.59765625" style="52" customWidth="1"/>
+    <col min="8" max="8" width="11.59765625" style="52" customWidth="1"/>
+    <col min="9" max="9" width="11.265625" style="52" customWidth="1"/>
+    <col min="10" max="10" width="11.3984375" style="52" customWidth="1"/>
+    <col min="11" max="11" width="5.59765625" style="52" customWidth="1"/>
     <col min="12" max="12" width="9" style="52"/>
-    <col min="13" max="13" width="11.2636363636364" style="52" customWidth="1"/>
-    <col min="14" max="14" width="12.8636363636364" style="52" customWidth="1"/>
-    <col min="15" max="15" width="15.2636363636364" style="52" customWidth="1"/>
-    <col min="16" max="16" width="4.6" style="52" customWidth="1"/>
+    <col min="13" max="13" width="11.265625" style="52" customWidth="1"/>
+    <col min="14" max="14" width="12.86328125" style="52" customWidth="1"/>
+    <col min="15" max="15" width="15.265625" style="52" customWidth="1"/>
+    <col min="16" max="16" width="4.59765625" style="52" customWidth="1"/>
     <col min="17" max="17" width="5" style="52" customWidth="1"/>
     <col min="18" max="16384" width="9" style="52"/>
   </cols>
   <sheetData>
-    <row r="3" ht="17.75" spans="2:17">
+    <row r="3" spans="2:17" ht="16.899999999999999">
       <c r="D3" s="53" t="s">
         <v>79</v>
       </c>
@@ -5667,7 +5156,7 @@
       <c r="P3" s="54"/>
       <c r="Q3" s="54"/>
     </row>
-    <row r="4" ht="16" spans="2:17">
+    <row r="4" spans="2:17" ht="14.25">
       <c r="B4" s="55" t="s">
         <v>80</v>
       </c>
@@ -5725,7 +5214,7 @@
         <v>91</v>
       </c>
       <c r="E5" s="52">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="F5" s="56">
         <v>0.6</v>
@@ -5734,10 +5223,10 @@
         <v>0.6</v>
       </c>
       <c r="H5" s="56">
-        <v>189.216</v>
+        <v>189.21600000000001</v>
       </c>
       <c r="I5" s="56">
-        <v>88.3008</v>
+        <v>88.300799999999995</v>
       </c>
       <c r="J5" s="52">
         <v>60</v>
@@ -5774,7 +5263,7 @@
         <v>91</v>
       </c>
       <c r="E6" s="52">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="F6" s="56">
         <v>0.6</v>
@@ -5783,10 +5272,10 @@
         <v>0.6</v>
       </c>
       <c r="H6" s="56">
-        <v>189.216</v>
+        <v>189.21600000000001</v>
       </c>
       <c r="I6" s="56">
-        <v>88.3008</v>
+        <v>88.300799999999995</v>
       </c>
       <c r="J6" s="52">
         <v>60</v>
@@ -5820,7 +5309,7 @@
         <v>91</v>
       </c>
       <c r="E7" s="52">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="F7" s="56">
         <v>0.1</v>
@@ -5829,16 +5318,16 @@
         <v>0.6</v>
       </c>
       <c r="H7" s="56">
-        <v>141.912</v>
+        <v>141.91200000000001</v>
       </c>
       <c r="I7" s="56">
-        <v>75.6864</v>
+        <v>75.686400000000006</v>
       </c>
       <c r="J7" s="52">
         <v>60</v>
       </c>
       <c r="K7" s="57">
-        <v>0.869565217391304</v>
+        <v>0.86956521739130399</v>
       </c>
       <c r="N7" s="52" t="str">
         <f t="shared" si="0"/>
@@ -5866,7 +5355,7 @@
         <v>91</v>
       </c>
       <c r="E8" s="52">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="F8" s="56">
         <v>0.3</v>
@@ -5901,7 +5390,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="9" ht="13" spans="2:17">
+    <row r="9" spans="2:17" ht="13.15">
       <c r="B9" s="58" t="s">
         <v>99</v>
       </c>
@@ -5913,7 +5402,7 @@
       </c>
       <c r="E9" s="52">
         <f t="shared" ref="E9:K9" si="1">E7</f>
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="F9" s="56">
         <f t="shared" si="1"/>
@@ -5925,11 +5414,11 @@
       </c>
       <c r="H9" s="56">
         <f t="shared" si="1"/>
-        <v>141.912</v>
+        <v>141.91200000000001</v>
       </c>
       <c r="I9" s="56">
         <f t="shared" si="1"/>
-        <v>75.6864</v>
+        <v>75.686400000000006</v>
       </c>
       <c r="J9" s="52">
         <f t="shared" si="1"/>
@@ -5937,7 +5426,7 @@
       </c>
       <c r="K9" s="57">
         <f t="shared" si="1"/>
-        <v>0.869565217391304</v>
+        <v>0.86956521739130399</v>
       </c>
       <c r="N9" s="52" t="str">
         <f t="shared" si="0"/>
@@ -5966,7 +5455,7 @@
       </c>
       <c r="E10" s="52">
         <f>E8</f>
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="F10" s="56"/>
       <c r="G10" s="56"/>
@@ -6035,34 +5524,33 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:AK40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="8" max="8" width="17.6" customWidth="1"/>
-    <col min="10" max="10" width="10.8636363636364" customWidth="1"/>
+    <col min="8" max="8" width="17.59765625" customWidth="1"/>
+    <col min="10" max="10" width="10.86328125" customWidth="1"/>
     <col min="11" max="13" width="5" customWidth="1"/>
-    <col min="14" max="14" width="8.4" customWidth="1"/>
+    <col min="14" max="14" width="8.3984375" customWidth="1"/>
     <col min="15" max="15" width="2" customWidth="1"/>
-    <col min="16" max="16" width="3.6" customWidth="1"/>
-    <col min="17" max="17" width="17.6" customWidth="1"/>
+    <col min="16" max="16" width="3.59765625" customWidth="1"/>
+    <col min="17" max="17" width="17.59765625" customWidth="1"/>
     <col min="21" max="21" width="2" customWidth="1"/>
-    <col min="22" max="22" width="17.6" customWidth="1"/>
+    <col min="22" max="22" width="17.59765625" customWidth="1"/>
     <col min="23" max="25" width="6" customWidth="1"/>
     <col min="26" max="26" width="2" customWidth="1"/>
-    <col min="27" max="27" width="17.6" customWidth="1"/>
-    <col min="28" max="28" width="11.4" customWidth="1"/>
+    <col min="27" max="27" width="17.59765625" customWidth="1"/>
+    <col min="28" max="28" width="11.3984375" customWidth="1"/>
     <col min="29" max="31" width="5" customWidth="1"/>
-    <col min="33" max="33" width="19.8636363636364" customWidth="1"/>
-    <col min="34" max="34" width="5.6" customWidth="1"/>
+    <col min="33" max="33" width="19.86328125" customWidth="1"/>
+    <col min="34" max="34" width="5.59765625" customWidth="1"/>
     <col min="35" max="37" width="5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6226,7 +5714,7 @@
         <v>439.05</v>
       </c>
       <c r="N3" s="39">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="O3" s="38"/>
       <c r="P3" s="40">
@@ -6238,15 +5726,15 @@
       </c>
       <c r="R3" s="39">
         <f>$P3*K3</f>
-        <v>29.109</v>
+        <v>29.109000000000002</v>
       </c>
       <c r="S3" s="39">
         <f t="shared" ref="S3:T5" si="2">$P3*L3</f>
-        <v>13.226</v>
+        <v>13.226000000000001</v>
       </c>
       <c r="T3" s="39">
         <f t="shared" si="2"/>
-        <v>8.781</v>
+        <v>8.7810000000000006</v>
       </c>
       <c r="V3" t="str">
         <f t="shared" ref="V3:V5" si="3">$H3</f>
@@ -6297,7 +5785,7 @@
         <v>661.3</v>
       </c>
       <c r="E4" s="37">
-        <v>138.45</v>
+        <v>138.44999999999999</v>
       </c>
       <c r="F4" s="37">
         <v>1368.75</v>
@@ -6315,17 +5803,17 @@
         <v>338.75</v>
       </c>
       <c r="L4" s="38">
-        <v>138.45</v>
+        <v>138.44999999999999</v>
       </c>
       <c r="M4" s="38">
         <v>87.3</v>
       </c>
       <c r="N4" s="39">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="O4" s="39"/>
       <c r="P4" s="40">
-        <v>0.035</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="Q4" t="str">
         <f t="shared" si="1"/>
@@ -6333,28 +5821,28 @@
       </c>
       <c r="R4" s="39">
         <f t="shared" ref="R4:R5" si="4">$P4*K4</f>
-        <v>11.85625</v>
+        <v>11.856249999999999</v>
       </c>
       <c r="S4" s="39">
         <f t="shared" si="2"/>
-        <v>4.84575</v>
+        <v>4.8457499999999998</v>
       </c>
       <c r="T4" s="39">
         <f t="shared" si="2"/>
-        <v>3.0555</v>
+        <v>3.0554999999999999</v>
       </c>
       <c r="V4" t="str">
         <f t="shared" si="3"/>
         <v>H2Conv_LOHC</v>
       </c>
       <c r="W4">
-        <v>0.925</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="X4">
         <v>0.95</v>
       </c>
       <c r="Y4">
-        <v>0.975</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="AA4" t="str">
         <f t="shared" ref="AA4:AA5" si="5">H4</f>
@@ -6416,7 +5904,7 @@
         <v>799.5</v>
       </c>
       <c r="N5" s="39">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="O5" s="39"/>
       <c r="P5" s="40">
@@ -6462,7 +5950,7 @@
         <v>0.255</v>
       </c>
       <c r="AD5" s="9">
-        <v>0.225</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="AE5" s="9">
         <v>0.1875</v>
@@ -6489,7 +5977,7 @@
         <v>0.02</v>
       </c>
       <c r="E6" s="44">
-        <v>0.035</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="F6" s="44">
         <v>0.04</v>
@@ -6509,7 +5997,7 @@
         <v>0.875</v>
       </c>
       <c r="E7" s="44">
-        <v>0.925</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="F7" s="44">
         <v>0.95</v>
@@ -6552,7 +6040,7 @@
         <v>0.875</v>
       </c>
       <c r="E9" s="44">
-        <v>0.975</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="F9" s="44">
         <v>1</v>
@@ -6563,7 +6051,7 @@
       </c>
       <c r="I9">
         <f>F11*3.6/120</f>
-        <v>0.225</v>
+        <v>0.22500000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -6737,7 +6225,7 @@
         <v>752.1</v>
       </c>
       <c r="F14" s="48">
-        <v>649.45</v>
+        <v>649.45000000000005</v>
       </c>
       <c r="H14" t="s">
         <v>143</v>
@@ -6758,11 +6246,11 @@
         <v>276.55</v>
       </c>
       <c r="N14" s="39">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="O14" s="38"/>
       <c r="P14" s="40">
-        <v>0.035</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="Q14" t="str">
         <f t="shared" ref="Q14:Q16" si="6">$H14</f>
@@ -6770,15 +6258,15 @@
       </c>
       <c r="R14" s="39">
         <f>$P14*K14</f>
-        <v>40.39175</v>
+        <v>40.391750000000002</v>
       </c>
       <c r="S14" s="39">
         <f t="shared" ref="S14:T16" si="7">$P14*L14</f>
-        <v>16.02475</v>
+        <v>16.024750000000001</v>
       </c>
       <c r="T14" s="39">
         <f t="shared" si="7"/>
-        <v>9.67925</v>
+        <v>9.6792499999999997</v>
       </c>
       <c r="V14" t="str">
         <f t="shared" ref="V14:V16" si="8">$H14</f>
@@ -6798,10 +6286,10 @@
         <v>0.06</v>
       </c>
       <c r="AD14" s="9">
-        <v>0.045</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="AE14" s="9">
-        <v>0.0225</v>
+        <v>2.2499999999999999E-2</v>
       </c>
       <c r="AF14" s="9">
         <v>0.4</v>
@@ -6847,11 +6335,11 @@
         <v>169.75</v>
       </c>
       <c r="N15" s="39">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="O15" s="39"/>
       <c r="P15" s="40">
-        <v>0.045</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="Q15" t="str">
         <f t="shared" si="6"/>
@@ -6859,15 +6347,15 @@
       </c>
       <c r="R15" s="39">
         <f t="shared" ref="R15:R16" si="9">$P15*K15</f>
-        <v>33.8445</v>
+        <v>33.844499999999996</v>
       </c>
       <c r="S15" s="39">
         <f t="shared" si="7"/>
-        <v>14.4675</v>
+        <v>14.467499999999999</v>
       </c>
       <c r="T15" s="39">
         <f t="shared" si="7"/>
-        <v>7.63875</v>
+        <v>7.6387499999999999</v>
       </c>
       <c r="V15" t="str">
         <f t="shared" si="8"/>
@@ -6927,7 +6415,7 @@
         <v>16</v>
       </c>
       <c r="K16" s="38">
-        <v>649.45</v>
+        <v>649.45000000000005</v>
       </c>
       <c r="L16" s="38">
         <v>267.3</v>
@@ -6936,11 +6424,11 @@
         <v>125.45</v>
       </c>
       <c r="N16" s="39">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="O16" s="39"/>
       <c r="P16" s="40">
-        <v>0.035</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="Q16" t="str">
         <f t="shared" si="6"/>
@@ -6952,11 +6440,11 @@
       </c>
       <c r="S16" s="39">
         <f t="shared" si="7"/>
-        <v>9.3555</v>
+        <v>9.3554999999999993</v>
       </c>
       <c r="T16" s="39">
         <f t="shared" si="7"/>
-        <v>4.39075</v>
+        <v>4.3907499999999997</v>
       </c>
       <c r="V16" t="str">
         <f t="shared" si="8"/>
@@ -6973,13 +6461,13 @@
         <v>102</v>
       </c>
       <c r="AC16" s="9">
-        <v>0.0225</v>
+        <v>2.2499999999999999E-2</v>
       </c>
       <c r="AD16" s="9">
-        <v>0.01575</v>
+        <v>1.575E-2</v>
       </c>
       <c r="AE16" s="9">
-        <v>0.009</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="AF16" s="9">
         <v>0.4</v>
@@ -7003,13 +6491,13 @@
       </c>
       <c r="C17" s="49"/>
       <c r="D17" s="44">
-        <v>0.035</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="E17" s="44">
-        <v>0.045</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="F17" s="44">
-        <v>0.035</v>
+        <v>3.5000000000000003E-2</v>
       </c>
     </row>
     <row r="18" spans="1:33">
@@ -7065,7 +6553,7 @@
       </c>
       <c r="J19" s="39">
         <f t="shared" si="11"/>
-        <v>0.0225</v>
+        <v>2.2499999999999999E-2</v>
       </c>
       <c r="AA19" t="s">
         <v>120</v>
@@ -7102,11 +6590,11 @@
         <v>2</v>
       </c>
       <c r="F20" s="37">
-        <v>0.525</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="H20" s="39">
         <f t="shared" ref="H20:H24" si="12">D20*3.6/120</f>
-        <v>0.045</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="I20" s="39">
         <f t="shared" si="11"/>
@@ -7114,7 +6602,7 @@
       </c>
       <c r="J20" s="39">
         <f t="shared" si="11"/>
-        <v>0.01575</v>
+        <v>1.575E-2</v>
       </c>
       <c r="AA20" t="str">
         <f>V14</f>
@@ -7127,10 +6615,10 @@
         <v>0.42</v>
       </c>
       <c r="AD20" s="9">
-        <v>0.3315</v>
+        <v>0.33150000000000002</v>
       </c>
       <c r="AE20" s="9">
-        <v>0.243</v>
+        <v>0.24299999999999999</v>
       </c>
       <c r="AF20" t="s">
         <v>149</v>
@@ -7156,7 +6644,7 @@
       </c>
       <c r="H21" s="39">
         <f t="shared" si="12"/>
-        <v>0.0225</v>
+        <v>2.2499999999999999E-2</v>
       </c>
       <c r="I21" s="39">
         <f t="shared" si="11"/>
@@ -7164,7 +6652,7 @@
       </c>
       <c r="J21" s="39">
         <f t="shared" si="11"/>
-        <v>0.009</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="AA21" t="str">
         <f>V15</f>
@@ -7177,10 +6665,10 @@
         <v>0.51</v>
       </c>
       <c r="AD21" s="9">
-        <v>0.4245</v>
+        <v>0.42449999999999999</v>
       </c>
       <c r="AE21" s="9">
-        <v>0.339</v>
+        <v>0.33900000000000002</v>
       </c>
       <c r="AF21" t="s">
         <v>149</v>
@@ -7238,11 +6726,11 @@
       </c>
       <c r="H23" s="39">
         <f t="shared" si="12"/>
-        <v>0.3315</v>
+        <v>0.33150000000000002</v>
       </c>
       <c r="I23" s="39">
         <f t="shared" si="11"/>
-        <v>0.4245</v>
+        <v>0.42449999999999999</v>
       </c>
       <c r="J23" s="39">
         <f t="shared" si="11"/>
@@ -7266,11 +6754,11 @@
       </c>
       <c r="H24" s="39">
         <f t="shared" si="12"/>
-        <v>0.243</v>
+        <v>0.24299999999999999</v>
       </c>
       <c r="I24" s="39">
         <f t="shared" si="11"/>
-        <v>0.339</v>
+        <v>0.33900000000000002</v>
       </c>
       <c r="J24" s="39">
         <f t="shared" si="11"/>
@@ -7436,37 +6924,35 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B3:Y5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="11.2636363636364" customWidth="1"/>
-    <col min="3" max="3" width="14.6" customWidth="1"/>
-    <col min="4" max="4" width="26.4" customWidth="1"/>
-    <col min="5" max="5" width="20.2636363636364" customWidth="1"/>
+    <col min="2" max="2" width="11.265625" customWidth="1"/>
+    <col min="3" max="3" width="14.59765625" customWidth="1"/>
+    <col min="4" max="4" width="26.3984375" customWidth="1"/>
+    <col min="5" max="5" width="20.265625" customWidth="1"/>
     <col min="6" max="6" width="5" customWidth="1"/>
-    <col min="7" max="7" width="4.6" customWidth="1"/>
+    <col min="7" max="7" width="4.59765625" customWidth="1"/>
     <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="9" max="9" width="10.2636363636364" customWidth="1"/>
-    <col min="10" max="10" width="7.86363636363636" customWidth="1"/>
-    <col min="12" max="12" width="17.8636363636364" customWidth="1"/>
-    <col min="13" max="13" width="9.4" customWidth="1"/>
+    <col min="9" max="9" width="10.265625" customWidth="1"/>
+    <col min="10" max="10" width="7.86328125" customWidth="1"/>
+    <col min="12" max="12" width="17.86328125" customWidth="1"/>
+    <col min="13" max="13" width="9.3984375" customWidth="1"/>
     <col min="14" max="14" width="12" customWidth="1"/>
-    <col min="15" max="15" width="8.86363636363636" customWidth="1"/>
+    <col min="15" max="15" width="8.86328125" customWidth="1"/>
     <col min="16" max="16" width="14" customWidth="1"/>
-    <col min="17" max="17" width="6.86363636363636" customWidth="1"/>
-    <col min="18" max="18" width="11.8636363636364" customWidth="1"/>
-    <col min="19" max="19" width="7.86363636363636" customWidth="1"/>
-    <col min="20" max="20" width="12.8636363636364" customWidth="1"/>
-    <col min="21" max="21" width="4.6" customWidth="1"/>
+    <col min="17" max="17" width="6.86328125" customWidth="1"/>
+    <col min="18" max="18" width="11.86328125" customWidth="1"/>
+    <col min="19" max="19" width="7.86328125" customWidth="1"/>
+    <col min="20" max="20" width="12.86328125" customWidth="1"/>
+    <col min="21" max="21" width="4.59765625" customWidth="1"/>
     <col min="22" max="22" width="9" customWidth="1"/>
-    <col min="23" max="23" width="4.4" customWidth="1"/>
+    <col min="23" max="23" width="4.3984375" customWidth="1"/>
     <col min="24" max="24" width="5" customWidth="1"/>
     <col min="25" max="25" width="9" customWidth="1"/>
   </cols>
@@ -7592,16 +7078,16 @@
         <v>71</v>
       </c>
       <c r="S5" s="9">
-        <v>2.13470319634703</v>
+        <v>2.1347031963470302</v>
       </c>
       <c r="T5" s="9">
         <v>1.72231735159817</v>
       </c>
       <c r="U5" s="9">
-        <v>0.5525</v>
+        <v>0.55249999999999999</v>
       </c>
       <c r="V5" s="9">
-        <v>0.5525</v>
+        <v>0.55249999999999999</v>
       </c>
       <c r="W5">
         <v>20</v>
@@ -7610,46 +7096,48 @@
         <v>0.85</v>
       </c>
       <c r="Y5">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="B1:BO66"/>
-  <sheetFormatPr defaultColWidth="8.8" defaultRowHeight="14.5"/>
+  <dimension ref="B1:BP66"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="32.5272727272727" customWidth="1"/>
-    <col min="3" max="3" width="30.7272727272727" customWidth="1"/>
+    <col min="2" max="2" width="32.53125" customWidth="1"/>
+    <col min="3" max="3" width="30.73046875" customWidth="1"/>
     <col min="4" max="4" width="50" customWidth="1"/>
-    <col min="5" max="5" width="29.9272727272727" customWidth="1"/>
-    <col min="6" max="9" width="33.7272727272727" customWidth="1"/>
-    <col min="10" max="10" width="19.2636363636364" customWidth="1"/>
-    <col min="11" max="11" width="14.6" customWidth="1"/>
-    <col min="12" max="12" width="14.2636363636364" customWidth="1"/>
-    <col min="13" max="13" width="13.0636363636364" customWidth="1"/>
-    <col min="14" max="14" width="12.8" customWidth="1"/>
-    <col min="15" max="15" width="6.8" customWidth="1"/>
-    <col min="16" max="16" width="15.3363636363636" customWidth="1"/>
-    <col min="17" max="17" width="6.2" customWidth="1"/>
-    <col min="18" max="18" width="14.5272727272727" customWidth="1"/>
-    <col min="23" max="23" width="20.2" customWidth="1"/>
-    <col min="24" max="24" width="18.5272727272727" customWidth="1"/>
-    <col min="25" max="25" width="19.2" customWidth="1"/>
-    <col min="32" max="32" width="118.727272727273" customWidth="1"/>
-    <col min="36" max="36" width="13.5272727272727" customWidth="1"/>
-    <col min="48" max="48" width="14.5272727272727" customWidth="1"/>
+    <col min="5" max="5" width="29.9296875" customWidth="1"/>
+    <col min="6" max="9" width="33.73046875" customWidth="1"/>
+    <col min="10" max="10" width="19.265625" customWidth="1"/>
+    <col min="11" max="11" width="14.59765625" customWidth="1"/>
+    <col min="12" max="12" width="14.265625" customWidth="1"/>
+    <col min="13" max="13" width="13.06640625" customWidth="1"/>
+    <col min="14" max="14" width="12.796875" customWidth="1"/>
+    <col min="15" max="15" width="6.796875" customWidth="1"/>
+    <col min="16" max="16" width="15.33203125" customWidth="1"/>
+    <col min="17" max="17" width="6.19921875" customWidth="1"/>
+    <col min="18" max="18" width="14.53125" customWidth="1"/>
+    <col min="23" max="23" width="20.19921875" customWidth="1"/>
+    <col min="24" max="24" width="18.53125" customWidth="1"/>
+    <col min="25" max="25" width="19.19921875" customWidth="1"/>
+    <col min="32" max="32" width="21.265625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.53125" customWidth="1"/>
+    <col min="44" max="44" width="6.06640625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="13.19921875" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="5.265625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="5.9296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:51">
+    <row r="1" spans="2:52">
       <c r="X1" s="2"/>
       <c r="Y1" s="3" t="s">
         <v>118</v>
@@ -7662,7 +7150,7 @@
       <c r="AE1" s="2"/>
       <c r="AF1" s="2"/>
     </row>
-    <row r="2" spans="2:51">
+    <row r="2" spans="2:52">
       <c r="B2" t="s">
         <v>1</v>
       </c>
@@ -7677,7 +7165,7 @@
       <c r="AE2" s="3"/>
       <c r="AF2" s="3"/>
     </row>
-    <row r="3" spans="2:51">
+    <row r="3" spans="2:52">
       <c r="B3" s="5" t="s">
         <v>8</v>
       </c>
@@ -7727,7 +7215,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="4" spans="2:51">
+    <row r="4" spans="2:52">
       <c r="B4" s="5" t="s">
         <v>184</v>
       </c>
@@ -7754,7 +7242,7 @@
         <v>185</v>
       </c>
       <c r="Z4" s="3">
-        <v>0.095</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="AA4" s="3">
         <v>0</v>
@@ -7769,13 +7257,13 @@
         <v>3.528</v>
       </c>
       <c r="AE4" s="3">
-        <v>0.946</v>
+        <v>0.94599999999999995</v>
       </c>
       <c r="AF4" s="3">
         <v>1.085</v>
       </c>
     </row>
-    <row r="5" spans="2:51">
+    <row r="5" spans="2:52">
       <c r="B5" s="5" t="s">
         <v>189</v>
       </c>
@@ -7806,7 +7294,7 @@
       <c r="AE5" s="4"/>
       <c r="AF5" s="4"/>
     </row>
-    <row r="6" spans="2:51">
+    <row r="6" spans="2:52">
       <c r="B6" s="5" t="s">
         <v>184</v>
       </c>
@@ -7836,7 +7324,7 @@
       <c r="AE6" s="4"/>
       <c r="AF6" s="4"/>
     </row>
-    <row r="7" spans="2:51">
+    <row r="7" spans="2:52">
       <c r="B7" s="5"/>
       <c r="C7" s="5" t="s">
         <v>194</v>
@@ -7861,7 +7349,7 @@
       <c r="AE7" s="4"/>
       <c r="AF7" s="4"/>
     </row>
-    <row r="8" spans="2:51">
+    <row r="8" spans="2:52">
       <c r="B8" s="5"/>
       <c r="C8" s="5" t="s">
         <v>195</v>
@@ -7886,7 +7374,7 @@
       <c r="AE8" s="4"/>
       <c r="AF8" s="4"/>
     </row>
-    <row r="9" spans="2:51">
+    <row r="9" spans="2:52">
       <c r="B9" s="5"/>
       <c r="C9" s="5" t="s">
         <v>196</v>
@@ -7911,7 +7399,7 @@
       <c r="AE9" s="4"/>
       <c r="AF9" s="4"/>
     </row>
-    <row r="10" spans="2:51">
+    <row r="10" spans="2:52">
       <c r="B10" s="5"/>
       <c r="C10" s="5" t="s">
         <v>197</v>
@@ -7936,7 +7424,7 @@
       <c r="AE10" s="4"/>
       <c r="AF10" s="4"/>
     </row>
-    <row r="11" spans="2:51">
+    <row r="11" spans="2:52">
       <c r="B11" s="5"/>
       <c r="C11" s="5" t="s">
         <v>198</v>
@@ -7961,7 +7449,7 @@
       <c r="AE11" s="4"/>
       <c r="AF11" s="4"/>
     </row>
-    <row r="12" spans="2:51">
+    <row r="12" spans="2:52">
       <c r="B12" s="5"/>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
@@ -7977,7 +7465,7 @@
       <c r="AE12" s="4"/>
       <c r="AF12" s="4"/>
     </row>
-    <row r="13" spans="2:51">
+    <row r="13" spans="2:52">
       <c r="W13" s="4"/>
       <c r="X13" s="7"/>
       <c r="Y13" s="4"/>
@@ -7989,7 +7477,7 @@
       <c r="AE13" s="4"/>
       <c r="AF13" s="4"/>
     </row>
-    <row r="14" spans="2:51">
+    <row r="14" spans="2:52">
       <c r="G14" t="s">
         <v>199</v>
       </c>
@@ -8006,7 +7494,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="15" spans="2:51">
+    <row r="15" spans="2:52">
       <c r="B15" t="s">
         <v>2</v>
       </c>
@@ -8121,8 +7609,14 @@
       <c r="AV15" s="8" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="16" spans="2:51">
+      <c r="AW15" t="s">
+        <v>208</v>
+      </c>
+      <c r="AX15" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="16" spans="2:52">
       <c r="B16" t="s">
         <v>185</v>
       </c>
@@ -8139,7 +7633,7 @@
         <v>0.92</v>
       </c>
       <c r="I16" s="9">
-        <v>1.314</v>
+        <v>1.3140000000000001</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -8181,7 +7675,7 @@
         <v>0.9</v>
       </c>
       <c r="AM16" s="9">
-        <v>1.314</v>
+        <v>1.3140000000000001</v>
       </c>
       <c r="AN16">
         <v>1</v>
@@ -8195,11 +7689,17 @@
       <c r="AV16" s="10">
         <v>3000</v>
       </c>
-      <c r="AY16" s="10">
+      <c r="AW16">
+        <v>1</v>
+      </c>
+      <c r="AX16">
+        <v>1</v>
+      </c>
+      <c r="AZ16" s="10">
         <v>10</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="16" spans="2:67">
+    <row r="17" spans="2:68" s="1" customFormat="1" ht="15.4">
       <c r="D17" s="11"/>
       <c r="F17" s="1" t="s">
         <v>209</v>
@@ -8211,7 +7711,7 @@
       <c r="I17" s="12"/>
       <c r="K17" s="12">
         <f>1/H16</f>
-        <v>1.08695652173913</v>
+        <v>1.0869565217391304</v>
       </c>
       <c r="W17"/>
       <c r="Y17" s="13" t="s">
@@ -8237,7 +7737,7 @@
       <c r="AM17" s="9"/>
       <c r="AN17"/>
       <c r="AO17" s="9">
-        <v>1.08695652173913</v>
+        <v>1.0869565217391299</v>
       </c>
       <c r="AQ17"/>
       <c r="AR17"/>
@@ -8264,8 +7764,9 @@
       <c r="BM17"/>
       <c r="BN17"/>
       <c r="BO17"/>
-    </row>
-    <row r="18" spans="2:67">
+      <c r="BP17"/>
+    </row>
+    <row r="18" spans="2:68">
       <c r="D18" s="5"/>
       <c r="F18" s="5" t="str">
         <f>C25</f>
@@ -8291,7 +7792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="2:67">
+    <row r="19" spans="2:68">
       <c r="B19" t="s">
         <v>190</v>
       </c>
@@ -8299,7 +7800,7 @@
         <v>212</v>
       </c>
       <c r="I19" s="9">
-        <v>29.89194313</v>
+        <v>29.891943130000001</v>
       </c>
       <c r="L19">
         <v>1</v>
@@ -8328,7 +7829,7 @@
       </c>
       <c r="AM19" s="9">
         <f>AM16</f>
-        <v>1.314</v>
+        <v>1.3140000000000001</v>
       </c>
       <c r="AN19">
         <v>1</v>
@@ -8342,11 +7843,17 @@
       <c r="AV19" s="10">
         <v>3500</v>
       </c>
-      <c r="AY19" s="10">
+      <c r="AW19">
+        <v>1</v>
+      </c>
+      <c r="AX19">
+        <v>1</v>
+      </c>
+      <c r="AZ19" s="10">
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="2:67">
+    <row r="20" spans="2:68">
       <c r="AH20" s="5"/>
       <c r="AJ20" t="s">
         <v>209</v>
@@ -8356,10 +7863,10 @@
       </c>
       <c r="AM20" s="9"/>
       <c r="AO20" s="9">
-        <v>1.08695652173913</v>
-      </c>
-    </row>
-    <row r="21" spans="2:67">
+        <v>1.0869565217391299</v>
+      </c>
+    </row>
+    <row r="21" spans="2:68">
       <c r="AH21" s="5"/>
       <c r="AJ21" s="5" t="s">
         <v>211</v>
@@ -8372,7 +7879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="2:67">
+    <row r="22" spans="2:68">
       <c r="X22" s="4"/>
       <c r="Y22" s="4"/>
       <c r="Z22" s="4"/>
@@ -8393,7 +7900,7 @@
       </c>
       <c r="AM22" s="9">
         <f>AM19</f>
-        <v>1.314</v>
+        <v>1.3140000000000001</v>
       </c>
       <c r="AN22">
         <v>1</v>
@@ -8407,11 +7914,17 @@
       <c r="AV22" s="10">
         <v>4000</v>
       </c>
-      <c r="AY22" s="10">
+      <c r="AW22">
+        <v>1</v>
+      </c>
+      <c r="AX22">
+        <v>1</v>
+      </c>
+      <c r="AZ22" s="10">
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="2:67">
+    <row r="23" spans="2:68">
       <c r="B23" s="5" t="s">
         <v>151</v>
       </c>
@@ -8435,10 +7948,10 @@
       <c r="AL23" s="10"/>
       <c r="AM23" s="9"/>
       <c r="AO23" s="9">
-        <v>1.08695652173913</v>
-      </c>
-    </row>
-    <row r="24" spans="2:67">
+        <v>1.0869565217391299</v>
+      </c>
+    </row>
+    <row r="24" spans="2:68">
       <c r="B24" s="5" t="s">
         <v>213</v>
       </c>
@@ -8479,7 +7992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:67">
+    <row r="25" spans="2:68">
       <c r="B25" s="5" t="s">
         <v>214</v>
       </c>
@@ -8517,7 +8030,7 @@
       </c>
       <c r="AM25" s="9">
         <f>AM22</f>
-        <v>1.314</v>
+        <v>1.3140000000000001</v>
       </c>
       <c r="AN25">
         <v>1</v>
@@ -8531,11 +8044,17 @@
       <c r="AV25" s="10">
         <v>4000</v>
       </c>
-      <c r="AY25" s="10">
+      <c r="AW25">
+        <v>1</v>
+      </c>
+      <c r="AX25">
+        <v>1</v>
+      </c>
+      <c r="AZ25" s="10">
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="2:67">
+    <row r="26" spans="2:68">
       <c r="C26" s="5" t="s">
         <v>209</v>
       </c>
@@ -8562,10 +8081,10 @@
       <c r="AL26" s="10"/>
       <c r="AM26" s="9"/>
       <c r="AO26" s="9">
-        <v>1.08695652173913</v>
-      </c>
-    </row>
-    <row r="27" spans="2:67">
+        <v>1.0869565217391299</v>
+      </c>
+    </row>
+    <row r="27" spans="2:68">
       <c r="W27" s="4"/>
       <c r="X27" s="4"/>
       <c r="Y27" s="4"/>
@@ -8582,7 +8101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="2:67">
+    <row r="28" spans="2:68">
       <c r="W28" s="4"/>
       <c r="X28" s="4"/>
       <c r="Y28" s="4"/>
@@ -8603,7 +8122,7 @@
       </c>
       <c r="AM28" s="9">
         <f>AM25</f>
-        <v>1.314</v>
+        <v>1.3140000000000001</v>
       </c>
       <c r="AN28">
         <v>1</v>
@@ -8617,11 +8136,17 @@
       <c r="AV28" s="10">
         <v>4000</v>
       </c>
-      <c r="AY28" s="10">
+      <c r="AW28">
+        <v>1</v>
+      </c>
+      <c r="AX28">
+        <v>1</v>
+      </c>
+      <c r="AZ28" s="10">
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="2:67">
+    <row r="29" spans="2:68">
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -8639,10 +8164,10 @@
       <c r="AL29" s="10"/>
       <c r="AM29" s="9"/>
       <c r="AO29" s="9">
-        <v>1.08695652173913</v>
-      </c>
-    </row>
-    <row r="30" spans="2:67">
+        <v>1.0869565217391299</v>
+      </c>
+    </row>
+    <row r="30" spans="2:68">
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="17" t="s">
@@ -8665,7 +8190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="2:67">
+    <row r="31" spans="2:68">
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
       <c r="D31" s="2"/>
@@ -8690,7 +8215,7 @@
       </c>
       <c r="AM31" s="9">
         <f>AM28</f>
-        <v>1.314</v>
+        <v>1.3140000000000001</v>
       </c>
       <c r="AN31">
         <v>1</v>
@@ -8704,11 +8229,17 @@
       <c r="AV31" s="10">
         <v>4000</v>
       </c>
-      <c r="AY31" s="10">
+      <c r="AW31">
+        <v>1</v>
+      </c>
+      <c r="AX31">
+        <v>1</v>
+      </c>
+      <c r="AZ31" s="10">
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="2:67">
+    <row r="32" spans="2:68">
       <c r="B32" s="3" t="s">
         <v>176</v>
       </c>
@@ -8730,7 +8261,7 @@
       </c>
       <c r="AM32" s="9"/>
       <c r="AO32" s="9">
-        <v>1.08695652173913</v>
+        <v>1.0869565217391299</v>
       </c>
     </row>
     <row r="33" spans="2:45">
@@ -8745,7 +8276,7 @@
       </c>
       <c r="E33" s="20">
         <f>[6]EnergyUseFromEverBatt_Min_!$AW$6</f>
-        <v>0.0473</v>
+        <v>4.7300000000000002E-2</v>
       </c>
       <c r="AH33" s="5"/>
       <c r="AJ33" s="5" t="s">
@@ -8759,7 +8290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" ht="16" spans="2:45">
+    <row r="34" spans="2:45" ht="15.4">
       <c r="B34" s="6" t="s">
         <v>188</v>
       </c>
@@ -8772,10 +8303,10 @@
       </c>
       <c r="E34" s="20">
         <f>[6]EnergyUseFromEverBatt_Min_!$AW$7</f>
-        <v>0.171166666666667</v>
-      </c>
-    </row>
-    <row r="35" ht="16" spans="2:45">
+        <v>0.17116666666666699</v>
+      </c>
+    </row>
+    <row r="35" spans="2:45" ht="15.4">
       <c r="B35" s="6" t="s">
         <v>188</v>
       </c>
@@ -8788,10 +8319,10 @@
       </c>
       <c r="E35" s="20">
         <f>[6]EnergyUseFromEverBatt_Min_!$AW$8</f>
-        <v>0.466366666666667</v>
-      </c>
-    </row>
-    <row r="36" ht="16" spans="2:45">
+        <v>0.46636666666666698</v>
+      </c>
+    </row>
+    <row r="36" spans="2:45" ht="15.4">
       <c r="B36" s="6" t="s">
         <v>188</v>
       </c>
@@ -8804,7 +8335,7 @@
       </c>
       <c r="E36" s="20">
         <f>[6]EnergyUseFromEverBatt_Min_!$AW$9</f>
-        <v>0.0956666666666667</v>
+        <v>9.5666666666666705E-2</v>
       </c>
     </row>
     <row r="43" spans="2:45">
@@ -8829,7 +8360,7 @@
       <c r="R43" s="8"/>
       <c r="S43" s="15"/>
     </row>
-    <row r="44" ht="16" spans="2:45">
+    <row r="44" spans="2:45" ht="15.4">
       <c r="B44" s="22" t="s">
         <v>80</v>
       </c>
@@ -8865,7 +8396,7 @@
       <c r="R44" s="8"/>
       <c r="S44" s="8"/>
     </row>
-    <row r="45" ht="16" spans="2:45">
+    <row r="45" spans="2:45" ht="15.4">
       <c r="B45" s="27" t="s">
         <v>185</v>
       </c>
@@ -9237,7 +8768,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/SubRes_Tmpl/SubRES_H2-Production.xlsx
+++ b/SubRes_Tmpl/SubRES_H2-Production.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\KiNESYS_BattCircularity-main\SubRes_Tmpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CA87521-2B74-460B-A4E2-F505E635EBC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="8260" activeTab="5"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SectFuel" sheetId="2" r:id="rId1"/>
@@ -83,12 +89,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Rocco De Miglio</author>
   </authors>
   <commentList>
-    <comment ref="O39" authorId="0">
+    <comment ref="O39" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -116,13 +122,13 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>xli9</author>
     <author>Amit Kanudia</author>
   </authors>
   <commentList>
-    <comment ref="BA16" authorId="0">
+    <comment ref="BA16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000001000000}">
       <text>
         <r>
           <rPr>
@@ -144,7 +150,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y17" authorId="0">
+    <comment ref="Y17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000002000000}">
       <text>
         <r>
           <rPr>
@@ -166,7 +172,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P19" authorId="1">
+    <comment ref="P19" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0500-000003000000}">
       <text>
         <r>
           <rPr>
@@ -190,7 +196,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BA19" authorId="0">
+    <comment ref="BA19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000004000000}">
       <text>
         <r>
           <rPr>
@@ -212,7 +218,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BA22" authorId="0">
+    <comment ref="BA22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000005000000}">
       <text>
         <r>
           <rPr>
@@ -234,7 +240,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BA25" authorId="0">
+    <comment ref="BA25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000006000000}">
       <text>
         <r>
           <rPr>
@@ -256,7 +262,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BA28" authorId="0">
+    <comment ref="BA28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000007000000}">
       <text>
         <r>
           <rPr>
@@ -278,7 +284,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BA31" authorId="0">
+    <comment ref="BA31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000008000000}">
       <text>
         <r>
           <rPr>
@@ -300,7 +306,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C33" authorId="0">
+    <comment ref="C33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000009000000}">
       <text>
         <r>
           <rPr>
@@ -322,14 +328,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="AY34" authorId="0">
+    <comment ref="AY34" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-00000A000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="Times New Roman"/>
-            <charset val="0"/>
           </rPr>
           <t>xli9:</t>
         </r>
@@ -337,7 +342,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Times New Roman"/>
-            <charset val="0"/>
           </rPr>
           <t xml:space="preserve">
 1,000-MW, 10-hour facility — so in US-style capacity-expansion modeling, 10 h is effectively the central assumption for new closed-loop PSH.
@@ -1083,19 +1087,15 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="9">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* \-??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="\Te\x\t"/>
-    <numFmt numFmtId="179" formatCode="#,##0.000"/>
-    <numFmt numFmtId="180" formatCode="#,##0.0_ "/>
-    <numFmt numFmtId="181" formatCode="0.0"/>
-    <numFmt numFmtId="182" formatCode="0.000"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="5">
+    <numFmt numFmtId="168" formatCode="\Te\x\t"/>
+    <numFmt numFmtId="169" formatCode="#,##0.000"/>
+    <numFmt numFmtId="170" formatCode="#,##0.0_ "/>
+    <numFmt numFmtId="171" formatCode="0.0"/>
+    <numFmt numFmtId="172" formatCode="0.000"/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1123,7 +1123,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.2"/>
+      <sz val="10.199999999999999"/>
       <color rgb="FF212529"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
@@ -1225,130 +1225,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="Times New Roman"/>
-      <charset val="0"/>
     </font>
     <font>
       <b/>
@@ -1376,10 +1254,16 @@
       <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
-      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="49">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1394,7 +1278,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.349986266670736"/>
+        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1406,7 +1290,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799951170384838"/>
+        <fgColor theme="4" tint="0.79992065187536243"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1418,7 +1302,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399914548173467"/>
+        <fgColor theme="9" tint="0.39988402966399123"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1430,7 +1314,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.0499893185216834"/>
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1454,7 +1338,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799920651875362"/>
+        <fgColor theme="5" tint="0.79989013336588644"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1472,7 +1356,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799920651875362"/>
+        <fgColor theme="9" tint="0.79989013336588644"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1484,7 +1368,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1500,176 +1384,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="34">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -1811,7 +1527,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.399914548173467"/>
+        <color theme="4" tint="0.39988402966399123"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1857,7 +1573,7 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </left>
       <right/>
       <top/>
@@ -1867,7 +1583,7 @@
     <border>
       <left/>
       <right style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </right>
       <top/>
       <bottom/>
@@ -1884,7 +1600,7 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </left>
       <right/>
       <top style="thin">
@@ -1896,7 +1612,7 @@
     <border>
       <left/>
       <right style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </right>
       <top style="thin">
         <color auto="1"/>
@@ -1937,7 +1653,7 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </left>
       <right/>
       <top/>
@@ -1949,7 +1665,7 @@
     <border>
       <left/>
       <right style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </right>
       <top/>
       <bottom style="thin">
@@ -1957,283 +1673,65 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="51">
+  <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="27" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="9" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="185">
+  <cellXfs count="186">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="178" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="178" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="49" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="6" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -2252,12 +1750,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
@@ -2267,7 +1765,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2276,42 +1774,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="13"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="15"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="14"/>
-    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" xfId="50" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="50" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="50" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="168" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="7"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="2"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="3"/>
+    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" xfId="7" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="7" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="7" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="24" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="5" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2329,19 +1815,16 @@
     <xf numFmtId="0" fontId="11" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="13" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="13" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="13" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2362,13 +1845,13 @@
     <xf numFmtId="0" fontId="13" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="13" fillId="12" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="13" fillId="12" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="13" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2395,25 +1878,25 @@
     <xf numFmtId="0" fontId="14" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="14" fillId="13" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="14" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="14" fillId="13" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="14" fillId="13" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="14" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="14" fillId="13" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="14" fillId="13" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="14" fillId="13" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="14" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="14" fillId="13" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="13" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="13" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="13" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2425,25 +1908,25 @@
     <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="13" fillId="14" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="14" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="14" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="14" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="14" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="13" fillId="14" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="14" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="14" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="14" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="14" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2455,25 +1938,25 @@
     <xf numFmtId="0" fontId="13" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="13" fillId="15" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="15" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="15" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="15" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="15" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="13" fillId="15" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="15" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="15" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="15" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="15" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2485,25 +1968,25 @@
     <xf numFmtId="0" fontId="13" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="13" fillId="16" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="16" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="16" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="14" fillId="16" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="14" fillId="16" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="14" fillId="16" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="14" fillId="16" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="13" fillId="16" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="16" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="16" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="16" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="16" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="16" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="16" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2518,25 +2001,25 @@
     <xf numFmtId="0" fontId="13" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="13" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="18" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="14" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="14" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="14" fillId="18" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="14" fillId="18" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="13" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="18" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="18" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="18" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="17" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2548,25 +2031,25 @@
     <xf numFmtId="0" fontId="13" fillId="16" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="13" fillId="16" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="16" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="16" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="14" fillId="16" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="14" fillId="16" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="14" fillId="16" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="14" fillId="16" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="13" fillId="16" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="16" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="16" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="16" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="16" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="16" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="16" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2575,25 +2058,25 @@
     <xf numFmtId="1" fontId="13" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="13" fillId="19" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="19" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="19" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="19" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="19" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="13" fillId="19" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="19" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="19" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="19" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="19" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="19" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2605,25 +2088,25 @@
     <xf numFmtId="1" fontId="13" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="13" fillId="20" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="20" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="20" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="20" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="20" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="13" fillId="20" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="20" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="20" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="20" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="20" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="20" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2635,25 +2118,25 @@
     <xf numFmtId="0" fontId="13" fillId="19" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="13" fillId="19" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="19" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="19" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="19" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="19" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="19" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="13" fillId="19" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="13" fillId="19" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="19" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="19" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="19" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="19" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="19" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="19" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2664,72 +2147,54 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="51">
+  <cellStyles count="8">
+    <cellStyle name="Heading 2" xfId="2" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="3" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="4" builtinId="19"/>
+    <cellStyle name="Neutral" xfId="5" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
-    <cellStyle name="Normal 10" xfId="49"/>
-    <cellStyle name="Normal 2" xfId="50"/>
+    <cellStyle name="Normal 10" xfId="6" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="Normal 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="New Microsoft Excel Worksheet"/>
       <sheetName val="AGR_Fuels"/>
@@ -2745,8 +2210,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="IEA Data"/>
       <sheetName val="E&amp;D Drivers"/>
@@ -2858,8 +2326,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="IEA Data"/>
       <sheetName val="E&amp;D Drivers"/>
@@ -2971,8 +2442,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Cover"/>
       <sheetName val="H2 transport"/>
@@ -3008,8 +2482,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Cover"/>
       <sheetName val="ELC_Lists"/>
@@ -3043,8 +2520,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Discuss_log"/>
       <sheetName val="Cover"/>
@@ -3089,22 +2569,22 @@
       <sheetData sheetId="13">
         <row r="6">
           <cell r="AW6">
-            <v>0.0473</v>
+            <v>4.7300000000000002E-2</v>
           </cell>
         </row>
         <row r="7">
           <cell r="AW7">
-            <v>0.171166666666667</v>
+            <v>0.17116666666666699</v>
           </cell>
         </row>
         <row r="8">
           <cell r="AW8">
-            <v>0.466366666666667</v>
+            <v>0.46636666666666698</v>
           </cell>
         </row>
         <row r="9">
           <cell r="AW9">
-            <v>0.0956666666666667</v>
+            <v>9.5666666666666705E-2</v>
           </cell>
         </row>
       </sheetData>
@@ -3376,29 +2856,29 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B3:P7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="11.8636363636364" customWidth="1"/>
-    <col min="3" max="3" width="9.4" customWidth="1"/>
-    <col min="4" max="4" width="15.2636363636364" customWidth="1"/>
+    <col min="2" max="2" width="11.86328125" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" customWidth="1"/>
+    <col min="4" max="4" width="15.265625" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="6.4" customWidth="1"/>
-    <col min="7" max="7" width="8.26363636363636" customWidth="1"/>
-    <col min="9" max="9" width="11.2636363636364" customWidth="1"/>
-    <col min="10" max="10" width="11.8636363636364" customWidth="1"/>
-    <col min="11" max="11" width="20.6" customWidth="1"/>
-    <col min="12" max="12" width="8.6" customWidth="1"/>
-    <col min="13" max="13" width="4.6" customWidth="1"/>
-    <col min="14" max="14" width="5.26363636363636" customWidth="1"/>
-    <col min="15" max="15" width="10.2636363636364" customWidth="1"/>
-    <col min="16" max="16" width="7.86363636363636" customWidth="1"/>
+    <col min="6" max="6" width="6.3984375" customWidth="1"/>
+    <col min="7" max="7" width="8.265625" customWidth="1"/>
+    <col min="9" max="9" width="11.265625" customWidth="1"/>
+    <col min="10" max="10" width="11.86328125" customWidth="1"/>
+    <col min="11" max="11" width="20.59765625" customWidth="1"/>
+    <col min="12" max="12" width="8.59765625" customWidth="1"/>
+    <col min="13" max="13" width="4.59765625" customWidth="1"/>
+    <col min="14" max="14" width="5.265625" customWidth="1"/>
+    <col min="15" max="15" width="10.265625" customWidth="1"/>
+    <col min="16" max="16" width="7.86328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:16">
@@ -3564,63 +3044,61 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Y39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="2" width="11.1363636363636" customWidth="1"/>
+    <col min="1" max="2" width="11.1328125" customWidth="1"/>
     <col min="3" max="5" width="14" customWidth="1"/>
-    <col min="6" max="8" width="11.8636363636364" customWidth="1"/>
-    <col min="9" max="9" width="20.2636363636364" customWidth="1"/>
-    <col min="10" max="10" width="15.6" customWidth="1"/>
-    <col min="11" max="11" width="20.2636363636364" customWidth="1"/>
-    <col min="12" max="12" width="15.6" customWidth="1"/>
-    <col min="13" max="13" width="20.2636363636364" customWidth="1"/>
-    <col min="14" max="14" width="15.6" customWidth="1"/>
-    <col min="15" max="15" width="18.8636363636364" customWidth="1"/>
-    <col min="16" max="16" width="4.4" customWidth="1"/>
-    <col min="17" max="17" width="8.13636363636364" customWidth="1"/>
-    <col min="20" max="20" width="18.1363636363636" customWidth="1"/>
+    <col min="6" max="8" width="11.86328125" customWidth="1"/>
+    <col min="9" max="9" width="20.265625" customWidth="1"/>
+    <col min="10" max="10" width="15.59765625" customWidth="1"/>
+    <col min="11" max="11" width="20.265625" customWidth="1"/>
+    <col min="12" max="12" width="15.59765625" customWidth="1"/>
+    <col min="13" max="13" width="20.265625" customWidth="1"/>
+    <col min="14" max="14" width="15.59765625" customWidth="1"/>
+    <col min="15" max="15" width="18.86328125" customWidth="1"/>
+    <col min="16" max="16" width="4.3984375" customWidth="1"/>
+    <col min="17" max="17" width="8.1328125" customWidth="1"/>
+    <col min="20" max="20" width="18.1328125" customWidth="1"/>
     <col min="21" max="21" width="24" customWidth="1"/>
-    <col min="22" max="22" width="4.6" customWidth="1"/>
-    <col min="23" max="23" width="4.13636363636364" customWidth="1"/>
-    <col min="24" max="24" width="7.72727272727273" customWidth="1"/>
-    <col min="25" max="25" width="7.13636363636364" customWidth="1"/>
+    <col min="22" max="22" width="4.59765625" customWidth="1"/>
+    <col min="23" max="23" width="4.1328125" customWidth="1"/>
+    <col min="24" max="24" width="7.73046875" customWidth="1"/>
+    <col min="25" max="25" width="7.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33.75" customHeight="1" spans="1:20">
+    <row r="1" spans="1:20" ht="33.75" customHeight="1">
       <c r="A1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="59" t="s">
+      <c r="C1" s="180" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="60" t="s">
+      <c r="D1" s="180"/>
+      <c r="E1" s="180"/>
+      <c r="F1" s="181" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="59"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="59" t="s">
+      <c r="G1" s="180"/>
+      <c r="H1" s="182"/>
+      <c r="I1" s="180" t="s">
         <v>32</v>
       </c>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="59"/>
-      <c r="O1" s="62" t="s">
+      <c r="J1" s="180"/>
+      <c r="K1" s="180"/>
+      <c r="L1" s="180"/>
+      <c r="M1" s="180"/>
+      <c r="N1" s="180"/>
+      <c r="O1" s="183" t="s">
         <v>33</v>
       </c>
-      <c r="P1" s="63"/>
-      <c r="Q1" s="63"/>
+      <c r="P1" s="59"/>
+      <c r="Q1" s="59"/>
       <c r="S1" t="s">
         <v>34</v>
       </c>
@@ -3629,953 +3107,953 @@
       </c>
     </row>
     <row r="2" spans="1:20">
-      <c r="C2" s="64" t="s">
+      <c r="C2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="64" t="s">
+      <c r="D2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="64" t="s">
+      <c r="E2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="64" t="s">
+      <c r="F2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="64" t="s">
+      <c r="G2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="H2" s="64" t="s">
+      <c r="H2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="I2" s="64" t="s">
+      <c r="I2" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="J2" s="64" t="s">
+      <c r="J2" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="K2" s="64" t="str">
+      <c r="K2" s="60" t="str">
         <f>I2</f>
         <v>input~GASNGA</v>
       </c>
-      <c r="L2" s="64" t="str">
+      <c r="L2" s="60" t="str">
         <f>J2</f>
         <v>input~ELC_gc</v>
       </c>
-      <c r="M2" s="64" t="str">
+      <c r="M2" s="60" t="str">
         <f>K2</f>
         <v>input~GASNGA</v>
       </c>
-      <c r="N2" s="64" t="str">
+      <c r="N2" s="60" t="str">
         <f>L2</f>
         <v>input~ELC_gc</v>
       </c>
-      <c r="O2" s="63"/>
-      <c r="P2" s="63"/>
-      <c r="Q2" s="63"/>
+      <c r="O2" s="184"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
     </row>
     <row r="3" spans="1:20">
-      <c r="C3" s="64">
+      <c r="C3" s="60">
         <v>2020</v>
       </c>
-      <c r="D3" s="64">
+      <c r="D3" s="60">
         <v>2030</v>
       </c>
-      <c r="E3" s="64">
+      <c r="E3" s="60">
         <v>2050</v>
       </c>
-      <c r="F3" s="64">
+      <c r="F3" s="60">
         <f>C3</f>
         <v>2020</v>
       </c>
-      <c r="G3" s="64">
+      <c r="G3" s="60">
         <f t="shared" ref="G3:H3" si="0">D3</f>
         <v>2030</v>
       </c>
-      <c r="H3" s="64">
+      <c r="H3" s="60">
         <f t="shared" si="0"/>
         <v>2050</v>
       </c>
-      <c r="I3" s="64">
+      <c r="I3" s="60">
         <v>2015</v>
       </c>
-      <c r="J3" s="64">
+      <c r="J3" s="60">
         <v>2015</v>
       </c>
-      <c r="K3" s="64">
+      <c r="K3" s="60">
         <v>2030</v>
       </c>
-      <c r="L3" s="64">
+      <c r="L3" s="60">
         <v>2030</v>
       </c>
-      <c r="M3" s="64">
+      <c r="M3" s="60">
         <v>2050</v>
       </c>
-      <c r="N3" s="64">
+      <c r="N3" s="60">
         <v>2050</v>
       </c>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-    </row>
-    <row r="4" ht="26" spans="1:20">
-      <c r="C4" s="65">
+      <c r="O3" s="184"/>
+      <c r="P3" s="59"/>
+      <c r="Q3" s="59"/>
+    </row>
+    <row r="4" spans="1:20" ht="26.25">
+      <c r="C4" s="61">
         <v>2020</v>
       </c>
-      <c r="D4" s="65">
+      <c r="D4" s="61">
         <v>2030</v>
       </c>
-      <c r="E4" s="65" t="s">
+      <c r="E4" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="66">
+      <c r="F4" s="62">
         <v>2015</v>
       </c>
-      <c r="G4" s="65">
+      <c r="G4" s="61">
         <v>2030</v>
       </c>
-      <c r="H4" s="67" t="s">
+      <c r="H4" s="63" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="65" t="s">
+      <c r="I4" s="61" t="s">
         <v>41</v>
       </c>
-      <c r="J4" s="65" t="s">
+      <c r="J4" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="K4" s="68" t="s">
+      <c r="K4" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="L4" s="69" t="s">
+      <c r="L4" s="65" t="s">
         <v>44</v>
       </c>
-      <c r="M4" s="65" t="s">
+      <c r="M4" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="N4" s="65" t="s">
+      <c r="N4" s="61" t="s">
         <v>46</v>
       </c>
-      <c r="O4" s="70"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
+      <c r="O4" s="185"/>
+      <c r="P4" s="59"/>
+      <c r="Q4" s="59"/>
     </row>
     <row r="5" spans="1:20">
-      <c r="C5" s="71">
+      <c r="C5" s="66">
         <v>550</v>
       </c>
-      <c r="D5" s="71">
+      <c r="D5" s="66">
         <v>500</v>
       </c>
-      <c r="E5" s="71">
+      <c r="E5" s="66">
         <v>450</v>
       </c>
-      <c r="F5" s="72">
+      <c r="F5" s="67">
         <v>22</v>
       </c>
-      <c r="G5" s="73">
+      <c r="G5" s="68">
         <v>20</v>
       </c>
-      <c r="H5" s="74">
+      <c r="H5" s="69">
         <v>18</v>
       </c>
-      <c r="I5" s="75">
+      <c r="I5" s="70">
         <v>1.33</v>
       </c>
-      <c r="J5" s="75">
-        <v>0.094</v>
-      </c>
-      <c r="K5" s="76">
+      <c r="J5" s="70">
+        <v>9.4E-2</v>
+      </c>
+      <c r="K5" s="71">
         <v>1.3</v>
       </c>
-      <c r="L5" s="77">
-        <v>0.094</v>
-      </c>
-      <c r="M5" s="75">
+      <c r="L5" s="72">
+        <v>9.4E-2</v>
+      </c>
+      <c r="M5" s="70">
         <v>1.28</v>
       </c>
-      <c r="N5" s="75">
-        <v>0.094</v>
-      </c>
-      <c r="O5" s="78" t="s">
+      <c r="N5" s="70">
+        <v>9.4E-2</v>
+      </c>
+      <c r="O5" s="73" t="s">
         <v>47</v>
       </c>
-      <c r="P5" s="79"/>
-      <c r="Q5" s="79"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
     </row>
     <row r="6" spans="1:20">
-      <c r="C6" s="80">
+      <c r="C6" s="75">
         <v>900</v>
       </c>
-      <c r="D6" s="80">
+      <c r="D6" s="75">
         <v>850</v>
       </c>
-      <c r="E6" s="80">
+      <c r="E6" s="75">
         <v>800</v>
       </c>
-      <c r="F6" s="81">
+      <c r="F6" s="76">
         <v>36</v>
       </c>
-      <c r="G6" s="82">
+      <c r="G6" s="77">
         <v>34</v>
       </c>
-      <c r="H6" s="83">
+      <c r="H6" s="78">
         <v>32</v>
       </c>
-      <c r="I6" s="84">
+      <c r="I6" s="79">
         <v>1.33</v>
       </c>
-      <c r="J6" s="84">
-        <v>1.094</v>
-      </c>
-      <c r="K6" s="85">
+      <c r="J6" s="79">
+        <v>1.0940000000000001</v>
+      </c>
+      <c r="K6" s="80">
         <v>1.3</v>
       </c>
-      <c r="L6" s="86">
-        <v>1.094</v>
-      </c>
-      <c r="M6" s="84">
+      <c r="L6" s="81">
+        <v>1.0940000000000001</v>
+      </c>
+      <c r="M6" s="79">
         <v>1.28</v>
       </c>
-      <c r="N6" s="84">
-        <v>1.094</v>
-      </c>
-      <c r="O6" s="87" t="s">
+      <c r="N6" s="79">
+        <v>1.0940000000000001</v>
+      </c>
+      <c r="O6" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="P6" s="88"/>
-      <c r="Q6" s="88"/>
+      <c r="P6" s="83"/>
+      <c r="Q6" s="83"/>
     </row>
     <row r="7" spans="1:20">
-      <c r="C7" s="71">
+      <c r="C7" s="66">
         <v>1978</v>
       </c>
-      <c r="D7" s="71">
+      <c r="D7" s="66">
         <v>1598</v>
       </c>
-      <c r="E7" s="71">
+      <c r="E7" s="66">
         <v>1450</v>
       </c>
-      <c r="F7" s="72">
+      <c r="F7" s="67">
         <v>57</v>
       </c>
-      <c r="G7" s="73">
+      <c r="G7" s="68">
         <v>31</v>
       </c>
-      <c r="H7" s="74">
+      <c r="H7" s="69">
         <v>28</v>
       </c>
-      <c r="I7" s="75">
+      <c r="I7" s="70">
         <v>1.53</v>
       </c>
-      <c r="J7" s="75">
-        <v>0.094</v>
-      </c>
-      <c r="K7" s="76">
+      <c r="J7" s="70">
+        <v>9.4E-2</v>
+      </c>
+      <c r="K7" s="71">
         <v>1.47</v>
       </c>
-      <c r="L7" s="77">
-        <v>0.094</v>
-      </c>
-      <c r="M7" s="75">
+      <c r="L7" s="72">
+        <v>9.4E-2</v>
+      </c>
+      <c r="M7" s="70">
         <v>1.43</v>
       </c>
-      <c r="N7" s="75">
-        <v>0.094</v>
-      </c>
-      <c r="O7" s="78" t="s">
+      <c r="N7" s="70">
+        <v>9.4E-2</v>
+      </c>
+      <c r="O7" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="P7" s="79"/>
-      <c r="Q7" s="79"/>
+      <c r="P7" s="74"/>
+      <c r="Q7" s="74"/>
     </row>
     <row r="8" spans="1:20">
-      <c r="C8" s="89">
+      <c r="C8" s="84">
         <v>1610</v>
       </c>
-      <c r="D8" s="89">
+      <c r="D8" s="84">
         <v>740</v>
       </c>
-      <c r="E8" s="89">
+      <c r="E8" s="84">
         <v>200</v>
       </c>
-      <c r="F8" s="81">
+      <c r="F8" s="76">
         <v>49</v>
       </c>
-      <c r="G8" s="82">
+      <c r="G8" s="77">
         <v>15</v>
       </c>
-      <c r="H8" s="83">
+      <c r="H8" s="78">
         <v>10</v>
       </c>
-      <c r="I8" s="84">
+      <c r="I8" s="79">
         <v>0</v>
       </c>
-      <c r="J8" s="84">
+      <c r="J8" s="79">
         <v>1.39</v>
       </c>
-      <c r="K8" s="85">
+      <c r="K8" s="80">
         <v>0</v>
       </c>
-      <c r="L8" s="86">
+      <c r="L8" s="81">
         <v>1.19</v>
       </c>
-      <c r="M8" s="84">
+      <c r="M8" s="79">
         <v>0</v>
       </c>
-      <c r="N8" s="84">
+      <c r="N8" s="79">
         <v>1.17</v>
       </c>
-      <c r="O8" s="87" t="s">
+      <c r="O8" s="82" t="s">
         <v>50</v>
       </c>
-      <c r="P8" s="88"/>
-      <c r="Q8" s="88"/>
+      <c r="P8" s="83"/>
+      <c r="Q8" s="83"/>
     </row>
     <row r="9" spans="1:20">
-      <c r="C9" s="90">
+      <c r="C9" s="85">
         <v>2530</v>
       </c>
-      <c r="D9" s="90">
+      <c r="D9" s="85">
         <v>1175</v>
       </c>
-      <c r="E9" s="90">
+      <c r="E9" s="85">
         <v>350</v>
       </c>
-      <c r="F9" s="72">
+      <c r="F9" s="67">
         <v>77</v>
       </c>
-      <c r="G9" s="73">
+      <c r="G9" s="68">
         <v>34</v>
       </c>
-      <c r="H9" s="74">
+      <c r="H9" s="69">
         <v>18</v>
       </c>
-      <c r="I9" s="75">
+      <c r="I9" s="70">
         <v>0</v>
       </c>
-      <c r="J9" s="75">
+      <c r="J9" s="70">
         <v>1.5</v>
       </c>
-      <c r="K9" s="76">
+      <c r="K9" s="71">
         <v>0</v>
       </c>
-      <c r="L9" s="77">
+      <c r="L9" s="72">
         <v>1.25</v>
       </c>
-      <c r="M9" s="75">
+      <c r="M9" s="70">
         <v>0</v>
       </c>
-      <c r="N9" s="75">
+      <c r="N9" s="70">
         <v>1.19</v>
       </c>
-      <c r="O9" s="78" t="s">
+      <c r="O9" s="73" t="s">
         <v>51</v>
       </c>
-      <c r="P9" s="79"/>
-      <c r="Q9" s="79"/>
+      <c r="P9" s="74"/>
+      <c r="Q9" s="74"/>
     </row>
     <row r="10" spans="1:20">
-      <c r="C10" s="89">
+      <c r="C10" s="84">
         <v>1265</v>
       </c>
-      <c r="D10" s="89">
+      <c r="D10" s="84">
         <v>600</v>
       </c>
-      <c r="E10" s="89">
+      <c r="E10" s="84">
         <v>180</v>
       </c>
-      <c r="F10" s="81">
+      <c r="F10" s="76">
         <v>28</v>
       </c>
-      <c r="G10" s="82">
+      <c r="G10" s="77">
         <v>14</v>
       </c>
-      <c r="H10" s="83">
+      <c r="H10" s="78">
         <v>9</v>
       </c>
-      <c r="I10" s="84">
+      <c r="I10" s="79">
         <v>0</v>
       </c>
-      <c r="J10" s="84">
+      <c r="J10" s="79">
         <v>1.3952</v>
       </c>
-      <c r="K10" s="85">
+      <c r="K10" s="80">
         <v>0</v>
       </c>
-      <c r="L10" s="86">
+      <c r="L10" s="81">
         <v>1.268</v>
       </c>
-      <c r="M10" s="84">
+      <c r="M10" s="79">
         <v>0</v>
       </c>
-      <c r="N10" s="84">
+      <c r="N10" s="79">
         <v>1.18</v>
       </c>
-      <c r="O10" s="87" t="s">
+      <c r="O10" s="82" t="s">
         <v>52</v>
       </c>
-      <c r="P10" s="88"/>
-      <c r="Q10" s="88"/>
+      <c r="P10" s="83"/>
+      <c r="Q10" s="83"/>
     </row>
     <row r="11" spans="1:20">
-      <c r="C11" s="90">
+      <c r="C11" s="85">
         <v>1897.5</v>
       </c>
-      <c r="D11" s="90">
+      <c r="D11" s="85">
         <v>715</v>
       </c>
-      <c r="E11" s="90">
+      <c r="E11" s="85">
         <v>300</v>
       </c>
-      <c r="F11" s="72">
+      <c r="F11" s="67">
         <v>41</v>
       </c>
-      <c r="G11" s="73">
+      <c r="G11" s="68">
         <v>17</v>
       </c>
-      <c r="H11" s="74">
+      <c r="H11" s="69">
         <v>15</v>
       </c>
-      <c r="I11" s="75">
+      <c r="I11" s="70">
         <v>0</v>
       </c>
-      <c r="J11" s="75">
+      <c r="J11" s="70">
         <v>1.3952</v>
       </c>
-      <c r="K11" s="76">
+      <c r="K11" s="71">
         <v>0</v>
       </c>
-      <c r="L11" s="77">
+      <c r="L11" s="72">
         <v>1.268</v>
       </c>
-      <c r="M11" s="75">
+      <c r="M11" s="70">
         <v>0</v>
       </c>
-      <c r="N11" s="75">
+      <c r="N11" s="70">
         <v>1.2</v>
       </c>
-      <c r="O11" s="78" t="s">
+      <c r="O11" s="73" t="s">
         <v>53</v>
       </c>
-      <c r="P11" s="79"/>
-      <c r="Q11" s="79"/>
+      <c r="P11" s="74"/>
+      <c r="Q11" s="74"/>
     </row>
     <row r="12" spans="1:20">
-      <c r="C12" s="89">
-        <v>3332.08823529412</v>
-      </c>
-      <c r="D12" s="89">
+      <c r="C12" s="84">
+        <v>3332.0882352941198</v>
+      </c>
+      <c r="D12" s="84">
         <v>1421.39215686275</v>
       </c>
-      <c r="E12" s="89">
+      <c r="E12" s="84">
         <v>600</v>
       </c>
-      <c r="F12" s="81">
-        <v>55.825</v>
-      </c>
-      <c r="G12" s="82">
+      <c r="F12" s="76">
+        <v>55.825000000000003</v>
+      </c>
+      <c r="G12" s="77">
         <v>36.18</v>
       </c>
-      <c r="H12" s="83">
+      <c r="H12" s="78">
         <v>39</v>
       </c>
-      <c r="I12" s="84">
-        <v>1.99666703875969</v>
-      </c>
-      <c r="J12" s="84">
-        <v>0.83712</v>
-      </c>
-      <c r="K12" s="85">
+      <c r="I12" s="79">
+        <v>1.9966670387596901</v>
+      </c>
+      <c r="J12" s="79">
+        <v>0.83711999999999998</v>
+      </c>
+      <c r="K12" s="80">
         <v>1.45562727909392</v>
       </c>
-      <c r="L12" s="86">
-        <v>0.7608</v>
-      </c>
-      <c r="M12" s="84">
-        <v>0.333333333333333</v>
-      </c>
-      <c r="N12" s="84">
-        <v>0.708</v>
-      </c>
-      <c r="O12" s="87" t="s">
+      <c r="L12" s="81">
+        <v>0.76080000000000003</v>
+      </c>
+      <c r="M12" s="79">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="N12" s="79">
+        <v>0.70799999999999996</v>
+      </c>
+      <c r="O12" s="82" t="s">
         <v>54</v>
       </c>
-      <c r="P12" s="88"/>
-      <c r="Q12" s="88"/>
+      <c r="P12" s="83"/>
+      <c r="Q12" s="83"/>
     </row>
     <row r="13" spans="1:20">
-      <c r="C13" s="90">
-        <v>5331.34117647059</v>
-      </c>
-      <c r="D13" s="90">
-        <v>2920.89411764706</v>
-      </c>
-      <c r="E13" s="90">
+      <c r="C13" s="85">
+        <v>5331.3411764705897</v>
+      </c>
+      <c r="D13" s="85">
+        <v>2920.8941176470598</v>
+      </c>
+      <c r="E13" s="85">
         <v>1100</v>
       </c>
-      <c r="F13" s="72">
-        <v>94.9025</v>
-      </c>
-      <c r="G13" s="73">
-        <v>63.315</v>
-      </c>
-      <c r="H13" s="74">
+      <c r="F13" s="67">
+        <v>94.902500000000003</v>
+      </c>
+      <c r="G13" s="68">
+        <v>63.314999999999998</v>
+      </c>
+      <c r="H13" s="69">
         <v>48.75</v>
       </c>
-      <c r="I13" s="75">
-        <v>1.99666703875969</v>
-      </c>
-      <c r="J13" s="75">
-        <v>0.83712</v>
-      </c>
-      <c r="K13" s="76">
+      <c r="I13" s="70">
+        <v>1.9966670387596901</v>
+      </c>
+      <c r="J13" s="70">
+        <v>0.83711999999999998</v>
+      </c>
+      <c r="K13" s="71">
         <v>1.45562727909392</v>
       </c>
-      <c r="L13" s="77">
-        <v>0.7608</v>
-      </c>
-      <c r="M13" s="75">
-        <v>0.333333333333333</v>
-      </c>
-      <c r="N13" s="75">
+      <c r="L13" s="72">
+        <v>0.76080000000000003</v>
+      </c>
+      <c r="M13" s="70">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="N13" s="70">
         <v>0.72</v>
       </c>
-      <c r="O13" s="78" t="s">
+      <c r="O13" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="P13" s="79"/>
-      <c r="Q13" s="79"/>
+      <c r="P13" s="74"/>
+      <c r="Q13" s="74"/>
     </row>
     <row r="14" spans="1:20">
-      <c r="C14" s="91">
+      <c r="C14" s="86">
         <v>1200</v>
       </c>
-      <c r="D14" s="91">
+      <c r="D14" s="86">
         <v>733</v>
       </c>
-      <c r="E14" s="91">
+      <c r="E14" s="86">
         <v>263</v>
       </c>
-      <c r="F14" s="92">
+      <c r="F14" s="87">
         <v>42</v>
       </c>
-      <c r="G14" s="93">
+      <c r="G14" s="88">
         <v>22</v>
       </c>
-      <c r="H14" s="94">
+      <c r="H14" s="89">
         <v>9</v>
       </c>
-      <c r="I14" s="95">
+      <c r="I14" s="90">
         <v>0</v>
       </c>
-      <c r="J14" s="96">
+      <c r="J14" s="91">
         <v>0.01</v>
       </c>
-      <c r="K14" s="97">
+      <c r="K14" s="92">
         <v>0</v>
       </c>
-      <c r="L14" s="98">
+      <c r="L14" s="93">
         <v>0.01</v>
       </c>
-      <c r="M14" s="96">
+      <c r="M14" s="91">
         <v>0</v>
       </c>
-      <c r="N14" s="96">
+      <c r="N14" s="91">
         <v>0.01</v>
       </c>
-      <c r="O14" s="99" t="s">
+      <c r="O14" s="94" t="s">
         <v>56</v>
       </c>
-      <c r="P14" s="100"/>
-      <c r="Q14" s="100"/>
+      <c r="P14" s="95"/>
+      <c r="Q14" s="95"/>
     </row>
     <row r="15" spans="1:20">
-      <c r="C15" s="101">
+      <c r="C15" s="96">
         <v>450</v>
       </c>
-      <c r="D15" s="101">
+      <c r="D15" s="96">
         <v>450</v>
       </c>
-      <c r="E15" s="101">
+      <c r="E15" s="96">
         <v>450</v>
       </c>
-      <c r="F15" s="102">
+      <c r="F15" s="97">
         <v>18</v>
       </c>
-      <c r="G15" s="103">
+      <c r="G15" s="98">
         <v>18</v>
       </c>
-      <c r="H15" s="104">
+      <c r="H15" s="99">
         <v>18</v>
       </c>
-      <c r="I15" s="105">
+      <c r="I15" s="100">
         <v>0.265822784810126</v>
       </c>
-      <c r="J15" s="106">
+      <c r="J15" s="101">
         <v>0.06</v>
       </c>
-      <c r="K15" s="107">
+      <c r="K15" s="102">
         <v>0.265822784810126</v>
       </c>
-      <c r="L15" s="108">
+      <c r="L15" s="103">
         <v>0.06</v>
       </c>
-      <c r="M15" s="106">
+      <c r="M15" s="101">
         <v>0.265822784810126</v>
       </c>
-      <c r="N15" s="106">
+      <c r="N15" s="101">
         <v>0.06</v>
       </c>
-      <c r="O15" s="109" t="s">
+      <c r="O15" s="104" t="s">
         <v>57</v>
       </c>
-      <c r="P15" s="110"/>
-      <c r="Q15" s="110"/>
+      <c r="P15" s="105"/>
+      <c r="Q15" s="105"/>
     </row>
     <row r="16" spans="1:20">
-      <c r="C16" s="111">
+      <c r="C16" s="106">
         <v>200</v>
       </c>
-      <c r="D16" s="111">
+      <c r="D16" s="106">
         <v>200</v>
       </c>
-      <c r="E16" s="111">
+      <c r="E16" s="106">
         <v>200</v>
       </c>
-      <c r="F16" s="112">
+      <c r="F16" s="107">
         <v>20</v>
       </c>
-      <c r="G16" s="113">
+      <c r="G16" s="108">
         <v>20</v>
       </c>
-      <c r="H16" s="114">
+      <c r="H16" s="109">
         <v>20</v>
       </c>
-      <c r="I16" s="115">
-        <v>0.013</v>
-      </c>
-      <c r="J16" s="116">
-        <v>0.036</v>
-      </c>
-      <c r="K16" s="117">
-        <v>0.013</v>
-      </c>
-      <c r="L16" s="118">
-        <v>0.036</v>
-      </c>
-      <c r="M16" s="116">
-        <v>0.013</v>
-      </c>
-      <c r="N16" s="116">
-        <v>0.036</v>
-      </c>
-      <c r="O16" s="119" t="s">
+      <c r="I16" s="110">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="J16" s="111">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="K16" s="112">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="L16" s="113">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="M16" s="111">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="N16" s="111">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="O16" s="114" t="s">
         <v>58</v>
       </c>
-      <c r="P16" s="120"/>
-      <c r="Q16" s="120"/>
+      <c r="P16" s="115"/>
+      <c r="Q16" s="115"/>
     </row>
     <row r="17" spans="1:25">
-      <c r="C17" s="101">
+      <c r="C17" s="96">
         <v>175</v>
       </c>
-      <c r="D17" s="101">
+      <c r="D17" s="96">
         <v>175</v>
       </c>
-      <c r="E17" s="101">
+      <c r="E17" s="96">
         <v>175</v>
       </c>
-      <c r="F17" s="102">
+      <c r="F17" s="97">
         <v>5</v>
       </c>
-      <c r="G17" s="103">
+      <c r="G17" s="98">
         <v>5</v>
       </c>
-      <c r="H17" s="104">
+      <c r="H17" s="99">
         <v>5</v>
       </c>
-      <c r="I17" s="105">
-        <v>0.014</v>
-      </c>
-      <c r="J17" s="106">
+      <c r="I17" s="100">
+        <v>1.4E-2</v>
+      </c>
+      <c r="J17" s="101">
         <v>0</v>
       </c>
-      <c r="K17" s="107">
-        <v>0.014</v>
-      </c>
-      <c r="L17" s="108">
+      <c r="K17" s="102">
+        <v>1.4E-2</v>
+      </c>
+      <c r="L17" s="103">
         <v>0</v>
       </c>
-      <c r="M17" s="106">
-        <v>0.014</v>
-      </c>
-      <c r="N17" s="106">
+      <c r="M17" s="101">
+        <v>1.4E-2</v>
+      </c>
+      <c r="N17" s="101">
         <v>0</v>
       </c>
-      <c r="O17" s="109" t="s">
+      <c r="O17" s="104" t="s">
         <v>59</v>
       </c>
-      <c r="P17" s="110"/>
-      <c r="Q17" s="110"/>
+      <c r="P17" s="105"/>
+      <c r="Q17" s="105"/>
     </row>
     <row r="18" spans="1:25">
-      <c r="C18" s="121">
+      <c r="C18" s="116">
         <v>1000</v>
       </c>
-      <c r="D18" s="121">
+      <c r="D18" s="116">
         <v>720</v>
       </c>
-      <c r="E18" s="121">
+      <c r="E18" s="116">
         <v>364</v>
       </c>
-      <c r="F18" s="122">
+      <c r="F18" s="117">
         <v>50</v>
       </c>
-      <c r="G18" s="123">
+      <c r="G18" s="118">
         <v>31</v>
       </c>
-      <c r="H18" s="124">
+      <c r="H18" s="119">
         <v>18</v>
       </c>
-      <c r="I18" s="125">
+      <c r="I18" s="120">
         <v>0.2389</v>
       </c>
-      <c r="J18" s="126">
-        <v>0.03056</v>
-      </c>
-      <c r="K18" s="127">
+      <c r="J18" s="121">
+        <v>3.056E-2</v>
+      </c>
+      <c r="K18" s="122">
         <v>0.2389</v>
       </c>
-      <c r="L18" s="128">
-        <v>0.03056</v>
-      </c>
-      <c r="M18" s="126">
+      <c r="L18" s="123">
+        <v>3.056E-2</v>
+      </c>
+      <c r="M18" s="121">
         <v>0.2389</v>
       </c>
-      <c r="N18" s="126">
-        <v>0.03056</v>
-      </c>
-      <c r="O18" s="129" t="s">
+      <c r="N18" s="121">
+        <v>3.056E-2</v>
+      </c>
+      <c r="O18" s="124" t="s">
         <v>60</v>
       </c>
-      <c r="P18" s="130"/>
-      <c r="Q18" s="130"/>
+      <c r="P18" s="125"/>
+      <c r="Q18" s="125"/>
     </row>
     <row r="19" spans="1:25">
-      <c r="C19" s="131">
+      <c r="C19" s="126">
         <v>1556</v>
       </c>
-      <c r="D19" s="131">
+      <c r="D19" s="126">
         <v>1143</v>
       </c>
-      <c r="E19" s="132">
+      <c r="E19" s="127">
         <v>673</v>
       </c>
-      <c r="F19" s="133">
+      <c r="F19" s="128">
         <v>54</v>
       </c>
-      <c r="G19" s="134">
+      <c r="G19" s="129">
         <v>40</v>
       </c>
-      <c r="H19" s="135">
+      <c r="H19" s="130">
         <v>24</v>
       </c>
-      <c r="I19" s="136">
-        <v>0.035</v>
-      </c>
-      <c r="J19" s="137">
+      <c r="I19" s="131">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="J19" s="132">
         <v>0.02</v>
       </c>
-      <c r="K19" s="138">
-        <v>0.035</v>
-      </c>
-      <c r="L19" s="139">
+      <c r="K19" s="133">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="L19" s="134">
         <v>0.02</v>
       </c>
-      <c r="M19" s="137">
-        <v>0.035</v>
-      </c>
-      <c r="N19" s="137">
+      <c r="M19" s="132">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="N19" s="132">
         <v>0.02</v>
       </c>
-      <c r="O19" s="140" t="s">
+      <c r="O19" s="135" t="s">
         <v>61</v>
       </c>
-      <c r="P19" s="141"/>
-      <c r="Q19" s="141"/>
+      <c r="P19" s="136"/>
+      <c r="Q19" s="136"/>
     </row>
     <row r="20" spans="1:25">
-      <c r="C20" s="142">
+      <c r="C20" s="137">
         <v>2332</v>
       </c>
-      <c r="D20" s="142">
+      <c r="D20" s="137">
         <v>1511</v>
       </c>
-      <c r="E20" s="142">
+      <c r="E20" s="137">
         <v>965</v>
       </c>
-      <c r="F20" s="143">
+      <c r="F20" s="138">
         <v>163</v>
       </c>
-      <c r="G20" s="144">
+      <c r="G20" s="139">
         <v>106</v>
       </c>
-      <c r="H20" s="145">
+      <c r="H20" s="140">
         <v>68</v>
       </c>
-      <c r="I20" s="146">
-        <v>0.463266666666667</v>
-      </c>
-      <c r="J20" s="147">
+      <c r="I20" s="141">
+        <v>0.46326666666666699</v>
+      </c>
+      <c r="J20" s="142">
         <v>1.91881040892193</v>
       </c>
-      <c r="K20" s="148">
-        <v>0.39244195142278</v>
-      </c>
-      <c r="L20" s="149">
+      <c r="K20" s="143">
+        <v>0.39244195142277999</v>
+      </c>
+      <c r="L20" s="144">
         <v>1.60098120886331</v>
       </c>
-      <c r="M20" s="147">
+      <c r="M20" s="142">
         <v>0.37890902062421</v>
       </c>
-      <c r="N20" s="147">
-        <v>1.56940834539103</v>
-      </c>
-      <c r="O20" s="150" t="s">
+      <c r="N20" s="142">
+        <v>1.5694083453910299</v>
+      </c>
+      <c r="O20" s="145" t="s">
         <v>62</v>
       </c>
-      <c r="P20" s="130"/>
-      <c r="Q20" s="130"/>
+      <c r="P20" s="125"/>
+      <c r="Q20" s="125"/>
     </row>
     <row r="21" spans="1:25">
-      <c r="C21" s="151">
-        <v>769.876819708847</v>
-      </c>
-      <c r="D21" s="151">
-        <v>648.044461034383</v>
-      </c>
-      <c r="E21" s="151">
-        <v>518.290592438013</v>
-      </c>
-      <c r="F21" s="152">
+      <c r="C21" s="146">
+        <v>769.87681970884705</v>
+      </c>
+      <c r="D21" s="146">
+        <v>648.04446103438295</v>
+      </c>
+      <c r="E21" s="146">
+        <v>518.29059243801305</v>
+      </c>
+      <c r="F21" s="147">
         <v>26.9456886898096</v>
       </c>
-      <c r="G21" s="153">
-        <v>22.6815561362034</v>
-      </c>
-      <c r="H21" s="154">
+      <c r="G21" s="148">
+        <v>22.681556136203401</v>
+      </c>
+      <c r="H21" s="149">
         <v>18.1401707353305</v>
       </c>
-      <c r="I21" s="155">
-        <v>2.77777777777778</v>
-      </c>
-      <c r="J21" s="156">
-        <v>2.22222222222222</v>
-      </c>
-      <c r="K21" s="157">
-        <v>1.66666666666667</v>
-      </c>
-      <c r="L21" s="158">
-        <v>1.38888888888889</v>
-      </c>
-      <c r="M21" s="156">
-        <v>1.13888888888889</v>
-      </c>
-      <c r="N21" s="156">
+      <c r="I21" s="150">
+        <v>2.7777777777777799</v>
+      </c>
+      <c r="J21" s="151">
+        <v>2.2222222222222201</v>
+      </c>
+      <c r="K21" s="152">
+        <v>1.6666666666666701</v>
+      </c>
+      <c r="L21" s="153">
+        <v>1.3888888888888899</v>
+      </c>
+      <c r="M21" s="151">
+        <v>1.1388888888888899</v>
+      </c>
+      <c r="N21" s="151">
         <v>0.3</v>
       </c>
-      <c r="O21" s="159" t="s">
+      <c r="O21" s="154" t="s">
         <v>63</v>
       </c>
-      <c r="P21" s="160"/>
-      <c r="Q21" s="160"/>
+      <c r="P21" s="155"/>
+      <c r="Q21" s="155"/>
     </row>
     <row r="22" spans="1:25">
-      <c r="C22" s="161">
-        <v>1259.79843225084</v>
-      </c>
-      <c r="D22" s="161">
-        <v>894.301356227448</v>
-      </c>
-      <c r="E22" s="161">
+      <c r="C22" s="156">
+        <v>1259.7984322508401</v>
+      </c>
+      <c r="D22" s="156">
+        <v>894.30135622744797</v>
+      </c>
+      <c r="E22" s="156">
         <v>495</v>
       </c>
-      <c r="F22" s="162">
-        <v>44.0929451287794</v>
-      </c>
-      <c r="G22" s="163">
-        <v>31.3005474679607</v>
-      </c>
-      <c r="H22" s="164">
-        <v>17.325</v>
-      </c>
-      <c r="I22" s="165">
+      <c r="F22" s="157">
+        <v>44.092945128779398</v>
+      </c>
+      <c r="G22" s="158">
+        <v>31.300547467960701</v>
+      </c>
+      <c r="H22" s="159">
+        <v>17.324999999999999</v>
+      </c>
+      <c r="I22" s="160">
         <v>2</v>
       </c>
-      <c r="J22" s="166">
+      <c r="J22" s="161">
         <v>0.3</v>
       </c>
-      <c r="K22" s="167">
+      <c r="K22" s="162">
         <v>1.80555555555556</v>
       </c>
-      <c r="L22" s="168">
+      <c r="L22" s="163">
         <v>0.3</v>
       </c>
-      <c r="M22" s="166">
+      <c r="M22" s="161">
         <v>1.5</v>
       </c>
-      <c r="N22" s="166">
+      <c r="N22" s="161">
         <v>0.3</v>
       </c>
-      <c r="O22" s="169" t="s">
+      <c r="O22" s="164" t="s">
         <v>64</v>
       </c>
-      <c r="P22" s="170"/>
-      <c r="Q22" s="170"/>
+      <c r="P22" s="165"/>
+      <c r="Q22" s="165"/>
     </row>
     <row r="23" spans="1:25">
-      <c r="C23" s="171">
+      <c r="C23" s="166">
         <v>174</v>
       </c>
-      <c r="D23" s="171">
+      <c r="D23" s="166">
         <v>174</v>
       </c>
-      <c r="E23" s="171">
+      <c r="E23" s="166">
         <v>174</v>
       </c>
-      <c r="F23" s="172">
+      <c r="F23" s="167">
         <v>3</v>
       </c>
-      <c r="G23" s="173">
+      <c r="G23" s="168">
         <v>3</v>
       </c>
-      <c r="H23" s="174">
+      <c r="H23" s="169">
         <v>3</v>
       </c>
-      <c r="I23" s="175">
+      <c r="I23" s="170">
         <v>0</v>
       </c>
-      <c r="J23" s="176">
-        <v>0.205882352941176</v>
-      </c>
-      <c r="K23" s="177">
+      <c r="J23" s="171">
+        <v>0.20588235294117599</v>
+      </c>
+      <c r="K23" s="172">
         <v>0</v>
       </c>
-      <c r="L23" s="178">
-        <v>0.205882352941176</v>
-      </c>
-      <c r="M23" s="176">
+      <c r="L23" s="173">
+        <v>0.20588235294117599</v>
+      </c>
+      <c r="M23" s="171">
         <v>0</v>
       </c>
-      <c r="N23" s="176">
-        <v>0.205882352941176</v>
-      </c>
-      <c r="O23" s="179" t="s">
+      <c r="N23" s="171">
+        <v>0.20588235294117599</v>
+      </c>
+      <c r="O23" s="174" t="s">
         <v>65</v>
       </c>
-      <c r="P23" s="160"/>
-      <c r="Q23" s="160"/>
-    </row>
-    <row r="26" ht="17.75" spans="1:25">
+      <c r="P23" s="155"/>
+      <c r="Q23" s="155"/>
+    </row>
+    <row r="26" spans="1:25" ht="16.899999999999999">
       <c r="C26" s="53" t="s">
         <v>66</v>
       </c>
@@ -4583,7 +4061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" ht="15.25" spans="1:25">
+    <row r="27" spans="1:25">
       <c r="A27" s="54" t="s">
         <v>4</v>
       </c>
@@ -4706,7 +4184,7 @@
       </c>
       <c r="J28" s="9">
         <f t="shared" si="2"/>
-        <v>0.094</v>
+        <v>9.4E-2</v>
       </c>
       <c r="K28" s="9">
         <f t="shared" si="2"/>
@@ -4714,7 +4192,7 @@
       </c>
       <c r="L28" s="9">
         <f t="shared" si="2"/>
-        <v>0.094</v>
+        <v>9.4E-2</v>
       </c>
       <c r="M28" s="9">
         <f t="shared" si="2"/>
@@ -4722,16 +4200,16 @@
       </c>
       <c r="N28" s="9">
         <f t="shared" si="2"/>
-        <v>0.094</v>
-      </c>
-      <c r="O28" s="180" t="s">
+        <v>9.4E-2</v>
+      </c>
+      <c r="O28" s="175" t="s">
         <v>70</v>
       </c>
       <c r="P28">
         <v>25</v>
       </c>
       <c r="Q28">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="S28" t="str">
         <f>IF(O28="","*","PRE")</f>
@@ -4793,25 +4271,25 @@
         <f t="shared" si="4"/>
         <v>1.33</v>
       </c>
-      <c r="J29" s="181">
+      <c r="J29" s="176">
         <f t="shared" si="4"/>
-        <v>1.094</v>
+        <v>1.0940000000000001</v>
       </c>
       <c r="K29" s="9">
         <f t="shared" si="4"/>
         <v>1.3</v>
       </c>
-      <c r="L29" s="181">
+      <c r="L29" s="176">
         <f t="shared" si="4"/>
-        <v>1.094</v>
+        <v>1.0940000000000001</v>
       </c>
       <c r="M29" s="9">
         <f t="shared" si="4"/>
         <v>1.28</v>
       </c>
-      <c r="N29" s="181">
+      <c r="N29" s="176">
         <f t="shared" si="4"/>
-        <v>1.094</v>
+        <v>1.0940000000000001</v>
       </c>
       <c r="O29" t="s">
         <v>73</v>
@@ -4820,7 +4298,7 @@
         <v>25</v>
       </c>
       <c r="Q29">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="S29" t="str">
         <f t="shared" ref="S29:S39" si="5">IF(O29="","*","PRE")</f>
@@ -4884,7 +4362,7 @@
       </c>
       <c r="J30" s="9">
         <f t="shared" si="7"/>
-        <v>0.094</v>
+        <v>9.4E-2</v>
       </c>
       <c r="K30" s="9">
         <f t="shared" si="7"/>
@@ -4892,7 +4370,7 @@
       </c>
       <c r="L30" s="9">
         <f t="shared" si="7"/>
-        <v>0.094</v>
+        <v>9.4E-2</v>
       </c>
       <c r="M30" s="9">
         <f t="shared" si="7"/>
@@ -4900,9 +4378,9 @@
       </c>
       <c r="N30" s="9">
         <f t="shared" si="7"/>
-        <v>0.094</v>
-      </c>
-      <c r="O30" s="180" t="s">
+        <v>9.4E-2</v>
+      </c>
+      <c r="O30" s="175" t="s">
         <v>70</v>
       </c>
       <c r="S30" t="str">
@@ -4983,7 +4461,7 @@
         <v>25</v>
       </c>
       <c r="Q31">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="S31" t="str">
         <f t="shared" si="5"/>
@@ -5056,7 +4534,7 @@
         <f t="shared" si="9"/>
         <v>1.19</v>
       </c>
-      <c r="O32" s="180" t="s">
+      <c r="O32" s="175" t="s">
         <v>70</v>
       </c>
       <c r="S32" t="str">
@@ -5137,7 +4615,7 @@
         <v>25</v>
       </c>
       <c r="Q33">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="S33" t="str">
         <f t="shared" si="5"/>
@@ -5210,7 +4688,7 @@
         <f t="shared" si="11"/>
         <v>1.2</v>
       </c>
-      <c r="O34" s="180" t="s">
+      <c r="O34" s="175" t="s">
         <v>70</v>
       </c>
       <c r="S34" t="str">
@@ -5247,7 +4725,7 @@
       </c>
       <c r="C35" s="38">
         <f t="shared" ref="C35:N35" si="12">C12</f>
-        <v>3332.08823529412</v>
+        <v>3332.0882352941198</v>
       </c>
       <c r="D35" s="38">
         <f t="shared" si="12"/>
@@ -5259,7 +4737,7 @@
       </c>
       <c r="F35" s="38">
         <f t="shared" si="12"/>
-        <v>55.825</v>
+        <v>55.825000000000003</v>
       </c>
       <c r="G35" s="38">
         <f t="shared" si="12"/>
@@ -5271,11 +4749,11 @@
       </c>
       <c r="I35" s="9">
         <f t="shared" si="12"/>
-        <v>1.99666703875969</v>
+        <v>1.9966670387596901</v>
       </c>
       <c r="J35" s="9">
         <f t="shared" si="12"/>
-        <v>0.83712</v>
+        <v>0.83711999999999998</v>
       </c>
       <c r="K35" s="9">
         <f t="shared" si="12"/>
@@ -5283,15 +4761,15 @@
       </c>
       <c r="L35" s="9">
         <f t="shared" si="12"/>
-        <v>0.7608</v>
+        <v>0.76080000000000003</v>
       </c>
       <c r="M35" s="9">
         <f t="shared" si="12"/>
-        <v>0.333333333333333</v>
+        <v>0.33333333333333298</v>
       </c>
       <c r="N35" s="9">
         <f t="shared" si="12"/>
-        <v>0.708</v>
+        <v>0.70799999999999996</v>
       </c>
       <c r="O35" t="s">
         <v>76</v>
@@ -5300,7 +4778,7 @@
         <v>25</v>
       </c>
       <c r="Q35">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="S35" t="str">
         <f t="shared" si="5"/>
@@ -5330,11 +4808,11 @@
     <row r="36" spans="1:25">
       <c r="C36" s="38">
         <f t="shared" ref="C36:N36" si="13">C13</f>
-        <v>5331.34117647059</v>
+        <v>5331.3411764705897</v>
       </c>
       <c r="D36" s="38">
         <f t="shared" si="13"/>
-        <v>2920.89411764706</v>
+        <v>2920.8941176470598</v>
       </c>
       <c r="E36" s="38">
         <f t="shared" si="13"/>
@@ -5342,11 +4820,11 @@
       </c>
       <c r="F36" s="38">
         <f t="shared" si="13"/>
-        <v>94.9025</v>
+        <v>94.902500000000003</v>
       </c>
       <c r="G36" s="38">
         <f t="shared" si="13"/>
-        <v>63.315</v>
+        <v>63.314999999999998</v>
       </c>
       <c r="H36" s="38">
         <f t="shared" si="13"/>
@@ -5354,11 +4832,11 @@
       </c>
       <c r="I36" s="9">
         <f t="shared" si="13"/>
-        <v>1.99666703875969</v>
+        <v>1.9966670387596901</v>
       </c>
       <c r="J36" s="9">
         <f t="shared" si="13"/>
-        <v>0.83712</v>
+        <v>0.83711999999999998</v>
       </c>
       <c r="K36" s="9">
         <f t="shared" si="13"/>
@@ -5366,17 +4844,17 @@
       </c>
       <c r="L36" s="9">
         <f t="shared" si="13"/>
-        <v>0.7608</v>
+        <v>0.76080000000000003</v>
       </c>
       <c r="M36" s="9">
         <f t="shared" si="13"/>
-        <v>0.333333333333333</v>
+        <v>0.33333333333333298</v>
       </c>
       <c r="N36" s="9">
         <f t="shared" si="13"/>
         <v>0.72</v>
       </c>
-      <c r="O36" s="180" t="s">
+      <c r="O36" s="175" t="s">
         <v>70</v>
       </c>
       <c r="S36" t="str">
@@ -5407,15 +4885,15 @@
     <row r="37" spans="1:25">
       <c r="C37" s="38">
         <f t="shared" ref="C37:N37" si="14">C21</f>
-        <v>769.876819708847</v>
+        <v>769.87681970884705</v>
       </c>
       <c r="D37" s="38">
         <f t="shared" si="14"/>
-        <v>648.044461034383</v>
+        <v>648.04446103438295</v>
       </c>
       <c r="E37" s="38">
         <f t="shared" si="14"/>
-        <v>518.290592438013</v>
+        <v>518.29059243801305</v>
       </c>
       <c r="F37" s="38">
         <f t="shared" si="14"/>
@@ -5423,7 +4901,7 @@
       </c>
       <c r="G37" s="38">
         <f t="shared" si="14"/>
-        <v>22.6815561362034</v>
+        <v>22.681556136203401</v>
       </c>
       <c r="H37" s="38">
         <f t="shared" si="14"/>
@@ -5431,29 +4909,29 @@
       </c>
       <c r="I37" s="9">
         <f t="shared" si="14"/>
-        <v>2.77777777777778</v>
+        <v>2.7777777777777799</v>
       </c>
       <c r="J37" s="9">
         <f t="shared" si="14"/>
-        <v>2.22222222222222</v>
+        <v>2.2222222222222201</v>
       </c>
       <c r="K37" s="9">
         <f t="shared" si="14"/>
-        <v>1.66666666666667</v>
+        <v>1.6666666666666701</v>
       </c>
       <c r="L37" s="9">
         <f t="shared" si="14"/>
-        <v>1.38888888888889</v>
+        <v>1.3888888888888899</v>
       </c>
       <c r="M37" s="9">
         <f t="shared" si="14"/>
-        <v>1.13888888888889</v>
+        <v>1.1388888888888899</v>
       </c>
       <c r="N37" s="9">
         <f t="shared" si="14"/>
         <v>0.3</v>
       </c>
-      <c r="O37" s="180" t="s">
+      <c r="O37" s="175" t="s">
         <v>70</v>
       </c>
       <c r="S37" t="str">
@@ -5484,11 +4962,11 @@
     <row r="38" spans="1:25">
       <c r="C38" s="38">
         <f t="shared" ref="C38:N38" si="15">C22</f>
-        <v>1259.79843225084</v>
+        <v>1259.7984322508401</v>
       </c>
       <c r="D38" s="38">
         <f t="shared" si="15"/>
-        <v>894.301356227448</v>
+        <v>894.30135622744797</v>
       </c>
       <c r="E38" s="38">
         <f t="shared" si="15"/>
@@ -5496,15 +4974,15 @@
       </c>
       <c r="F38" s="38">
         <f t="shared" si="15"/>
-        <v>44.0929451287794</v>
+        <v>44.092945128779398</v>
       </c>
       <c r="G38" s="38">
         <f t="shared" si="15"/>
-        <v>31.3005474679607</v>
+        <v>31.300547467960701</v>
       </c>
       <c r="H38" s="38">
         <f t="shared" si="15"/>
-        <v>17.325</v>
+        <v>17.324999999999999</v>
       </c>
       <c r="I38" s="9">
         <f t="shared" si="15"/>
@@ -5530,7 +5008,7 @@
         <f t="shared" si="15"/>
         <v>0.3</v>
       </c>
-      <c r="O38" s="180" t="s">
+      <c r="O38" s="175" t="s">
         <v>70</v>
       </c>
       <c r="S38" t="str">
@@ -5559,77 +5037,77 @@
       </c>
     </row>
     <row r="39" spans="1:25">
-      <c r="A39" s="182" t="str">
+      <c r="A39" s="177" t="str">
         <f>A35</f>
         <v>HH2</v>
       </c>
-      <c r="B39" s="182" t="s">
+      <c r="B39" s="177" t="s">
         <v>69</v>
       </c>
-      <c r="C39" s="183">
+      <c r="C39" s="178">
         <f>C29</f>
         <v>900</v>
       </c>
-      <c r="D39" s="183">
+      <c r="D39" s="178">
         <f t="shared" ref="D39:H39" si="16">D29</f>
         <v>850</v>
       </c>
-      <c r="E39" s="183">
+      <c r="E39" s="178">
         <f t="shared" si="16"/>
         <v>800</v>
       </c>
-      <c r="F39" s="183">
+      <c r="F39" s="178">
         <f t="shared" si="16"/>
         <v>36</v>
       </c>
-      <c r="G39" s="183">
+      <c r="G39" s="178">
         <f t="shared" si="16"/>
         <v>34</v>
       </c>
-      <c r="H39" s="183">
+      <c r="H39" s="178">
         <f t="shared" si="16"/>
         <v>32</v>
       </c>
-      <c r="I39" s="184">
+      <c r="I39" s="179">
         <v>1.25</v>
       </c>
-      <c r="J39" s="184">
+      <c r="J39" s="179">
         <v>0.12</v>
       </c>
-      <c r="K39" s="184">
+      <c r="K39" s="179">
         <v>1.25</v>
       </c>
-      <c r="L39" s="184">
+      <c r="L39" s="179">
         <v>0.12</v>
       </c>
-      <c r="M39" s="184">
+      <c r="M39" s="179">
         <v>1.25</v>
       </c>
-      <c r="N39" s="184">
+      <c r="N39" s="179">
         <v>0.12</v>
       </c>
-      <c r="O39" s="182" t="s">
+      <c r="O39" s="177" t="s">
         <v>77</v>
       </c>
-      <c r="P39" s="182">
+      <c r="P39" s="177">
         <v>25</v>
       </c>
-      <c r="Q39" s="182">
-        <v>31.536</v>
-      </c>
-      <c r="R39" s="182"/>
-      <c r="S39" s="182" t="str">
+      <c r="Q39" s="177">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="R39" s="177"/>
+      <c r="S39" s="177" t="str">
         <f t="shared" si="5"/>
         <v>PRE</v>
       </c>
-      <c r="T39" s="182" t="str">
+      <c r="T39" s="177" t="str">
         <f t="shared" si="6"/>
         <v>H2prd_Gas_ATR_CCS</v>
       </c>
-      <c r="U39" s="182" t="s">
+      <c r="U39" s="177" t="s">
         <v>78</v>
       </c>
-      <c r="V39" s="182" t="s">
+      <c r="V39" s="177" t="s">
         <v>71</v>
       </c>
       <c r="W39" t="s">
@@ -5650,39 +5128,37 @@
     <mergeCell ref="O1:O4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B3:Q12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9" style="52"/>
-    <col min="2" max="2" width="12.8636363636364" style="52" customWidth="1"/>
-    <col min="3" max="3" width="8.86363636363636" style="52" customWidth="1"/>
-    <col min="4" max="4" width="14.8636363636364" style="52" customWidth="1"/>
+    <col min="2" max="2" width="12.86328125" style="52" customWidth="1"/>
+    <col min="3" max="3" width="8.86328125" style="52" customWidth="1"/>
+    <col min="4" max="4" width="14.86328125" style="52" customWidth="1"/>
     <col min="5" max="5" width="9" style="52" customWidth="1"/>
-    <col min="6" max="6" width="10.2636363636364" style="52" customWidth="1"/>
-    <col min="7" max="7" width="4.6" style="52" customWidth="1"/>
-    <col min="8" max="8" width="11.6" style="52" customWidth="1"/>
-    <col min="9" max="9" width="11.2636363636364" style="52" customWidth="1"/>
-    <col min="10" max="10" width="11.4" style="52" customWidth="1"/>
-    <col min="11" max="11" width="5.6" style="52" customWidth="1"/>
+    <col min="6" max="6" width="10.265625" style="52" customWidth="1"/>
+    <col min="7" max="7" width="4.59765625" style="52" customWidth="1"/>
+    <col min="8" max="8" width="11.59765625" style="52" customWidth="1"/>
+    <col min="9" max="9" width="11.265625" style="52" customWidth="1"/>
+    <col min="10" max="10" width="11.3984375" style="52" customWidth="1"/>
+    <col min="11" max="11" width="5.59765625" style="52" customWidth="1"/>
     <col min="12" max="12" width="9" style="52"/>
-    <col min="13" max="13" width="11.2636363636364" style="52" customWidth="1"/>
-    <col min="14" max="14" width="12.8636363636364" style="52" customWidth="1"/>
-    <col min="15" max="15" width="15.2636363636364" style="52" customWidth="1"/>
-    <col min="16" max="16" width="4.6" style="52" customWidth="1"/>
+    <col min="13" max="13" width="11.265625" style="52" customWidth="1"/>
+    <col min="14" max="14" width="12.86328125" style="52" customWidth="1"/>
+    <col min="15" max="15" width="15.265625" style="52" customWidth="1"/>
+    <col min="16" max="16" width="4.59765625" style="52" customWidth="1"/>
     <col min="17" max="17" width="5" style="52" customWidth="1"/>
     <col min="18" max="16384" width="9" style="52"/>
   </cols>
   <sheetData>
-    <row r="3" ht="17.75" spans="2:17">
+    <row r="3" spans="2:17" ht="16.899999999999999">
       <c r="D3" s="53" t="s">
         <v>79</v>
       </c>
@@ -5694,7 +5170,7 @@
       <c r="P3" s="54"/>
       <c r="Q3" s="54"/>
     </row>
-    <row r="4" ht="16" spans="2:17">
+    <row r="4" spans="2:17" ht="14.25">
       <c r="B4" s="55" t="s">
         <v>80</v>
       </c>
@@ -5752,7 +5228,7 @@
         <v>91</v>
       </c>
       <c r="E5" s="52">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="F5" s="56">
         <v>0.6</v>
@@ -5761,10 +5237,10 @@
         <v>0.6</v>
       </c>
       <c r="H5" s="56">
-        <v>189.216</v>
+        <v>189.21600000000001</v>
       </c>
       <c r="I5" s="56">
-        <v>88.3008</v>
+        <v>88.300799999999995</v>
       </c>
       <c r="J5" s="52">
         <v>60</v>
@@ -5801,7 +5277,7 @@
         <v>91</v>
       </c>
       <c r="E6" s="52">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="F6" s="56">
         <v>0.6</v>
@@ -5810,10 +5286,10 @@
         <v>0.6</v>
       </c>
       <c r="H6" s="56">
-        <v>189.216</v>
+        <v>189.21600000000001</v>
       </c>
       <c r="I6" s="56">
-        <v>88.3008</v>
+        <v>88.300799999999995</v>
       </c>
       <c r="J6" s="52">
         <v>60</v>
@@ -5847,7 +5323,7 @@
         <v>91</v>
       </c>
       <c r="E7" s="52">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="F7" s="56">
         <v>0.1</v>
@@ -5856,16 +5332,16 @@
         <v>0.6</v>
       </c>
       <c r="H7" s="56">
-        <v>141.912</v>
+        <v>141.91200000000001</v>
       </c>
       <c r="I7" s="56">
-        <v>75.6864</v>
+        <v>75.686400000000006</v>
       </c>
       <c r="J7" s="52">
         <v>60</v>
       </c>
       <c r="K7" s="57">
-        <v>0.869565217391304</v>
+        <v>0.86956521739130399</v>
       </c>
       <c r="N7" s="52" t="str">
         <f t="shared" si="0"/>
@@ -5893,7 +5369,7 @@
         <v>91</v>
       </c>
       <c r="E8" s="52">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="F8" s="56">
         <v>0.3</v>
@@ -5928,7 +5404,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="9" ht="13" spans="2:17">
+    <row r="9" spans="2:17" ht="13.15">
       <c r="B9" s="58" t="s">
         <v>99</v>
       </c>
@@ -5940,7 +5416,7 @@
       </c>
       <c r="E9" s="52">
         <f t="shared" ref="E9:K9" si="1">E7</f>
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="F9" s="56">
         <f t="shared" si="1"/>
@@ -5952,11 +5428,11 @@
       </c>
       <c r="H9" s="56">
         <f t="shared" si="1"/>
-        <v>141.912</v>
+        <v>141.91200000000001</v>
       </c>
       <c r="I9" s="56">
         <f t="shared" si="1"/>
-        <v>75.6864</v>
+        <v>75.686400000000006</v>
       </c>
       <c r="J9" s="52">
         <f t="shared" si="1"/>
@@ -5964,7 +5440,7 @@
       </c>
       <c r="K9" s="57">
         <f t="shared" si="1"/>
-        <v>0.869565217391304</v>
+        <v>0.86956521739130399</v>
       </c>
       <c r="N9" s="52" t="str">
         <f t="shared" si="0"/>
@@ -5993,7 +5469,7 @@
       </c>
       <c r="E10" s="52">
         <f>E8</f>
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="F10" s="56"/>
       <c r="G10" s="56"/>
@@ -6062,34 +5538,33 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:AK40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="8" max="8" width="17.6" customWidth="1"/>
-    <col min="10" max="10" width="10.8636363636364" customWidth="1"/>
+    <col min="8" max="8" width="17.59765625" customWidth="1"/>
+    <col min="10" max="10" width="10.86328125" customWidth="1"/>
     <col min="11" max="13" width="5" customWidth="1"/>
-    <col min="14" max="14" width="8.4" customWidth="1"/>
+    <col min="14" max="14" width="8.3984375" customWidth="1"/>
     <col min="15" max="15" width="2" customWidth="1"/>
-    <col min="16" max="16" width="3.6" customWidth="1"/>
-    <col min="17" max="17" width="17.6" customWidth="1"/>
+    <col min="16" max="16" width="3.59765625" customWidth="1"/>
+    <col min="17" max="17" width="17.59765625" customWidth="1"/>
     <col min="21" max="21" width="2" customWidth="1"/>
-    <col min="22" max="22" width="17.6" customWidth="1"/>
+    <col min="22" max="22" width="17.59765625" customWidth="1"/>
     <col min="23" max="25" width="6" customWidth="1"/>
     <col min="26" max="26" width="2" customWidth="1"/>
-    <col min="27" max="27" width="17.6" customWidth="1"/>
-    <col min="28" max="28" width="11.4" customWidth="1"/>
+    <col min="27" max="27" width="17.59765625" customWidth="1"/>
+    <col min="28" max="28" width="11.3984375" customWidth="1"/>
     <col min="29" max="31" width="5" customWidth="1"/>
-    <col min="33" max="33" width="19.8636363636364" customWidth="1"/>
-    <col min="34" max="34" width="5.6" customWidth="1"/>
+    <col min="33" max="33" width="19.86328125" customWidth="1"/>
+    <col min="34" max="34" width="5.59765625" customWidth="1"/>
     <col min="35" max="37" width="5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6253,7 +5728,7 @@
         <v>439.05</v>
       </c>
       <c r="N3" s="39">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="O3" s="38"/>
       <c r="P3" s="40">
@@ -6265,15 +5740,15 @@
       </c>
       <c r="R3" s="39">
         <f>$P3*K3</f>
-        <v>29.109</v>
+        <v>29.109000000000002</v>
       </c>
       <c r="S3" s="39">
         <f t="shared" ref="S3:T5" si="2">$P3*L3</f>
-        <v>13.226</v>
+        <v>13.226000000000001</v>
       </c>
       <c r="T3" s="39">
         <f t="shared" si="2"/>
-        <v>8.781</v>
+        <v>8.7810000000000006</v>
       </c>
       <c r="V3" t="str">
         <f t="shared" ref="V3:V5" si="3">$H3</f>
@@ -6324,7 +5799,7 @@
         <v>661.3</v>
       </c>
       <c r="E4" s="37">
-        <v>138.45</v>
+        <v>138.44999999999999</v>
       </c>
       <c r="F4" s="37">
         <v>1368.75</v>
@@ -6342,17 +5817,17 @@
         <v>338.75</v>
       </c>
       <c r="L4" s="38">
-        <v>138.45</v>
+        <v>138.44999999999999</v>
       </c>
       <c r="M4" s="38">
         <v>87.3</v>
       </c>
       <c r="N4" s="39">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="O4" s="39"/>
       <c r="P4" s="40">
-        <v>0.035</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="Q4" t="str">
         <f t="shared" si="1"/>
@@ -6360,28 +5835,28 @@
       </c>
       <c r="R4" s="39">
         <f t="shared" ref="R4:R5" si="4">$P4*K4</f>
-        <v>11.85625</v>
+        <v>11.856249999999999</v>
       </c>
       <c r="S4" s="39">
         <f t="shared" si="2"/>
-        <v>4.84575</v>
+        <v>4.8457499999999998</v>
       </c>
       <c r="T4" s="39">
         <f t="shared" si="2"/>
-        <v>3.0555</v>
+        <v>3.0554999999999999</v>
       </c>
       <c r="V4" t="str">
         <f t="shared" si="3"/>
         <v>H2Conv_LOHC</v>
       </c>
       <c r="W4">
-        <v>0.925</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="X4">
         <v>0.95</v>
       </c>
       <c r="Y4">
-        <v>0.975</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="AA4" t="str">
         <f t="shared" ref="AA4:AA5" si="5">H4</f>
@@ -6443,7 +5918,7 @@
         <v>799.5</v>
       </c>
       <c r="N5" s="39">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="O5" s="39"/>
       <c r="P5" s="40">
@@ -6489,7 +5964,7 @@
         <v>0.255</v>
       </c>
       <c r="AD5" s="9">
-        <v>0.225</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="AE5" s="9">
         <v>0.1875</v>
@@ -6516,7 +5991,7 @@
         <v>0.02</v>
       </c>
       <c r="E6" s="44">
-        <v>0.035</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="F6" s="44">
         <v>0.04</v>
@@ -6536,7 +6011,7 @@
         <v>0.875</v>
       </c>
       <c r="E7" s="44">
-        <v>0.925</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="F7" s="44">
         <v>0.95</v>
@@ -6579,7 +6054,7 @@
         <v>0.875</v>
       </c>
       <c r="E9" s="44">
-        <v>0.975</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="F9" s="44">
         <v>1</v>
@@ -6590,7 +6065,7 @@
       </c>
       <c r="I9">
         <f>F11*3.6/120</f>
-        <v>0.225</v>
+        <v>0.22500000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -6764,7 +6239,7 @@
         <v>752.1</v>
       </c>
       <c r="F14" s="48">
-        <v>649.45</v>
+        <v>649.45000000000005</v>
       </c>
       <c r="H14" t="s">
         <v>143</v>
@@ -6785,11 +6260,11 @@
         <v>276.55</v>
       </c>
       <c r="N14" s="39">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="O14" s="38"/>
       <c r="P14" s="40">
-        <v>0.035</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="Q14" t="str">
         <f t="shared" ref="Q14:Q16" si="6">$H14</f>
@@ -6797,15 +6272,15 @@
       </c>
       <c r="R14" s="39">
         <f>$P14*K14</f>
-        <v>40.39175</v>
+        <v>40.391750000000002</v>
       </c>
       <c r="S14" s="39">
         <f t="shared" ref="S14:T16" si="7">$P14*L14</f>
-        <v>16.02475</v>
+        <v>16.024750000000001</v>
       </c>
       <c r="T14" s="39">
         <f t="shared" si="7"/>
-        <v>9.67925</v>
+        <v>9.6792499999999997</v>
       </c>
       <c r="V14" t="str">
         <f t="shared" ref="V14:V16" si="8">$H14</f>
@@ -6825,10 +6300,10 @@
         <v>0.06</v>
       </c>
       <c r="AD14" s="9">
-        <v>0.045</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="AE14" s="9">
-        <v>0.0225</v>
+        <v>2.2499999999999999E-2</v>
       </c>
       <c r="AF14" s="9">
         <v>0.4</v>
@@ -6874,11 +6349,11 @@
         <v>169.75</v>
       </c>
       <c r="N15" s="39">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="O15" s="39"/>
       <c r="P15" s="40">
-        <v>0.045</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="Q15" t="str">
         <f t="shared" si="6"/>
@@ -6886,15 +6361,15 @@
       </c>
       <c r="R15" s="39">
         <f t="shared" ref="R15:R16" si="9">$P15*K15</f>
-        <v>33.8445</v>
+        <v>33.844499999999996</v>
       </c>
       <c r="S15" s="39">
         <f t="shared" si="7"/>
-        <v>14.4675</v>
+        <v>14.467499999999999</v>
       </c>
       <c r="T15" s="39">
         <f t="shared" si="7"/>
-        <v>7.63875</v>
+        <v>7.6387499999999999</v>
       </c>
       <c r="V15" t="str">
         <f t="shared" si="8"/>
@@ -6954,7 +6429,7 @@
         <v>16</v>
       </c>
       <c r="K16" s="38">
-        <v>649.45</v>
+        <v>649.45000000000005</v>
       </c>
       <c r="L16" s="38">
         <v>267.3</v>
@@ -6963,11 +6438,11 @@
         <v>125.45</v>
       </c>
       <c r="N16" s="39">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="O16" s="39"/>
       <c r="P16" s="40">
-        <v>0.035</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="Q16" t="str">
         <f t="shared" si="6"/>
@@ -6979,11 +6454,11 @@
       </c>
       <c r="S16" s="39">
         <f t="shared" si="7"/>
-        <v>9.3555</v>
+        <v>9.3554999999999993</v>
       </c>
       <c r="T16" s="39">
         <f t="shared" si="7"/>
-        <v>4.39075</v>
+        <v>4.3907499999999997</v>
       </c>
       <c r="V16" t="str">
         <f t="shared" si="8"/>
@@ -7000,13 +6475,13 @@
         <v>102</v>
       </c>
       <c r="AC16" s="9">
-        <v>0.0225</v>
+        <v>2.2499999999999999E-2</v>
       </c>
       <c r="AD16" s="9">
-        <v>0.01575</v>
+        <v>1.575E-2</v>
       </c>
       <c r="AE16" s="9">
-        <v>0.009</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="AF16" s="9">
         <v>0.4</v>
@@ -7030,13 +6505,13 @@
       </c>
       <c r="C17" s="49"/>
       <c r="D17" s="44">
-        <v>0.035</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="E17" s="44">
-        <v>0.045</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="F17" s="44">
-        <v>0.035</v>
+        <v>3.5000000000000003E-2</v>
       </c>
     </row>
     <row r="18" spans="1:33">
@@ -7092,7 +6567,7 @@
       </c>
       <c r="J19" s="39">
         <f t="shared" si="11"/>
-        <v>0.0225</v>
+        <v>2.2499999999999999E-2</v>
       </c>
       <c r="AA19" t="s">
         <v>120</v>
@@ -7129,11 +6604,11 @@
         <v>2</v>
       </c>
       <c r="F20" s="37">
-        <v>0.525</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="H20" s="39">
         <f t="shared" ref="H20:H24" si="12">D20*3.6/120</f>
-        <v>0.045</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="I20" s="39">
         <f t="shared" si="11"/>
@@ -7141,7 +6616,7 @@
       </c>
       <c r="J20" s="39">
         <f t="shared" si="11"/>
-        <v>0.01575</v>
+        <v>1.575E-2</v>
       </c>
       <c r="AA20" t="str">
         <f>V14</f>
@@ -7154,10 +6629,10 @@
         <v>0.42</v>
       </c>
       <c r="AD20" s="9">
-        <v>0.3315</v>
+        <v>0.33150000000000002</v>
       </c>
       <c r="AE20" s="9">
-        <v>0.243</v>
+        <v>0.24299999999999999</v>
       </c>
       <c r="AF20" t="s">
         <v>149</v>
@@ -7183,7 +6658,7 @@
       </c>
       <c r="H21" s="39">
         <f t="shared" si="12"/>
-        <v>0.0225</v>
+        <v>2.2499999999999999E-2</v>
       </c>
       <c r="I21" s="39">
         <f t="shared" si="11"/>
@@ -7191,7 +6666,7 @@
       </c>
       <c r="J21" s="39">
         <f t="shared" si="11"/>
-        <v>0.009</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="AA21" t="str">
         <f>V15</f>
@@ -7204,10 +6679,10 @@
         <v>0.51</v>
       </c>
       <c r="AD21" s="9">
-        <v>0.4245</v>
+        <v>0.42449999999999999</v>
       </c>
       <c r="AE21" s="9">
-        <v>0.339</v>
+        <v>0.33900000000000002</v>
       </c>
       <c r="AF21" t="s">
         <v>149</v>
@@ -7265,11 +6740,11 @@
       </c>
       <c r="H23" s="39">
         <f t="shared" si="12"/>
-        <v>0.3315</v>
+        <v>0.33150000000000002</v>
       </c>
       <c r="I23" s="39">
         <f t="shared" si="11"/>
-        <v>0.4245</v>
+        <v>0.42449999999999999</v>
       </c>
       <c r="J23" s="39">
         <f t="shared" si="11"/>
@@ -7293,11 +6768,11 @@
       </c>
       <c r="H24" s="39">
         <f t="shared" si="12"/>
-        <v>0.243</v>
+        <v>0.24299999999999999</v>
       </c>
       <c r="I24" s="39">
         <f t="shared" si="11"/>
-        <v>0.339</v>
+        <v>0.33900000000000002</v>
       </c>
       <c r="J24" s="39">
         <f t="shared" si="11"/>
@@ -7463,37 +6938,35 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B3:Y5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="11.2636363636364" customWidth="1"/>
-    <col min="3" max="3" width="14.6" customWidth="1"/>
-    <col min="4" max="4" width="26.4" customWidth="1"/>
-    <col min="5" max="5" width="20.2636363636364" customWidth="1"/>
+    <col min="2" max="2" width="11.265625" customWidth="1"/>
+    <col min="3" max="3" width="14.59765625" customWidth="1"/>
+    <col min="4" max="4" width="26.3984375" customWidth="1"/>
+    <col min="5" max="5" width="20.265625" customWidth="1"/>
     <col min="6" max="6" width="5" customWidth="1"/>
-    <col min="7" max="7" width="4.6" customWidth="1"/>
+    <col min="7" max="7" width="4.59765625" customWidth="1"/>
     <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="9" max="9" width="10.2636363636364" customWidth="1"/>
-    <col min="10" max="10" width="7.86363636363636" customWidth="1"/>
-    <col min="12" max="12" width="17.8636363636364" customWidth="1"/>
-    <col min="13" max="13" width="9.4" customWidth="1"/>
+    <col min="9" max="9" width="10.265625" customWidth="1"/>
+    <col min="10" max="10" width="7.86328125" customWidth="1"/>
+    <col min="12" max="12" width="17.86328125" customWidth="1"/>
+    <col min="13" max="13" width="9.3984375" customWidth="1"/>
     <col min="14" max="14" width="12" customWidth="1"/>
-    <col min="15" max="15" width="8.86363636363636" customWidth="1"/>
+    <col min="15" max="15" width="8.86328125" customWidth="1"/>
     <col min="16" max="16" width="14" customWidth="1"/>
-    <col min="17" max="17" width="6.86363636363636" customWidth="1"/>
-    <col min="18" max="18" width="11.8636363636364" customWidth="1"/>
-    <col min="19" max="19" width="7.86363636363636" customWidth="1"/>
-    <col min="20" max="20" width="12.8636363636364" customWidth="1"/>
-    <col min="21" max="21" width="4.6" customWidth="1"/>
+    <col min="17" max="17" width="6.86328125" customWidth="1"/>
+    <col min="18" max="18" width="11.86328125" customWidth="1"/>
+    <col min="19" max="19" width="7.86328125" customWidth="1"/>
+    <col min="20" max="20" width="12.86328125" customWidth="1"/>
+    <col min="21" max="21" width="4.59765625" customWidth="1"/>
     <col min="22" max="22" width="9" customWidth="1"/>
-    <col min="23" max="23" width="4.4" customWidth="1"/>
+    <col min="23" max="23" width="4.3984375" customWidth="1"/>
     <col min="24" max="24" width="5" customWidth="1"/>
     <col min="25" max="25" width="9" customWidth="1"/>
   </cols>
@@ -7619,16 +7092,16 @@
         <v>71</v>
       </c>
       <c r="S5" s="9">
-        <v>2.13470319634703</v>
+        <v>2.1347031963470302</v>
       </c>
       <c r="T5" s="9">
         <v>1.72231735159817</v>
       </c>
       <c r="U5" s="9">
-        <v>0.5525</v>
+        <v>0.55249999999999999</v>
       </c>
       <c r="V5" s="9">
-        <v>0.5525</v>
+        <v>0.55249999999999999</v>
       </c>
       <c r="W5">
         <v>20</v>
@@ -7637,49 +7110,49 @@
         <v>0.85</v>
       </c>
       <c r="Y5">
-        <v>31.536</v>
+        <v>31.536000000000001</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="B1:BP66"/>
-  <sheetFormatPr defaultColWidth="8.8" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="32.5272727272727" customWidth="1"/>
-    <col min="3" max="3" width="30.7272727272727" customWidth="1"/>
+    <col min="2" max="2" width="32.53125" customWidth="1"/>
+    <col min="3" max="3" width="30.73046875" customWidth="1"/>
     <col min="4" max="4" width="50" customWidth="1"/>
-    <col min="5" max="5" width="29.9272727272727" customWidth="1"/>
-    <col min="6" max="9" width="33.7272727272727" customWidth="1"/>
-    <col min="10" max="10" width="19.2636363636364" customWidth="1"/>
-    <col min="11" max="11" width="14.6" customWidth="1"/>
-    <col min="12" max="12" width="14.2636363636364" customWidth="1"/>
-    <col min="13" max="13" width="13.0636363636364" customWidth="1"/>
-    <col min="14" max="14" width="12.8" customWidth="1"/>
-    <col min="15" max="15" width="6.8" customWidth="1"/>
-    <col min="16" max="16" width="15.3363636363636" customWidth="1"/>
-    <col min="17" max="17" width="6.2" customWidth="1"/>
-    <col min="18" max="18" width="14.5272727272727" customWidth="1"/>
-    <col min="23" max="23" width="20.2" customWidth="1"/>
-    <col min="24" max="24" width="18.5272727272727" customWidth="1"/>
-    <col min="25" max="25" width="19.2" customWidth="1"/>
-    <col min="32" max="32" width="21.2636363636364" customWidth="1"/>
-    <col min="36" max="36" width="13.5272727272727" customWidth="1"/>
-    <col min="40" max="40" width="19.6363636363636" customWidth="1"/>
-    <col min="43" max="43" width="13.0909090909091" customWidth="1"/>
-    <col min="44" max="44" width="7.09090909090909" customWidth="1"/>
-    <col min="46" max="46" width="15.3636363636364" customWidth="1"/>
-    <col min="48" max="48" width="13.2" customWidth="1"/>
-    <col min="49" max="49" width="5.26363636363636" customWidth="1"/>
-    <col min="50" max="50" width="5.92727272727273" customWidth="1"/>
+    <col min="5" max="5" width="29.9296875" customWidth="1"/>
+    <col min="6" max="9" width="33.73046875" customWidth="1"/>
+    <col min="10" max="10" width="19.265625" customWidth="1"/>
+    <col min="11" max="11" width="14.59765625" customWidth="1"/>
+    <col min="12" max="12" width="14.265625" customWidth="1"/>
+    <col min="13" max="13" width="13.06640625" customWidth="1"/>
+    <col min="14" max="14" width="12.796875" customWidth="1"/>
+    <col min="15" max="15" width="6.796875" customWidth="1"/>
+    <col min="16" max="16" width="15.33203125" customWidth="1"/>
+    <col min="17" max="17" width="6.19921875" customWidth="1"/>
+    <col min="18" max="18" width="14.53125" customWidth="1"/>
+    <col min="23" max="23" width="20.19921875" customWidth="1"/>
+    <col min="24" max="24" width="18.53125" customWidth="1"/>
+    <col min="25" max="25" width="19.19921875" customWidth="1"/>
+    <col min="32" max="32" width="21.265625" customWidth="1"/>
+    <col min="36" max="36" width="13.53125" customWidth="1"/>
+    <col min="40" max="40" width="19.59765625" customWidth="1"/>
+    <col min="41" max="41" width="13.1328125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="13.06640625" customWidth="1"/>
+    <col min="44" max="44" width="7.06640625" customWidth="1"/>
+    <col min="46" max="46" width="15.33203125" customWidth="1"/>
+    <col min="48" max="48" width="13.19921875" customWidth="1"/>
+    <col min="49" max="49" width="5.265625" customWidth="1"/>
+    <col min="50" max="50" width="5.9296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:53">
@@ -7787,7 +7260,7 @@
         <v>185</v>
       </c>
       <c r="Z4" s="3">
-        <v>0.095</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="AA4" s="3">
         <v>0</v>
@@ -7802,7 +7275,7 @@
         <v>3.528</v>
       </c>
       <c r="AE4" s="3">
-        <v>0.946</v>
+        <v>0.94599999999999995</v>
       </c>
       <c r="AF4" s="3">
         <v>1.085</v>
@@ -8193,7 +7666,7 @@
         <v>0.92</v>
       </c>
       <c r="I16" s="9">
-        <v>1.314</v>
+        <v>1.3140000000000001</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -8232,7 +7705,7 @@
         <v>0.9</v>
       </c>
       <c r="AM16" s="9">
-        <v>1.314</v>
+        <v>1.3140000000000001</v>
       </c>
       <c r="AN16">
         <v>1</v>
@@ -8253,7 +7726,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="16" spans="2:68">
+    <row r="17" spans="2:68" s="1" customFormat="1" ht="15.4">
       <c r="D17" s="11"/>
       <c r="F17" s="1" t="s">
         <v>212</v>
@@ -8265,7 +7738,7 @@
       <c r="I17" s="12"/>
       <c r="K17" s="12">
         <f>1/H16</f>
-        <v>1.08695652173913</v>
+        <v>1.0869565217391299</v>
       </c>
       <c r="W17"/>
       <c r="Y17" s="13" t="s">
@@ -8291,7 +7764,7 @@
       <c r="AM17" s="9"/>
       <c r="AN17"/>
       <c r="AO17" s="9">
-        <v>1.08695652173913</v>
+        <v>1</v>
       </c>
       <c r="AQ17"/>
       <c r="AR17"/>
@@ -8353,7 +7826,7 @@
         <v>215</v>
       </c>
       <c r="I19" s="9">
-        <v>29.89194313</v>
+        <v>29.891943130000001</v>
       </c>
       <c r="L19">
         <v>1</v>
@@ -8382,7 +7855,7 @@
       </c>
       <c r="AM19" s="9">
         <f>AM16</f>
-        <v>1.314</v>
+        <v>1.3140000000000001</v>
       </c>
       <c r="AN19">
         <v>1</v>
@@ -8413,7 +7886,7 @@
       </c>
       <c r="AM20" s="9"/>
       <c r="AO20" s="9">
-        <v>1.08695652173913</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:68">
@@ -8450,7 +7923,7 @@
       </c>
       <c r="AM22" s="9">
         <f>AM19</f>
-        <v>1.314</v>
+        <v>1.3140000000000001</v>
       </c>
       <c r="AN22">
         <v>1</v>
@@ -8495,7 +7968,7 @@
       <c r="AL23" s="10"/>
       <c r="AM23" s="9"/>
       <c r="AO23" s="9">
-        <v>1.08695652173913</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="2:68">
@@ -8577,7 +8050,7 @@
       </c>
       <c r="AM25" s="9">
         <f>AM22</f>
-        <v>1.314</v>
+        <v>1.3140000000000001</v>
       </c>
       <c r="AN25">
         <v>1</v>
@@ -8625,7 +8098,7 @@
       <c r="AL26" s="10"/>
       <c r="AM26" s="9"/>
       <c r="AO26" s="9">
-        <v>1.08695652173913</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="2:68">
@@ -8666,7 +8139,7 @@
       </c>
       <c r="AM28" s="9">
         <f>AM25</f>
-        <v>1.314</v>
+        <v>1.3140000000000001</v>
       </c>
       <c r="AN28">
         <v>1</v>
@@ -8705,7 +8178,7 @@
       <c r="AL29" s="10"/>
       <c r="AM29" s="9"/>
       <c r="AO29" s="9">
-        <v>1.08695652173913</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="2:68">
@@ -8756,7 +8229,7 @@
       </c>
       <c r="AM31" s="9">
         <f>AM28</f>
-        <v>1.314</v>
+        <v>1.3140000000000001</v>
       </c>
       <c r="AN31">
         <v>1</v>
@@ -8799,7 +8272,7 @@
       </c>
       <c r="AM32" s="9"/>
       <c r="AO32" s="9">
-        <v>1.08695652173913</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:51">
@@ -8814,7 +8287,7 @@
       </c>
       <c r="E33" s="20">
         <f>[6]EnergyUseFromEverBatt_Min_!$AW$6</f>
-        <v>0.0473</v>
+        <v>4.7300000000000002E-2</v>
       </c>
       <c r="AH33" s="5"/>
       <c r="AJ33" s="5" t="s">
@@ -8828,7 +8301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" ht="16" spans="2:51">
+    <row r="34" spans="2:51" ht="15.4">
       <c r="B34" s="6" t="s">
         <v>188</v>
       </c>
@@ -8841,7 +8314,7 @@
       </c>
       <c r="E34" s="20">
         <f>[6]EnergyUseFromEverBatt_Min_!$AW$7</f>
-        <v>0.171166666666667</v>
+        <v>0.17116666666666699</v>
       </c>
       <c r="AF34" t="s">
         <v>199</v>
@@ -8885,7 +8358,7 @@
         <v>1566.7</v>
       </c>
     </row>
-    <row r="35" ht="16" spans="2:51">
+    <row r="35" spans="2:51" ht="15.4">
       <c r="B35" s="6" t="s">
         <v>188</v>
       </c>
@@ -8898,7 +8371,7 @@
       </c>
       <c r="E35" s="20">
         <f>[6]EnergyUseFromEverBatt_Min_!$AW$8</f>
-        <v>0.466366666666667</v>
+        <v>0.46636666666666698</v>
       </c>
       <c r="AJ35" t="s">
         <v>212</v>
@@ -8907,10 +8380,10 @@
         <v>212</v>
       </c>
       <c r="AO35">
-        <v>1.09</v>
-      </c>
-    </row>
-    <row r="36" ht="16" spans="2:51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:51" ht="15.4">
       <c r="B36" s="6" t="s">
         <v>188</v>
       </c>
@@ -8923,7 +8396,7 @@
       </c>
       <c r="E36" s="20">
         <f>[6]EnergyUseFromEverBatt_Min_!$AW$9</f>
-        <v>0.0956666666666667</v>
+        <v>9.5666666666666705E-2</v>
       </c>
       <c r="AJ36" s="5" t="s">
         <v>214</v>
@@ -8960,7 +8433,7 @@
       <c r="R43" s="8"/>
       <c r="S43" s="15"/>
     </row>
-    <row r="44" ht="16" spans="2:51">
+    <row r="44" spans="2:51" ht="15.4">
       <c r="B44" s="22" t="s">
         <v>80</v>
       </c>
@@ -8996,7 +8469,7 @@
       <c r="R44" s="8"/>
       <c r="S44" s="8"/>
     </row>
-    <row r="45" ht="16" spans="2:51">
+    <row r="45" spans="2:51" ht="15.4">
       <c r="B45" s="27" t="s">
         <v>185</v>
       </c>
@@ -9368,7 +8841,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/SubRes_Tmpl/SubRES_H2-Production.xlsx
+++ b/SubRes_Tmpl/SubRES_H2-Production.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\KiNESYS_BattCircularity-main\SubRes_Tmpl\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CA87521-2B74-460B-A4E2-F505E635EBC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="18350" windowHeight="8260" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="SectFuel" sheetId="2" r:id="rId1"/>
@@ -89,12 +83,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Rocco De Miglio</author>
   </authors>
   <commentList>
-    <comment ref="O39" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="O39" authorId="0">
       <text>
         <r>
           <rPr>
@@ -122,13 +116,13 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>xli9</author>
     <author>Amit Kanudia</author>
   </authors>
   <commentList>
-    <comment ref="BA16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000001000000}">
+    <comment ref="BA16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -150,7 +144,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000002000000}">
+    <comment ref="Y17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -172,7 +166,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P19" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0500-000003000000}">
+    <comment ref="P19" authorId="1">
       <text>
         <r>
           <rPr>
@@ -196,7 +190,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BA19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000004000000}">
+    <comment ref="BA19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -218,7 +212,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BA22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000005000000}">
+    <comment ref="BA22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -240,7 +234,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BA25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000006000000}">
+    <comment ref="BA25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -262,7 +256,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BA28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000007000000}">
+    <comment ref="BA28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -284,7 +278,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BA31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000008000000}">
+    <comment ref="BA31" authorId="0">
       <text>
         <r>
           <rPr>
@@ -306,7 +300,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000009000000}">
+    <comment ref="C33" authorId="0">
       <text>
         <r>
           <rPr>
@@ -328,13 +322,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="AY34" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-00000A000000}">
+    <comment ref="AY34" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="Times New Roman"/>
+            <charset val="134"/>
           </rPr>
           <t>xli9:</t>
         </r>
@@ -342,6 +337,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Times New Roman"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
 1,000-MW, 10-hour facility — so in US-style capacity-expansion modeling, 10 h is effectively the central assumption for new closed-loop PSH.
@@ -1087,15 +1083,19 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
-    <numFmt numFmtId="168" formatCode="\Te\x\t"/>
-    <numFmt numFmtId="169" formatCode="#,##0.000"/>
-    <numFmt numFmtId="170" formatCode="#,##0.0_ "/>
-    <numFmt numFmtId="171" formatCode="0.0"/>
-    <numFmt numFmtId="172" formatCode="0.000"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="9">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* \-??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="\Te\x\t"/>
+    <numFmt numFmtId="179" formatCode="#,##0.000"/>
+    <numFmt numFmtId="180" formatCode="#,##0.0_ "/>
+    <numFmt numFmtId="181" formatCode="0.0"/>
+    <numFmt numFmtId="182" formatCode="0.000"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="38">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1123,7 +1123,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.199999999999999"/>
+      <sz val="10.2"/>
       <color rgb="FF212529"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
@@ -1225,22 +1225,128 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="1"/>
@@ -1251,19 +1357,18 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="51">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1278,7 +1383,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <fgColor theme="0" tint="-0.349986266670736"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1290,7 +1395,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79992065187536243"/>
+        <fgColor theme="4" tint="0.799920651875362"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1302,7 +1407,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39988402966399123"/>
+        <fgColor theme="9" tint="0.399884029663991"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1314,7 +1419,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <fgColor theme="0" tint="-0.0499893185216834"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1338,7 +1443,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79989013336588644"/>
+        <fgColor theme="5" tint="0.799890133365886"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1356,7 +1461,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79989013336588644"/>
+        <fgColor theme="9" tint="0.799890133365886"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1368,7 +1473,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1384,8 +1489,188 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="27">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -1527,7 +1812,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.39988402966399123"/>
+        <color theme="4" tint="0.399884029663991"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1573,7 +1858,7 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
+        <color theme="0" tint="-0.249946592608417"/>
       </left>
       <right/>
       <top/>
@@ -1583,7 +1868,7 @@
     <border>
       <left/>
       <right style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
+        <color theme="0" tint="-0.249946592608417"/>
       </right>
       <top/>
       <bottom/>
@@ -1600,7 +1885,7 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
+        <color theme="0" tint="-0.249946592608417"/>
       </left>
       <right/>
       <top style="thin">
@@ -1612,7 +1897,7 @@
     <border>
       <left/>
       <right style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
+        <color theme="0" tint="-0.249946592608417"/>
       </right>
       <top style="thin">
         <color auto="1"/>
@@ -1653,7 +1938,7 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
+        <color theme="0" tint="-0.249946592608417"/>
       </left>
       <right/>
       <top/>
@@ -1665,7 +1950,7 @@
     <border>
       <left/>
       <right style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
+        <color theme="0" tint="-0.249946592608417"/>
       </right>
       <top/>
       <bottom style="thin">
@@ -1673,65 +1958,283 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="8">
+  <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="27" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="186">
+  <cellXfs count="185">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="178" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="178" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="6" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="49" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -1750,12 +2253,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
@@ -1765,7 +2268,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1774,30 +2277,42 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="7"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="2"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="4"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="3"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" xfId="7" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="7" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="7" applyFont="1"/>
+    <xf numFmtId="178" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="13"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="15"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="14"/>
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" xfId="50" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="50" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="50" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="5" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="24" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1815,16 +2330,19 @@
     <xf numFmtId="0" fontId="11" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="13" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="13" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="13" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="13" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="13" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1845,13 +2363,13 @@
     <xf numFmtId="0" fontId="13" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="13" fillId="12" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="13" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="13" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="13" fillId="12" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="13" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1878,25 +2396,25 @@
     <xf numFmtId="0" fontId="14" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="14" fillId="13" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="14" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="14" fillId="13" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="14" fillId="13" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="14" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="14" fillId="13" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="14" fillId="13" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="14" fillId="13" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="13" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="14" fillId="13" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="14" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="14" fillId="13" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="14" fillId="13" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1908,25 +2426,25 @@
     <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="13" fillId="14" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="13" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="13" fillId="14" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="13" fillId="14" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="13" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="13" fillId="14" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="13" fillId="14" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="13" fillId="14" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="14" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="13" fillId="14" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="13" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="13" fillId="14" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="13" fillId="14" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1938,25 +2456,25 @@
     <xf numFmtId="0" fontId="13" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="13" fillId="15" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="13" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="13" fillId="15" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="13" fillId="15" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="13" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="13" fillId="15" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="13" fillId="15" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="13" fillId="15" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="15" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="13" fillId="15" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="13" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="13" fillId="15" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="13" fillId="15" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1968,25 +2486,25 @@
     <xf numFmtId="0" fontId="13" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="13" fillId="16" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="13" fillId="16" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="13" fillId="16" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="14" fillId="16" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="14" fillId="16" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="14" fillId="16" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="14" fillId="16" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="13" fillId="16" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="16" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="16" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="14" fillId="16" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="14" fillId="16" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="14" fillId="16" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="14" fillId="16" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2001,25 +2519,25 @@
     <xf numFmtId="0" fontId="13" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="13" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="13" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="13" fillId="18" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="14" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="14" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="14" fillId="18" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="14" fillId="18" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="13" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="18" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="14" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="14" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="14" fillId="18" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="14" fillId="18" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="17" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2031,25 +2549,25 @@
     <xf numFmtId="0" fontId="13" fillId="16" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="13" fillId="16" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="13" fillId="16" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="13" fillId="16" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="14" fillId="16" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="14" fillId="16" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="14" fillId="16" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="14" fillId="16" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="13" fillId="16" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="16" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="16" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="14" fillId="16" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="14" fillId="16" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="14" fillId="16" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="14" fillId="16" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2058,25 +2576,25 @@
     <xf numFmtId="1" fontId="13" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="13" fillId="19" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="13" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="13" fillId="19" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="13" fillId="19" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="13" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="13" fillId="19" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="13" fillId="19" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="13" fillId="19" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="19" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="13" fillId="19" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="13" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="13" fillId="19" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="13" fillId="19" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="19" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2088,25 +2606,25 @@
     <xf numFmtId="1" fontId="13" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="13" fillId="20" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="13" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="13" fillId="20" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="13" fillId="20" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="13" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="13" fillId="20" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="13" fillId="20" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="13" fillId="20" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="20" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="13" fillId="20" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="13" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="13" fillId="20" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="13" fillId="20" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="20" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2118,25 +2636,25 @@
     <xf numFmtId="0" fontId="13" fillId="19" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="13" fillId="19" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="13" fillId="19" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="13" fillId="19" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="13" fillId="19" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="13" fillId="19" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="13" fillId="19" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="13" fillId="19" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="13" fillId="19" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="19" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="19" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="13" fillId="19" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="13" fillId="19" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="13" fillId="19" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="13" fillId="19" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2147,54 +2665,72 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="8">
-    <cellStyle name="Heading 2" xfId="2" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="3" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="4" builtinId="19"/>
-    <cellStyle name="Neutral" xfId="5" builtinId="28"/>
+  <cellStyles count="51">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="6" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="Normal 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal 10" xfId="49"/>
+    <cellStyle name="Normal 2" xfId="50"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="New Microsoft Excel Worksheet"/>
       <sheetName val="AGR_Fuels"/>
@@ -2210,11 +2746,8 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="IEA Data"/>
       <sheetName val="E&amp;D Drivers"/>
@@ -2326,11 +2859,8 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="IEA Data"/>
       <sheetName val="E&amp;D Drivers"/>
@@ -2442,11 +2972,8 @@
 </file>
 
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Cover"/>
       <sheetName val="H2 transport"/>
@@ -2482,11 +3009,8 @@
 </file>
 
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Cover"/>
       <sheetName val="ELC_Lists"/>
@@ -2520,11 +3044,8 @@
 </file>
 
 <file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Discuss_log"/>
       <sheetName val="Cover"/>
@@ -2569,22 +3090,22 @@
       <sheetData sheetId="13">
         <row r="6">
           <cell r="AW6">
-            <v>4.7300000000000002E-2</v>
+            <v>0.0473</v>
           </cell>
         </row>
         <row r="7">
           <cell r="AW7">
-            <v>0.17116666666666699</v>
+            <v>0.171166666666667</v>
           </cell>
         </row>
         <row r="8">
           <cell r="AW8">
-            <v>0.46636666666666698</v>
+            <v>0.466366666666667</v>
           </cell>
         </row>
         <row r="9">
           <cell r="AW9">
-            <v>9.5666666666666705E-2</v>
+            <v>0.0956666666666667</v>
           </cell>
         </row>
       </sheetData>
@@ -2856,29 +3377,29 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="B3:P7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="6"/>
   <cols>
-    <col min="2" max="2" width="11.86328125" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" customWidth="1"/>
-    <col min="4" max="4" width="15.265625" customWidth="1"/>
+    <col min="2" max="2" width="11.8636363636364" customWidth="1"/>
+    <col min="3" max="3" width="9.4" customWidth="1"/>
+    <col min="4" max="4" width="15.2636363636364" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="6.3984375" customWidth="1"/>
-    <col min="7" max="7" width="8.265625" customWidth="1"/>
-    <col min="9" max="9" width="11.265625" customWidth="1"/>
-    <col min="10" max="10" width="11.86328125" customWidth="1"/>
-    <col min="11" max="11" width="20.59765625" customWidth="1"/>
-    <col min="12" max="12" width="8.59765625" customWidth="1"/>
-    <col min="13" max="13" width="4.59765625" customWidth="1"/>
-    <col min="14" max="14" width="5.265625" customWidth="1"/>
-    <col min="15" max="15" width="10.265625" customWidth="1"/>
-    <col min="16" max="16" width="7.86328125" customWidth="1"/>
+    <col min="6" max="6" width="6.4" customWidth="1"/>
+    <col min="7" max="7" width="8.26363636363636" customWidth="1"/>
+    <col min="9" max="9" width="11.2636363636364" customWidth="1"/>
+    <col min="10" max="10" width="11.8636363636364" customWidth="1"/>
+    <col min="11" max="11" width="20.6" customWidth="1"/>
+    <col min="12" max="12" width="8.6" customWidth="1"/>
+    <col min="13" max="13" width="4.6" customWidth="1"/>
+    <col min="14" max="14" width="5.26363636363636" customWidth="1"/>
+    <col min="15" max="15" width="10.2636363636364" customWidth="1"/>
+    <col min="16" max="16" width="7.86363636363636" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:16">
@@ -3044,61 +3565,63 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:Y39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="2" width="11.1328125" customWidth="1"/>
+    <col min="1" max="2" width="11.1363636363636" customWidth="1"/>
     <col min="3" max="5" width="14" customWidth="1"/>
-    <col min="6" max="8" width="11.86328125" customWidth="1"/>
-    <col min="9" max="9" width="20.265625" customWidth="1"/>
-    <col min="10" max="10" width="15.59765625" customWidth="1"/>
-    <col min="11" max="11" width="20.265625" customWidth="1"/>
-    <col min="12" max="12" width="15.59765625" customWidth="1"/>
-    <col min="13" max="13" width="20.265625" customWidth="1"/>
-    <col min="14" max="14" width="15.59765625" customWidth="1"/>
-    <col min="15" max="15" width="18.86328125" customWidth="1"/>
-    <col min="16" max="16" width="4.3984375" customWidth="1"/>
-    <col min="17" max="17" width="8.1328125" customWidth="1"/>
-    <col min="20" max="20" width="18.1328125" customWidth="1"/>
+    <col min="6" max="8" width="11.8636363636364" customWidth="1"/>
+    <col min="9" max="9" width="20.2636363636364" customWidth="1"/>
+    <col min="10" max="10" width="15.6" customWidth="1"/>
+    <col min="11" max="11" width="20.2636363636364" customWidth="1"/>
+    <col min="12" max="12" width="15.6" customWidth="1"/>
+    <col min="13" max="13" width="20.2636363636364" customWidth="1"/>
+    <col min="14" max="14" width="15.6" customWidth="1"/>
+    <col min="15" max="15" width="18.8636363636364" customWidth="1"/>
+    <col min="16" max="16" width="4.4" customWidth="1"/>
+    <col min="17" max="17" width="8.13636363636364" customWidth="1"/>
+    <col min="20" max="20" width="18.1363636363636" customWidth="1"/>
     <col min="21" max="21" width="24" customWidth="1"/>
-    <col min="22" max="22" width="4.59765625" customWidth="1"/>
-    <col min="23" max="23" width="4.1328125" customWidth="1"/>
-    <col min="24" max="24" width="7.73046875" customWidth="1"/>
-    <col min="25" max="25" width="7.1328125" customWidth="1"/>
+    <col min="22" max="22" width="4.6" customWidth="1"/>
+    <col min="23" max="23" width="4.13636363636364" customWidth="1"/>
+    <col min="24" max="24" width="7.72727272727273" customWidth="1"/>
+    <col min="25" max="25" width="7.13636363636364" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="33.75" customHeight="1">
+    <row r="1" ht="33.75" customHeight="1" spans="1:20">
       <c r="A1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="180" t="s">
+      <c r="C1" s="59" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="180"/>
-      <c r="E1" s="180"/>
-      <c r="F1" s="181" t="s">
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="60" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="180"/>
-      <c r="H1" s="182"/>
-      <c r="I1" s="180" t="s">
+      <c r="G1" s="59"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="J1" s="180"/>
-      <c r="K1" s="180"/>
-      <c r="L1" s="180"/>
-      <c r="M1" s="180"/>
-      <c r="N1" s="180"/>
-      <c r="O1" s="183" t="s">
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="59"/>
+      <c r="O1" s="62" t="s">
         <v>33</v>
       </c>
-      <c r="P1" s="59"/>
-      <c r="Q1" s="59"/>
+      <c r="P1" s="63"/>
+      <c r="Q1" s="63"/>
       <c r="S1" t="s">
         <v>34</v>
       </c>
@@ -3107,953 +3630,953 @@
       </c>
     </row>
     <row r="2" spans="1:20">
-      <c r="C2" s="60" t="s">
+      <c r="C2" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="60" t="s">
+      <c r="D2" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="60" t="s">
+      <c r="E2" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="60" t="s">
+      <c r="F2" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="60" t="s">
+      <c r="G2" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="H2" s="60" t="s">
+      <c r="H2" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="I2" s="60" t="s">
+      <c r="I2" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="J2" s="60" t="s">
+      <c r="J2" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="K2" s="60" t="str">
+      <c r="K2" s="64" t="str">
         <f>I2</f>
         <v>input~GASNGA</v>
       </c>
-      <c r="L2" s="60" t="str">
+      <c r="L2" s="64" t="str">
         <f>J2</f>
         <v>input~ELC_gc</v>
       </c>
-      <c r="M2" s="60" t="str">
+      <c r="M2" s="64" t="str">
         <f>K2</f>
         <v>input~GASNGA</v>
       </c>
-      <c r="N2" s="60" t="str">
+      <c r="N2" s="64" t="str">
         <f>L2</f>
         <v>input~ELC_gc</v>
       </c>
-      <c r="O2" s="184"/>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="59"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
     </row>
     <row r="3" spans="1:20">
-      <c r="C3" s="60">
+      <c r="C3" s="64">
         <v>2020</v>
       </c>
-      <c r="D3" s="60">
+      <c r="D3" s="64">
         <v>2030</v>
       </c>
-      <c r="E3" s="60">
+      <c r="E3" s="64">
         <v>2050</v>
       </c>
-      <c r="F3" s="60">
+      <c r="F3" s="64">
         <f>C3</f>
         <v>2020</v>
       </c>
-      <c r="G3" s="60">
+      <c r="G3" s="64">
         <f t="shared" ref="G3:H3" si="0">D3</f>
         <v>2030</v>
       </c>
-      <c r="H3" s="60">
+      <c r="H3" s="64">
         <f t="shared" si="0"/>
         <v>2050</v>
       </c>
-      <c r="I3" s="60">
+      <c r="I3" s="64">
         <v>2015</v>
       </c>
-      <c r="J3" s="60">
+      <c r="J3" s="64">
         <v>2015</v>
       </c>
-      <c r="K3" s="60">
+      <c r="K3" s="64">
         <v>2030</v>
       </c>
-      <c r="L3" s="60">
+      <c r="L3" s="64">
         <v>2030</v>
       </c>
-      <c r="M3" s="60">
+      <c r="M3" s="64">
         <v>2050</v>
       </c>
-      <c r="N3" s="60">
+      <c r="N3" s="64">
         <v>2050</v>
       </c>
-      <c r="O3" s="184"/>
-      <c r="P3" s="59"/>
-      <c r="Q3" s="59"/>
-    </row>
-    <row r="4" spans="1:20" ht="26.25">
-      <c r="C4" s="61">
+      <c r="O3" s="63"/>
+      <c r="P3" s="63"/>
+      <c r="Q3" s="63"/>
+    </row>
+    <row r="4" ht="26" spans="1:20">
+      <c r="C4" s="65">
         <v>2020</v>
       </c>
-      <c r="D4" s="61">
+      <c r="D4" s="65">
         <v>2030</v>
       </c>
-      <c r="E4" s="61" t="s">
+      <c r="E4" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="62">
+      <c r="F4" s="66">
         <v>2015</v>
       </c>
-      <c r="G4" s="61">
+      <c r="G4" s="65">
         <v>2030</v>
       </c>
-      <c r="H4" s="63" t="s">
+      <c r="H4" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="61" t="s">
+      <c r="I4" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="J4" s="61" t="s">
+      <c r="J4" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="K4" s="64" t="s">
+      <c r="K4" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="L4" s="65" t="s">
+      <c r="L4" s="69" t="s">
         <v>44</v>
       </c>
-      <c r="M4" s="61" t="s">
+      <c r="M4" s="65" t="s">
         <v>45</v>
       </c>
-      <c r="N4" s="61" t="s">
+      <c r="N4" s="65" t="s">
         <v>46</v>
       </c>
-      <c r="O4" s="185"/>
-      <c r="P4" s="59"/>
-      <c r="Q4" s="59"/>
+      <c r="O4" s="70"/>
+      <c r="P4" s="63"/>
+      <c r="Q4" s="63"/>
     </row>
     <row r="5" spans="1:20">
-      <c r="C5" s="66">
+      <c r="C5" s="71">
         <v>550</v>
       </c>
-      <c r="D5" s="66">
+      <c r="D5" s="71">
         <v>500</v>
       </c>
-      <c r="E5" s="66">
+      <c r="E5" s="71">
         <v>450</v>
       </c>
-      <c r="F5" s="67">
+      <c r="F5" s="72">
         <v>22</v>
       </c>
-      <c r="G5" s="68">
+      <c r="G5" s="73">
         <v>20</v>
       </c>
-      <c r="H5" s="69">
+      <c r="H5" s="74">
         <v>18</v>
       </c>
-      <c r="I5" s="70">
+      <c r="I5" s="75">
         <v>1.33</v>
       </c>
-      <c r="J5" s="70">
-        <v>9.4E-2</v>
-      </c>
-      <c r="K5" s="71">
+      <c r="J5" s="75">
+        <v>0.094</v>
+      </c>
+      <c r="K5" s="76">
         <v>1.3</v>
       </c>
-      <c r="L5" s="72">
-        <v>9.4E-2</v>
-      </c>
-      <c r="M5" s="70">
+      <c r="L5" s="77">
+        <v>0.094</v>
+      </c>
+      <c r="M5" s="75">
         <v>1.28</v>
       </c>
-      <c r="N5" s="70">
-        <v>9.4E-2</v>
-      </c>
-      <c r="O5" s="73" t="s">
+      <c r="N5" s="75">
+        <v>0.094</v>
+      </c>
+      <c r="O5" s="78" t="s">
         <v>47</v>
       </c>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
     </row>
     <row r="6" spans="1:20">
-      <c r="C6" s="75">
+      <c r="C6" s="80">
         <v>900</v>
       </c>
-      <c r="D6" s="75">
+      <c r="D6" s="80">
         <v>850</v>
       </c>
-      <c r="E6" s="75">
+      <c r="E6" s="80">
         <v>800</v>
       </c>
-      <c r="F6" s="76">
+      <c r="F6" s="81">
         <v>36</v>
       </c>
-      <c r="G6" s="77">
+      <c r="G6" s="82">
         <v>34</v>
       </c>
-      <c r="H6" s="78">
+      <c r="H6" s="83">
         <v>32</v>
       </c>
-      <c r="I6" s="79">
+      <c r="I6" s="84">
         <v>1.33</v>
       </c>
-      <c r="J6" s="79">
-        <v>1.0940000000000001</v>
-      </c>
-      <c r="K6" s="80">
+      <c r="J6" s="84">
+        <v>1.094</v>
+      </c>
+      <c r="K6" s="85">
         <v>1.3</v>
       </c>
-      <c r="L6" s="81">
-        <v>1.0940000000000001</v>
-      </c>
-      <c r="M6" s="79">
+      <c r="L6" s="86">
+        <v>1.094</v>
+      </c>
+      <c r="M6" s="84">
         <v>1.28</v>
       </c>
-      <c r="N6" s="79">
-        <v>1.0940000000000001</v>
-      </c>
-      <c r="O6" s="82" t="s">
+      <c r="N6" s="84">
+        <v>1.094</v>
+      </c>
+      <c r="O6" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="P6" s="83"/>
-      <c r="Q6" s="83"/>
+      <c r="P6" s="88"/>
+      <c r="Q6" s="88"/>
     </row>
     <row r="7" spans="1:20">
-      <c r="C7" s="66">
+      <c r="C7" s="71">
         <v>1978</v>
       </c>
-      <c r="D7" s="66">
+      <c r="D7" s="71">
         <v>1598</v>
       </c>
-      <c r="E7" s="66">
+      <c r="E7" s="71">
         <v>1450</v>
       </c>
-      <c r="F7" s="67">
+      <c r="F7" s="72">
         <v>57</v>
       </c>
-      <c r="G7" s="68">
+      <c r="G7" s="73">
         <v>31</v>
       </c>
-      <c r="H7" s="69">
+      <c r="H7" s="74">
         <v>28</v>
       </c>
-      <c r="I7" s="70">
+      <c r="I7" s="75">
         <v>1.53</v>
       </c>
-      <c r="J7" s="70">
-        <v>9.4E-2</v>
-      </c>
-      <c r="K7" s="71">
+      <c r="J7" s="75">
+        <v>0.094</v>
+      </c>
+      <c r="K7" s="76">
         <v>1.47</v>
       </c>
-      <c r="L7" s="72">
-        <v>9.4E-2</v>
-      </c>
-      <c r="M7" s="70">
+      <c r="L7" s="77">
+        <v>0.094</v>
+      </c>
+      <c r="M7" s="75">
         <v>1.43</v>
       </c>
-      <c r="N7" s="70">
-        <v>9.4E-2</v>
-      </c>
-      <c r="O7" s="73" t="s">
+      <c r="N7" s="75">
+        <v>0.094</v>
+      </c>
+      <c r="O7" s="78" t="s">
         <v>49</v>
       </c>
-      <c r="P7" s="74"/>
-      <c r="Q7" s="74"/>
+      <c r="P7" s="79"/>
+      <c r="Q7" s="79"/>
     </row>
     <row r="8" spans="1:20">
-      <c r="C8" s="84">
+      <c r="C8" s="89">
         <v>1610</v>
       </c>
-      <c r="D8" s="84">
+      <c r="D8" s="89">
         <v>740</v>
       </c>
-      <c r="E8" s="84">
+      <c r="E8" s="89">
         <v>200</v>
       </c>
-      <c r="F8" s="76">
+      <c r="F8" s="81">
         <v>49</v>
       </c>
-      <c r="G8" s="77">
+      <c r="G8" s="82">
         <v>15</v>
       </c>
-      <c r="H8" s="78">
+      <c r="H8" s="83">
         <v>10</v>
       </c>
-      <c r="I8" s="79">
+      <c r="I8" s="84">
         <v>0</v>
       </c>
-      <c r="J8" s="79">
+      <c r="J8" s="84">
         <v>1.39</v>
       </c>
-      <c r="K8" s="80">
+      <c r="K8" s="85">
         <v>0</v>
       </c>
-      <c r="L8" s="81">
+      <c r="L8" s="86">
         <v>1.19</v>
       </c>
-      <c r="M8" s="79">
+      <c r="M8" s="84">
         <v>0</v>
       </c>
-      <c r="N8" s="79">
+      <c r="N8" s="84">
         <v>1.17</v>
       </c>
-      <c r="O8" s="82" t="s">
+      <c r="O8" s="87" t="s">
         <v>50</v>
       </c>
-      <c r="P8" s="83"/>
-      <c r="Q8" s="83"/>
+      <c r="P8" s="88"/>
+      <c r="Q8" s="88"/>
     </row>
     <row r="9" spans="1:20">
-      <c r="C9" s="85">
+      <c r="C9" s="90">
         <v>2530</v>
       </c>
-      <c r="D9" s="85">
+      <c r="D9" s="90">
         <v>1175</v>
       </c>
-      <c r="E9" s="85">
+      <c r="E9" s="90">
         <v>350</v>
       </c>
-      <c r="F9" s="67">
+      <c r="F9" s="72">
         <v>77</v>
       </c>
-      <c r="G9" s="68">
+      <c r="G9" s="73">
         <v>34</v>
       </c>
-      <c r="H9" s="69">
+      <c r="H9" s="74">
         <v>18</v>
       </c>
-      <c r="I9" s="70">
+      <c r="I9" s="75">
         <v>0</v>
       </c>
-      <c r="J9" s="70">
+      <c r="J9" s="75">
         <v>1.5</v>
       </c>
-      <c r="K9" s="71">
+      <c r="K9" s="76">
         <v>0</v>
       </c>
-      <c r="L9" s="72">
+      <c r="L9" s="77">
         <v>1.25</v>
       </c>
-      <c r="M9" s="70">
+      <c r="M9" s="75">
         <v>0</v>
       </c>
-      <c r="N9" s="70">
+      <c r="N9" s="75">
         <v>1.19</v>
       </c>
-      <c r="O9" s="73" t="s">
+      <c r="O9" s="78" t="s">
         <v>51</v>
       </c>
-      <c r="P9" s="74"/>
-      <c r="Q9" s="74"/>
+      <c r="P9" s="79"/>
+      <c r="Q9" s="79"/>
     </row>
     <row r="10" spans="1:20">
-      <c r="C10" s="84">
+      <c r="C10" s="89">
         <v>1265</v>
       </c>
-      <c r="D10" s="84">
+      <c r="D10" s="89">
         <v>600</v>
       </c>
-      <c r="E10" s="84">
+      <c r="E10" s="89">
         <v>180</v>
       </c>
-      <c r="F10" s="76">
+      <c r="F10" s="81">
         <v>28</v>
       </c>
-      <c r="G10" s="77">
+      <c r="G10" s="82">
         <v>14</v>
       </c>
-      <c r="H10" s="78">
+      <c r="H10" s="83">
         <v>9</v>
       </c>
-      <c r="I10" s="79">
+      <c r="I10" s="84">
         <v>0</v>
       </c>
-      <c r="J10" s="79">
+      <c r="J10" s="84">
         <v>1.3952</v>
       </c>
-      <c r="K10" s="80">
+      <c r="K10" s="85">
         <v>0</v>
       </c>
-      <c r="L10" s="81">
+      <c r="L10" s="86">
         <v>1.268</v>
       </c>
-      <c r="M10" s="79">
+      <c r="M10" s="84">
         <v>0</v>
       </c>
-      <c r="N10" s="79">
+      <c r="N10" s="84">
         <v>1.18</v>
       </c>
-      <c r="O10" s="82" t="s">
+      <c r="O10" s="87" t="s">
         <v>52</v>
       </c>
-      <c r="P10" s="83"/>
-      <c r="Q10" s="83"/>
+      <c r="P10" s="88"/>
+      <c r="Q10" s="88"/>
     </row>
     <row r="11" spans="1:20">
-      <c r="C11" s="85">
+      <c r="C11" s="90">
         <v>1897.5</v>
       </c>
-      <c r="D11" s="85">
+      <c r="D11" s="90">
         <v>715</v>
       </c>
-      <c r="E11" s="85">
+      <c r="E11" s="90">
         <v>300</v>
       </c>
-      <c r="F11" s="67">
+      <c r="F11" s="72">
         <v>41</v>
       </c>
-      <c r="G11" s="68">
+      <c r="G11" s="73">
         <v>17</v>
       </c>
-      <c r="H11" s="69">
+      <c r="H11" s="74">
         <v>15</v>
       </c>
-      <c r="I11" s="70">
+      <c r="I11" s="75">
         <v>0</v>
       </c>
-      <c r="J11" s="70">
+      <c r="J11" s="75">
         <v>1.3952</v>
       </c>
-      <c r="K11" s="71">
+      <c r="K11" s="76">
         <v>0</v>
       </c>
-      <c r="L11" s="72">
+      <c r="L11" s="77">
         <v>1.268</v>
       </c>
-      <c r="M11" s="70">
+      <c r="M11" s="75">
         <v>0</v>
       </c>
-      <c r="N11" s="70">
+      <c r="N11" s="75">
         <v>1.2</v>
       </c>
-      <c r="O11" s="73" t="s">
+      <c r="O11" s="78" t="s">
         <v>53</v>
       </c>
-      <c r="P11" s="74"/>
-      <c r="Q11" s="74"/>
+      <c r="P11" s="79"/>
+      <c r="Q11" s="79"/>
     </row>
     <row r="12" spans="1:20">
-      <c r="C12" s="84">
-        <v>3332.0882352941198</v>
-      </c>
-      <c r="D12" s="84">
+      <c r="C12" s="89">
+        <v>3332.08823529412</v>
+      </c>
+      <c r="D12" s="89">
         <v>1421.39215686275</v>
       </c>
-      <c r="E12" s="84">
+      <c r="E12" s="89">
         <v>600</v>
       </c>
-      <c r="F12" s="76">
-        <v>55.825000000000003</v>
-      </c>
-      <c r="G12" s="77">
+      <c r="F12" s="81">
+        <v>55.825</v>
+      </c>
+      <c r="G12" s="82">
         <v>36.18</v>
       </c>
-      <c r="H12" s="78">
+      <c r="H12" s="83">
         <v>39</v>
       </c>
-      <c r="I12" s="79">
-        <v>1.9966670387596901</v>
-      </c>
-      <c r="J12" s="79">
-        <v>0.83711999999999998</v>
-      </c>
-      <c r="K12" s="80">
+      <c r="I12" s="84">
+        <v>1.99666703875969</v>
+      </c>
+      <c r="J12" s="84">
+        <v>0.83712</v>
+      </c>
+      <c r="K12" s="85">
         <v>1.45562727909392</v>
       </c>
-      <c r="L12" s="81">
-        <v>0.76080000000000003</v>
-      </c>
-      <c r="M12" s="79">
-        <v>0.33333333333333298</v>
-      </c>
-      <c r="N12" s="79">
-        <v>0.70799999999999996</v>
-      </c>
-      <c r="O12" s="82" t="s">
+      <c r="L12" s="86">
+        <v>0.7608</v>
+      </c>
+      <c r="M12" s="84">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="N12" s="84">
+        <v>0.708</v>
+      </c>
+      <c r="O12" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="P12" s="83"/>
-      <c r="Q12" s="83"/>
+      <c r="P12" s="88"/>
+      <c r="Q12" s="88"/>
     </row>
     <row r="13" spans="1:20">
-      <c r="C13" s="85">
-        <v>5331.3411764705897</v>
-      </c>
-      <c r="D13" s="85">
-        <v>2920.8941176470598</v>
-      </c>
-      <c r="E13" s="85">
+      <c r="C13" s="90">
+        <v>5331.34117647059</v>
+      </c>
+      <c r="D13" s="90">
+        <v>2920.89411764706</v>
+      </c>
+      <c r="E13" s="90">
         <v>1100</v>
       </c>
-      <c r="F13" s="67">
-        <v>94.902500000000003</v>
-      </c>
-      <c r="G13" s="68">
-        <v>63.314999999999998</v>
-      </c>
-      <c r="H13" s="69">
+      <c r="F13" s="72">
+        <v>94.9025</v>
+      </c>
+      <c r="G13" s="73">
+        <v>63.315</v>
+      </c>
+      <c r="H13" s="74">
         <v>48.75</v>
       </c>
-      <c r="I13" s="70">
-        <v>1.9966670387596901</v>
-      </c>
-      <c r="J13" s="70">
-        <v>0.83711999999999998</v>
-      </c>
-      <c r="K13" s="71">
+      <c r="I13" s="75">
+        <v>1.99666703875969</v>
+      </c>
+      <c r="J13" s="75">
+        <v>0.83712</v>
+      </c>
+      <c r="K13" s="76">
         <v>1.45562727909392</v>
       </c>
-      <c r="L13" s="72">
-        <v>0.76080000000000003</v>
-      </c>
-      <c r="M13" s="70">
-        <v>0.33333333333333298</v>
-      </c>
-      <c r="N13" s="70">
+      <c r="L13" s="77">
+        <v>0.7608</v>
+      </c>
+      <c r="M13" s="75">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="N13" s="75">
         <v>0.72</v>
       </c>
-      <c r="O13" s="73" t="s">
+      <c r="O13" s="78" t="s">
         <v>55</v>
       </c>
-      <c r="P13" s="74"/>
-      <c r="Q13" s="74"/>
+      <c r="P13" s="79"/>
+      <c r="Q13" s="79"/>
     </row>
     <row r="14" spans="1:20">
-      <c r="C14" s="86">
+      <c r="C14" s="91">
         <v>1200</v>
       </c>
-      <c r="D14" s="86">
+      <c r="D14" s="91">
         <v>733</v>
       </c>
-      <c r="E14" s="86">
+      <c r="E14" s="91">
         <v>263</v>
       </c>
-      <c r="F14" s="87">
+      <c r="F14" s="92">
         <v>42</v>
       </c>
-      <c r="G14" s="88">
+      <c r="G14" s="93">
         <v>22</v>
       </c>
-      <c r="H14" s="89">
+      <c r="H14" s="94">
         <v>9</v>
       </c>
-      <c r="I14" s="90">
+      <c r="I14" s="95">
         <v>0</v>
       </c>
-      <c r="J14" s="91">
+      <c r="J14" s="96">
         <v>0.01</v>
       </c>
-      <c r="K14" s="92">
+      <c r="K14" s="97">
         <v>0</v>
       </c>
-      <c r="L14" s="93">
+      <c r="L14" s="98">
         <v>0.01</v>
       </c>
-      <c r="M14" s="91">
+      <c r="M14" s="96">
         <v>0</v>
       </c>
-      <c r="N14" s="91">
+      <c r="N14" s="96">
         <v>0.01</v>
       </c>
-      <c r="O14" s="94" t="s">
+      <c r="O14" s="99" t="s">
         <v>56</v>
       </c>
-      <c r="P14" s="95"/>
-      <c r="Q14" s="95"/>
+      <c r="P14" s="100"/>
+      <c r="Q14" s="100"/>
     </row>
     <row r="15" spans="1:20">
-      <c r="C15" s="96">
+      <c r="C15" s="101">
         <v>450</v>
       </c>
-      <c r="D15" s="96">
+      <c r="D15" s="101">
         <v>450</v>
       </c>
-      <c r="E15" s="96">
+      <c r="E15" s="101">
         <v>450</v>
       </c>
-      <c r="F15" s="97">
+      <c r="F15" s="102">
         <v>18</v>
       </c>
-      <c r="G15" s="98">
+      <c r="G15" s="103">
         <v>18</v>
       </c>
-      <c r="H15" s="99">
+      <c r="H15" s="104">
         <v>18</v>
       </c>
-      <c r="I15" s="100">
+      <c r="I15" s="105">
         <v>0.265822784810126</v>
       </c>
-      <c r="J15" s="101">
+      <c r="J15" s="106">
         <v>0.06</v>
       </c>
-      <c r="K15" s="102">
+      <c r="K15" s="107">
         <v>0.265822784810126</v>
       </c>
-      <c r="L15" s="103">
+      <c r="L15" s="108">
         <v>0.06</v>
       </c>
-      <c r="M15" s="101">
+      <c r="M15" s="106">
         <v>0.265822784810126</v>
       </c>
-      <c r="N15" s="101">
+      <c r="N15" s="106">
         <v>0.06</v>
       </c>
-      <c r="O15" s="104" t="s">
+      <c r="O15" s="109" t="s">
         <v>57</v>
       </c>
-      <c r="P15" s="105"/>
-      <c r="Q15" s="105"/>
+      <c r="P15" s="110"/>
+      <c r="Q15" s="110"/>
     </row>
     <row r="16" spans="1:20">
-      <c r="C16" s="106">
+      <c r="C16" s="111">
         <v>200</v>
       </c>
-      <c r="D16" s="106">
+      <c r="D16" s="111">
         <v>200</v>
       </c>
-      <c r="E16" s="106">
+      <c r="E16" s="111">
         <v>200</v>
       </c>
-      <c r="F16" s="107">
+      <c r="F16" s="112">
         <v>20</v>
       </c>
-      <c r="G16" s="108">
+      <c r="G16" s="113">
         <v>20</v>
       </c>
-      <c r="H16" s="109">
+      <c r="H16" s="114">
         <v>20</v>
       </c>
-      <c r="I16" s="110">
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="J16" s="111">
-        <v>3.5999999999999997E-2</v>
-      </c>
-      <c r="K16" s="112">
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="L16" s="113">
-        <v>3.5999999999999997E-2</v>
-      </c>
-      <c r="M16" s="111">
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="N16" s="111">
-        <v>3.5999999999999997E-2</v>
-      </c>
-      <c r="O16" s="114" t="s">
+      <c r="I16" s="115">
+        <v>0.013</v>
+      </c>
+      <c r="J16" s="116">
+        <v>0.036</v>
+      </c>
+      <c r="K16" s="117">
+        <v>0.013</v>
+      </c>
+      <c r="L16" s="118">
+        <v>0.036</v>
+      </c>
+      <c r="M16" s="116">
+        <v>0.013</v>
+      </c>
+      <c r="N16" s="116">
+        <v>0.036</v>
+      </c>
+      <c r="O16" s="119" t="s">
         <v>58</v>
       </c>
-      <c r="P16" s="115"/>
-      <c r="Q16" s="115"/>
+      <c r="P16" s="120"/>
+      <c r="Q16" s="120"/>
     </row>
     <row r="17" spans="1:25">
-      <c r="C17" s="96">
+      <c r="C17" s="101">
         <v>175</v>
       </c>
-      <c r="D17" s="96">
+      <c r="D17" s="101">
         <v>175</v>
       </c>
-      <c r="E17" s="96">
+      <c r="E17" s="101">
         <v>175</v>
       </c>
-      <c r="F17" s="97">
+      <c r="F17" s="102">
         <v>5</v>
       </c>
-      <c r="G17" s="98">
+      <c r="G17" s="103">
         <v>5</v>
       </c>
-      <c r="H17" s="99">
+      <c r="H17" s="104">
         <v>5</v>
       </c>
-      <c r="I17" s="100">
-        <v>1.4E-2</v>
-      </c>
-      <c r="J17" s="101">
+      <c r="I17" s="105">
+        <v>0.014</v>
+      </c>
+      <c r="J17" s="106">
         <v>0</v>
       </c>
-      <c r="K17" s="102">
-        <v>1.4E-2</v>
-      </c>
-      <c r="L17" s="103">
+      <c r="K17" s="107">
+        <v>0.014</v>
+      </c>
+      <c r="L17" s="108">
         <v>0</v>
       </c>
-      <c r="M17" s="101">
-        <v>1.4E-2</v>
-      </c>
-      <c r="N17" s="101">
+      <c r="M17" s="106">
+        <v>0.014</v>
+      </c>
+      <c r="N17" s="106">
         <v>0</v>
       </c>
-      <c r="O17" s="104" t="s">
+      <c r="O17" s="109" t="s">
         <v>59</v>
       </c>
-      <c r="P17" s="105"/>
-      <c r="Q17" s="105"/>
+      <c r="P17" s="110"/>
+      <c r="Q17" s="110"/>
     </row>
     <row r="18" spans="1:25">
-      <c r="C18" s="116">
+      <c r="C18" s="121">
         <v>1000</v>
       </c>
-      <c r="D18" s="116">
+      <c r="D18" s="121">
         <v>720</v>
       </c>
-      <c r="E18" s="116">
+      <c r="E18" s="121">
         <v>364</v>
       </c>
-      <c r="F18" s="117">
+      <c r="F18" s="122">
         <v>50</v>
       </c>
-      <c r="G18" s="118">
+      <c r="G18" s="123">
         <v>31</v>
       </c>
-      <c r="H18" s="119">
+      <c r="H18" s="124">
         <v>18</v>
       </c>
-      <c r="I18" s="120">
+      <c r="I18" s="125">
         <v>0.2389</v>
       </c>
-      <c r="J18" s="121">
-        <v>3.056E-2</v>
-      </c>
-      <c r="K18" s="122">
+      <c r="J18" s="126">
+        <v>0.03056</v>
+      </c>
+      <c r="K18" s="127">
         <v>0.2389</v>
       </c>
-      <c r="L18" s="123">
-        <v>3.056E-2</v>
-      </c>
-      <c r="M18" s="121">
+      <c r="L18" s="128">
+        <v>0.03056</v>
+      </c>
+      <c r="M18" s="126">
         <v>0.2389</v>
       </c>
-      <c r="N18" s="121">
-        <v>3.056E-2</v>
-      </c>
-      <c r="O18" s="124" t="s">
+      <c r="N18" s="126">
+        <v>0.03056</v>
+      </c>
+      <c r="O18" s="129" t="s">
         <v>60</v>
       </c>
-      <c r="P18" s="125"/>
-      <c r="Q18" s="125"/>
+      <c r="P18" s="130"/>
+      <c r="Q18" s="130"/>
     </row>
     <row r="19" spans="1:25">
-      <c r="C19" s="126">
+      <c r="C19" s="131">
         <v>1556</v>
       </c>
-      <c r="D19" s="126">
+      <c r="D19" s="131">
         <v>1143</v>
       </c>
-      <c r="E19" s="127">
+      <c r="E19" s="132">
         <v>673</v>
       </c>
-      <c r="F19" s="128">
+      <c r="F19" s="133">
         <v>54</v>
       </c>
-      <c r="G19" s="129">
+      <c r="G19" s="134">
         <v>40</v>
       </c>
-      <c r="H19" s="130">
+      <c r="H19" s="135">
         <v>24</v>
       </c>
-      <c r="I19" s="131">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="J19" s="132">
+      <c r="I19" s="136">
+        <v>0.035</v>
+      </c>
+      <c r="J19" s="137">
         <v>0.02</v>
       </c>
-      <c r="K19" s="133">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="L19" s="134">
+      <c r="K19" s="138">
+        <v>0.035</v>
+      </c>
+      <c r="L19" s="139">
         <v>0.02</v>
       </c>
-      <c r="M19" s="132">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="N19" s="132">
+      <c r="M19" s="137">
+        <v>0.035</v>
+      </c>
+      <c r="N19" s="137">
         <v>0.02</v>
       </c>
-      <c r="O19" s="135" t="s">
+      <c r="O19" s="140" t="s">
         <v>61</v>
       </c>
-      <c r="P19" s="136"/>
-      <c r="Q19" s="136"/>
+      <c r="P19" s="141"/>
+      <c r="Q19" s="141"/>
     </row>
     <row r="20" spans="1:25">
-      <c r="C20" s="137">
+      <c r="C20" s="142">
         <v>2332</v>
       </c>
-      <c r="D20" s="137">
+      <c r="D20" s="142">
         <v>1511</v>
       </c>
-      <c r="E20" s="137">
+      <c r="E20" s="142">
         <v>965</v>
       </c>
-      <c r="F20" s="138">
+      <c r="F20" s="143">
         <v>163</v>
       </c>
-      <c r="G20" s="139">
+      <c r="G20" s="144">
         <v>106</v>
       </c>
-      <c r="H20" s="140">
+      <c r="H20" s="145">
         <v>68</v>
       </c>
-      <c r="I20" s="141">
-        <v>0.46326666666666699</v>
-      </c>
-      <c r="J20" s="142">
+      <c r="I20" s="146">
+        <v>0.463266666666667</v>
+      </c>
+      <c r="J20" s="147">
         <v>1.91881040892193</v>
       </c>
-      <c r="K20" s="143">
-        <v>0.39244195142277999</v>
-      </c>
-      <c r="L20" s="144">
+      <c r="K20" s="148">
+        <v>0.39244195142278</v>
+      </c>
+      <c r="L20" s="149">
         <v>1.60098120886331</v>
       </c>
-      <c r="M20" s="142">
+      <c r="M20" s="147">
         <v>0.37890902062421</v>
       </c>
-      <c r="N20" s="142">
-        <v>1.5694083453910299</v>
-      </c>
-      <c r="O20" s="145" t="s">
+      <c r="N20" s="147">
+        <v>1.56940834539103</v>
+      </c>
+      <c r="O20" s="150" t="s">
         <v>62</v>
       </c>
-      <c r="P20" s="125"/>
-      <c r="Q20" s="125"/>
+      <c r="P20" s="130"/>
+      <c r="Q20" s="130"/>
     </row>
     <row r="21" spans="1:25">
-      <c r="C21" s="146">
-        <v>769.87681970884705</v>
-      </c>
-      <c r="D21" s="146">
-        <v>648.04446103438295</v>
-      </c>
-      <c r="E21" s="146">
-        <v>518.29059243801305</v>
-      </c>
-      <c r="F21" s="147">
+      <c r="C21" s="151">
+        <v>769.876819708847</v>
+      </c>
+      <c r="D21" s="151">
+        <v>648.044461034383</v>
+      </c>
+      <c r="E21" s="151">
+        <v>518.290592438013</v>
+      </c>
+      <c r="F21" s="152">
         <v>26.9456886898096</v>
       </c>
-      <c r="G21" s="148">
-        <v>22.681556136203401</v>
-      </c>
-      <c r="H21" s="149">
+      <c r="G21" s="153">
+        <v>22.6815561362034</v>
+      </c>
+      <c r="H21" s="154">
         <v>18.1401707353305</v>
       </c>
-      <c r="I21" s="150">
-        <v>2.7777777777777799</v>
-      </c>
-      <c r="J21" s="151">
-        <v>2.2222222222222201</v>
-      </c>
-      <c r="K21" s="152">
-        <v>1.6666666666666701</v>
-      </c>
-      <c r="L21" s="153">
-        <v>1.3888888888888899</v>
-      </c>
-      <c r="M21" s="151">
-        <v>1.1388888888888899</v>
-      </c>
-      <c r="N21" s="151">
+      <c r="I21" s="155">
+        <v>2.77777777777778</v>
+      </c>
+      <c r="J21" s="156">
+        <v>2.22222222222222</v>
+      </c>
+      <c r="K21" s="157">
+        <v>1.66666666666667</v>
+      </c>
+      <c r="L21" s="158">
+        <v>1.38888888888889</v>
+      </c>
+      <c r="M21" s="156">
+        <v>1.13888888888889</v>
+      </c>
+      <c r="N21" s="156">
         <v>0.3</v>
       </c>
-      <c r="O21" s="154" t="s">
+      <c r="O21" s="159" t="s">
         <v>63</v>
       </c>
-      <c r="P21" s="155"/>
-      <c r="Q21" s="155"/>
+      <c r="P21" s="160"/>
+      <c r="Q21" s="160"/>
     </row>
     <row r="22" spans="1:25">
-      <c r="C22" s="156">
-        <v>1259.7984322508401</v>
-      </c>
-      <c r="D22" s="156">
-        <v>894.30135622744797</v>
-      </c>
-      <c r="E22" s="156">
+      <c r="C22" s="161">
+        <v>1259.79843225084</v>
+      </c>
+      <c r="D22" s="161">
+        <v>894.301356227448</v>
+      </c>
+      <c r="E22" s="161">
         <v>495</v>
       </c>
-      <c r="F22" s="157">
-        <v>44.092945128779398</v>
-      </c>
-      <c r="G22" s="158">
-        <v>31.300547467960701</v>
-      </c>
-      <c r="H22" s="159">
-        <v>17.324999999999999</v>
-      </c>
-      <c r="I22" s="160">
+      <c r="F22" s="162">
+        <v>44.0929451287794</v>
+      </c>
+      <c r="G22" s="163">
+        <v>31.3005474679607</v>
+      </c>
+      <c r="H22" s="164">
+        <v>17.325</v>
+      </c>
+      <c r="I22" s="165">
         <v>2</v>
       </c>
-      <c r="J22" s="161">
+      <c r="J22" s="166">
         <v>0.3</v>
       </c>
-      <c r="K22" s="162">
+      <c r="K22" s="167">
         <v>1.80555555555556</v>
       </c>
-      <c r="L22" s="163">
+      <c r="L22" s="168">
         <v>0.3</v>
       </c>
-      <c r="M22" s="161">
+      <c r="M22" s="166">
         <v>1.5</v>
       </c>
-      <c r="N22" s="161">
+      <c r="N22" s="166">
         <v>0.3</v>
       </c>
-      <c r="O22" s="164" t="s">
+      <c r="O22" s="169" t="s">
         <v>64</v>
       </c>
-      <c r="P22" s="165"/>
-      <c r="Q22" s="165"/>
+      <c r="P22" s="170"/>
+      <c r="Q22" s="170"/>
     </row>
     <row r="23" spans="1:25">
-      <c r="C23" s="166">
+      <c r="C23" s="171">
         <v>174</v>
       </c>
-      <c r="D23" s="166">
+      <c r="D23" s="171">
         <v>174</v>
       </c>
-      <c r="E23" s="166">
+      <c r="E23" s="171">
         <v>174</v>
       </c>
-      <c r="F23" s="167">
+      <c r="F23" s="172">
         <v>3</v>
       </c>
-      <c r="G23" s="168">
+      <c r="G23" s="173">
         <v>3</v>
       </c>
-      <c r="H23" s="169">
+      <c r="H23" s="174">
         <v>3</v>
       </c>
-      <c r="I23" s="170">
+      <c r="I23" s="175">
         <v>0</v>
       </c>
-      <c r="J23" s="171">
-        <v>0.20588235294117599</v>
-      </c>
-      <c r="K23" s="172">
+      <c r="J23" s="176">
+        <v>0.205882352941176</v>
+      </c>
+      <c r="K23" s="177">
         <v>0</v>
       </c>
-      <c r="L23" s="173">
-        <v>0.20588235294117599</v>
-      </c>
-      <c r="M23" s="171">
+      <c r="L23" s="178">
+        <v>0.205882352941176</v>
+      </c>
+      <c r="M23" s="176">
         <v>0</v>
       </c>
-      <c r="N23" s="171">
-        <v>0.20588235294117599</v>
-      </c>
-      <c r="O23" s="174" t="s">
+      <c r="N23" s="176">
+        <v>0.205882352941176</v>
+      </c>
+      <c r="O23" s="179" t="s">
         <v>65</v>
       </c>
-      <c r="P23" s="155"/>
-      <c r="Q23" s="155"/>
-    </row>
-    <row r="26" spans="1:25" ht="16.899999999999999">
+      <c r="P23" s="160"/>
+      <c r="Q23" s="160"/>
+    </row>
+    <row r="26" ht="17.75" spans="1:25">
       <c r="C26" s="53" t="s">
         <v>66</v>
       </c>
@@ -4061,7 +4584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:25">
+    <row r="27" ht="15.25" spans="1:25">
       <c r="A27" s="54" t="s">
         <v>4</v>
       </c>
@@ -4184,7 +4707,7 @@
       </c>
       <c r="J28" s="9">
         <f t="shared" si="2"/>
-        <v>9.4E-2</v>
+        <v>0.094</v>
       </c>
       <c r="K28" s="9">
         <f t="shared" si="2"/>
@@ -4192,7 +4715,7 @@
       </c>
       <c r="L28" s="9">
         <f t="shared" si="2"/>
-        <v>9.4E-2</v>
+        <v>0.094</v>
       </c>
       <c r="M28" s="9">
         <f t="shared" si="2"/>
@@ -4200,16 +4723,16 @@
       </c>
       <c r="N28" s="9">
         <f t="shared" si="2"/>
-        <v>9.4E-2</v>
-      </c>
-      <c r="O28" s="175" t="s">
+        <v>0.094</v>
+      </c>
+      <c r="O28" s="180" t="s">
         <v>70</v>
       </c>
       <c r="P28">
         <v>25</v>
       </c>
       <c r="Q28">
-        <v>31.536000000000001</v>
+        <v>31.536</v>
       </c>
       <c r="S28" t="str">
         <f>IF(O28="","*","PRE")</f>
@@ -4271,25 +4794,25 @@
         <f t="shared" si="4"/>
         <v>1.33</v>
       </c>
-      <c r="J29" s="176">
+      <c r="J29" s="181">
         <f t="shared" si="4"/>
-        <v>1.0940000000000001</v>
+        <v>1.094</v>
       </c>
       <c r="K29" s="9">
         <f t="shared" si="4"/>
         <v>1.3</v>
       </c>
-      <c r="L29" s="176">
+      <c r="L29" s="181">
         <f t="shared" si="4"/>
-        <v>1.0940000000000001</v>
+        <v>1.094</v>
       </c>
       <c r="M29" s="9">
         <f t="shared" si="4"/>
         <v>1.28</v>
       </c>
-      <c r="N29" s="176">
+      <c r="N29" s="181">
         <f t="shared" si="4"/>
-        <v>1.0940000000000001</v>
+        <v>1.094</v>
       </c>
       <c r="O29" t="s">
         <v>73</v>
@@ -4298,7 +4821,7 @@
         <v>25</v>
       </c>
       <c r="Q29">
-        <v>31.536000000000001</v>
+        <v>31.536</v>
       </c>
       <c r="S29" t="str">
         <f t="shared" ref="S29:S39" si="5">IF(O29="","*","PRE")</f>
@@ -4362,7 +4885,7 @@
       </c>
       <c r="J30" s="9">
         <f t="shared" si="7"/>
-        <v>9.4E-2</v>
+        <v>0.094</v>
       </c>
       <c r="K30" s="9">
         <f t="shared" si="7"/>
@@ -4370,7 +4893,7 @@
       </c>
       <c r="L30" s="9">
         <f t="shared" si="7"/>
-        <v>9.4E-2</v>
+        <v>0.094</v>
       </c>
       <c r="M30" s="9">
         <f t="shared" si="7"/>
@@ -4378,9 +4901,9 @@
       </c>
       <c r="N30" s="9">
         <f t="shared" si="7"/>
-        <v>9.4E-2</v>
-      </c>
-      <c r="O30" s="175" t="s">
+        <v>0.094</v>
+      </c>
+      <c r="O30" s="180" t="s">
         <v>70</v>
       </c>
       <c r="S30" t="str">
@@ -4461,7 +4984,7 @@
         <v>25</v>
       </c>
       <c r="Q31">
-        <v>31.536000000000001</v>
+        <v>31.536</v>
       </c>
       <c r="S31" t="str">
         <f t="shared" si="5"/>
@@ -4534,7 +5057,7 @@
         <f t="shared" si="9"/>
         <v>1.19</v>
       </c>
-      <c r="O32" s="175" t="s">
+      <c r="O32" s="180" t="s">
         <v>70</v>
       </c>
       <c r="S32" t="str">
@@ -4615,7 +5138,7 @@
         <v>25</v>
       </c>
       <c r="Q33">
-        <v>31.536000000000001</v>
+        <v>31.536</v>
       </c>
       <c r="S33" t="str">
         <f t="shared" si="5"/>
@@ -4688,7 +5211,7 @@
         <f t="shared" si="11"/>
         <v>1.2</v>
       </c>
-      <c r="O34" s="175" t="s">
+      <c r="O34" s="180" t="s">
         <v>70</v>
       </c>
       <c r="S34" t="str">
@@ -4725,7 +5248,7 @@
       </c>
       <c r="C35" s="38">
         <f t="shared" ref="C35:N35" si="12">C12</f>
-        <v>3332.0882352941198</v>
+        <v>3332.08823529412</v>
       </c>
       <c r="D35" s="38">
         <f t="shared" si="12"/>
@@ -4737,7 +5260,7 @@
       </c>
       <c r="F35" s="38">
         <f t="shared" si="12"/>
-        <v>55.825000000000003</v>
+        <v>55.825</v>
       </c>
       <c r="G35" s="38">
         <f t="shared" si="12"/>
@@ -4749,11 +5272,11 @@
       </c>
       <c r="I35" s="9">
         <f t="shared" si="12"/>
-        <v>1.9966670387596901</v>
+        <v>1.99666703875969</v>
       </c>
       <c r="J35" s="9">
         <f t="shared" si="12"/>
-        <v>0.83711999999999998</v>
+        <v>0.83712</v>
       </c>
       <c r="K35" s="9">
         <f t="shared" si="12"/>
@@ -4761,15 +5284,15 @@
       </c>
       <c r="L35" s="9">
         <f t="shared" si="12"/>
-        <v>0.76080000000000003</v>
+        <v>0.7608</v>
       </c>
       <c r="M35" s="9">
         <f t="shared" si="12"/>
-        <v>0.33333333333333298</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="N35" s="9">
         <f t="shared" si="12"/>
-        <v>0.70799999999999996</v>
+        <v>0.708</v>
       </c>
       <c r="O35" t="s">
         <v>76</v>
@@ -4778,7 +5301,7 @@
         <v>25</v>
       </c>
       <c r="Q35">
-        <v>31.536000000000001</v>
+        <v>31.536</v>
       </c>
       <c r="S35" t="str">
         <f t="shared" si="5"/>
@@ -4808,11 +5331,11 @@
     <row r="36" spans="1:25">
       <c r="C36" s="38">
         <f t="shared" ref="C36:N36" si="13">C13</f>
-        <v>5331.3411764705897</v>
+        <v>5331.34117647059</v>
       </c>
       <c r="D36" s="38">
         <f t="shared" si="13"/>
-        <v>2920.8941176470598</v>
+        <v>2920.89411764706</v>
       </c>
       <c r="E36" s="38">
         <f t="shared" si="13"/>
@@ -4820,11 +5343,11 @@
       </c>
       <c r="F36" s="38">
         <f t="shared" si="13"/>
-        <v>94.902500000000003</v>
+        <v>94.9025</v>
       </c>
       <c r="G36" s="38">
         <f t="shared" si="13"/>
-        <v>63.314999999999998</v>
+        <v>63.315</v>
       </c>
       <c r="H36" s="38">
         <f t="shared" si="13"/>
@@ -4832,11 +5355,11 @@
       </c>
       <c r="I36" s="9">
         <f t="shared" si="13"/>
-        <v>1.9966670387596901</v>
+        <v>1.99666703875969</v>
       </c>
       <c r="J36" s="9">
         <f t="shared" si="13"/>
-        <v>0.83711999999999998</v>
+        <v>0.83712</v>
       </c>
       <c r="K36" s="9">
         <f t="shared" si="13"/>
@@ -4844,17 +5367,17 @@
       </c>
       <c r="L36" s="9">
         <f t="shared" si="13"/>
-        <v>0.76080000000000003</v>
+        <v>0.7608</v>
       </c>
       <c r="M36" s="9">
         <f t="shared" si="13"/>
-        <v>0.33333333333333298</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="N36" s="9">
         <f t="shared" si="13"/>
         <v>0.72</v>
       </c>
-      <c r="O36" s="175" t="s">
+      <c r="O36" s="180" t="s">
         <v>70</v>
       </c>
       <c r="S36" t="str">
@@ -4885,15 +5408,15 @@
     <row r="37" spans="1:25">
       <c r="C37" s="38">
         <f t="shared" ref="C37:N37" si="14">C21</f>
-        <v>769.87681970884705</v>
+        <v>769.876819708847</v>
       </c>
       <c r="D37" s="38">
         <f t="shared" si="14"/>
-        <v>648.04446103438295</v>
+        <v>648.044461034383</v>
       </c>
       <c r="E37" s="38">
         <f t="shared" si="14"/>
-        <v>518.29059243801305</v>
+        <v>518.290592438013</v>
       </c>
       <c r="F37" s="38">
         <f t="shared" si="14"/>
@@ -4901,7 +5424,7 @@
       </c>
       <c r="G37" s="38">
         <f t="shared" si="14"/>
-        <v>22.681556136203401</v>
+        <v>22.6815561362034</v>
       </c>
       <c r="H37" s="38">
         <f t="shared" si="14"/>
@@ -4909,29 +5432,29 @@
       </c>
       <c r="I37" s="9">
         <f t="shared" si="14"/>
-        <v>2.7777777777777799</v>
+        <v>2.77777777777778</v>
       </c>
       <c r="J37" s="9">
         <f t="shared" si="14"/>
-        <v>2.2222222222222201</v>
+        <v>2.22222222222222</v>
       </c>
       <c r="K37" s="9">
         <f t="shared" si="14"/>
-        <v>1.6666666666666701</v>
+        <v>1.66666666666667</v>
       </c>
       <c r="L37" s="9">
         <f t="shared" si="14"/>
-        <v>1.3888888888888899</v>
+        <v>1.38888888888889</v>
       </c>
       <c r="M37" s="9">
         <f t="shared" si="14"/>
-        <v>1.1388888888888899</v>
+        <v>1.13888888888889</v>
       </c>
       <c r="N37" s="9">
         <f t="shared" si="14"/>
         <v>0.3</v>
       </c>
-      <c r="O37" s="175" t="s">
+      <c r="O37" s="180" t="s">
         <v>70</v>
       </c>
       <c r="S37" t="str">
@@ -4962,11 +5485,11 @@
     <row r="38" spans="1:25">
       <c r="C38" s="38">
         <f t="shared" ref="C38:N38" si="15">C22</f>
-        <v>1259.7984322508401</v>
+        <v>1259.79843225084</v>
       </c>
       <c r="D38" s="38">
         <f t="shared" si="15"/>
-        <v>894.30135622744797</v>
+        <v>894.301356227448</v>
       </c>
       <c r="E38" s="38">
         <f t="shared" si="15"/>
@@ -4974,15 +5497,15 @@
       </c>
       <c r="F38" s="38">
         <f t="shared" si="15"/>
-        <v>44.092945128779398</v>
+        <v>44.0929451287794</v>
       </c>
       <c r="G38" s="38">
         <f t="shared" si="15"/>
-        <v>31.300547467960701</v>
+        <v>31.3005474679607</v>
       </c>
       <c r="H38" s="38">
         <f t="shared" si="15"/>
-        <v>17.324999999999999</v>
+        <v>17.325</v>
       </c>
       <c r="I38" s="9">
         <f t="shared" si="15"/>
@@ -5008,7 +5531,7 @@
         <f t="shared" si="15"/>
         <v>0.3</v>
       </c>
-      <c r="O38" s="175" t="s">
+      <c r="O38" s="180" t="s">
         <v>70</v>
       </c>
       <c r="S38" t="str">
@@ -5037,77 +5560,77 @@
       </c>
     </row>
     <row r="39" spans="1:25">
-      <c r="A39" s="177" t="str">
+      <c r="A39" s="182" t="str">
         <f>A35</f>
         <v>HH2</v>
       </c>
-      <c r="B39" s="177" t="s">
+      <c r="B39" s="182" t="s">
         <v>69</v>
       </c>
-      <c r="C39" s="178">
+      <c r="C39" s="183">
         <f>C29</f>
         <v>900</v>
       </c>
-      <c r="D39" s="178">
+      <c r="D39" s="183">
         <f t="shared" ref="D39:H39" si="16">D29</f>
         <v>850</v>
       </c>
-      <c r="E39" s="178">
+      <c r="E39" s="183">
         <f t="shared" si="16"/>
         <v>800</v>
       </c>
-      <c r="F39" s="178">
+      <c r="F39" s="183">
         <f t="shared" si="16"/>
         <v>36</v>
       </c>
-      <c r="G39" s="178">
+      <c r="G39" s="183">
         <f t="shared" si="16"/>
         <v>34</v>
       </c>
-      <c r="H39" s="178">
+      <c r="H39" s="183">
         <f t="shared" si="16"/>
         <v>32</v>
       </c>
-      <c r="I39" s="179">
+      <c r="I39" s="184">
         <v>1.25</v>
       </c>
-      <c r="J39" s="179">
+      <c r="J39" s="184">
         <v>0.12</v>
       </c>
-      <c r="K39" s="179">
+      <c r="K39" s="184">
         <v>1.25</v>
       </c>
-      <c r="L39" s="179">
+      <c r="L39" s="184">
         <v>0.12</v>
       </c>
-      <c r="M39" s="179">
+      <c r="M39" s="184">
         <v>1.25</v>
       </c>
-      <c r="N39" s="179">
+      <c r="N39" s="184">
         <v>0.12</v>
       </c>
-      <c r="O39" s="177" t="s">
+      <c r="O39" s="182" t="s">
         <v>77</v>
       </c>
-      <c r="P39" s="177">
+      <c r="P39" s="182">
         <v>25</v>
       </c>
-      <c r="Q39" s="177">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="R39" s="177"/>
-      <c r="S39" s="177" t="str">
+      <c r="Q39" s="182">
+        <v>31.536</v>
+      </c>
+      <c r="R39" s="182"/>
+      <c r="S39" s="182" t="str">
         <f t="shared" si="5"/>
         <v>PRE</v>
       </c>
-      <c r="T39" s="177" t="str">
+      <c r="T39" s="182" t="str">
         <f t="shared" si="6"/>
         <v>H2prd_Gas_ATR_CCS</v>
       </c>
-      <c r="U39" s="177" t="s">
+      <c r="U39" s="182" t="s">
         <v>78</v>
       </c>
-      <c r="V39" s="177" t="s">
+      <c r="V39" s="182" t="s">
         <v>71</v>
       </c>
       <c r="W39" t="s">
@@ -5128,37 +5651,39 @@
     <mergeCell ref="O1:O4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="B3:Q12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="9" style="52"/>
-    <col min="2" max="2" width="12.86328125" style="52" customWidth="1"/>
-    <col min="3" max="3" width="8.86328125" style="52" customWidth="1"/>
-    <col min="4" max="4" width="14.86328125" style="52" customWidth="1"/>
+    <col min="2" max="2" width="12.8636363636364" style="52" customWidth="1"/>
+    <col min="3" max="3" width="8.86363636363636" style="52" customWidth="1"/>
+    <col min="4" max="4" width="14.8636363636364" style="52" customWidth="1"/>
     <col min="5" max="5" width="9" style="52" customWidth="1"/>
-    <col min="6" max="6" width="10.265625" style="52" customWidth="1"/>
-    <col min="7" max="7" width="4.59765625" style="52" customWidth="1"/>
-    <col min="8" max="8" width="11.59765625" style="52" customWidth="1"/>
-    <col min="9" max="9" width="11.265625" style="52" customWidth="1"/>
-    <col min="10" max="10" width="11.3984375" style="52" customWidth="1"/>
-    <col min="11" max="11" width="5.59765625" style="52" customWidth="1"/>
+    <col min="6" max="6" width="10.2636363636364" style="52" customWidth="1"/>
+    <col min="7" max="7" width="4.6" style="52" customWidth="1"/>
+    <col min="8" max="8" width="11.6" style="52" customWidth="1"/>
+    <col min="9" max="9" width="11.2636363636364" style="52" customWidth="1"/>
+    <col min="10" max="10" width="11.4" style="52" customWidth="1"/>
+    <col min="11" max="11" width="5.6" style="52" customWidth="1"/>
     <col min="12" max="12" width="9" style="52"/>
-    <col min="13" max="13" width="11.265625" style="52" customWidth="1"/>
-    <col min="14" max="14" width="12.86328125" style="52" customWidth="1"/>
-    <col min="15" max="15" width="15.265625" style="52" customWidth="1"/>
-    <col min="16" max="16" width="4.59765625" style="52" customWidth="1"/>
+    <col min="13" max="13" width="11.2636363636364" style="52" customWidth="1"/>
+    <col min="14" max="14" width="12.8636363636364" style="52" customWidth="1"/>
+    <col min="15" max="15" width="15.2636363636364" style="52" customWidth="1"/>
+    <col min="16" max="16" width="4.6" style="52" customWidth="1"/>
     <col min="17" max="17" width="5" style="52" customWidth="1"/>
     <col min="18" max="16384" width="9" style="52"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:17" ht="16.899999999999999">
+    <row r="3" ht="17.75" spans="2:17">
       <c r="D3" s="53" t="s">
         <v>79</v>
       </c>
@@ -5170,7 +5695,7 @@
       <c r="P3" s="54"/>
       <c r="Q3" s="54"/>
     </row>
-    <row r="4" spans="2:17" ht="14.25">
+    <row r="4" ht="16" spans="2:17">
       <c r="B4" s="55" t="s">
         <v>80</v>
       </c>
@@ -5228,7 +5753,7 @@
         <v>91</v>
       </c>
       <c r="E5" s="52">
-        <v>31.536000000000001</v>
+        <v>31.536</v>
       </c>
       <c r="F5" s="56">
         <v>0.6</v>
@@ -5237,10 +5762,10 @@
         <v>0.6</v>
       </c>
       <c r="H5" s="56">
-        <v>189.21600000000001</v>
+        <v>189.216</v>
       </c>
       <c r="I5" s="56">
-        <v>88.300799999999995</v>
+        <v>88.3008</v>
       </c>
       <c r="J5" s="52">
         <v>60</v>
@@ -5277,7 +5802,7 @@
         <v>91</v>
       </c>
       <c r="E6" s="52">
-        <v>31.536000000000001</v>
+        <v>31.536</v>
       </c>
       <c r="F6" s="56">
         <v>0.6</v>
@@ -5286,10 +5811,10 @@
         <v>0.6</v>
       </c>
       <c r="H6" s="56">
-        <v>189.21600000000001</v>
+        <v>189.216</v>
       </c>
       <c r="I6" s="56">
-        <v>88.300799999999995</v>
+        <v>88.3008</v>
       </c>
       <c r="J6" s="52">
         <v>60</v>
@@ -5323,7 +5848,7 @@
         <v>91</v>
       </c>
       <c r="E7" s="52">
-        <v>31.536000000000001</v>
+        <v>31.536</v>
       </c>
       <c r="F7" s="56">
         <v>0.1</v>
@@ -5332,16 +5857,16 @@
         <v>0.6</v>
       </c>
       <c r="H7" s="56">
-        <v>141.91200000000001</v>
+        <v>141.912</v>
       </c>
       <c r="I7" s="56">
-        <v>75.686400000000006</v>
+        <v>75.6864</v>
       </c>
       <c r="J7" s="52">
         <v>60</v>
       </c>
       <c r="K7" s="57">
-        <v>0.86956521739130399</v>
+        <v>0.869565217391304</v>
       </c>
       <c r="N7" s="52" t="str">
         <f t="shared" si="0"/>
@@ -5369,7 +5894,7 @@
         <v>91</v>
       </c>
       <c r="E8" s="52">
-        <v>31.536000000000001</v>
+        <v>31.536</v>
       </c>
       <c r="F8" s="56">
         <v>0.3</v>
@@ -5404,7 +5929,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="9" spans="2:17" ht="13.15">
+    <row r="9" ht="13" spans="2:17">
       <c r="B9" s="58" t="s">
         <v>99</v>
       </c>
@@ -5416,7 +5941,7 @@
       </c>
       <c r="E9" s="52">
         <f t="shared" ref="E9:K9" si="1">E7</f>
-        <v>31.536000000000001</v>
+        <v>31.536</v>
       </c>
       <c r="F9" s="56">
         <f t="shared" si="1"/>
@@ -5428,11 +5953,11 @@
       </c>
       <c r="H9" s="56">
         <f t="shared" si="1"/>
-        <v>141.91200000000001</v>
+        <v>141.912</v>
       </c>
       <c r="I9" s="56">
         <f t="shared" si="1"/>
-        <v>75.686400000000006</v>
+        <v>75.6864</v>
       </c>
       <c r="J9" s="52">
         <f t="shared" si="1"/>
@@ -5440,7 +5965,7 @@
       </c>
       <c r="K9" s="57">
         <f t="shared" si="1"/>
-        <v>0.86956521739130399</v>
+        <v>0.869565217391304</v>
       </c>
       <c r="N9" s="52" t="str">
         <f t="shared" si="0"/>
@@ -5469,7 +5994,7 @@
       </c>
       <c r="E10" s="52">
         <f>E8</f>
-        <v>31.536000000000001</v>
+        <v>31.536</v>
       </c>
       <c r="F10" s="56"/>
       <c r="G10" s="56"/>
@@ -5538,33 +6063,34 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:AK40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="8" max="8" width="17.59765625" customWidth="1"/>
-    <col min="10" max="10" width="10.86328125" customWidth="1"/>
+    <col min="8" max="8" width="17.6" customWidth="1"/>
+    <col min="10" max="10" width="10.8636363636364" customWidth="1"/>
     <col min="11" max="13" width="5" customWidth="1"/>
-    <col min="14" max="14" width="8.3984375" customWidth="1"/>
+    <col min="14" max="14" width="8.4" customWidth="1"/>
     <col min="15" max="15" width="2" customWidth="1"/>
-    <col min="16" max="16" width="3.59765625" customWidth="1"/>
-    <col min="17" max="17" width="17.59765625" customWidth="1"/>
+    <col min="16" max="16" width="3.6" customWidth="1"/>
+    <col min="17" max="17" width="17.6" customWidth="1"/>
     <col min="21" max="21" width="2" customWidth="1"/>
-    <col min="22" max="22" width="17.59765625" customWidth="1"/>
+    <col min="22" max="22" width="17.6" customWidth="1"/>
     <col min="23" max="25" width="6" customWidth="1"/>
     <col min="26" max="26" width="2" customWidth="1"/>
-    <col min="27" max="27" width="17.59765625" customWidth="1"/>
-    <col min="28" max="28" width="11.3984375" customWidth="1"/>
+    <col min="27" max="27" width="17.6" customWidth="1"/>
+    <col min="28" max="28" width="11.4" customWidth="1"/>
     <col min="29" max="31" width="5" customWidth="1"/>
-    <col min="33" max="33" width="19.86328125" customWidth="1"/>
-    <col min="34" max="34" width="5.59765625" customWidth="1"/>
+    <col min="33" max="33" width="19.8636363636364" customWidth="1"/>
+    <col min="34" max="34" width="5.6" customWidth="1"/>
     <col min="35" max="37" width="5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5728,7 +6254,7 @@
         <v>439.05</v>
       </c>
       <c r="N3" s="39">
-        <v>31.536000000000001</v>
+        <v>31.536</v>
       </c>
       <c r="O3" s="38"/>
       <c r="P3" s="40">
@@ -5740,15 +6266,15 @@
       </c>
       <c r="R3" s="39">
         <f>$P3*K3</f>
-        <v>29.109000000000002</v>
+        <v>29.109</v>
       </c>
       <c r="S3" s="39">
         <f t="shared" ref="S3:T5" si="2">$P3*L3</f>
-        <v>13.226000000000001</v>
+        <v>13.226</v>
       </c>
       <c r="T3" s="39">
         <f t="shared" si="2"/>
-        <v>8.7810000000000006</v>
+        <v>8.781</v>
       </c>
       <c r="V3" t="str">
         <f t="shared" ref="V3:V5" si="3">$H3</f>
@@ -5799,7 +6325,7 @@
         <v>661.3</v>
       </c>
       <c r="E4" s="37">
-        <v>138.44999999999999</v>
+        <v>138.45</v>
       </c>
       <c r="F4" s="37">
         <v>1368.75</v>
@@ -5817,17 +6343,17 @@
         <v>338.75</v>
       </c>
       <c r="L4" s="38">
-        <v>138.44999999999999</v>
+        <v>138.45</v>
       </c>
       <c r="M4" s="38">
         <v>87.3</v>
       </c>
       <c r="N4" s="39">
-        <v>31.536000000000001</v>
+        <v>31.536</v>
       </c>
       <c r="O4" s="39"/>
       <c r="P4" s="40">
-        <v>3.5000000000000003E-2</v>
+        <v>0.035</v>
       </c>
       <c r="Q4" t="str">
         <f t="shared" si="1"/>
@@ -5835,28 +6361,28 @@
       </c>
       <c r="R4" s="39">
         <f t="shared" ref="R4:R5" si="4">$P4*K4</f>
-        <v>11.856249999999999</v>
+        <v>11.85625</v>
       </c>
       <c r="S4" s="39">
         <f t="shared" si="2"/>
-        <v>4.8457499999999998</v>
+        <v>4.84575</v>
       </c>
       <c r="T4" s="39">
         <f t="shared" si="2"/>
-        <v>3.0554999999999999</v>
+        <v>3.0555</v>
       </c>
       <c r="V4" t="str">
         <f t="shared" si="3"/>
         <v>H2Conv_LOHC</v>
       </c>
       <c r="W4">
-        <v>0.92500000000000004</v>
+        <v>0.925</v>
       </c>
       <c r="X4">
         <v>0.95</v>
       </c>
       <c r="Y4">
-        <v>0.97499999999999998</v>
+        <v>0.975</v>
       </c>
       <c r="AA4" t="str">
         <f t="shared" ref="AA4:AA5" si="5">H4</f>
@@ -5918,7 +6444,7 @@
         <v>799.5</v>
       </c>
       <c r="N5" s="39">
-        <v>31.536000000000001</v>
+        <v>31.536</v>
       </c>
       <c r="O5" s="39"/>
       <c r="P5" s="40">
@@ -5964,7 +6490,7 @@
         <v>0.255</v>
       </c>
       <c r="AD5" s="9">
-        <v>0.22500000000000001</v>
+        <v>0.225</v>
       </c>
       <c r="AE5" s="9">
         <v>0.1875</v>
@@ -5991,7 +6517,7 @@
         <v>0.02</v>
       </c>
       <c r="E6" s="44">
-        <v>3.5000000000000003E-2</v>
+        <v>0.035</v>
       </c>
       <c r="F6" s="44">
         <v>0.04</v>
@@ -6011,7 +6537,7 @@
         <v>0.875</v>
       </c>
       <c r="E7" s="44">
-        <v>0.92500000000000004</v>
+        <v>0.925</v>
       </c>
       <c r="F7" s="44">
         <v>0.95</v>
@@ -6054,7 +6580,7 @@
         <v>0.875</v>
       </c>
       <c r="E9" s="44">
-        <v>0.97499999999999998</v>
+        <v>0.975</v>
       </c>
       <c r="F9" s="44">
         <v>1</v>
@@ -6065,7 +6591,7 @@
       </c>
       <c r="I9">
         <f>F11*3.6/120</f>
-        <v>0.22500000000000001</v>
+        <v>0.225</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -6239,7 +6765,7 @@
         <v>752.1</v>
       </c>
       <c r="F14" s="48">
-        <v>649.45000000000005</v>
+        <v>649.45</v>
       </c>
       <c r="H14" t="s">
         <v>143</v>
@@ -6260,11 +6786,11 @@
         <v>276.55</v>
       </c>
       <c r="N14" s="39">
-        <v>31.536000000000001</v>
+        <v>31.536</v>
       </c>
       <c r="O14" s="38"/>
       <c r="P14" s="40">
-        <v>3.5000000000000003E-2</v>
+        <v>0.035</v>
       </c>
       <c r="Q14" t="str">
         <f t="shared" ref="Q14:Q16" si="6">$H14</f>
@@ -6272,15 +6798,15 @@
       </c>
       <c r="R14" s="39">
         <f>$P14*K14</f>
-        <v>40.391750000000002</v>
+        <v>40.39175</v>
       </c>
       <c r="S14" s="39">
         <f t="shared" ref="S14:T16" si="7">$P14*L14</f>
-        <v>16.024750000000001</v>
+        <v>16.02475</v>
       </c>
       <c r="T14" s="39">
         <f t="shared" si="7"/>
-        <v>9.6792499999999997</v>
+        <v>9.67925</v>
       </c>
       <c r="V14" t="str">
         <f t="shared" ref="V14:V16" si="8">$H14</f>
@@ -6300,10 +6826,10 @@
         <v>0.06</v>
       </c>
       <c r="AD14" s="9">
-        <v>4.4999999999999998E-2</v>
+        <v>0.045</v>
       </c>
       <c r="AE14" s="9">
-        <v>2.2499999999999999E-2</v>
+        <v>0.0225</v>
       </c>
       <c r="AF14" s="9">
         <v>0.4</v>
@@ -6349,11 +6875,11 @@
         <v>169.75</v>
       </c>
       <c r="N15" s="39">
-        <v>31.536000000000001</v>
+        <v>31.536</v>
       </c>
       <c r="O15" s="39"/>
       <c r="P15" s="40">
-        <v>4.4999999999999998E-2</v>
+        <v>0.045</v>
       </c>
       <c r="Q15" t="str">
         <f t="shared" si="6"/>
@@ -6361,15 +6887,15 @@
       </c>
       <c r="R15" s="39">
         <f t="shared" ref="R15:R16" si="9">$P15*K15</f>
-        <v>33.844499999999996</v>
+        <v>33.8445</v>
       </c>
       <c r="S15" s="39">
         <f t="shared" si="7"/>
-        <v>14.467499999999999</v>
+        <v>14.4675</v>
       </c>
       <c r="T15" s="39">
         <f t="shared" si="7"/>
-        <v>7.6387499999999999</v>
+        <v>7.63875</v>
       </c>
       <c r="V15" t="str">
         <f t="shared" si="8"/>
@@ -6429,7 +6955,7 @@
         <v>16</v>
       </c>
       <c r="K16" s="38">
-        <v>649.45000000000005</v>
+        <v>649.45</v>
       </c>
       <c r="L16" s="38">
         <v>267.3</v>
@@ -6438,11 +6964,11 @@
         <v>125.45</v>
       </c>
       <c r="N16" s="39">
-        <v>31.536000000000001</v>
+        <v>31.536</v>
       </c>
       <c r="O16" s="39"/>
       <c r="P16" s="40">
-        <v>3.5000000000000003E-2</v>
+        <v>0.035</v>
       </c>
       <c r="Q16" t="str">
         <f t="shared" si="6"/>
@@ -6454,11 +6980,11 @@
       </c>
       <c r="S16" s="39">
         <f t="shared" si="7"/>
-        <v>9.3554999999999993</v>
+        <v>9.3555</v>
       </c>
       <c r="T16" s="39">
         <f t="shared" si="7"/>
-        <v>4.3907499999999997</v>
+        <v>4.39075</v>
       </c>
       <c r="V16" t="str">
         <f t="shared" si="8"/>
@@ -6475,13 +7001,13 @@
         <v>102</v>
       </c>
       <c r="AC16" s="9">
-        <v>2.2499999999999999E-2</v>
+        <v>0.0225</v>
       </c>
       <c r="AD16" s="9">
-        <v>1.575E-2</v>
+        <v>0.01575</v>
       </c>
       <c r="AE16" s="9">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AF16" s="9">
         <v>0.4</v>
@@ -6505,13 +7031,13 @@
       </c>
       <c r="C17" s="49"/>
       <c r="D17" s="44">
-        <v>3.5000000000000003E-2</v>
+        <v>0.035</v>
       </c>
       <c r="E17" s="44">
-        <v>4.4999999999999998E-2</v>
+        <v>0.045</v>
       </c>
       <c r="F17" s="44">
-        <v>3.5000000000000003E-2</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="18" spans="1:33">
@@ -6567,7 +7093,7 @@
       </c>
       <c r="J19" s="39">
         <f t="shared" si="11"/>
-        <v>2.2499999999999999E-2</v>
+        <v>0.0225</v>
       </c>
       <c r="AA19" t="s">
         <v>120</v>
@@ -6604,11 +7130,11 @@
         <v>2</v>
       </c>
       <c r="F20" s="37">
-        <v>0.52500000000000002</v>
+        <v>0.525</v>
       </c>
       <c r="H20" s="39">
         <f t="shared" ref="H20:H24" si="12">D20*3.6/120</f>
-        <v>4.4999999999999998E-2</v>
+        <v>0.045</v>
       </c>
       <c r="I20" s="39">
         <f t="shared" si="11"/>
@@ -6616,7 +7142,7 @@
       </c>
       <c r="J20" s="39">
         <f t="shared" si="11"/>
-        <v>1.575E-2</v>
+        <v>0.01575</v>
       </c>
       <c r="AA20" t="str">
         <f>V14</f>
@@ -6629,10 +7155,10 @@
         <v>0.42</v>
       </c>
       <c r="AD20" s="9">
-        <v>0.33150000000000002</v>
+        <v>0.3315</v>
       </c>
       <c r="AE20" s="9">
-        <v>0.24299999999999999</v>
+        <v>0.243</v>
       </c>
       <c r="AF20" t="s">
         <v>149</v>
@@ -6658,7 +7184,7 @@
       </c>
       <c r="H21" s="39">
         <f t="shared" si="12"/>
-        <v>2.2499999999999999E-2</v>
+        <v>0.0225</v>
       </c>
       <c r="I21" s="39">
         <f t="shared" si="11"/>
@@ -6666,7 +7192,7 @@
       </c>
       <c r="J21" s="39">
         <f t="shared" si="11"/>
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AA21" t="str">
         <f>V15</f>
@@ -6679,10 +7205,10 @@
         <v>0.51</v>
       </c>
       <c r="AD21" s="9">
-        <v>0.42449999999999999</v>
+        <v>0.4245</v>
       </c>
       <c r="AE21" s="9">
-        <v>0.33900000000000002</v>
+        <v>0.339</v>
       </c>
       <c r="AF21" t="s">
         <v>149</v>
@@ -6740,11 +7266,11 @@
       </c>
       <c r="H23" s="39">
         <f t="shared" si="12"/>
-        <v>0.33150000000000002</v>
+        <v>0.3315</v>
       </c>
       <c r="I23" s="39">
         <f t="shared" si="11"/>
-        <v>0.42449999999999999</v>
+        <v>0.4245</v>
       </c>
       <c r="J23" s="39">
         <f t="shared" si="11"/>
@@ -6768,11 +7294,11 @@
       </c>
       <c r="H24" s="39">
         <f t="shared" si="12"/>
-        <v>0.24299999999999999</v>
+        <v>0.243</v>
       </c>
       <c r="I24" s="39">
         <f t="shared" si="11"/>
-        <v>0.33900000000000002</v>
+        <v>0.339</v>
       </c>
       <c r="J24" s="39">
         <f t="shared" si="11"/>
@@ -6938,35 +7464,37 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="B3:Y5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="2" max="2" width="11.265625" customWidth="1"/>
-    <col min="3" max="3" width="14.59765625" customWidth="1"/>
-    <col min="4" max="4" width="26.3984375" customWidth="1"/>
-    <col min="5" max="5" width="20.265625" customWidth="1"/>
+    <col min="2" max="2" width="11.2636363636364" customWidth="1"/>
+    <col min="3" max="3" width="14.6" customWidth="1"/>
+    <col min="4" max="4" width="26.4" customWidth="1"/>
+    <col min="5" max="5" width="20.2636363636364" customWidth="1"/>
     <col min="6" max="6" width="5" customWidth="1"/>
-    <col min="7" max="7" width="4.59765625" customWidth="1"/>
+    <col min="7" max="7" width="4.6" customWidth="1"/>
     <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="9" max="9" width="10.265625" customWidth="1"/>
-    <col min="10" max="10" width="7.86328125" customWidth="1"/>
-    <col min="12" max="12" width="17.86328125" customWidth="1"/>
-    <col min="13" max="13" width="9.3984375" customWidth="1"/>
+    <col min="9" max="9" width="10.2636363636364" customWidth="1"/>
+    <col min="10" max="10" width="7.86363636363636" customWidth="1"/>
+    <col min="12" max="12" width="17.8636363636364" customWidth="1"/>
+    <col min="13" max="13" width="9.4" customWidth="1"/>
     <col min="14" max="14" width="12" customWidth="1"/>
-    <col min="15" max="15" width="8.86328125" customWidth="1"/>
+    <col min="15" max="15" width="8.86363636363636" customWidth="1"/>
     <col min="16" max="16" width="14" customWidth="1"/>
-    <col min="17" max="17" width="6.86328125" customWidth="1"/>
-    <col min="18" max="18" width="11.86328125" customWidth="1"/>
-    <col min="19" max="19" width="7.86328125" customWidth="1"/>
-    <col min="20" max="20" width="12.86328125" customWidth="1"/>
-    <col min="21" max="21" width="4.59765625" customWidth="1"/>
+    <col min="17" max="17" width="6.86363636363636" customWidth="1"/>
+    <col min="18" max="18" width="11.8636363636364" customWidth="1"/>
+    <col min="19" max="19" width="7.86363636363636" customWidth="1"/>
+    <col min="20" max="20" width="12.8636363636364" customWidth="1"/>
+    <col min="21" max="21" width="4.6" customWidth="1"/>
     <col min="22" max="22" width="9" customWidth="1"/>
-    <col min="23" max="23" width="4.3984375" customWidth="1"/>
+    <col min="23" max="23" width="4.4" customWidth="1"/>
     <col min="24" max="24" width="5" customWidth="1"/>
     <col min="25" max="25" width="9" customWidth="1"/>
   </cols>
@@ -7092,16 +7620,16 @@
         <v>71</v>
       </c>
       <c r="S5" s="9">
-        <v>2.1347031963470302</v>
+        <v>2.13470319634703</v>
       </c>
       <c r="T5" s="9">
         <v>1.72231735159817</v>
       </c>
       <c r="U5" s="9">
-        <v>0.55249999999999999</v>
+        <v>0.5525</v>
       </c>
       <c r="V5" s="9">
-        <v>0.55249999999999999</v>
+        <v>0.5525</v>
       </c>
       <c r="W5">
         <v>20</v>
@@ -7110,49 +7638,51 @@
         <v>0.85</v>
       </c>
       <c r="Y5">
-        <v>31.536000000000001</v>
+        <v>31.536</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="B1:BP66"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.8" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="32.53125" customWidth="1"/>
-    <col min="3" max="3" width="30.73046875" customWidth="1"/>
+    <col min="2" max="2" width="32.5272727272727" customWidth="1"/>
+    <col min="3" max="3" width="30.7272727272727" customWidth="1"/>
     <col min="4" max="4" width="50" customWidth="1"/>
-    <col min="5" max="5" width="29.9296875" customWidth="1"/>
-    <col min="6" max="9" width="33.73046875" customWidth="1"/>
-    <col min="10" max="10" width="19.265625" customWidth="1"/>
-    <col min="11" max="11" width="14.59765625" customWidth="1"/>
-    <col min="12" max="12" width="14.265625" customWidth="1"/>
-    <col min="13" max="13" width="13.06640625" customWidth="1"/>
-    <col min="14" max="14" width="12.796875" customWidth="1"/>
-    <col min="15" max="15" width="6.796875" customWidth="1"/>
-    <col min="16" max="16" width="15.33203125" customWidth="1"/>
-    <col min="17" max="17" width="6.19921875" customWidth="1"/>
-    <col min="18" max="18" width="14.53125" customWidth="1"/>
-    <col min="23" max="23" width="20.19921875" customWidth="1"/>
-    <col min="24" max="24" width="18.53125" customWidth="1"/>
-    <col min="25" max="25" width="19.19921875" customWidth="1"/>
-    <col min="32" max="32" width="21.265625" customWidth="1"/>
-    <col min="36" max="36" width="13.53125" customWidth="1"/>
-    <col min="40" max="40" width="19.59765625" customWidth="1"/>
-    <col min="41" max="41" width="13.1328125" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="13.06640625" customWidth="1"/>
-    <col min="44" max="44" width="7.06640625" customWidth="1"/>
-    <col min="46" max="46" width="15.33203125" customWidth="1"/>
-    <col min="48" max="48" width="13.19921875" customWidth="1"/>
-    <col min="49" max="49" width="5.265625" customWidth="1"/>
-    <col min="50" max="50" width="5.9296875" customWidth="1"/>
+    <col min="5" max="5" width="29.9272727272727" customWidth="1"/>
+    <col min="6" max="9" width="33.7272727272727" customWidth="1"/>
+    <col min="10" max="10" width="19.2636363636364" customWidth="1"/>
+    <col min="11" max="11" width="14.6" customWidth="1"/>
+    <col min="12" max="12" width="14.2636363636364" customWidth="1"/>
+    <col min="13" max="13" width="13.0636363636364" customWidth="1"/>
+    <col min="14" max="14" width="12.8" customWidth="1"/>
+    <col min="15" max="15" width="6.8" customWidth="1"/>
+    <col min="16" max="16" width="15.3363636363636" customWidth="1"/>
+    <col min="17" max="17" width="6.2" customWidth="1"/>
+    <col min="18" max="18" width="14.5272727272727" customWidth="1"/>
+    <col min="23" max="23" width="20.2" customWidth="1"/>
+    <col min="24" max="24" width="18.5272727272727" customWidth="1"/>
+    <col min="25" max="25" width="19.2" customWidth="1"/>
+    <col min="32" max="32" width="21.2636363636364" customWidth="1"/>
+    <col min="36" max="36" width="13.5272727272727" customWidth="1"/>
+    <col min="40" max="40" width="19.6" customWidth="1"/>
+    <col min="41" max="41" width="13.1363636363636" customWidth="1"/>
+    <col min="43" max="43" width="13.0636363636364" customWidth="1"/>
+    <col min="44" max="44" width="7.06363636363636" customWidth="1"/>
+    <col min="45" max="45" width="20" customWidth="1"/>
+    <col min="46" max="46" width="15.3363636363636" customWidth="1"/>
+    <col min="48" max="48" width="13.2" customWidth="1"/>
+    <col min="49" max="49" width="6.18181818181818" customWidth="1"/>
+    <col min="50" max="50" width="6.90909090909091" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:53">
@@ -7260,7 +7790,7 @@
         <v>185</v>
       </c>
       <c r="Z4" s="3">
-        <v>9.5000000000000001E-2</v>
+        <v>0.095</v>
       </c>
       <c r="AA4" s="3">
         <v>0</v>
@@ -7275,7 +7805,7 @@
         <v>3.528</v>
       </c>
       <c r="AE4" s="3">
-        <v>0.94599999999999995</v>
+        <v>0.946</v>
       </c>
       <c r="AF4" s="3">
         <v>1.085</v>
@@ -7666,7 +8196,7 @@
         <v>0.92</v>
       </c>
       <c r="I16" s="9">
-        <v>1.3140000000000001</v>
+        <v>1.314</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -7705,7 +8235,7 @@
         <v>0.9</v>
       </c>
       <c r="AM16" s="9">
-        <v>1.3140000000000001</v>
+        <v>1.314</v>
       </c>
       <c r="AN16">
         <v>1</v>
@@ -7716,17 +8246,13 @@
       <c r="AV16" s="10">
         <v>3000</v>
       </c>
-      <c r="AW16">
-        <v>1</v>
-      </c>
-      <c r="AX16">
-        <v>1</v>
-      </c>
+      <c r="AW16"/>
+      <c r="AX16"/>
       <c r="BA16" s="10">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="2:68" s="1" customFormat="1" ht="15.4">
+    <row r="17" s="1" customFormat="1" ht="16" spans="2:68">
       <c r="D17" s="11"/>
       <c r="F17" s="1" t="s">
         <v>212</v>
@@ -7738,7 +8264,7 @@
       <c r="I17" s="12"/>
       <c r="K17" s="12">
         <f>1/H16</f>
-        <v>1.0869565217391299</v>
+        <v>1.08695652173913</v>
       </c>
       <c r="W17"/>
       <c r="Y17" s="13" t="s">
@@ -7826,7 +8352,7 @@
         <v>215</v>
       </c>
       <c r="I19" s="9">
-        <v>29.891943130000001</v>
+        <v>29.89194313</v>
       </c>
       <c r="L19">
         <v>1</v>
@@ -7855,7 +8381,7 @@
       </c>
       <c r="AM19" s="9">
         <f>AM16</f>
-        <v>1.3140000000000001</v>
+        <v>1.314</v>
       </c>
       <c r="AN19">
         <v>1</v>
@@ -7866,12 +8392,8 @@
       <c r="AV19" s="10">
         <v>3500</v>
       </c>
-      <c r="AW19">
-        <v>1</v>
-      </c>
-      <c r="AX19">
-        <v>1</v>
-      </c>
+      <c r="AW19"/>
+      <c r="AX19"/>
       <c r="BA19" s="10">
         <v>12</v>
       </c>
@@ -7923,7 +8445,7 @@
       </c>
       <c r="AM22" s="9">
         <f>AM19</f>
-        <v>1.3140000000000001</v>
+        <v>1.314</v>
       </c>
       <c r="AN22">
         <v>1</v>
@@ -7934,12 +8456,8 @@
       <c r="AV22" s="10">
         <v>4000</v>
       </c>
-      <c r="AW22">
-        <v>1</v>
-      </c>
-      <c r="AX22">
-        <v>1</v>
-      </c>
+      <c r="AW22"/>
+      <c r="AX22"/>
       <c r="BA22" s="10">
         <v>13</v>
       </c>
@@ -8050,7 +8568,7 @@
       </c>
       <c r="AM25" s="9">
         <f>AM22</f>
-        <v>1.3140000000000001</v>
+        <v>1.314</v>
       </c>
       <c r="AN25">
         <v>1</v>
@@ -8061,12 +8579,8 @@
       <c r="AV25" s="10">
         <v>4000</v>
       </c>
-      <c r="AW25">
-        <v>1</v>
-      </c>
-      <c r="AX25">
-        <v>1</v>
-      </c>
+      <c r="AW25"/>
+      <c r="AX25"/>
       <c r="BA25" s="10">
         <v>13</v>
       </c>
@@ -8139,7 +8653,7 @@
       </c>
       <c r="AM28" s="9">
         <f>AM25</f>
-        <v>1.3140000000000001</v>
+        <v>1.314</v>
       </c>
       <c r="AN28">
         <v>1</v>
@@ -8150,12 +8664,8 @@
       <c r="AV28" s="10">
         <v>4000</v>
       </c>
-      <c r="AW28">
-        <v>1</v>
-      </c>
-      <c r="AX28">
-        <v>1</v>
-      </c>
+      <c r="AW28"/>
+      <c r="AX28"/>
       <c r="BA28" s="10">
         <v>13</v>
       </c>
@@ -8229,7 +8739,7 @@
       </c>
       <c r="AM31" s="9">
         <f>AM28</f>
-        <v>1.3140000000000001</v>
+        <v>1.314</v>
       </c>
       <c r="AN31">
         <v>1</v>
@@ -8240,12 +8750,8 @@
       <c r="AV31" s="10">
         <v>4000</v>
       </c>
-      <c r="AW31">
-        <v>1</v>
-      </c>
-      <c r="AX31">
-        <v>1</v>
-      </c>
+      <c r="AW31"/>
+      <c r="AX31"/>
       <c r="BA31" s="10">
         <v>13</v>
       </c>
@@ -8287,7 +8793,7 @@
       </c>
       <c r="E33" s="20">
         <f>[6]EnergyUseFromEverBatt_Min_!$AW$6</f>
-        <v>4.7300000000000002E-2</v>
+        <v>0.0473</v>
       </c>
       <c r="AH33" s="5"/>
       <c r="AJ33" s="5" t="s">
@@ -8301,7 +8807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="2:51" ht="15.4">
+    <row r="34" ht="16" spans="2:51">
       <c r="B34" s="6" t="s">
         <v>188</v>
       </c>
@@ -8314,7 +8820,7 @@
       </c>
       <c r="E34" s="20">
         <f>[6]EnergyUseFromEverBatt_Min_!$AW$7</f>
-        <v>0.17116666666666699</v>
+        <v>0.171166666666667</v>
       </c>
       <c r="AF34" t="s">
         <v>199</v>
@@ -8347,18 +8853,12 @@
       <c r="AU34">
         <v>2020</v>
       </c>
-      <c r="AW34">
-        <v>1</v>
-      </c>
-      <c r="AX34">
-        <v>1</v>
-      </c>
       <c r="AY34">
         <f>156.67*10</f>
         <v>1566.7</v>
       </c>
     </row>
-    <row r="35" spans="2:51" ht="15.4">
+    <row r="35" ht="16" spans="2:51">
       <c r="B35" s="6" t="s">
         <v>188</v>
       </c>
@@ -8371,7 +8871,7 @@
       </c>
       <c r="E35" s="20">
         <f>[6]EnergyUseFromEverBatt_Min_!$AW$8</f>
-        <v>0.46636666666666698</v>
+        <v>0.466366666666667</v>
       </c>
       <c r="AJ35" t="s">
         <v>212</v>
@@ -8383,7 +8883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="2:51" ht="15.4">
+    <row r="36" ht="16" spans="2:51">
       <c r="B36" s="6" t="s">
         <v>188</v>
       </c>
@@ -8396,7 +8896,7 @@
       </c>
       <c r="E36" s="20">
         <f>[6]EnergyUseFromEverBatt_Min_!$AW$9</f>
-        <v>9.5666666666666705E-2</v>
+        <v>0.0956666666666667</v>
       </c>
       <c r="AJ36" s="5" t="s">
         <v>214</v>
@@ -8433,7 +8933,7 @@
       <c r="R43" s="8"/>
       <c r="S43" s="15"/>
     </row>
-    <row r="44" spans="2:51" ht="15.4">
+    <row r="44" ht="16" spans="2:51">
       <c r="B44" s="22" t="s">
         <v>80</v>
       </c>
@@ -8469,7 +8969,7 @@
       <c r="R44" s="8"/>
       <c r="S44" s="8"/>
     </row>
-    <row r="45" spans="2:51" ht="15.4">
+    <row r="45" ht="16" spans="2:51">
       <c r="B45" s="27" t="s">
         <v>185</v>
       </c>
@@ -8841,6 +9341,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>